--- a/build/custom-roles-run/CustomRoles_WordingVIU_2026-07-13.xlsx
+++ b/build/custom-roles-run/CustomRoles_WordingVIU_2026-07-13.xlsx
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>138</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -779,10 +779,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -801,10 +801,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="B32" t="n">
+        <v>10</v>
+      </c>
+      <c r="C32" t="n">
         <v>1</v>
-      </c>
-      <c r="C32" t="n">
-        <v>10</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -1157,7 +1157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2575,12 +2575,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C26348</t>
+          <t>C26346</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26348</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26346</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>The role name cannot be left empty when editing</t>
+          <t>The Office User system role cannot be edited (lock icon, eye only)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2608,32 +2608,32 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>UI: clearing the Role Name on Edit shows inline error "Role name is a required field" (name cannot be left empty when editing).</t>
+          <t>UI: on the Roles list the Office User row shows a lock and only the eye (visibility) icon — no pencil; the eye opens the read-only Permission Summary (View Permissions). NOTE for dev: the direct /roles-permissions/{id}/edit URL still loads an editable form (FE route not guarded) — list-level gating is correct.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C26350</t>
+          <t>C26347</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26350</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26347</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3531</v>
+        <v>3530</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Delete Role</t>
+          <t>Edit Role</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>A custom role with 0 users can be deleted from the three-dot menu</t>
+          <t>The Time Clock User system role cannot be edited (lock icon, eye only)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2648,32 +2648,32 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>UI: Bilal - Cus (0 users) 3-dot menu shows Delete -&gt; "Confirmation" dialog to delete.</t>
+          <t>UI: on the Roles list the Time Clock User row shows a lock and only the eye icon — no pencil; the eye opens the read-only Permission Summary. Same /edit-URL FE-gap note as C26346.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C26351</t>
+          <t>C26348</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26351</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26348</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3531</v>
+        <v>3530</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Delete Role</t>
+          <t>Edit Role</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>A custom role with 1 or more users cannot be deleted</t>
+          <t>The role name cannot be left empty when editing</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2688,32 +2688,32 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>UI: Parth Cust1 (1 user) 3-dot menu shows only View Permissions, no Delete option.</t>
+          <t>UI: clearing the Role Name on Edit shows inline error "Role name is a required field" (name cannot be left empty when editing).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C26353</t>
+          <t>C26349</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26353</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26349</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3531</v>
+        <v>3530</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Delete Role</t>
+          <t>Edit Role</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>System roles have no Delete option anywhere</t>
+          <t>Editing: at least one permission must be turned on to save</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2728,19 +2728,19 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>UI: editable system role 3-dot shows only View Permissions (no Delete); non-editable system roles have no 3-dot at all. No Delete anywhere for system roles.</t>
+          <t>UI: editing a role down to zero permissions -&gt; Save opens "Confirm Permission Updates" (Removed permissions listed) -&gt; Confirm shows toast "At least one permission is required. Please try to resolve this." and the role is NOT saved (stays on edit). Submit-time validation enforces at least one permission. screenshot edit-zero-perm.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C26354</t>
+          <t>C26350</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26354</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26350</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>The assigned-user count is correct when a delete is blocked</t>
+          <t>A custom role with 0 users can be deleted from the three-dot menu</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2768,32 +2768,32 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>UI: Parth Cust1 Users column shows 1; its menu has no Delete — the assigned-user count matches the blocked-delete state.</t>
+          <t>UI: Bilal - Cus (0 users) 3-dot menu shows Delete -&gt; "Confirmation" dialog to delete.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C26355</t>
+          <t>C26351</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26355</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26351</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Permission Summary</t>
+          <t>Delete Role</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>The eye icon on the Roles list opens the read-only Permission Summary</t>
+          <t>A custom role with 1 or more users cannot be deleted</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2808,32 +2808,32 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>UI: the eye (visibility) icon opens the read-only Permission Summary ("View Permissions") at /roles-permissions/{id}/summary — no Save/Delete/edit controls.</t>
+          <t>UI: Parth Cust1 (1 user) 3-dot menu shows only View Permissions, no Delete option.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C26357</t>
+          <t>C26352</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26357</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26352</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Permission Summary</t>
+          <t>Delete Role</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>The eye icon on the Office row opens the Permission Summary</t>
+          <t>After moving the assigned users to another role, the role can be deleted</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2848,32 +2848,32 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>UI: the eye icon on the Office User row opens the read-only Permission Summary (View Permissions).</t>
+          <t>UI/API: assigned Tech to a custom role -&gt; usersCount=1, isDeletable=false, DELETE blocked (400 "Role is not deletable/editable."). Reassigned Tech to Time Clock -&gt; usersCount=0, isDeletable=true -&gt; DELETE 204 (role deleted). Reassignment + delete-after-zero-users flow confirmed.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C26358</t>
+          <t>C26353</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26358</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26353</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Permission Summary</t>
+          <t>Delete Role</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>The eye icon on the Time Clock User row opens the Permission Summary</t>
+          <t>System roles have no Delete option anywhere</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2888,32 +2888,32 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>UI: the eye icon on the Time Clock User row opens the read-only Permission Summary (summary route renders read-only).</t>
+          <t>UI: editable system role 3-dot shows only View Permissions (no Delete); non-editable system roles have no 3-dot at all. No Delete anywhere for system roles.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>C26359</t>
+          <t>C26354</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26359</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26354</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Permission Summary</t>
+          <t>Delete Role</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>The Permission Summary is grouped and shows each setting's on/off state</t>
+          <t>The assigned-user count is correct when a delete is blocked</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2928,32 +2928,32 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>UI: the Permission Summary is grouped by card and shows each setting on/off — Office User summary read exactly matches the role: WO View ON / WO C&amp;E off / Customers View+C&amp;E+Delete ON / Invoicing C&amp;E off / Reports ON / See Financial Data ON / AP-AR ON.</t>
+          <t>UI: Parth Cust1 Users column shows 1; its menu has no Delete — the assigned-user count matches the blocked-delete state.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>C26360</t>
+          <t>C26355</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26360</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26355</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CRUD Cascade Rules</t>
+          <t>Permission Summary</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ticking Create &amp; Edit on Work orders also ticks View</t>
+          <t>The eye icon on the Roles list opens the read-only Permission Summary</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2968,32 +2968,32 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>UI: on blank Create Role form, ticking Work orders Create &amp; Edit auto-ticks View (aria-checked View ON, C&amp;E ON). screenshot cascade-final.</t>
+          <t>UI: the eye (visibility) icon opens the read-only Permission Summary ("View Permissions") at /roles-permissions/{id}/summary — no Save/Delete/edit controls.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>C26361</t>
+          <t>C26357</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26361</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26357</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CRUD Cascade Rules</t>
+          <t>Permission Summary</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ticking Delete on Work orders also ticks Create &amp; Edit and View</t>
+          <t>The eye icon on the Office row opens the Permission Summary</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3008,32 +3008,32 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>UI: ticking Work orders Delete auto-ticks Create &amp; Edit and View (all ON).</t>
+          <t>UI: the eye icon on the Office User row opens the read-only Permission Summary (View Permissions).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>C26362</t>
+          <t>C26358</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26362</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26358</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CRUD Cascade Rules</t>
+          <t>Permission Summary</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Unticking View on Work orders also unticks Create &amp; Edit and Delete</t>
+          <t>The eye icon on the Time Clock User row opens the Permission Summary</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3048,32 +3048,32 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>UI: unticking Work orders View clears Create &amp; Edit and Delete (all off).</t>
+          <t>UI: the eye icon on the Time Clock User row opens the read-only Permission Summary (summary route renders read-only).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>C26363</t>
+          <t>C26359</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26363</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26359</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>CRUD Cascade Rules</t>
+          <t>Permission Summary</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Unticking Create &amp; Edit on Work orders also unticks Delete but keeps View</t>
+          <t>The Permission Summary is grouped and shows each setting's on/off state</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3088,19 +3088,19 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>UI: unticking Work orders Create &amp; Edit clears Delete but keeps View ON.</t>
+          <t>UI: the Permission Summary is grouped by card and shows each setting on/off — Office User summary read exactly matches the role: WO View ON / WO C&amp;E off / Customers View+C&amp;E+Delete ON / Invoicing C&amp;E off / Reports ON / See Financial Data ON / AP-AR ON.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>C26364</t>
+          <t>C26360</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26364</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26360</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>The same tick-cascade works on the Schedule card</t>
+          <t>Ticking Create &amp; Edit on Work orders also ticks View</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3128,19 +3128,19 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>UI: Schedule card tick Delete auto-ticks Create &amp; Edit + View (all ON).</t>
+          <t>UI: on blank Create Role form, ticking Work orders Create &amp; Edit auto-ticks View (aria-checked View ON, C&amp;E ON). screenshot cascade-final.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>C26365</t>
+          <t>C26361</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26365</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26361</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>The same untick-cascade works on the Customers card</t>
+          <t>Ticking Delete on Work orders also ticks Create &amp; Edit and View</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3168,19 +3168,19 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>UI: Customers card untick View clears Create &amp; Edit + Delete (all off).</t>
+          <t>UI: ticking Work orders Delete auto-ticks Create &amp; Edit and View (all ON).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C26366</t>
+          <t>C26362</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26366</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26362</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cascade works on Part sales with no See-Financial dialog when See Financial Data is already ON</t>
+          <t>Unticking View on Work orders also unticks Create &amp; Edit and Delete</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3208,19 +3208,19 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>UI: with See Financial Data already ON, Part sales tick Delete cascades View+C&amp;E with NO dialog.</t>
+          <t>UI: unticking Work orders View clears Create &amp; Edit and Delete (all off).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C26367</t>
+          <t>C26363</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26367</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26363</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cascade works on the Catalog and Inventory card</t>
+          <t>Unticking Create &amp; Edit on Work orders also unticks Delete but keeps View</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3248,19 +3248,19 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>UI: Catalog and Inventory tick Delete cascades View+C&amp;E (all ON), no dialog.</t>
+          <t>UI: unticking Work orders Create &amp; Edit clears Delete but keeps View ON.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>C26368</t>
+          <t>C26364</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26368</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26364</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Cascade works on the Vendor and order management card</t>
+          <t>The same tick-cascade works on the Schedule card</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3288,19 +3288,19 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>UI: Vendor and order management tick Delete cascades View+C&amp;E (all ON), no dialog.</t>
+          <t>UI: Schedule card tick Delete auto-ticks Create &amp; Edit + View (all ON).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>C26369</t>
+          <t>C26365</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26369</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26365</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cascade works on the Invoicing &amp; payments card when See Financial Data is ON</t>
+          <t>The same untick-cascade works on the Customers card</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3328,19 +3328,19 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>UI: with SFD ON, Invoicing &amp; payments tick Create&amp;Edit cascades View ON, no SFD dialog.</t>
+          <t>UI: Customers card untick View clears Create &amp; Edit + Delete (all off).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>C26370</t>
+          <t>C26366</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26370</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26366</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>The Work order lines card has no View column (View comes from Work orders)</t>
+          <t>Cascade works on Part sales with no See-Financial dialog when See Financial Data is already ON</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3363,24 +3363,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Work order lines card structure (no View column) build-verified.</t>
+          <t>UI: with See Financial Data already ON, Part sales tick Delete cascades View+C&amp;E with NO dialog.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C26371</t>
+          <t>C26367</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26371</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26367</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>The Timesheets card has no Delete box</t>
+          <t>Cascade works on the Catalog and Inventory card</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3403,24 +3403,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Timesheets card has no Delete (build-verified).</t>
+          <t>UI: Catalog and Inventory tick Delete cascades View+C&amp;E (all ON), no dialog.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C26372</t>
+          <t>C26368</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26372</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26368</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ticking Create &amp; Edit on Work order lines also ticks Work orders View</t>
+          <t>Cascade works on the Vendor and order management card</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3448,19 +3448,19 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>UI: ticking Work order lines Create &amp; Edit on blank form opens dialog "Enable Work Orders: View? — Work Order Lines requires Work Orders: View. Enable it to grant this permission?" [Cancel|Enable]; Enable -&gt; WO View ON + WOL C&amp;E ON.</t>
+          <t>UI: Vendor and order management tick Delete cascades View+C&amp;E (all ON), no dialog.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C26373</t>
+          <t>C26369</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26373</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26369</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Unticking Work orders View clears Work order lines Create &amp; Edit and Delete</t>
+          <t>Cascade works on the Invoicing &amp; payments card when See Financial Data is ON</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>UI: unticking Work orders View clears Work order lines Create &amp; Edit and Delete (all off).</t>
+          <t>UI: with SFD ON, Invoicing &amp; payments tick Create&amp;Edit cascades View ON, no SFD dialog.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C26374</t>
+          <t>C26370</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26374</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26370</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Work Orders Permissions</t>
+          <t>CRUD Cascade Rules</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Work orders View gives access to the work order list and detail</t>
+          <t>The Work order lines card has no View column (View comes from Work orders)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3523,37 +3523,37 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>UI: a role with Work Orders View (Technician; also WOCust) loads the Work Orders list at /workorders with all columns and rows. WO View grants list access.</t>
+          <t>Work order lines card structure (no View column) build-verified.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C26378</t>
+          <t>C26371</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26378</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26371</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Work Orders Permissions</t>
+          <t>CRUD Cascade Rules</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>The Work orders sub-toggles are shown but disabled when Work orders View is OFF</t>
+          <t>The Timesheets card has no Delete box</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3563,37 +3563,37 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>UI: on blank form (WO View off) the Work orders sub-toggles Review work orders / Pick parts / Order parts are shown but DISABLED (aria-disabled); ticking Work orders View enables them.</t>
+          <t>Timesheets card has no Delete (build-verified).</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C26382</t>
+          <t>C26372</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26382</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26372</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Work Orders Permissions</t>
+          <t>CRUD Cascade Rules</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pick parts and Order parts are independent toggles</t>
+          <t>Ticking Create &amp; Edit on Work order lines also ticks Work orders View</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3608,32 +3608,32 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>UI: Pick parts and Order parts are independent — ticking Pick parts leaves Order parts off.</t>
+          <t>UI: ticking Work order lines Create &amp; Edit on blank form opens dialog "Enable Work Orders: View? — Work Order Lines requires Work Orders: View. Enable it to grant this permission?" [Cancel|Enable]; Enable -&gt; WO View ON + WOL C&amp;E ON.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C26394</t>
+          <t>C26373</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26394</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26373</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3536</v>
+        <v>3533</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Schedule Permissions</t>
+          <t>CRUD Cascade Rules</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Schedule View shows the calendar with all technicians</t>
+          <t>Unticking Work orders View clears Work order lines Create &amp; Edit and Delete</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3648,32 +3648,32 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>UI: a role with Schedule View (ZZAUTOTEST Viewer) opens /schedule and the calendar renders. Schedule appears in top nav.</t>
+          <t>UI: unticking Work orders View clears Work order lines Create &amp; Edit and Delete (all off).</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C26397</t>
+          <t>C26374</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26397</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26374</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3536</v>
+        <v>3534</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Schedule Permissions</t>
+          <t>Work Orders Permissions</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Schedule View OFF hides Schedule from the top navigation</t>
+          <t>Work orders View gives access to the work order list and detail</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3688,32 +3688,32 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>UI: the WOCust custom role (no scheduleView) has NO Schedule item in the top navigation — Schedule View OFF hides Schedule from nav.</t>
+          <t>UI: a role with Work Orders View (Technician; also WOCust) loads the Work Orders list at /workorders with all columns and rows. WO View grants list access.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C26398</t>
+          <t>C26378</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26398</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26378</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3537</v>
+        <v>3534</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Work Orders Permissions</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Customers View gives access to customer records, contacts, vehicles and history</t>
+          <t>The Work orders sub-toggles are shown but disabled when Work orders View is OFF</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3728,32 +3728,32 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>UI: a role with Customers View opens /customers and the customer list renders (customer records accessible; contacts/vehicles/history are sub-views of a record). Customers appears in nav.</t>
+          <t>UI: on blank form (WO View off) the Work orders sub-toggles Review work orders / Pick parts / Order parts are shown but DISABLED (aria-disabled); ticking Work orders View enables them.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C26404</t>
+          <t>C26382</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26404</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26382</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3537</v>
+        <v>3534</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Work Orders Permissions</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Customers View OFF hides Customers from the top navigation</t>
+          <t>Pick parts and Order parts are independent toggles</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3768,32 +3768,32 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>UI: the Time Clock User role (no customersView) shows top nav Work Orders | Schedule only — no Customers entry. Customers View OFF hides Customers from the top navigation.</t>
+          <t>UI: Pick parts and Order parts are independent — ticking Pick parts leaves Order parts off.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C26406</t>
+          <t>C26394</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26406</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26394</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3538</v>
+        <v>3536</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Schedule Permissions</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Turning Parts Department ON shows exactly 3 child cards</t>
+          <t>Schedule View shows the calendar with all technicians</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3803,37 +3803,37 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Parts Department children + descriptions build-verified (PermissionGrid).</t>
+          <t>UI: a role with Schedule View (ZZAUTOTEST Viewer) opens /schedule and the calendar renders. Schedule appears in top nav.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C26407</t>
+          <t>C26397</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26407</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26397</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3538</v>
+        <v>3536</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Schedule Permissions</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Turning Parts Department OFF hides the 3 child cards</t>
+          <t>Schedule View OFF hides Schedule from the top navigation</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3848,32 +3848,32 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>UI: on blank form the 3 child cards (Part sales/Catalog and Inventory/Vendor and order management) are absent; toggling Parts Department ON reveals all 3.</t>
+          <t>UI: the WOCust custom role (no scheduleView) has NO Schedule item in the top navigation — Schedule View OFF hides Schedule from nav.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C26408</t>
+          <t>C26398</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26408</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26398</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>A saved role with Parts Department OFF hides the Parts navigation and its pages</t>
+          <t>Customers View gives access to customer records, contacts, vehicles and history</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3888,32 +3888,32 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>UI: the Technician role (no Parts Department perms) has NO Parts item in the top navigation — Parts Department OFF hides the Parts navigation.</t>
+          <t>UI: a role with Customers View opens /customers and the customer list renders (customer records accessible; contacts/vehicles/history are sub-views of a record). Customers appears in nav.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C26409</t>
+          <t>C26402</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26409</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26402</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Turning Parts Department OFF then ON keeps the 3 child card choices</t>
+          <t>AP/AR OFF hides the 7 sensitive customer fields on Edit Customer</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3928,32 +3928,32 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>UI: Parts Department OFF hides 3 children then ON again retains prior child choices (Part sales Delete + Catalog Delete stayed ON).</t>
+          <t>UI: role with View and Manage AP/AR Data OFF (Service Advisor) — Edit Customer modal has NO sensitive fields (no Credit Limit, Taxes, Default Labor Rate, etc). With AP/AR ON they are present. screenshot customer-aparOFF vs customer-aparON.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C26413</t>
+          <t>C26403</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26413</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26403</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Catalog and Inventory View gives read access to the catalog and inventory</t>
+          <t>AP/AR ON shows the 7 sensitive customer fields on Edit Customer</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3968,32 +3968,32 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>UI: a role with Catalog and Inventory View opens /parts/parts-catalogue and the catalogue renders (read access to the catalog).</t>
+          <t>UI (role with View and Manage AP/AR Data ON): the Edit Customer modal shows all 7 sensitive fields — Credit Terms, Credit Limit, Default Labor Rate, Default Shop Supplies, Min, Max, Taxes (and PO-required). screenshot customer-apar-on.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>C26416</t>
+          <t>C26404</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26416</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26404</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vendor and order management View gives visibility of vendors, purchase orders and deliveries</t>
+          <t>Customers View OFF hides Customers from the top navigation</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4008,19 +4008,19 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>UI: a role with Vendor and order management View opens /parts/orders and the Purchase Orders list renders (visibility of vendors/POs/deliveries).</t>
+          <t>UI: the Time Clock User role (no customersView) shows top nav Work Orders | Schedule only — no Customers entry. Customers View OFF hides Customers from the top navigation.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C27876</t>
+          <t>C26406</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27876</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26406</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>A Vendor and order management View-only role can open the Purchase Orders list and a purchase order</t>
+          <t>Turning Parts Department ON shows exactly 3 child cards</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4043,37 +4043,37 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>UI: a Vendor and order management View-only role (ZZAUTOTEST Viewer) opens the Purchase Orders list at /parts/orders successfully (list access confirmed).</t>
+          <t>Parts Department children + descriptions build-verified (PermissionGrid).</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C27740</t>
+          <t>C26407</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27740</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26407</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>The Invoicing &amp; payments delete column is labelled 'Delete / Reverse'</t>
+          <t>Turning Parts Department OFF hides the 3 child cards</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4083,37 +4083,37 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>'Delete / Reverse' column confirmed in build (PermissionGrid).</t>
+          <t>UI: on blank form the 3 child cards (Part sales/Catalog and Inventory/Vendor and order management) are absent; toggling Parts Department ON reveals all 3.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>C26429</t>
+          <t>C26408</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26429</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26408</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3540</v>
+        <v>3538</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>The Timesheets card shows View and Create &amp; Edit only (no Delete)</t>
+          <t>A saved role with Parts Department OFF hides the Parts navigation and its pages</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4123,37 +4123,37 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Timesheets card title + 'Track and review technician labor hours and time entries.' + no Delete column build-verified (PermissionGrid).</t>
+          <t>UI: the Technician role (no Parts Department perms) has NO Parts item in the top navigation — Parts Department OFF hides the Parts navigation.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>C26432</t>
+          <t>C26409</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26432</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26409</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3540</v>
+        <v>3538</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Clock in / clock out is always available, whatever the Timesheets permission</t>
+          <t>Turning Parts Department OFF then ON keeps the 3 child card choices</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4168,32 +4168,32 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>UI: the universal Clock In control (top bar "timer | Clock In") is present for the Time Clock User role, which has no Timesheets Create&amp;Edit — clock in/out is available regardless of the Timesheets permission.</t>
+          <t>UI: Parts Department OFF hides 3 children then ON again retains prior child choices (Part sales Delete + Catalog Delete stayed ON).</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>C26435</t>
+          <t>C26410</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26435</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26410</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3541</v>
+        <v>3538</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Reports ON gives access to the Reports page with all reports (no per-report on/off)</t>
+          <t>Part sales View gives read access to part sales records</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4208,32 +4208,32 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>UI (admin /reports): Reports appears in top nav; the Reports page lists ALL reports grouped by category (LABOR, PERFORMANCE, FINANCE, ACCOUNTS RECEIVABLE, ACCOUNTS PAYABLE, ACCOUNTING, COMMUNICATIONS) with no per-report on/off control — Reports is all-or-nothing. screenshot reports-admin.</t>
+          <t>UI (Parts Manager): the Part Sales list at /parts/part-sales loads via in-app nav (columns Number/Status, "New Part Sale" button). NOTE: a direct URL goto to /parts/part-sales redirects to /workorders even for a fully-permissioned role — this is an SPA route-guard-on-fresh-load quirk (not a permission bug); in-app navigation works.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>C26436</t>
+          <t>C26411</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26436</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26411</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3541</v>
+        <v>3538</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Reports OFF removes Reports from the top navigation</t>
+          <t>Part sales Create &amp; Edit lets the user create part sales, returns and transactions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4248,32 +4248,32 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>UI: the Technician role (no reportsPageAccess) has NO Reports item in the top navigation — Reports OFF removes Reports from nav.</t>
+          <t>UI (Parts Manager, partSalesCreateAndEdit): the Part Sales page shows the "New Part Sale" create control.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>C26441</t>
+          <t>C26413</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26441</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26413</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3542</v>
+        <v>3538</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Turning Settings ON reveals its sub-toggles</t>
+          <t>Catalog and Inventory View gives read access to the catalog and inventory</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4283,37 +4283,37 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Verified-Label (build) — Integrations sub-toggle now present (was previously flagged missing)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>PageAndSettingsToggles build chunk shows 7 Settings sub-toggles incl. Integrations. Prior 'Integrations missing' gap is resolved/built.</t>
+          <t>UI: a role with Catalog and Inventory View opens /parts/parts-catalogue and the catalogue renders (read access to the catalog).</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>C26442</t>
+          <t>C26414</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26442</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26414</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3542</v>
+        <v>3538</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Turning Settings OFF hides its sub-toggles</t>
+          <t>Catalog and Inventory Create &amp; Edit lets the user create/edit items and make adjustments (cost/price shown only with See Financial Data)</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4328,32 +4328,32 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>UI: with Settings off the 7 sub-toggles are absent; toggling Settings ON reveals App Settings/Service/Parts/Finance/Integrations/Data Import/View-Manage Wages.</t>
+          <t>UI (Parts Manager, catalogInventoryCreateAndEdit): the Catalog page shows the "New Catalog Part" create control.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>C26443</t>
+          <t>C26416</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26443</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26416</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3542</v>
+        <v>3538</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>A saved role with Settings OFF has no Settings area in the sidebar</t>
+          <t>Vendor and order management View gives visibility of vendors, purchase orders and deliveries</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4368,32 +4368,32 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>UI: the Technician role (no settings* perms) has no Settings area in the sidebar — a saved role with Settings OFF has no Settings section.</t>
+          <t>UI: a role with Vendor and order management View opens /parts/orders and the Purchase Orders list renders (visibility of vendors/POs/deliveries).</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>C26444</t>
+          <t>C26417</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26444</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26417</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3542</v>
+        <v>3538</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Turning Settings OFF then ON keeps the sub-toggle choices</t>
+          <t>Vendor and order management Create &amp; Edit lets the user manage vendors, purchase orders, receiving and returns</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4408,32 +4408,32 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>UI: turning Settings OFF then ON keeps the sub-toggle choices (App Settings + Finance stayed ON after the parent was toggled off then on).</t>
+          <t>UI (Parts Manager, vendorOrderManagementCreateAndEdit): the Purchase Orders page shows the "New PO" create control.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>C27395</t>
+          <t>C27876</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27395</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27876</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3542</v>
+        <v>3538</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Turning off the last Settings sub-toggle collapses the Settings section</t>
+          <t>A Vendor and order management View-only role can open the Purchase Orders list and a purchase order</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4448,32 +4448,32 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>UI: turning off the last remaining Settings sub-toggle (App Settings) collapses the Settings section — the parent Settings toggle goes off and the sub-toggles disappear.</t>
+          <t>UI: a Vendor and order management View-only role (ZZAUTOTEST Viewer) opens the Purchase Orders list at /parts/orders successfully (list access confirmed).</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>C26452</t>
+          <t>C27740</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26452</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27740</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3543</v>
+        <v>3539</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>The Work orders card has 'Full View' and 'Tech view' options</t>
+          <t>The Invoicing &amp; payments delete column is labelled 'Delete / Reverse'</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4488,32 +4488,32 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>'View mode', 'Full View', 'Tech view' confirmed in build (WoSettingsRow).</t>
+          <t>'Delete / Reverse' column confirmed in build (PermissionGrid).</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>C26453</t>
+          <t>C26429</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26453</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26429</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3543</v>
+        <v>3540</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>The Full View description</t>
+          <t>The Timesheets card shows View and Create &amp; Edit only (no Delete)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4523,37 +4523,37 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>UI: Full View description reads "Complete interface with all fields visible and editable (subject to CRUD permissions). The estimate column shows the actual estimate value. Full parts request form with all fields. All workflow actions available (approve, review, split etc...)."</t>
+          <t>Timesheets card title + 'Track and review technician labor hours and time entries.' + no Delete column build-verified (PermissionGrid).</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>C26454</t>
+          <t>C26432</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26454</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26432</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3543</v>
+        <v>3540</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>The Tech view description, and Tech view stays disabled until a Work orders permission is on</t>
+          <t>Clock in / clock out is always available, whatever the Timesheets permission</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4563,37 +4563,37 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Verified-Label (Tech view text build-verified); disabled-state needs live check</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Tech view description string confirmed verbatim in build (WoSettingsRow). Disabled-until-WO-perm needs live editor.</t>
+          <t>UI: the universal Clock In control (top bar "timer | Clock In") is present for the Time Clock User role, which has no Timesheets Create&amp;Edit — clock in/out is available regardless of the Timesheets permission.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>C26455</t>
+          <t>C26435</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26455</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26435</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3543</v>
+        <v>3541</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Tech view: the Estimate column shows the Tech Time value</t>
+          <t>Reports ON gives access to the Reports page with all reports (no per-report on/off)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4608,32 +4608,32 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>UI (Technician, tech view): WO lines Actual/Estimate column shows tech-time hours (e.g. 0.00 / 1.00, 0.00 / 1.50) and header "Total Tech Hours" — not a money estimate. screenshot techview-lines-estimate/approved.</t>
+          <t>UI (admin /reports): Reports appears in top nav; the Reports page lists ALL reports grouped by category (LABOR, PERFORMANCE, FINANCE, ACCOUNTS RECEIVABLE, ACCOUNTS PAYABLE, ACCOUNTING, COMMUNICATIONS) with no per-report on/off control — Reports is all-or-nothing. screenshot reports-admin.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>C26456</t>
+          <t>C26436</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26456</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26436</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3543</v>
+        <v>3541</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Tech view: the tech time input field is hidden on work order lines</t>
+          <t>Reports OFF removes Reports from the top navigation</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4648,32 +4648,32 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>UI (tech view): no tech-time input field rendered on the WO lines for this user (0 tech-time inputs found).</t>
+          <t>UI: the Technician role (no reportsPageAccess) has NO Reports item in the top navigation — Reports OFF removes Reports from nav.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>C26457</t>
+          <t>C26441</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26457</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26441</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Tech view: the user cannot approve work orders (no Approve button)</t>
+          <t>Turning Settings ON reveals its sub-toggles</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4683,37 +4683,37 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build) — Integrations sub-toggle now present (was previously flagged missing)</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>UI (tech view): no Approve button anywhere on the work order (estimate and approved WOs both) — Technician lacks Review Work Orders.</t>
+          <t>PageAndSettingsToggles build chunk shows 7 Settings sub-toggles incl. Integrations. Prior 'Integrations missing' gap is resolved/built.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>C26458</t>
+          <t>C26442</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26458</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26442</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Tech view: the user cannot approve work order lines</t>
+          <t>Turning Settings OFF hides its sub-toggles</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4728,32 +4728,32 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>UI (tech view): no approve-line action on any line; line actions are tech-only (Complete / Story / Start), no approve control.</t>
+          <t>UI: with Settings off the 7 sub-toggles are absent; toggling Settings ON reveals App Settings/Service/Parts/Finance/Integrations/Data Import/View-Manage Wages.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>C26463</t>
+          <t>C26443</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26463</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26443</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>View mode only changes the look, not what the user is allowed to do</t>
+          <t>A saved role with Settings OFF has no Settings area in the sidebar</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4768,32 +4768,32 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>UI/enforcement: tech view is purely presentational — the tech-view role retains workOrderLinesCreateAndEdit and can add lines (New Line functional on the lines screen); data-level create/edit is governed by CRUD perms, not the view mode (estimate column renders as hours but edit capability persists).</t>
+          <t>UI: the Technician role (no settings* perms) has no Settings area in the sidebar — a saved role with Settings OFF has no Settings section.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>C26465</t>
+          <t>C26444</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26465</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26444</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Tech view: the 'Send to Portal' button is hidden</t>
+          <t>Turning Settings OFF then ON keeps the sub-toggle choices</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4808,32 +4808,32 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>UI (tech view): the Send to Portal button is not shown anywhere on the work order (header, line, or action menus).</t>
+          <t>UI: turning Settings OFF then ON keeps the sub-toggle choices (App Settings + Finance stayed ON after the parent was toggled off then on).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>C26467</t>
+          <t>C27395</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26467</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27395</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>3544</v>
+        <v>3542</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>See Financial Data toggle appears in the Cross-Cutting Toggles card</t>
+          <t>Turning off the last Settings sub-toggle collapses the Settings section</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4843,37 +4843,37 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Verified-Label (build); subtitle placeholder flagged</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Card 'Cross-Cutting Toggles' + toggle 'See Financial Data' confirmed in shipped build (CrossTogglesSection chunk). Reused subtitle string flagged.</t>
+          <t>UI: turning off the last remaining Settings sub-toggle (App Settings) collapses the Settings section — the parent Settings toggle goes off and the sub-toggles disappear.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>C26468</t>
+          <t>C26452</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26468</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26452</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>See Financial Data ON: prices, costs, margins and labor rates are shown</t>
+          <t>The Work orders card has 'Full View' and 'Tech view' options</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4883,37 +4883,37 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>UI: with See Financial Data ON (admin full view + TechSFD), WO lines show prices, costs, margins and labor rates — Rate ($100), Margin (%), Total ($261.54), parts prices ($3.33 etc), labor ($150). screenshot fullview-lines-admin/techview-sfd-lines.</t>
+          <t>'View mode', 'Full View', 'Tech view' confirmed in build (WoSettingsRow).</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>C26469</t>
+          <t>C26453</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26469</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26453</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>See Financial Data OFF: money amounts, rates, costs and margins are hidden</t>
+          <t>The Full View description</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4928,32 +4928,32 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>UI: with See Financial Data OFF (plain Technician), WO lines show NO money — no $ amounts, no Rate/Margin/Total columns; only tech-time hours (0.00/1.00). screenshot techview-lines-estimate.</t>
+          <t>UI: Full View description reads "Complete interface with all fields visible and editable (subject to CRUD permissions). The estimate column shows the actual estimate value. Full parts request form with all fields. All workflow actions available (approve, review, split etc...)."</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>C26470</t>
+          <t>C26454</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26470</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26454</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>With See Financial Data OFF, Part sales and Invoicing &amp; payments stay inaccessible even with View, Create &amp; Edit and Delete on</t>
+          <t>The Tech view description, and Tech view stays disabled until a Work orders permission is on</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4963,37 +4963,37 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (Tech view text build-verified); disabled-state needs live check</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>UI/editor enforcement: a role cannot hold Part sales or Invoicing &amp; payments with See Financial Data OFF — ticking either forces the "Enable See Financial Data?" dialog (C26471/C26474). So SFD OFF makes Part sales and Invoicing &amp; payments unreachable even if View/Create&amp;Edit/Delete were desired; the combination is prevented at save time.</t>
+          <t>Tech view description string confirmed verbatim in build (WoSettingsRow). Disabled-until-WO-perm needs live editor.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>C26471</t>
+          <t>C26455</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26471</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26455</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ticking Part sales while See Financial Data is OFF asks you to turn See Financial Data on</t>
+          <t>Tech view: the Estimate column shows the Tech Time value</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5008,32 +5008,32 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>UI dialog: ticking Part sales while SFD off shows "Enable See Financial Data? — Part Sales requires See Financial Data. Enable it to grant this permission?" [Cancel|Enable].</t>
+          <t>UI (Technician, tech view): WO lines Actual/Estimate column shows tech-time hours (e.g. 0.00 / 1.00, 0.00 / 1.50) and header "Total Tech Hours" — not a money estimate. screenshot techview-lines-estimate/approved.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>C26472</t>
+          <t>C26456</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26472</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26456</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>'Enable See Financial Data?' dialog — Enable: turns See Financial Data on and keeps the box ticked</t>
+          <t>Tech view: the tech time input field is hidden on work order lines</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5048,32 +5048,32 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>UI: Enable on the SFD dialog turns See Financial Data ON and keeps Part sales View+Create&amp;Edit ticked.</t>
+          <t>UI (tech view): no tech-time input field rendered on the WO lines for this user (0 tech-time inputs found).</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>C26473</t>
+          <t>C26457</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26473</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26457</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>'Enable See Financial Data?' dialog — Cancel: undoes the tick</t>
+          <t>Tech view: the user cannot approve work orders (no Approve button)</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5088,32 +5088,32 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>UI: Cancel on the SFD dialog undoes the tick (See Financial Data off, Part sales off).</t>
+          <t>UI (tech view): no Approve button anywhere on the work order (estimate and approved WOs both) — Technician lacks Review Work Orders.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>C26474</t>
+          <t>C26458</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26474</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26458</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>The same 'Enable See Financial Data?' dialog appears for Invoicing &amp; payments when See Financial Data is OFF</t>
+          <t>Tech view: the user cannot approve work order lines</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5128,32 +5128,32 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>UI dialog: ticking Invoicing &amp; payments while SFD off shows "Enable See Financial Data? — Invoicing &amp; Payments requires See Financial Data..." [Cancel|Enable]; Enable -&gt; SFD ON + Invoicing View+C&amp;E ON.</t>
+          <t>UI (tech view): no approve-line action on any line; line actions are tech-only (Complete / Story / Start), no approve control.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>C26475</t>
+          <t>C26463</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26475</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26463</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Turning See Financial Data OFF asks you to also turn off the settings that depend on it</t>
+          <t>View mode only changes the look, not what the user is allowed to do</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5168,32 +5168,32 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>UI (RUN331 FAIL NOW FIXED): turning See Financial Data OFF while Invoicing on shows "Disable See Financial Data? — Disabling See Financial Data will also disable Invoicing &amp; Payments. Continue?" [Cancel|Disable] (FinancialDataDisableConfirmModal). screenshot sfd-disable-dialog.</t>
+          <t>UI/enforcement: tech view is purely presentational — the tech-view role retains workOrderLinesCreateAndEdit and can add lines (New Line functional on the lines screen); data-level create/edit is governed by CRUD perms, not the view mode (estimate column renders as hours but edit capability persists).</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>C27869</t>
+          <t>C26465</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27869</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26465</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Turning on Order parts while See Financial Data is OFF asks you to also turn on See Financial Data</t>
+          <t>Tech view: the 'Send to Portal' button is hidden</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5208,32 +5208,32 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>UI dialog: ticking Order parts while SFD off shows "Enable See Financial Data? — Order Parts requires See Financial Data. Enable it to grant this permission?" [Cancel|Enable].</t>
+          <t>UI (tech view): the Send to Portal button is not shown anywhere on the work order (header, line, or action menus).</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>C26485</t>
+          <t>C26467</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26485</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26467</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data works independently of See Financial Data</t>
+          <t>See Financial Data toggle appears in the Cross-Cutting Toggles card</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5243,37 +5243,37 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build); subtitle placeholder flagged</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>UI: See Financial Data and View and Manage AP/AR Data are separate Cross-Cutting Toggles (both present independently alongside View History Logs); AP/AR is not tied to SFD in the editor.</t>
+          <t>Card 'Cross-Cutting Toggles' + toggle 'See Financial Data' confirmed in shipped build (CrossTogglesSection chunk). Reused subtitle string flagged.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>C26492</t>
+          <t>C26468</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26492</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26468</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>3547</v>
+        <v>3544</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Staff Page Role Assignment</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Changing a user's role logs them out immediately</t>
+          <t>See Financial Data ON: prices, costs, margins and labor rates are shown</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5288,32 +5288,32 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>API/session: changing a user role logs them out immediately — the prior session is invalidated (409 Session has expired) right after the change.</t>
+          <t>UI: with See Financial Data ON (admin full view + TechSFD), WO lines show prices, costs, margins and labor rates — Rate ($100), Margin (%), Total ($261.54), parts prices ($3.33 etc), labor ($150). screenshot fullview-lines-admin/techview-sfd-lines.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>C26494</t>
+          <t>C26469</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26494</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26469</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>3547</v>
+        <v>3544</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Staff Page Role Assignment</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>A logged-in user is logged out immediately when their role changes</t>
+          <t>See Financial Data OFF: money amounts, rates, costs and margins are hidden</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5328,32 +5328,32 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>API/session: a logged-in user is logged out immediately when their role changes (session invalidated -&gt; 409 on next request).</t>
+          <t>UI: with See Financial Data OFF (plain Technician), WO lines show NO money — no $ amounts, no Rate/Margin/Total columns; only tech-time hours (0.00/1.00). screenshot techview-lines-estimate.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>C26495</t>
+          <t>C26470</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26495</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26470</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3548</v>
+        <v>3544</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Administrator: role permissions match the expected set</t>
+          <t>With See Financial Data OFF, Part sales and Invoicing &amp; payments stay inaccessible even with View, Create &amp; Edit and Delete on</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5363,37 +5363,37 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Administrator permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI/editor enforcement: a role cannot hold Part sales or Invoicing &amp; payments with See Financial Data OFF — ticking either forces the "Enable See Financial Data?" dialog (C26471/C26474). So SFD OFF makes Part sales and Invoicing &amp; payments unreachable even if View/Create&amp;Edit/Delete were desired; the combination is prevented at save time.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>C26496</t>
+          <t>C26471</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26496</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26471</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>3548</v>
+        <v>3544</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Service Manager: role permissions match the expected set</t>
+          <t>Ticking Part sales while See Financial Data is OFF asks you to turn See Financial Data on</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5403,37 +5403,37 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Service Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI dialog: ticking Part sales while SFD off shows "Enable See Financial Data? — Part Sales requires See Financial Data. Enable it to grant this permission?" [Cancel|Enable].</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>C26497</t>
+          <t>C26472</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26497</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26472</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>3548</v>
+        <v>3544</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Senior Service Advisor: role permissions match the expected set</t>
+          <t>'Enable See Financial Data?' dialog — Enable: turns See Financial Data on and keeps the box ticked</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5443,37 +5443,37 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Senior Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI: Enable on the SFD dialog turns See Financial Data ON and keeps Part sales View+Create&amp;Edit ticked.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>C26498</t>
+          <t>C26473</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26498</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26473</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>3548</v>
+        <v>3544</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Service Advisor: role permissions match the expected set</t>
+          <t>'Enable See Financial Data?' dialog — Cancel: undoes the tick</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5483,37 +5483,37 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI: Cancel on the SFD dialog undoes the tick (See Financial Data off, Part sales off).</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>C26499</t>
+          <t>C26474</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26499</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26474</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>3548</v>
+        <v>3544</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Foreman: role permissions match the expected set</t>
+          <t>The same 'Enable See Financial Data?' dialog appears for Invoicing &amp; payments when See Financial Data is OFF</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5523,37 +5523,37 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Foreman permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI dialog: ticking Invoicing &amp; payments while SFD off shows "Enable See Financial Data? — Invoicing &amp; Payments requires See Financial Data..." [Cancel|Enable]; Enable -&gt; SFD ON + Invoicing View+C&amp;E ON.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>C26500</t>
+          <t>C26475</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26500</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26475</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3548</v>
+        <v>3544</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Technician: role permissions match the expected set</t>
+          <t>Turning See Financial Data OFF asks you to also turn off the settings that depend on it</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5563,37 +5563,37 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI (RUN331 FAIL NOW FIXED): turning See Financial Data OFF while Invoicing on shows "Disable See Financial Data? — Disabling See Financial Data will also disable Invoicing &amp; Payments. Continue?" [Cancel|Disable] (FinancialDataDisableConfirmModal). screenshot sfd-disable-dialog.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>C26501</t>
+          <t>C27869</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26501</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27869</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>3548</v>
+        <v>3544</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Parts Manager: role permissions match the expected set</t>
+          <t>Turning on Order parts while See Financial Data is OFF asks you to also turn on See Financial Data</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5603,37 +5603,37 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Parts Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI dialog: ticking Order parts while SFD off shows "Enable See Financial Data? — Order Parts requires See Financial Data. Enable it to grant this permission?" [Cancel|Enable].</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>C26502</t>
+          <t>C26476</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26502</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26476</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Parts Technician: role permissions match the expected set</t>
+          <t>View and Manage AP/AR Data ON shows the Unpaid Invoices, Payments and Credits tabs on a customer</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5643,37 +5643,37 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Parts Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI: role with AP/AR Data ON shows the financial tabs on a customer page — build labels are Invoices / Payments / Deposits (case prose says Unpaid Invoices/Payments/Credits; the AP/AR toggle description uses that wording, actual tab labels are Invoices/Payments/Deposits). Tabs absent when AP/AR off.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>C26503</t>
+          <t>C26477</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26503</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26477</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Office User: role permissions match the expected set</t>
+          <t>View and Manage AP/AR Data ON shows the same three tabs on a vendor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5683,37 +5683,37 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Office User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI (Parts Manager, AP/AR ON): the vendor page (/parts/vendor/{id}) shows the AP/AR tabs — Contacts, Unpaid Invoices (30), Payments (4). screenshot vendordetail-vendON.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>C26504</t>
+          <t>C26478</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26504</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26478</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sales Representative: role permissions match the expected set</t>
+          <t>With Reports ON, all 6 AP/AR aging reports are listed (whether or not AP/AR is on)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5723,37 +5723,37 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Sales Representative permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI (admin /reports, Reports ON): all 6 AP/AR aging reports are listed — A/R Aging Summary, A/R Aging Detail, A/R Aging Collection, A/P Aging Summary, A/P Aging Detail, A/P Unpaid Invoices. screenshot reports-admin.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>C26505</t>
+          <t>C26480</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26505</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26480</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Time Clock User: role permissions match the expected set</t>
+          <t>View and Manage AP/AR Data OFF hides the three tabs on a customer</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5763,37 +5763,37 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Time Clock User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI: AP/AR Data OFF (Service Advisor) — the customer page shows only Work Orders/Part Sales/Contacts/Assets/Notes; the Invoices/Payments/Deposits tabs are hidden.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>C26506</t>
+          <t>C26481</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26506</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26481</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Customer portal is on by default only for Service Advisor, Senior Service Advisor, Service Manager and Parts Manager (and Administrator)</t>
+          <t>View and Manage AP/AR Data OFF hides the three tabs on a vendor</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5803,37 +5803,37 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (matches live per-role customerPortalPageAccess)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>customerPortalPageAccess per role confirmed live: on for Admin/SM/SSA/SA/PM; off for the rest (roles-matrix-2026-07-13).</t>
+          <t>UI (Service Advisor, AP/AR OFF): the same vendor page shows only the Contacts tab — Unpaid Invoices/Payments tabs are hidden. screenshot vendordetail-vendOFF.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>C26510</t>
+          <t>C26482</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26510</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26482</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>3549</v>
+        <v>3545</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Legacy 'Admin / Administrator' users become 'Administrator' after migration</t>
+          <t>With AP/AR OFF but Reports ON, all 6 AP/AR aging reports are still listed</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5848,32 +5848,32 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Live roles API: destination system role exists = "Admin" (build name; case prose says Administrator), isEditable=true, 89 users, 42 perms. Migration is a completed historical event; destination state verified (role present, editable with pencil, populated).</t>
+          <t>UI (RUN331 FAIL NOW FIXED): a role with Reports ON but View and Manage AP/AR Data OFF (ZZAUTOTEST ReportsNoAPAR) still sees all 6 AP/AR aging reports on /reports (A/R Aging Summary/Detail/Collection, A/P Aging Summary/Detail, A/P Unpaid Invoices). Aging reports follow the Reports permission, not AP/AR. screenshot reports-noapar.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>C26511</t>
+          <t>C26483</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26511</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26483</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>3549</v>
+        <v>3545</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Legacy 'Office' users become 'Office User' after migration</t>
+          <t>View and Manage AP/AR Data OFF hides the sensitive money fields on Edit Customer</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5888,32 +5888,32 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Live roles API: "Office User" exists, isEditable=false (lock + eye only), 5 users, 23 perms — matches legacy Office -&gt; Office User destination.</t>
+          <t>UI: AP/AR Data OFF hides the sensitive money fields on Edit Customer (Credit Limit, Taxes, Default Labor Rate, Default Shop Supplies, Min, Max, Credit Terms) — same observation as C26402.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>C26512</t>
+          <t>C26484</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26512</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26484</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>3549</v>
+        <v>3545</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Legacy 'Time Clock' users become 'Time Clock User' after migration</t>
+          <t>View and Manage AP/AR Data OFF still lets a user create invoices and take payments if Invoicing &amp; payments allows it</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5928,32 +5928,32 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Live roles API: "Time Clock User" exists, isEditable=false (lock + eye only), 11 users, 3 perms — matches legacy Time Clock -&gt; Time Clock User.</t>
+          <t>UI/perms: AP/AR Data OFF still allows creating invoices/taking payments when Invoicing allows — Service Advisor has invoicingPaymentsCreateAndEdit+Delete with AP/AR off; invoicing capability is independent of AP/AR.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>C26513</t>
+          <t>C26485</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26513</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26485</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>3549</v>
+        <v>3545</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Legacy 'Service Manager' users become 'Service Manager' after migration</t>
+          <t>View and Manage AP/AR Data works independently of See Financial Data</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5968,32 +5968,32 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Live roles API: "Service Manager" exists, isEditable=true, 3 users, 35 perms.</t>
+          <t>UI: See Financial Data and View and Manage AP/AR Data are separate Cross-Cutting Toggles (both present independently alongside View History Logs); AP/AR is not tied to SFD in the editor.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>C26514</t>
+          <t>C26486</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26514</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26486</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3549</v>
+        <v>3545</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Legacy 'Senior Service Advisor' users become 'Senior Service Advisor' after migration</t>
+          <t>View and Manage AP/AR Data OFF does not block any add/edit/delete area</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6008,32 +6008,32 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Live roles API: "Senior Service Advisor" exists, isEditable=true, 8 users, 32 perms.</t>
+          <t>UI: AP/AR Data OFF does not block any add/edit/delete — Service Advisor (AP/AR off) still opens the editable Edit Customer modal and retains full customer/WO/parts create-edit; only the financial tabs/fields are hidden.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>C26515</t>
+          <t>C26492</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26515</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26492</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>3549</v>
+        <v>3547</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Legacy 'Service Advisor' users become 'Service Advisor' after migration</t>
+          <t>Changing a user's role logs them out immediately</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -6048,32 +6048,32 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Live roles API: "Service Advisor" exists, isEditable=true, 2 users, 26 perms.</t>
+          <t>API/session: changing a user role logs them out immediately — the prior session is invalidated (409 Session has expired) right after the change.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>C26516</t>
+          <t>C26494</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26516</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26494</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3549</v>
+        <v>3547</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Legacy 'Foreman' users become 'Foreman' after migration</t>
+          <t>A logged-in user is logged out immediately when their role changes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6088,32 +6088,32 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Live roles API: "Foreman" exists, isEditable=true, 16 users, 23 perms.</t>
+          <t>API/session: a logged-in user is logged out immediately when their role changes (session invalidated -&gt; 409 on next request).</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>C26517</t>
+          <t>C26495</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26517</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26495</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Legacy 'Technician' users become 'Technician' after migration</t>
+          <t>Administrator: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -6123,37 +6123,37 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Live roles API: "Technician" exists, isEditable=true, 66 users, 6 perms, view_mode tech (confirmed via role detail) — matches legacy Technician destination.</t>
+          <t>Administrator permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>C26518</t>
+          <t>C26496</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26518</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26496</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Legacy 'Parts Manager' users become 'Parts Manager' after migration</t>
+          <t>Service Manager: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6163,37 +6163,37 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Live roles API: "Parts Manager" exists, isEditable=true, 4 users, 31 perms.</t>
+          <t>Service Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>C26519</t>
+          <t>C26497</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26519</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26497</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Legacy 'Parts Tech / Parts Technician' users become 'Parts Technician' after migration</t>
+          <t>Senior Service Advisor: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6203,37 +6203,37 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Live roles API: "Parts Technician" exists, isEditable=true, 10 users, 19 perms — matches legacy Parts Tech -&gt; Parts Technician.</t>
+          <t>Senior Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>C26520</t>
+          <t>C26498</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26520</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26498</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Legacy 'Sales Representative' users become 'Sales Representative' after migration</t>
+          <t>Service Advisor: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6243,37 +6243,37 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Live roles API: "Sales Representative" exists, isEditable=true, 15 users, 4 perms.</t>
+          <t>Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>C26525</t>
+          <t>C26499</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26525</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26499</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Changing a user's role logs that user out and forces them to log in again</t>
+          <t>Foreman: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6283,37 +6283,37 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>UI/API: after an admin changed the Tech user role, the user existing session returned 409 "Session has expired." on the next call — the role change logs the user out and forces re-login.</t>
+          <t>Foreman permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>C26528</t>
+          <t>C26500</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26528</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26500</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>3550</v>
+        <v>3548</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Staff Record Settings</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>The universal clock in / out is available to any active staff member, whatever their role</t>
+          <t>Technician: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6323,37 +6323,37 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>UI: the universal Clock In control appears in the top bar for every role observed (Admin, Technician, Time Clock User) — available to any active staff member whatever their role.</t>
+          <t>Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>C26532</t>
+          <t>C26501</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26532</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26501</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>3552</v>
+        <v>3548</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Create success message wording</t>
+          <t>Parts Manager: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6363,37 +6363,37 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>'Role created successfully.' confirmed in build.</t>
+          <t>Parts Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>C26533</t>
+          <t>C26502</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26533</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26502</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3552</v>
+        <v>3548</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Update success message wording</t>
+          <t>Parts Technician: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6403,37 +6403,37 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>'Role updated successfully.' confirmed in build.</t>
+          <t>Parts Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>C26534</t>
+          <t>C26503</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26534</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26503</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>3552</v>
+        <v>3548</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Deleting a custom role with 0 users shows a confirmation dialog</t>
+          <t>Office User: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6443,37 +6443,37 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>UI: deleting a 0-user custom role opens dialog "Confirmation — Are you sure you want to delete this role? This action cannot be undone." [Cancel|Delete]. screenshot delete-confirm-dialog.</t>
+          <t>Office User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>C26535</t>
+          <t>C26504</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26535</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26504</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>3552</v>
+        <v>3548</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Deleting a custom role that has users is blocked</t>
+          <t>Sales Representative: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6483,37 +6483,37 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>UI: a custom role with users (Parth Cust1, 1 user) has no Delete option in its 3-dot menu — deletion is blocked.</t>
+          <t>Sales Representative permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>C26536</t>
+          <t>C26505</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26536</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26505</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3552</v>
+        <v>3548</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Turning See Financial Data on shows a confirmation dialog</t>
+          <t>Time Clock User: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6523,37 +6523,37 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>'Enable See Financial Data?' + Cancel/Enable confirmed in build (FinancialDataConfirmModal).</t>
+          <t>Time Clock User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>C26537</t>
+          <t>C26506</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26537</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26506</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>3552</v>
+        <v>3548</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Creating a role with no name is blocked with a required-field error</t>
+          <t>Customer portal is on by default only for Service Advisor, Senior Service Advisor, Service Manager and Parts Manager (and Administrator)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6563,37 +6563,37 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (matches live per-role customerPortalPageAccess)</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>UI: creating a role with no name is blocked — Create disabled and inline "Role name is a required field" error when the field is touched/cleared.</t>
+          <t>customerPortalPageAccess per role confirmed live: on for Admin/SM/SSA/SA/PM; off for the rest (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>C26538</t>
+          <t>C26510</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26538</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26510</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Creating a role with the same permissions as an existing role shows a 'similar role' warning</t>
+          <t>Legacy 'Admin / Administrator' users become 'Administrator' after migration</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6608,32 +6608,32 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>UI: creating a role with the same permissions as an existing role shows "Similar role already exists" warning with "Create Anyway" (SimilarRoleWarningModal, keyed on identical permissions).</t>
+          <t>Live roles API: destination system role exists = "Admin" (build name; case prose says Administrator), isEditable=true, 89 users, 42 perms. Migration is a completed historical event; destination state verified (role present, editable with pencil, populated).</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>C26542</t>
+          <t>C26511</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26542</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26511</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>3553</v>
+        <v>3549</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Cross-Permission Combinations</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>A system role cannot be deleted</t>
+          <t>Legacy 'Office' users become 'Office User' after migration</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6643,37 +6643,37 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (all system roles deletable=false)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>deletable=false for all system roles (live roles API).</t>
+          <t>Live roles API: "Office User" exists, isEditable=false (lock + eye only), 5 users, 23 perms — matches legacy Office -&gt; Office User destination.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>C26543</t>
+          <t>C26512</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26543</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26512</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>3553</v>
+        <v>3549</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Cross-Permission Combinations</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Only Office User and Time Clock User are non-editable; every other system role (including Administrator) is editable</t>
+          <t>Legacy 'Time Clock' users become 'Time Clock User' after migration</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6683,50 +6683,850 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (editable flags match live)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Live roles API: Office User &amp; Time Clock User editable=false; all others (incl. Administrator) editable=true.</t>
+          <t>Live roles API: "Time Clock User" exists, isEditable=false (lock + eye only), 11 users, 3 perms — matches legacy Time Clock -&gt; Time Clock User.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
+          <t>C26513</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26513</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>3549</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Legacy 'Service Manager' users become 'Service Manager' after migration</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Live roles API: "Service Manager" exists, isEditable=true, 3 users, 35 perms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>C26514</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26514</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>3549</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Legacy 'Senior Service Advisor' users become 'Senior Service Advisor' after migration</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Live roles API: "Senior Service Advisor" exists, isEditable=true, 8 users, 32 perms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>C26515</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26515</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>3549</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Legacy 'Service Advisor' users become 'Service Advisor' after migration</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Live roles API: "Service Advisor" exists, isEditable=true, 2 users, 26 perms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>C26516</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26516</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>3549</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Legacy 'Foreman' users become 'Foreman' after migration</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Live roles API: "Foreman" exists, isEditable=true, 16 users, 23 perms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>C26517</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26517</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>3549</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Legacy 'Technician' users become 'Technician' after migration</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Live roles API: "Technician" exists, isEditable=true, 66 users, 6 perms, view_mode tech (confirmed via role detail) — matches legacy Technician destination.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>C26518</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26518</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>3549</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Legacy 'Parts Manager' users become 'Parts Manager' after migration</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Live roles API: "Parts Manager" exists, isEditable=true, 4 users, 31 perms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>C26519</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26519</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>3549</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Legacy 'Parts Tech / Parts Technician' users become 'Parts Technician' after migration</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Live roles API: "Parts Technician" exists, isEditable=true, 10 users, 19 perms — matches legacy Parts Tech -&gt; Parts Technician.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>C26520</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26520</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>3549</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Legacy 'Sales Representative' users become 'Sales Representative' after migration</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Live roles API: "Sales Representative" exists, isEditable=true, 15 users, 4 perms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>C26525</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26525</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>3549</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Changing a user's role logs that user out and forces them to log in again</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>UI/API: after an admin changed the Tech user role, the user existing session returned 409 "Session has expired." on the next call — the role change logs the user out and forces re-login.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>C26528</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26528</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>3550</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Staff Record Settings</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>The universal clock in / out is available to any active staff member, whatever their role</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>UI: the universal Clock In control appears in the top bar for every role observed (Admin, Technician, Time Clock User) — available to any active staff member whatever their role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>C26532</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26532</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>3552</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>User Feedback Strings</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Create success message wording</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Verified-Label (build)</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>'Role created successfully.' confirmed in build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>C26533</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26533</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>3552</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>User Feedback Strings</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Update success message wording</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Verified-Label (build)</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>'Role updated successfully.' confirmed in build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>C26534</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26534</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>3552</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>User Feedback Strings</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Deleting a custom role with 0 users shows a confirmation dialog</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>UI: deleting a 0-user custom role opens dialog "Confirmation — Are you sure you want to delete this role? This action cannot be undone." [Cancel|Delete]. screenshot delete-confirm-dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>C26535</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26535</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>3552</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>User Feedback Strings</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Deleting a custom role that has users is blocked</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>UI: a custom role with users (Parth Cust1, 1 user) has no Delete option in its 3-dot menu — deletion is blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>C26536</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26536</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>3552</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>User Feedback Strings</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Turning See Financial Data on shows a confirmation dialog</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Verified-Label (build)</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>'Enable See Financial Data?' + Cancel/Enable confirmed in build (FinancialDataConfirmModal).</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>C26537</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26537</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>3552</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>User Feedback Strings</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Creating a role with no name is blocked with a required-field error</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>UI: creating a role with no name is blocked — Create disabled and inline "Role name is a required field" error when the field is touched/cleared.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>C26538</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26538</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>3552</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>User Feedback Strings</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Creating a role with the same permissions as an existing role shows a 'similar role' warning</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>UI: creating a role with the same permissions as an existing role shows "Similar role already exists" warning with "Create Anyway" (SimilarRoleWarningModal, keyed on identical permissions).</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>C26542</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26542</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>A system role cannot be deleted</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Roles-API-Verified (all system roles deletable=false)</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>deletable=false for all system roles (live roles API).</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>C26543</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26543</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Only Office User and Time Clock User are non-editable; every other system role (including Administrator) is editable</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Roles-API-Verified (editable flags match live)</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Live roles API: Office User &amp; Time Clock User editable=false; all others (incl. Administrator) editable=true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>C26549</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26549</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AP/AR OFF hides the sensitive customer fields on both the Edit Customer window and the customer overview</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>UI: AP/AR Data OFF hides the sensitive customer fields on the Edit Customer modal (and the financial tabs on the customer overview) — confirmed via Service Advisor (off) vs CustAPAR (on).</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
           <t>C26551</t>
         </is>
       </c>
-      <c r="B139" s="4" t="inlineStr">
+      <c r="B159" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/26551</t>
         </is>
       </c>
-      <c r="C139" t="n">
+      <c r="C159" t="n">
         <v>3553</v>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D159" t="inlineStr">
         <is>
           <t>Cross-Permission Combinations</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="E159" t="inlineStr">
         <is>
           <t>Universal clock in/out works even for a user whose role has (almost) no permissions</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
         <is>
           <t>UI: the Time Clock User role (only 3 perms: scheduleView/timesheetsView/workOrdersView) still shows the universal Clock In control — universal clock in is not gated by role/permissions.</t>
         </is>
@@ -6872,6 +7672,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B137" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B138" r:id="rId137"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B159" r:id="rId158"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6883,7 +7703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6981,25 +7801,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C26346</t>
+          <t>C26356</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26346</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26356</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3530</v>
+        <v>3532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Edit Role</t>
+          <t>Permission Summary</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The Office User system role cannot be edited (lock icon, eye only)</t>
+          <t>You can view a role's Permission Summary from Edit Staff Member using the eye icon next to the Role dropdown</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -7009,37 +7829,37 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs live Roles list)</t>
+          <t>Blocked-UI: needs the Edit Staff Member modal Role selector + its eye (View Permissions) icon; the staff row action reached opens Manage-staff-enrollments (departments/workplaces), not the role editor. Follow-up: open Edit Staff Member via the correct control.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Office User editable=false confirmed in roles API; eye-only needs live list.</t>
+          <t>Eye-icon-in-staff-modal needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C26347</t>
+          <t>C26375</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26347</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26375</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3530</v>
+        <v>3534</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Edit Role</t>
+          <t>Work Orders Permissions</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>The Time Clock User system role cannot be edited (lock icon, eye only)</t>
+          <t>Work orders Create &amp; Edit lets the user create and change work orders</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -7049,37 +7869,37 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs live Roles list)</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Time Clock User editable=false confirmed in roles API; eye-only needs live list.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C26349</t>
+          <t>C26376</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26349</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26376</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3530</v>
+        <v>3534</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Edit Role</t>
+          <t>Work Orders Permissions</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Editing: at least one permission must be turned on to save</t>
+          <t>Work orders Delete lets the user delete work orders</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -7089,37 +7909,37 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs live editor)</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Save-block-on-empty needs live editor; exact message not re-captured this pass.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C26352</t>
+          <t>C26377</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26352</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26377</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3531</v>
+        <v>3534</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Delete Role</t>
+          <t>Work Orders Permissions</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>After moving the assigned users to another role, the role can be deleted</t>
+          <t>Work orders View OFF hides Work Orders from the top navigation</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -7129,37 +7949,37 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs live Staff + Roles list)</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Needs live UI + seeded role/user.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C26356</t>
+          <t>C26379</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26356</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26379</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3532</v>
+        <v>3534</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Permission Summary</t>
+          <t>Work Orders Permissions</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>You can view a role's Permission Summary from Edit Staff Member using the eye icon next to the Role dropdown</t>
+          <t>The Review work orders sub-toggle controls the Review action on work orders</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -7169,24 +7989,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Blocked-UI: needs the Edit Staff Member modal Role selector + its eye (View Permissions) icon; the staff row action reached opens Manage-staff-enrollments (departments/workplaces), not the role editor. Follow-up: open Edit Staff Member via the correct control.</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Eye-icon-in-staff-modal needs live UI.</t>
+          <t>Needs live UI + role edit.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C26375</t>
+          <t>C26380</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26375</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26380</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -7199,7 +8019,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Work orders Create &amp; Edit lets the user create and change work orders</t>
+          <t>Pick parts needs only Work orders View, not Create &amp; Edit</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -7221,12 +8041,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C26376</t>
+          <t>C26381</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26376</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26381</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -7239,7 +8059,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Work orders Delete lets the user delete work orders</t>
+          <t>Order parts needs Work orders View and See Financial Data (not Create &amp; Edit)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -7254,19 +8074,19 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Order parts+SFD dependency consistent with build (Order-parts enable-SFD modal). Behavior needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C26377</t>
+          <t>C26383</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26377</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26383</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -7279,7 +8099,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Work orders View OFF hides Work Orders from the top navigation</t>
+          <t>Without Create &amp; Edit, create/edit options are hidden on work orders</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -7301,12 +8121,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C26379</t>
+          <t>C26384</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26379</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26384</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -7319,7 +8139,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>The Review work orders sub-toggle controls the Review action on work orders</t>
+          <t>Without Delete, no delete option is shown on a work order</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -7334,19 +8154,19 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Needs live UI + role edit.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C26380</t>
+          <t>C26385</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26380</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26385</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -7359,7 +8179,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pick parts needs only Work orders View, not Create &amp; Edit</t>
+          <t>Creating a work order still works when Customers View is OFF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -7381,12 +8201,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C26381</t>
+          <t>C26386</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26381</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26386</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -7399,7 +8219,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Order parts needs Work orders View and See Financial Data (not Create &amp; Edit)</t>
+          <t>The customer name shows on the work order header even when Customers View is OFF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -7414,19 +8234,19 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Order parts+SFD dependency consistent with build (Order-parts enable-SFD modal). Behavior needs live UI.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C26383</t>
+          <t>C27868</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26383</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27868</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -7439,7 +8259,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Without Create &amp; Edit, create/edit options are hidden on work orders</t>
+          <t>Order parts controls the work order Parts tab (on shows it, off hides it)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -7454,19 +8274,19 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Consistent with build (Order parts gates WO Parts tab). Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C26384</t>
+          <t>C27873</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26384</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27873</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -7479,7 +8299,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Without Delete, no delete option is shown on a work order</t>
+          <t>Edit/delete options on another user's customer note are hidden without the right permission</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -7489,24 +8309,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded roles + notes)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded; customer notes governed by Customers permission (not WO Delete). API/element jargon stripped.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C26385</t>
+          <t>C29435</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26385</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29435</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -7519,7 +8339,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Creating a work order still works when Customers View is OFF</t>
+          <t>A Pick/Order Parts role can edit the Quantity on the Part Requests tab</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -7529,37 +8349,37 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role + WO)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded; element-id jargon stripped.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C26386</t>
+          <t>C26389</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26386</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26389</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3534</v>
+        <v>3535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Work Orders Permissions</t>
+          <t>Work Order Lines Permissions</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>The customer name shows on the work order header even when Customers View is OFF</t>
+          <t>Work order lines are visible whenever Work orders View is ON</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -7569,37 +8389,37 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role); no-WOL-View-column build-verified</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>WOL View comes from WO View (build-verified). Behavior needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C27868</t>
+          <t>C26390</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27868</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26390</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3534</v>
+        <v>3535</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Work Orders Permissions</t>
+          <t>Work Order Lines Permissions</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Order parts controls the work order Parts tab (on shows it, off hides it)</t>
+          <t>Work order lines Create &amp; Edit allows adding, editing, moving parts, authorizing and managing part requests</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -7614,32 +8434,32 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Consistent with build (Order parts gates WO Parts tab). Needs live UI.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C27873</t>
+          <t>C26391</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27873</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26391</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3534</v>
+        <v>3535</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Work Orders Permissions</t>
+          <t>Work Order Lines Permissions</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Edit/delete options on another user's customer note are hidden without the right permission</t>
+          <t>Work order lines Delete allows removing lines</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -7649,37 +8469,37 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded roles + notes)</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Reworded; customer notes governed by Customers permission (not WO Delete). API/element jargon stripped.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C29435</t>
+          <t>C26392</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29435</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26392</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3534</v>
+        <v>3535</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Work Orders Permissions</t>
+          <t>Work Order Lines Permissions</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>A Pick/Order Parts role can edit the Quantity on the Part Requests tab</t>
+          <t>Work orders View OFF makes work order lines unreachable</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -7689,24 +8509,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + WO)</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Reworded; element-id jargon stripped.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C26389</t>
+          <t>C26393</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26389</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26393</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -7719,7 +8539,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Work order lines are visible whenever Work orders View is ON</t>
+          <t>Work order lines are read-only when Create &amp; Edit is OFF</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -7729,24 +8549,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); no-WOL-View-column build-verified</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>WOL View comes from WO View (build-verified). Behavior needs live UI.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C26390</t>
+          <t>C27271</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26390</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27271</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -7759,7 +8579,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Work order lines Create &amp; Edit allows adding, editing, moving parts, authorizing and managing part requests</t>
+          <t>The Build Lines entry point is hidden for a Work Orders View-only role</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -7769,24 +8589,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role + ShopCoach on)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded; element-id jargon stripped. Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C26391</t>
+          <t>C27272</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26391</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27272</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -7799,7 +8619,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Work order lines Delete allows removing lines</t>
+          <t>The Build Lines entry point is shown for a role with Work order lines Create &amp; Edit</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -7809,24 +8629,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role + ShopCoach on)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded; element-id jargon stripped. Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C26392</t>
+          <t>C27866</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26392</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27866</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -7839,7 +8659,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Work orders View OFF makes work order lines unreachable</t>
+          <t>A default Technician (with Work order lines Create &amp; Edit) can bulk-complete another tech's line via Set Line Status</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -7849,24 +8669,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs default Technician role + seeded WO line)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded; SV-ref/URL/403 jargon stripped. Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C26393</t>
+          <t>C27870</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26393</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27870</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -7879,7 +8699,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Work order lines are read-only when Create &amp; Edit is OFF</t>
+          <t>Work order lines Create &amp; Edit lets the user mark a core OK/Not-OK and add line history</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -7889,37 +8709,37 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role + core part)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Needs live UI with a cored part.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C27271</t>
+          <t>C26395</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27271</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26395</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3535</v>
+        <v>3536</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Work Order Lines Permissions</t>
+          <t>Schedule Permissions</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>The Build Lines entry point is hidden for a Work Orders View-only role</t>
+          <t>Schedule Create &amp; Edit allows creating, changing and dragging appointments</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -7929,37 +8749,37 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + ShopCoach on)</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Reworded; element-id jargon stripped. Needs live UI.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C27272</t>
+          <t>C26396</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27272</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26396</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3535</v>
+        <v>3536</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Work Order Lines Permissions</t>
+          <t>Schedule Permissions</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>The Build Lines entry point is shown for a role with Work order lines Create &amp; Edit</t>
+          <t>Schedule Delete allows removing appointments</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -7969,37 +8789,37 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + ShopCoach on)</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Reworded; element-id jargon stripped. Needs live UI.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C27866</t>
+          <t>C27867</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27866</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27867</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3535</v>
+        <v>3536</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Work Order Lines Permissions</t>
+          <t>Schedule Permissions</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>A default Technician (with Work order lines Create &amp; Edit) can bulk-complete another tech's line via Set Line Status</t>
+          <t>A Schedule Create &amp; Edit only role can open 'Assign existing work order' and the unscheduled work order list loads</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -8009,37 +8829,37 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs default Technician role + seeded WO line)</t>
+          <t>Blocked-UI (needs seeded Schedule-only role)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Reworded; SV-ref/URL/403 jargon stripped. Needs live UI.</t>
+          <t>Reworded; API endpoint jargon stripped. Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C27870</t>
+          <t>C26399</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27870</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26399</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3535</v>
+        <v>3537</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Work Order Lines Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Work order lines Create &amp; Edit lets the user mark a core OK/Not-OK and add line history</t>
+          <t>Customers Create &amp; Edit allows creating customers, contacts and vehicles</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -8049,37 +8869,37 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + core part)</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Needs live UI with a cored part.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C26395</t>
+          <t>C26400</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26395</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26400</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3536</v>
+        <v>3537</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Schedule Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Schedule Create &amp; Edit allows creating, changing and dragging appointments</t>
+          <t>Customers Delete removes the customer record</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -8101,25 +8921,25 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C26396</t>
+          <t>C26401</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26396</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26401</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3536</v>
+        <v>3537</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Schedule Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Schedule Delete allows removing appointments</t>
+          <t>Customers Delete does NOT let the user delete customer payments (that needs Invoicing &amp; payments Delete)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -8141,25 +8961,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>C27867</t>
+          <t>C26405</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27867</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26405</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3536</v>
+        <v>3537</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Schedule Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>A Schedule Create &amp; Edit only role can open 'Assign existing work order' and the unscheduled work order list loads</t>
+          <t>Customer names still show on work orders and invoices even when Customers is hidden</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -8169,37 +8989,37 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded Schedule-only role)</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Reworded; API endpoint jargon stripped. Needs live UI.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>C26399</t>
+          <t>C26412</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26399</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26412</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3537</v>
+        <v>3538</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Customers Create &amp; Edit allows creating customers, contacts and vehicles</t>
+          <t>Part sales Delete lets the user delete part sales and reverse part sales invoices</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -8209,7 +9029,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: Part sales Delete affordance (delete/reverse a part sale) not located in this pass — the part-sale row menu did not open in the harness; needs the part-sale detail-page delete control with a with/without partSalesDelete contrast.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -8221,25 +9041,25 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>C26400</t>
+          <t>C26415</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26400</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26415</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3537</v>
+        <v>3538</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Customers Delete removes the customer record</t>
+          <t>Catalog and Inventory Delete removes catalog parts</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -8249,7 +9069,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: Catalog Delete affordance not located — the catalogue row more_vert menu did not open in the harness; needs the catalog-part detail delete control (Parts Manager has catalogInventoryDelete) vs a no-delete role.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -8261,25 +9081,25 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>C26401</t>
+          <t>C26418</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26401</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26418</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3537</v>
+        <v>3538</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Customers Delete does NOT let the user delete customer payments (that needs Invoicing &amp; payments Delete)</t>
+          <t>Vendor and order management Delete lets the user delete vendors and purchase orders and reverse vendor transactions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -8289,37 +9109,37 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: Vendor/PO Delete affordance (delete vendor/PO, reverse vendor txn) not located this pass; needs the vendor/PO detail delete control with/without vendorOrderManagementDelete.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Needs live UI; AP/AR dependency on the vendor Payments tab is build-observed.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C26402</t>
+          <t>C26419</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26402</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26419</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3537</v>
+        <v>3538</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AP/AR OFF hides the 7 sensitive customer fields on Edit Customer</t>
+          <t>Returning a part to inventory (restocking) is controlled by Vendor and order management</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -8329,7 +9149,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: restocking (return part to inventory) control not reached — needs a WO/PO with a picked part to exercise the return-to-inventory action gated by Vendor and order management.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -8341,25 +9161,25 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C26403</t>
+          <t>C26420</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26403</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26420</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3537</v>
+        <v>3539</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AP/AR ON shows the 7 sensitive customer fields on Edit Customer</t>
+          <t>Invoicing &amp; payments View shows the Finance tab and lets the user see invoices</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -8369,7 +9189,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: the Invoicing &amp; payments / Finance surface route was not confirmed (/invoices returned minimal content for the Viewer role). Follow-up: locate the Finance tab/invoices route and confirm invoicingPaymentsView access.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -8381,25 +9201,25 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C26405</t>
+          <t>C26421</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26405</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26421</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3537</v>
+        <v>3539</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Customer names still show on work orders and invoices even when Customers is hidden</t>
+          <t>Invoicing &amp; payments Create &amp; Edit lets the user create invoices and take payments</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -8421,25 +9241,25 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C26410</t>
+          <t>C26422</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26410</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26422</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3538</v>
+        <v>3539</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Part sales View gives read access to part sales records</t>
+          <t>Invoicing &amp; payments Delete lets the user delete payments and void transactions (but not reverse invoices)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -8449,7 +9269,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Blocked-UI: a Viewer role WITH Part sales View was redirected from /parts/part-sales to /workorders — part-sales list access could not be confirmed (route may differ or partSalesView alone may be insufficient). Follow-up: confirm the part-sales list route/gate.</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -8461,25 +9281,25 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C26411</t>
+          <t>C26423</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26411</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26423</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3538</v>
+        <v>3539</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Part sales Create &amp; Edit lets the user create part sales, returns and transactions</t>
+          <t>Deleting a customer payment needs Invoicing &amp; payments Delete, not Customers Delete</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8501,25 +9321,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C26412</t>
+          <t>C26425</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26412</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26425</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3538</v>
+        <v>3539</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Part sales Delete lets the user delete part sales and reverse part sales invoices</t>
+          <t>See Financial Data OFF makes Invoicing &amp; payments inaccessible even with View, Create &amp; Edit and Delete</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8541,25 +9361,25 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C26414</t>
+          <t>C26426</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26414</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26426</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3538</v>
+        <v>3539</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Catalog and Inventory Create &amp; Edit lets the user create/edit items and make adjustments (cost/price shown only with See Financial Data)</t>
+          <t>Invoicing &amp; payments View OFF with See Financial Data ON: prices show but invoices are not reachable</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8581,25 +9401,25 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C26415</t>
+          <t>C26427</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26415</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26427</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3538</v>
+        <v>3539</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Catalog and Inventory Delete removes catalog parts</t>
+          <t>The Send to Terminal action needs Invoicing &amp; payments Create &amp; Edit</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8621,25 +9441,25 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>C26417</t>
+          <t>C26428</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26417</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26428</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3538</v>
+        <v>3539</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Vendor and order management Create &amp; Edit lets the user manage vendors, purchase orders, receiving and returns</t>
+          <t>Taking Deposits on a work order needs Invoicing &amp; payments Create &amp; Edit</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8661,25 +9481,25 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>C26418</t>
+          <t>C27871</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26418</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27871</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3538</v>
+        <v>3539</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Vendor and order management Delete lets the user delete vendors and purchase orders and reverse vendor transactions</t>
+          <t>Deleting or cancelling a return is controlled by Invoicing &amp; payments Delete</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8689,37 +9509,37 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded roles + returns)</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Needs live UI; AP/AR dependency on the vendor Payments tab is build-observed.</t>
+          <t>Reworded; SV-ref/element-id jargon stripped.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>C26419</t>
+          <t>C29434</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26419</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29434</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3538</v>
+        <v>3539</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Returning a part to inventory (restocking) is controlled by Vendor and order management</t>
+          <t>Send to Terminal needs Invoicing &amp; payments Create &amp; Edit AND Customer portal ON</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -8729,24 +9549,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded roles + terminal)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded; feature-flag/element-id/SV jargon stripped.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>C26420</t>
+          <t>C29438</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26420</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29438</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -8759,7 +9579,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Invoicing &amp; payments View shows the Finance tab and lets the user see invoices</t>
+          <t>Invoicing &amp; payments Create &amp; Edit gives the edit control on the work order Financial Info card</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -8769,37 +9589,37 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Blocked-UI: the Invoicing &amp; payments / Finance surface route was not confirmed (/invoices returned minimal content for the Viewer role). Follow-up: locate the Finance tab/invoices route and confirm invoicingPaymentsView access.</t>
+          <t>Blocked-UI (needs seeded role + WO)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded; element-id/SV jargon stripped.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>C26421</t>
+          <t>C26430</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26421</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26430</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Invoicing &amp; payments Create &amp; Edit lets the user create invoices and take payments</t>
+          <t>Timesheets View only: timesheet entries are read-only</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -8814,32 +9634,32 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Read-only behavior needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>C26422</t>
+          <t>C26431</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26422</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26431</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Invoicing &amp; payments Delete lets the user delete payments and void transactions (but not reverse invoices)</t>
+          <t>Timesheets Create &amp; Edit lets the user edit entries</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -8854,32 +9674,32 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Edit behavior needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>C26423</t>
+          <t>C26433</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26423</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26433</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Deleting a customer payment needs Invoicing &amp; payments Delete, not Customers Delete</t>
+          <t>Timesheets View OFF with Reports ON: the timesheet activities report is still available</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -8894,32 +9714,32 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Report access needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C26425</t>
+          <t>C26434</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26425</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26434</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>See Financial Data OFF makes Invoicing &amp; payments inaccessible even with View, Create &amp; Edit and Delete</t>
+          <t>All Timesheets permissions OFF and Reports OFF: no timesheet navigation anywhere</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -8934,32 +9754,32 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Nav-hide needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C26426</t>
+          <t>C27394</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26426</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27394</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Invoicing &amp; payments View OFF with See Financial Data ON: prices show but invoices are not reachable</t>
+          <t>A clock-capable role without Timesheets View can still see and open My Timesheets</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -8969,37 +9789,37 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded clock-capable role)</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded, jargon stripped; needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>C26427</t>
+          <t>C26437</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26427</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26437</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3539</v>
+        <v>3541</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>The Send to Terminal action needs Invoicing &amp; payments Create &amp; Edit</t>
+          <t>Customer portal ON lets the user manage the customer portal</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -9009,37 +9829,37 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role); toggle label 'Customer portal' build-verified</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Toggle 'Customer portal' confirmed in build. Manage behavior needs live check.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>C26428</t>
+          <t>C26438</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26428</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26438</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3539</v>
+        <v>3541</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Taking Deposits on a work order needs Invoicing &amp; payments Create &amp; Edit</t>
+          <t>Customer portal OFF hides the customer portal from navigation</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -9054,32 +9874,32 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Nav-hide needs live check.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>C27871</t>
+          <t>C26439</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27871</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26439</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3539</v>
+        <v>3541</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Deleting or cancelling a return is controlled by Invoicing &amp; payments Delete</t>
+          <t>Billing Portal ON lets the user manage the billing portal</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -9089,37 +9909,37 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded roles + returns)</t>
+          <t>Blocked-UI (needs seeded role); toggle label 'Billing Portal' build-verified</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Reworded; SV-ref/element-id jargon stripped.</t>
+          <t>Toggle 'Billing Portal' confirmed in build. Manage behavior needs live check.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C29434</t>
+          <t>C26440</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29434</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26440</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3539</v>
+        <v>3541</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Send to Terminal needs Invoicing &amp; payments Create &amp; Edit AND Customer portal ON</t>
+          <t>Billing Portal OFF hides the Billing Portal item in the Settings area</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -9129,37 +9949,37 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded roles + terminal)</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Reworded; feature-flag/element-id/SV jargon stripped.</t>
+          <t>Nav-hide needs live check.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C29438</t>
+          <t>C26445</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29438</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26445</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3539</v>
+        <v>3542</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Invoicing &amp; payments Create &amp; Edit gives the edit control on the work order Financial Info card</t>
+          <t>App Settings ON gives access to the admin pages</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -9169,37 +9989,37 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + WO)</t>
+          <t>Blocked-UI (needs seeded role); page names build-verified</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Reworded; element-id/SV jargon stripped.</t>
+          <t>App Settings gates Departments/Settings/Staff/Roles &amp; Permissions/Locations (build route metadata).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C26430</t>
+          <t>C26446</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26430</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26446</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3540</v>
+        <v>3542</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Timesheets View only: timesheet entries are read-only</t>
+          <t>Service ON gives access to the Service configuration pages</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -9209,37 +10029,37 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role); page names build-verified</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Read-only behavior needs live UI.</t>
+          <t>Service gates Canned Lines/Inspection Templates/Labour Types/Vehicle Types (build route metadata).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C26431</t>
+          <t>C26447</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26431</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26447</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3540</v>
+        <v>3542</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Timesheets Create &amp; Edit lets the user edit entries</t>
+          <t>Parts ON gives access to the Parts configuration pages</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -9249,37 +10069,37 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role); page names build-verified</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Edit behavior needs live UI.</t>
+          <t>Parts gates Bins/Categories/Pricing (build route metadata).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C26433</t>
+          <t>C26448</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26433</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26448</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3540</v>
+        <v>3542</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Timesheets View OFF with Reports ON: the timesheet activities report is still available</t>
+          <t>Finance ON shows the Finance pages, and Integrations ON shows QuickBooks, IBS and Open API</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -9289,37 +10109,37 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role); page names build-verified</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Report access needs live UI.</t>
+          <t>Finance gates Payment Methods/Taxes; Integrations gates IBS/Open API/QuickBooks (build route metadata).</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C26434</t>
+          <t>C26449</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26434</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26449</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3540</v>
+        <v>3542</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>All Timesheets permissions OFF and Reports OFF: no timesheet navigation anywhere</t>
+          <t>Data Import ON gives access to the Imports pages</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -9329,37 +10149,37 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role); page names build-verified</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Nav-hide needs live UI.</t>
+          <t>Data Import gates Contacts/Inventory/Invoices/Vehicles/Vendors Import (build route metadata).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C27394</t>
+          <t>C26450</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27394</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26450</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3540</v>
+        <v>3542</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>A clock-capable role without Timesheets View can still see and open My Timesheets</t>
+          <t>View/Manage Wages ON lets the user manage wages</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -9369,37 +10189,37 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded clock-capable role)</t>
+          <t>Blocked-UI (needs seeded role); toggle label 'View/Manage Wages' build-verified</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Reworded, jargon stripped; needs live UI.</t>
+          <t>Toggle 'View/Manage Wages' confirmed in build. Wage editing needs live check.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C26437</t>
+          <t>C26451</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26437</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26451</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3541</v>
+        <v>3542</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Customer portal ON lets the user manage the customer portal</t>
+          <t>The Settings sub-toggles work independently (Service on, Finance off)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -9409,37 +10229,37 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); toggle label 'Customer portal' build-verified</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Toggle 'Customer portal' confirmed in build. Manage behavior needs live check.</t>
+          <t>Needs live check.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C26438</t>
+          <t>C29273</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26438</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29273</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3541</v>
+        <v>3542</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Customer portal OFF hides the customer portal from navigation</t>
+          <t>The Integrations admin pages depend on the Integrations sub-toggle, not on Finance</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -9449,37 +10269,37 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs two seeded roles)</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Nav-hide needs live check.</t>
+          <t>Steps-Separated case; reworded to layman, stripped element-id/URL jargon. Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C26439</t>
+          <t>C29274</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26439</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29274</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3541</v>
+        <v>3542</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Billing Portal ON lets the user manage the billing portal</t>
+          <t>The QuickBooks connection check does not run for roles without Integrations</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -9489,37 +10309,37 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); toggle label 'Billing Portal' build-verified</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Toggle 'Billing Portal' confirmed in build. Manage behavior needs live check.</t>
+          <t>Steps-Separated case; reworded to layman. Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C26440</t>
+          <t>C26460</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26440</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26460</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3541</v>
+        <v>3543</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Billing Portal OFF hides the Billing Portal item in the Settings area</t>
+          <t>Tech view: the parts request form shows fewer fields</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -9529,37 +10349,37 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: needs the New Part Request form opened in tech view vs full view to compare field counts; the lines screen is drivable but the request-form modal step was not reached this pass.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Nav-hide needs live check.</t>
+          <t>precise reason logged</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C26445</t>
+          <t>C26461</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26445</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26461</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3542</v>
+        <v>3543</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>App Settings ON gives access to the admin pages</t>
+          <t>Tech view: the user can add new work order lines but cannot edit existing ones</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -9569,37 +10389,37 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); page names build-verified</t>
+          <t>Blocked-UI: New Line (add) confirmed present in tech view, but the existing-line read-only lock was not directly exercised (would require attempting to edit a pending line inline). Precise follow-up: open a pending line editor as the tech.</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>App Settings gates Departments/Settings/Staff/Roles &amp; Permissions/Locations (build route metadata).</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C26446</t>
+          <t>C26462</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26446</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26462</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3542</v>
+        <v>3543</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Service ON gives access to the Service configuration pages</t>
+          <t>Tech view: a line becomes read-only once its authorization is approved</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -9609,37 +10429,37 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); page names build-verified</t>
+          <t>Blocked-UI: approved-WO lines showed only tech status actions (Complete/Story/Start) with no edit control (consistent with read-only), but the pending-&gt;approved edit-lock transition was not directly exercised.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Service gates Canned Lines/Inspection Templates/Labour Types/Vehicle Types (build route metadata).</t>
+          <t>Needs live UI + a second user.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C26447</t>
+          <t>C26466</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26447</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26466</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3542</v>
+        <v>3543</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Parts ON gives access to the Parts configuration pages</t>
+          <t>Full View: a user who can approve lines sees the 'Send to Portal' button</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -9649,37 +10469,37 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); page names build-verified</t>
+          <t>Blocked-UI: Send to Portal was NOT found on the full-view (admin) lines page body; it is likely in the WO header more_vert menu or gated by WO state — needs the header action menu expanded to confirm.</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Parts gates Bins/Categories/Pricing (build route metadata).</t>
+          <t>Send-to-Portal flow needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C26448</t>
+          <t>C26479</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26448</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26479</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3542</v>
+        <v>3545</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Finance ON shows the Finance pages, and Integrations ON shows QuickBooks, IBS and Open API</t>
+          <t>View and Manage AP/AR Data ON allows paying several invoices at once from the Unpaid Invoices tab</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -9689,37 +10509,37 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); page names build-verified</t>
+          <t>Blocked-UI (needs seeded role + live payment)</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Finance gates Payment Methods/Taxes; Integrations gates IBS/Open API/QuickBooks (build route metadata).</t>
+          <t>Bulk payment needs live UI + payment (create-customer-payment 500s intermittently per prior run).</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>C26449</t>
+          <t>C26488</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26449</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26488</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3542</v>
+        <v>3546</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>View History Logs</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Data Import ON gives access to the Imports pages</t>
+          <t>View History Logs ON: work order history and line history are visible (work orders only)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -9729,37 +10549,37 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); page names build-verified</t>
+          <t>Blocked-UI (needs seeded role); 'View History Logs' toggle build-verified</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Data Import gates Contacts/Inventory/Invoices/Vehicles/Vendors Import (build route metadata).</t>
+          <t>Cross-toggle 'View History Logs' confirmed in build. History visibility needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C26450</t>
+          <t>C26489</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26450</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26489</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3542</v>
+        <v>3546</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>View History Logs</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>View/Manage Wages ON lets the user manage wages</t>
+          <t>View History Logs OFF: work order history and line history are hidden (work orders only)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -9769,37 +10589,37 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); toggle label 'View/Manage Wages' build-verified</t>
+          <t>Blocked-UI (needs seeded role); labels build-verified</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Toggle 'View/Manage Wages' confirmed in build. Wage editing needs live check.</t>
+          <t>viewHistoryLogs also gates the 'Part History' page under Parts (build route metadata). History-hide needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C26451</t>
+          <t>C26490</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26451</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26490</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3542</v>
+        <v>3547</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>The Settings sub-toggles work independently (Service on, Finance off)</t>
+          <t>The Staff role dropdown groups roles into System Roles and Custom Roles</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -9809,37 +10629,37 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: the Edit Staff Member Role dropdown (System/Custom grouping) was not reached — the staff row click opened Manage-staff-enrollments. Follow-up: locate the Edit Staff Member action, open the Role selector.</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Needs live check.</t>
+          <t>11 system roles confirmed in live roles list (was '12'). Grouping labels need live Staff page.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>C29273</t>
+          <t>C26491</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29273</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26491</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3542</v>
+        <v>3547</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>The Integrations admin pages depend on the Integrations sub-toggle, not on Finance</t>
+          <t>The View Permissions button next to the role selector opens the Permission Summary</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -9849,37 +10669,37 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs two seeded roles)</t>
+          <t>Blocked-UI: View Permissions eye next to the staff Role selector not reached (same Edit-Staff-Member surface as C26490).</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Steps-Separated case; reworded to layman, stripped element-id/URL jargon. Needs live UI.</t>
+          <t>'View Permissions' confirmed in build. Needs live Staff page.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>C29274</t>
+          <t>C26493</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29274</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26493</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3542</v>
+        <v>3547</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>The QuickBooks connection check does not run for roles without Integrations</t>
+          <t>If a role change fails, the user keeps their previous role</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -9889,37 +10709,37 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: forcing a failed role change (to confirm the user keeps the prior role) requires inducing a server error on /change; not reproducible on demand this pass.</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Steps-Separated case; reworded to layman. Needs live UI.</t>
+          <t>Failed-save path needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>C26460</t>
+          <t>C26526</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26460</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26526</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3543</v>
+        <v>3550</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Staff Record Settings</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Tech view: the parts request form shows fewer fields</t>
+          <t>Whether a technician can be scheduled depends on their department, not their role</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -9929,37 +10749,37 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Blocked-UI: needs the New Part Request form opened in tech view vs full view to compare field counts; the lines screen is drivable but the request-form modal step was not reached this pass.</t>
+          <t>Blocked-UI (needs two seeded users + departments)</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>precise reason logged</t>
+          <t>Department-gated scheduling needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>C26461</t>
+          <t>C26527</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26461</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26527</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3543</v>
+        <v>3550</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Staff Record Settings</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Tech view: the user can add new work order lines but cannot edit existing ones</t>
+          <t>Clocking in on a work order line depends on the per-staff Time Clock setting</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -9969,37 +10789,37 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Blocked-UI: New Line (add) confirmed present in tech view, but the existing-line read-only lock was not directly exercised (would require attempting to edit a pending line inline). Precise follow-up: open a pending line editor as the tech.</t>
+          <t>Blocked-UI (needs two seeded users)</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Per-staff Time Clock gating needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>C26462</t>
+          <t>C26539</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26462</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26539</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3543</v>
+        <v>3552</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>User Feedback Strings</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Tech view: a line becomes read-only once its authorization is approved</t>
+          <t>Reassigning a staff member's role updates the row with no success message (billing note in the window)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -10009,37 +10829,37 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Blocked-UI: approved-WO lines showed only tech status actions (Complete/Story/Start) with no edit control (consistent with read-only), but the pending-&gt;approved edit-lock transition was not directly exercised.</t>
+          <t>Blocked-UI (needs live Staff page); billing note not re-captured this pass</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Needs live UI + a second user.</t>
+          <t>No-toast-on-reassign + billing note need live Staff page (EditStaffMember chunk not fetched).</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>C26466</t>
+          <t>C26540</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26466</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26540</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3543</v>
+        <v>3553</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Cross-Permission Combinations</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Full View: a user who can approve lines sees the 'Send to Portal' button</t>
+          <t>A role with all permissions off blocks the user from every feature</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -10049,37 +10869,37 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Blocked-UI: Send to Portal was NOT found on the full-view (admin) lines page body; it is likely in the WO header more_vert menu or gated by WO state — needs the header action menu expanded to confirm.</t>
+          <t>Blocked-UI (needs live role editor / roles list)</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Send-to-Portal flow needs live UI.</t>
+          <t>Needs seeded role.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>C26476</t>
+          <t>C26541</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26476</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26541</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3545</v>
+        <v>3553</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>Cross-Permission Combinations</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data ON shows the Unpaid Invoices, Payments and Credits tabs on a customer</t>
+          <t>A role with all permissions on behaves like Administrator but is still a custom role</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -10089,37 +10909,37 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + customer detail check); toggle label build-verified</t>
+          <t>Blocked-UI (needs live role editor / roles list)</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>AP/AR toggle label 'View and Manage AP/AR Data' confirmed in build (CrossTogglesSection). Tab visibility needs live UI.</t>
+          <t>Needs seeded role.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>C26477</t>
+          <t>C26544</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26477</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26544</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3545</v>
+        <v>3553</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>Cross-Permission Combinations</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data ON shows the same three tabs on a vendor</t>
+          <t>Being unable to open Customers does not stop a user from picking a customer when creating a work order</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -10129,37 +10949,37 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + vendor detail check)</t>
+          <t>Blocked-UI (needs live role editor / roles list)</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Vendor AP/AR tabs need live UI. Build gates VendorPaymentsTab/VendorDeliveriesTab on AP/AR data.</t>
+          <t>Needs seeded role.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>C26478</t>
+          <t>C26545</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26478</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26545</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3545</v>
+        <v>3553</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>Cross-Permission Combinations</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>With Reports ON, all 6 AP/AR aging reports are listed (whether or not AP/AR is on)</t>
+          <t>A Page Access toggle that is off overrides the add/edit/delete boxes inside it</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -10169,37 +10989,37 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + Reports check)</t>
+          <t>Blocked-UI (needs live role editor / roles list)</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Aging-report gating needs live check; report page names not re-confirmed from build this pass.</t>
+          <t>Needs seeded role.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>C26479</t>
+          <t>C26548</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26479</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26548</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3545</v>
+        <v>3553</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>Cross-Permission Combinations</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data ON allows paying several invoices at once from the Unpaid Invoices tab</t>
+          <t>View off with Create &amp; Edit on is prevented by the tick-cascade</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -10209,37 +11029,37 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + live payment)</t>
+          <t>Blocked-UI (needs live editor); cascade rule</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Bulk payment needs live UI + payment (create-customer-payment 500s intermittently per prior run).</t>
+          <t>Needs live editor; matches cascade rules.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>C26480</t>
+          <t>C26550</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26480</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26550</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3545</v>
+        <v>3553</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>Cross-Permission Combinations</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data OFF hides the three tabs on a customer</t>
+          <t>The last Administrator cannot be left with zero users</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -10249,810 +11069,10 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + customer detail check)</t>
+          <t>Blocked-UI (needs live role editor / roles list)</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
-        <is>
-          <t>Tab-hidden behavior needs live UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>C26481</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26481</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>3545</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>View and Manage AP/AR Data</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>View and Manage AP/AR Data OFF hides the three tabs on a vendor</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs seeded role + vendor detail check)</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Tab-hidden behavior needs live UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>C26482</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26482</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>3545</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>View and Manage AP/AR Data</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>With AP/AR OFF but Reports ON, all 6 AP/AR aging reports are still listed</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Blocked-UI; NOTE prior run FAILED here (aging still hid with AP/AR OFF) — re-test live</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>RUN331 recorded this as a FAIL (aging reports still gated by AP/AR, not Reports). Needs a fresh live re-test.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>C26483</t>
-        </is>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26483</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>3545</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>View and Manage AP/AR Data</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>View and Manage AP/AR Data OFF hides the sensitive money fields on Edit Customer</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs seeded role + Edit Customer check)</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Field-hiding needs live UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>C26484</t>
-        </is>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26484</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>3545</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>View and Manage AP/AR Data</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>View and Manage AP/AR Data OFF still lets a user create invoices and take payments if Invoicing &amp; payments allows it</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs seeded role + live invoice/payment)</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Needs live UI + payment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>C26486</t>
-        </is>
-      </c>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26486</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>3545</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>View and Manage AP/AR Data</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>View and Manage AP/AR Data OFF does not block any add/edit/delete area</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs seeded role + UI check)</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Needs live UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>C26488</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26488</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>3546</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>View History Logs</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>View History Logs ON: work order history and line history are visible (work orders only)</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs seeded role); 'View History Logs' toggle build-verified</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Cross-toggle 'View History Logs' confirmed in build. History visibility needs live UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>C26489</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26489</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>3546</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>View History Logs</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>View History Logs OFF: work order history and line history are hidden (work orders only)</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs seeded role); labels build-verified</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>viewHistoryLogs also gates the 'Part History' page under Parts (build route metadata). History-hide needs live UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>C26490</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26490</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>3547</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Staff Page Role Assignment</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>The Staff role dropdown groups roles into System Roles and Custom Roles</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Blocked-UI: the Edit Staff Member Role dropdown (System/Custom grouping) was not reached — the staff row click opened Manage-staff-enrollments. Follow-up: locate the Edit Staff Member action, open the Role selector.</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>11 system roles confirmed in live roles list (was '12'). Grouping labels need live Staff page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>C26491</t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26491</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>3547</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Staff Page Role Assignment</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>The View Permissions button next to the role selector opens the Permission Summary</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Blocked-UI: View Permissions eye next to the staff Role selector not reached (same Edit-Staff-Member surface as C26490).</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>'View Permissions' confirmed in build. Needs live Staff page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>C26493</t>
-        </is>
-      </c>
-      <c r="B94" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26493</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>3547</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Staff Page Role Assignment</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>If a role change fails, the user keeps their previous role</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Blocked-UI: forcing a failed role change (to confirm the user keeps the prior role) requires inducing a server error on /change; not reproducible on demand this pass.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Failed-save path needs live UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>C26526</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26526</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>3550</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Staff Record Settings</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Whether a technician can be scheduled depends on their department, not their role</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs two seeded users + departments)</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Department-gated scheduling needs live UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>C26527</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26527</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>3550</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Staff Record Settings</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>Clocking in on a work order line depends on the per-staff Time Clock setting</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs two seeded users)</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Per-staff Time Clock gating needs live UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>C26539</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26539</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>3552</v>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>User Feedback Strings</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Reassigning a staff member's role updates the row with no success message (billing note in the window)</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live Staff page); billing note not re-captured this pass</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>No-toast-on-reassign + billing note need live Staff page (EditStaffMember chunk not fetched).</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>C26540</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26540</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>A role with all permissions off blocks the user from every feature</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Needs seeded role.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>C26541</t>
-        </is>
-      </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26541</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>A role with all permissions on behaves like Administrator but is still a custom role</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Needs seeded role.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>C26544</t>
-        </is>
-      </c>
-      <c r="B100" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26544</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Being unable to open Customers does not stop a user from picking a customer when creating a work order</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Needs seeded role.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>C26545</t>
-        </is>
-      </c>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26545</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>A Page Access toggle that is off overrides the add/edit/delete boxes inside it</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Needs seeded role.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>C26548</t>
-        </is>
-      </c>
-      <c r="B102" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26548</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>View off with Create &amp; Edit on is prevented by the tick-cascade</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live editor); cascade rule</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Needs live editor; matches cascade rules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>C26549</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26549</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AP/AR OFF hides the sensitive customer fields on both the Edit Customer window and the customer overview</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs seeded role); overview-panel hiding needs live re-check</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Modal hiding expected; overview-panel behavior flagged for live re-check (build-vs-spec note in original).</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>C26550</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26550</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>The last Administrator cannot be left with zero users</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
         <is>
           <t>Needs live UI; invariant to confirm.</t>
         </is>
@@ -11143,26 +11163,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B82" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B83" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B96" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B97" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" r:id="rId103"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13294,17 +13294,17 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs live Roles list)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Office User editable=false confirmed in roles API; eye-only needs live list.</t>
+          <t>UI: on the Roles list the Office User row shows a lock and only the eye (visibility) icon — no pencil; the eye opens the read-only Permission Summary (View Permissions). NOTE for dev: the direct /roles-permissions/{id}/edit URL still loads an editable form (FE route not guarded) — list-level gating is correct.</t>
         </is>
       </c>
     </row>
@@ -13334,17 +13334,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs live Roles list)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Time Clock User editable=false confirmed in roles API; eye-only needs live list.</t>
+          <t>UI: on the Roles list the Time Clock User row shows a lock and only the eye icon — no pencil; the eye opens the read-only Permission Summary. Same /edit-URL FE-gap note as C26346.</t>
         </is>
       </c>
     </row>
@@ -13414,17 +13414,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs live editor)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Save-block-on-empty needs live editor; exact message not re-captured this pass.</t>
+          <t>UI: editing a role down to zero permissions -&gt; Save opens "Confirm Permission Updates" (Removed permissions listed) -&gt; Confirm shows toast "At least one permission is required. Please try to resolve this." and the role is NOT saved (stays on edit). Submit-time validation enforces at least one permission. screenshot edit-zero-perm.</t>
         </is>
       </c>
     </row>
@@ -13534,17 +13534,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs live Staff + Roles list)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Needs live UI + seeded role/user.</t>
+          <t>UI/API: assigned Tech to a custom role -&gt; usersCount=1, isDeletable=false, DELETE blocked (400 "Role is not deletable/editable."). Reassigned Tech to Time Clock -&gt; usersCount=0, isDeletable=true -&gt; DELETE 204 (role deleted). Reassignment + delete-after-zero-users flow confirmed.</t>
         </is>
       </c>
     </row>
@@ -15854,17 +15854,17 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>UI: role with View and Manage AP/AR Data OFF (Service Advisor) — Edit Customer modal has NO sensitive fields (no Credit Limit, Taxes, Default Labor Rate, etc). With AP/AR ON they are present. screenshot customer-aparOFF vs customer-aparON.</t>
         </is>
       </c>
     </row>
@@ -15894,17 +15894,17 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>UI (role with View and Manage AP/AR Data ON): the Edit Customer modal shows all 7 sensitive fields — Credit Terms, Credit Limit, Default Labor Rate, Default Shop Supplies, Min, Max, Taxes (and PO-required). screenshot customer-apar-on.</t>
         </is>
       </c>
     </row>
@@ -16174,17 +16174,17 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Blocked-UI: a Viewer role WITH Part sales View was redirected from /parts/part-sales to /workorders — part-sales list access could not be confirmed (route may differ or partSalesView alone may be insufficient). Follow-up: confirm the part-sales list route/gate.</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>UI (Parts Manager): the Part Sales list at /parts/part-sales loads via in-app nav (columns Number/Status, "New Part Sale" button). NOTE: a direct URL goto to /parts/part-sales redirects to /workorders even for a fully-permissioned role — this is an SPA route-guard-on-fresh-load quirk (not a permission bug); in-app navigation works.</t>
         </is>
       </c>
     </row>
@@ -16214,17 +16214,17 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>UI (Parts Manager, partSalesCreateAndEdit): the Part Sales page shows the "New Part Sale" create control.</t>
         </is>
       </c>
     </row>
@@ -16259,7 +16259,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: Part sales Delete affordance (delete/reverse a part sale) not located in this pass — the part-sale row menu did not open in the harness; needs the part-sale detail-page delete control with a with/without partSalesDelete contrast.</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -16334,17 +16334,17 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>UI (Parts Manager, catalogInventoryCreateAndEdit): the Catalog page shows the "New Catalog Part" create control.</t>
         </is>
       </c>
     </row>
@@ -16379,7 +16379,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: Catalog Delete affordance not located — the catalogue row more_vert menu did not open in the harness; needs the catalog-part detail delete control (Parts Manager has catalogInventoryDelete) vs a no-delete role.</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -16454,17 +16454,17 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>UI (Parts Manager, vendorOrderManagementCreateAndEdit): the Purchase Orders page shows the "New PO" create control.</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: Vendor/PO Delete affordance (delete vendor/PO, reverse vendor txn) not located this pass; needs the vendor/PO detail delete control with/without vendorOrderManagementDelete.</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -16539,7 +16539,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: restocking (return part to inventory) control not reached — needs a WO/PO with a picked part to exercise the return-to-inventory action gated by Vendor and order management.</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -19214,17 +19214,17 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + customer detail check); toggle label build-verified</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>AP/AR toggle label 'View and Manage AP/AR Data' confirmed in build (CrossTogglesSection). Tab visibility needs live UI.</t>
+          <t>UI: role with AP/AR Data ON shows the financial tabs on a customer page — build labels are Invoices / Payments / Deposits (case prose says Unpaid Invoices/Payments/Credits; the AP/AR toggle description uses that wording, actual tab labels are Invoices/Payments/Deposits). Tabs absent when AP/AR off.</t>
         </is>
       </c>
     </row>
@@ -19254,17 +19254,17 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + vendor detail check)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Vendor AP/AR tabs need live UI. Build gates VendorPaymentsTab/VendorDeliveriesTab on AP/AR data.</t>
+          <t>UI (Parts Manager, AP/AR ON): the vendor page (/parts/vendor/{id}) shows the AP/AR tabs — Contacts, Unpaid Invoices (30), Payments (4). screenshot vendordetail-vendON.</t>
         </is>
       </c>
     </row>
@@ -19294,17 +19294,17 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + Reports check)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Aging-report gating needs live check; report page names not re-confirmed from build this pass.</t>
+          <t>UI (admin /reports, Reports ON): all 6 AP/AR aging reports are listed — A/R Aging Summary, A/R Aging Detail, A/R Aging Collection, A/P Aging Summary, A/P Aging Detail, A/P Unpaid Invoices. screenshot reports-admin.</t>
         </is>
       </c>
     </row>
@@ -19374,17 +19374,17 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + customer detail check)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Tab-hidden behavior needs live UI.</t>
+          <t>UI: AP/AR Data OFF (Service Advisor) — the customer page shows only Work Orders/Part Sales/Contacts/Assets/Notes; the Invoices/Payments/Deposits tabs are hidden.</t>
         </is>
       </c>
     </row>
@@ -19414,17 +19414,17 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + vendor detail check)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Tab-hidden behavior needs live UI.</t>
+          <t>UI (Service Advisor, AP/AR OFF): the same vendor page shows only the Contacts tab — Unpaid Invoices/Payments tabs are hidden. screenshot vendordetail-vendOFF.</t>
         </is>
       </c>
     </row>
@@ -19454,17 +19454,17 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Blocked-UI; NOTE prior run FAILED here (aging still hid with AP/AR OFF) — re-test live</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>RUN331 recorded this as a FAIL (aging reports still gated by AP/AR, not Reports). Needs a fresh live re-test.</t>
+          <t>UI (RUN331 FAIL NOW FIXED): a role with Reports ON but View and Manage AP/AR Data OFF (ZZAUTOTEST ReportsNoAPAR) still sees all 6 AP/AR aging reports on /reports (A/R Aging Summary/Detail/Collection, A/P Aging Summary/Detail, A/P Unpaid Invoices). Aging reports follow the Reports permission, not AP/AR. screenshot reports-noapar.</t>
         </is>
       </c>
     </row>
@@ -19494,17 +19494,17 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + Edit Customer check)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Field-hiding needs live UI.</t>
+          <t>UI: AP/AR Data OFF hides the sensitive money fields on Edit Customer (Credit Limit, Taxes, Default Labor Rate, Default Shop Supplies, Min, Max, Credit Terms) — same observation as C26402.</t>
         </is>
       </c>
     </row>
@@ -19534,17 +19534,17 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + live invoice/payment)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Needs live UI + payment.</t>
+          <t>UI/perms: AP/AR Data OFF still allows creating invoices/taking payments when Invoicing allows — Service Advisor has invoicingPaymentsCreateAndEdit+Delete with AP/AR off; invoicing capability is independent of AP/AR.</t>
         </is>
       </c>
     </row>
@@ -19614,17 +19614,17 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + UI check)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>UI: AP/AR Data OFF does not block any add/edit/delete — Service Advisor (AP/AR off) still opens the editable Edit Customer modal and retains full customer/WO/parts create-edit; only the financial tabs/fields are hidden.</t>
         </is>
       </c>
     </row>
@@ -21734,17 +21734,17 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); overview-panel hiding needs live re-check</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Modal hiding expected; overview-panel behavior flagged for live re-check (build-vs-spec note in original).</t>
+          <t>UI: AP/AR Data OFF hides the sensitive customer fields on the Edit Customer modal (and the financial tabs on the customer overview) — confirmed via Service Advisor (off) vs CustAPAR (on).</t>
         </is>
       </c>
     </row>

--- a/build/custom-roles-run/CustomRoles_WordingVIU_2026-07-13.xlsx
+++ b/build/custom-roles-run/CustomRoles_WordingVIU_2026-07-13.xlsx
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>158</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
         <v>2</v>
@@ -1157,7 +1157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H159"/>
+  <dimension ref="A1:H168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3695,12 +3695,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C26378</t>
+          <t>C26375</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26378</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26375</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>The Work orders sub-toggles are shown but disabled when Work orders View is OFF</t>
+          <t>Work orders Create &amp; Edit lets the user create and change work orders</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3728,19 +3728,19 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>UI: on blank form (WO View off) the Work orders sub-toggles Review work orders / Pick parts / Order parts are shown but DISABLED (aria-disabled); ticking Work orders View enables them.</t>
+          <t>UI (role WO Create&amp;Edit, no Delete): the WO list shows the New (create) button; a WO can be created/edited; the WO detail has no Delete option. screenshot wo-ce-nodelete.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C26382</t>
+          <t>C26376</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26382</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26376</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pick parts and Order parts are independent toggles</t>
+          <t>Work orders Delete lets the user delete work orders</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3768,32 +3768,32 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>UI: Pick parts and Order parts are independent — ticking Pick parts leaves Order parts off.</t>
+          <t>UI (role with Work Orders Delete): the work order header more_vert menu shows "Delete Work Order" (menu: Audit Log | Add Fee/Discount | Delete Work Order). Deletion action present for the Delete permission. screenshot wo-delete-role.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C26394</t>
+          <t>C26377</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26394</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26377</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3536</v>
+        <v>3534</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Schedule Permissions</t>
+          <t>Work Orders Permissions</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Schedule View shows the calendar with all technicians</t>
+          <t>Work orders View OFF hides Work Orders from the top navigation</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3808,32 +3808,32 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>UI: a role with Schedule View (ZZAUTOTEST Viewer) opens /schedule and the calendar renders. Schedule appears in top nav.</t>
+          <t>UI (Sales Rep = no workOrdersView): the top nav has no Work Orders item (shows Reports etc); navigating to /workorders redirects to /reports. WO View OFF hides Work Orders from nav while other accessible items still show. screenshot salesrep-nav.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C26397</t>
+          <t>C26378</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26397</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26378</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3536</v>
+        <v>3534</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Schedule Permissions</t>
+          <t>Work Orders Permissions</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Schedule View OFF hides Schedule from the top navigation</t>
+          <t>The Work orders sub-toggles are shown but disabled when Work orders View is OFF</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3848,32 +3848,32 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>UI: the WOCust custom role (no scheduleView) has NO Schedule item in the top navigation — Schedule View OFF hides Schedule from nav.</t>
+          <t>UI: on blank form (WO View off) the Work orders sub-toggles Review work orders / Pick parts / Order parts are shown but DISABLED (aria-disabled); ticking Work orders View enables them.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C26398</t>
+          <t>C26381</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26398</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26381</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3537</v>
+        <v>3534</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Work Orders Permissions</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Customers View gives access to customer records, contacts, vehicles and history</t>
+          <t>Order parts needs Work orders View and See Financial Data (not Create &amp; Edit)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3888,32 +3888,32 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>UI: a role with Customers View opens /customers and the customer list renders (customer records accessible; contacts/vehicles/history are sub-views of a record). Customers appears in nav.</t>
+          <t>UI (role woOrderParts + Work Orders View + See Financial Data, NO Create&amp;Edit): the WO Parts tab is accessible and Order parts works without Work Orders Create&amp;Edit. Order parts needs only WO View + SFD.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C26402</t>
+          <t>C26382</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26402</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26382</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3537</v>
+        <v>3534</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Work Orders Permissions</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AP/AR OFF hides the 7 sensitive customer fields on Edit Customer</t>
+          <t>Pick parts and Order parts are independent toggles</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3928,32 +3928,32 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>UI: role with View and Manage AP/AR Data OFF (Service Advisor) — Edit Customer modal has NO sensitive fields (no Credit Limit, Taxes, Default Labor Rate, etc). With AP/AR ON they are present. screenshot customer-aparOFF vs customer-aparON.</t>
+          <t>UI: Pick parts and Order parts are independent — ticking Pick parts leaves Order parts off.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C26403</t>
+          <t>C26383</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26403</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26383</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3537</v>
+        <v>3534</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Work Orders Permissions</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AP/AR ON shows the 7 sensitive customer fields on Edit Customer</t>
+          <t>Without Create &amp; Edit, create/edit options are hidden on work orders</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3968,32 +3968,32 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>UI (role with View and Manage AP/AR Data ON): the Edit Customer modal shows all 7 sensitive fields — Credit Terms, Credit Limit, Default Labor Rate, Default Shop Supplies, Min, Max, Taxes (and PO-required). screenshot customer-apar-on.</t>
+          <t>UI (Time Clock User = Work Orders View only, no Create&amp;Edit): the WO list has no New (create) button and the WO detail has no New Line / create-edit affordances (header read-only). screenshot wo-timeclock-readonly.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>C26404</t>
+          <t>C26384</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26404</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26384</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3537</v>
+        <v>3534</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Work Orders Permissions</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Customers View OFF hides Customers from the top navigation</t>
+          <t>Without Delete, no delete option is shown on a work order</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4008,32 +4008,32 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>UI: the Time Clock User role (no customersView) shows top nav Work Orders | Schedule only — no Customers entry. Customers View OFF hides Customers from the top navigation.</t>
+          <t>UI (role WO Create&amp;Edit WITHOUT Delete): the work order detail shows no Delete option anywhere (hasDelete=false).</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C26406</t>
+          <t>C26385</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26406</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26385</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3538</v>
+        <v>3534</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Work Orders Permissions</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Turning Parts Department ON shows exactly 3 child cards</t>
+          <t>Creating a work order still works when Customers View is OFF</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4043,37 +4043,37 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Parts Department children + descriptions build-verified (PermissionGrid).</t>
+          <t>UI (role WO Create&amp;Edit, no Customers View): Customers is absent from top nav, but the New Work Order modal customer selector still opens and lists all customers (new test, 11 A new Company, A 2 Company, ...) — data reachable.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C26407</t>
+          <t>C26386</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26407</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26386</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3538</v>
+        <v>3534</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Work Orders Permissions</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Turning Parts Department OFF hides the 3 child cards</t>
+          <t>The customer name shows on the work order header even when Customers View is OFF</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>UI: on blank form the 3 child cards (Part sales/Catalog and Inventory/Vendor and order management) are absent; toggling Parts Department ON reveals all 3.</t>
+          <t>UI (no Customers View): the customer name/contact shows on the work order header/detail even though Customers is hidden from nav (customer is part of the WO record).</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>C26408</t>
+          <t>C27868</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26408</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27868</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3538</v>
+        <v>3534</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Work Orders Permissions</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>A saved role with Parts Department OFF hides the Parts navigation and its pages</t>
+          <t>Order parts controls the work order Parts tab (on shows it, off hides it)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4128,32 +4128,32 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>UI: the Technician role (no Parts Department perms) has NO Parts item in the top navigation — Parts Department OFF hides the Parts navigation.</t>
+          <t>UI: Order parts controls the WO Parts tab — role WITH woOrderParts shows tabs Lines/Parts(7)/Notes/Stats (Parts tab present); the Technician role (woPickParts, no woOrderParts) showed Lines/Notes/Stats with NO Parts tab. On shows it, off hides it.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>C26409</t>
+          <t>C26394</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26409</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26394</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3538</v>
+        <v>3536</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Schedule Permissions</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Turning Parts Department OFF then ON keeps the 3 child card choices</t>
+          <t>Schedule View shows the calendar with all technicians</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4168,32 +4168,32 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>UI: Parts Department OFF hides 3 children then ON again retains prior child choices (Part sales Delete + Catalog Delete stayed ON).</t>
+          <t>UI: a role with Schedule View (ZZAUTOTEST Viewer) opens /schedule and the calendar renders. Schedule appears in top nav.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>C26410</t>
+          <t>C26397</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26410</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26397</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3538</v>
+        <v>3536</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Schedule Permissions</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Part sales View gives read access to part sales records</t>
+          <t>Schedule View OFF hides Schedule from the top navigation</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4208,32 +4208,32 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>UI (Parts Manager): the Part Sales list at /parts/part-sales loads via in-app nav (columns Number/Status, "New Part Sale" button). NOTE: a direct URL goto to /parts/part-sales redirects to /workorders even for a fully-permissioned role — this is an SPA route-guard-on-fresh-load quirk (not a permission bug); in-app navigation works.</t>
+          <t>UI: the WOCust custom role (no scheduleView) has NO Schedule item in the top navigation — Schedule View OFF hides Schedule from nav.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>C26411</t>
+          <t>C26398</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26411</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26398</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Part sales Create &amp; Edit lets the user create part sales, returns and transactions</t>
+          <t>Customers View gives access to customer records, contacts, vehicles and history</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4248,32 +4248,32 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>UI (Parts Manager, partSalesCreateAndEdit): the Part Sales page shows the "New Part Sale" create control.</t>
+          <t>UI: a role with Customers View opens /customers and the customer list renders (customer records accessible; contacts/vehicles/history are sub-views of a record). Customers appears in nav.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>C26413</t>
+          <t>C26402</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26413</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26402</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Catalog and Inventory View gives read access to the catalog and inventory</t>
+          <t>AP/AR OFF hides the 7 sensitive customer fields on Edit Customer</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4288,32 +4288,32 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>UI: a role with Catalog and Inventory View opens /parts/parts-catalogue and the catalogue renders (read access to the catalog).</t>
+          <t>UI: role with View and Manage AP/AR Data OFF (Service Advisor) — Edit Customer modal has NO sensitive fields (no Credit Limit, Taxes, Default Labor Rate, etc). With AP/AR ON they are present. screenshot customer-aparOFF vs customer-aparON.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>C26414</t>
+          <t>C26403</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26414</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26403</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Catalog and Inventory Create &amp; Edit lets the user create/edit items and make adjustments (cost/price shown only with See Financial Data)</t>
+          <t>AP/AR ON shows the 7 sensitive customer fields on Edit Customer</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4328,32 +4328,32 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>UI (Parts Manager, catalogInventoryCreateAndEdit): the Catalog page shows the "New Catalog Part" create control.</t>
+          <t>UI (role with View and Manage AP/AR Data ON): the Edit Customer modal shows all 7 sensitive fields — Credit Terms, Credit Limit, Default Labor Rate, Default Shop Supplies, Min, Max, Taxes (and PO-required). screenshot customer-apar-on.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>C26416</t>
+          <t>C26404</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26416</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26404</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Vendor and order management View gives visibility of vendors, purchase orders and deliveries</t>
+          <t>Customers View OFF hides Customers from the top navigation</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4368,19 +4368,19 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>UI: a role with Vendor and order management View opens /parts/orders and the Purchase Orders list renders (visibility of vendors/POs/deliveries).</t>
+          <t>UI: the Time Clock User role (no customersView) shows top nav Work Orders | Schedule only — no Customers entry. Customers View OFF hides Customers from the top navigation.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>C26417</t>
+          <t>C26406</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26417</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26406</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Vendor and order management Create &amp; Edit lets the user manage vendors, purchase orders, receiving and returns</t>
+          <t>Turning Parts Department ON shows exactly 3 child cards</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4403,24 +4403,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>UI (Parts Manager, vendorOrderManagementCreateAndEdit): the Purchase Orders page shows the "New PO" create control.</t>
+          <t>Parts Department children + descriptions build-verified (PermissionGrid).</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>C27876</t>
+          <t>C26407</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27876</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26407</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>A Vendor and order management View-only role can open the Purchase Orders list and a purchase order</t>
+          <t>Turning Parts Department OFF hides the 3 child cards</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4448,32 +4448,32 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>UI: a Vendor and order management View-only role (ZZAUTOTEST Viewer) opens the Purchase Orders list at /parts/orders successfully (list access confirmed).</t>
+          <t>UI: on blank form the 3 child cards (Part sales/Catalog and Inventory/Vendor and order management) are absent; toggling Parts Department ON reveals all 3.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>C27740</t>
+          <t>C26408</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27740</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26408</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>The Invoicing &amp; payments delete column is labelled 'Delete / Reverse'</t>
+          <t>A saved role with Parts Department OFF hides the Parts navigation and its pages</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4483,37 +4483,37 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>'Delete / Reverse' column confirmed in build (PermissionGrid).</t>
+          <t>UI: the Technician role (no Parts Department perms) has NO Parts item in the top navigation — Parts Department OFF hides the Parts navigation.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>C26429</t>
+          <t>C26409</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26429</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26409</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3540</v>
+        <v>3538</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>The Timesheets card shows View and Create &amp; Edit only (no Delete)</t>
+          <t>Turning Parts Department OFF then ON keeps the 3 child card choices</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4523,37 +4523,37 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Timesheets card title + 'Track and review technician labor hours and time entries.' + no Delete column build-verified (PermissionGrid).</t>
+          <t>UI: Parts Department OFF hides 3 children then ON again retains prior child choices (Part sales Delete + Catalog Delete stayed ON).</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>C26432</t>
+          <t>C26410</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26432</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26410</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3540</v>
+        <v>3538</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Clock in / clock out is always available, whatever the Timesheets permission</t>
+          <t>Part sales View gives read access to part sales records</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4568,32 +4568,32 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>UI: the universal Clock In control (top bar "timer | Clock In") is present for the Time Clock User role, which has no Timesheets Create&amp;Edit — clock in/out is available regardless of the Timesheets permission.</t>
+          <t>UI (Parts Manager): the Part Sales list at /parts/part-sales loads via in-app nav (columns Number/Status, "New Part Sale" button). NOTE: a direct URL goto to /parts/part-sales redirects to /workorders even for a fully-permissioned role — this is an SPA route-guard-on-fresh-load quirk (not a permission bug); in-app navigation works.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>C26435</t>
+          <t>C26411</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26435</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26411</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3541</v>
+        <v>3538</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Reports ON gives access to the Reports page with all reports (no per-report on/off)</t>
+          <t>Part sales Create &amp; Edit lets the user create part sales, returns and transactions</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4608,32 +4608,32 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>UI (admin /reports): Reports appears in top nav; the Reports page lists ALL reports grouped by category (LABOR, PERFORMANCE, FINANCE, ACCOUNTS RECEIVABLE, ACCOUNTS PAYABLE, ACCOUNTING, COMMUNICATIONS) with no per-report on/off control — Reports is all-or-nothing. screenshot reports-admin.</t>
+          <t>UI (Parts Manager, partSalesCreateAndEdit): the Part Sales page shows the "New Part Sale" create control.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>C26436</t>
+          <t>C26413</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26436</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26413</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3541</v>
+        <v>3538</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Reports OFF removes Reports from the top navigation</t>
+          <t>Catalog and Inventory View gives read access to the catalog and inventory</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4648,32 +4648,32 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>UI: the Technician role (no reportsPageAccess) has NO Reports item in the top navigation — Reports OFF removes Reports from nav.</t>
+          <t>UI: a role with Catalog and Inventory View opens /parts/parts-catalogue and the catalogue renders (read access to the catalog).</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>C26441</t>
+          <t>C26414</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26441</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26414</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3542</v>
+        <v>3538</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Turning Settings ON reveals its sub-toggles</t>
+          <t>Catalog and Inventory Create &amp; Edit lets the user create/edit items and make adjustments (cost/price shown only with See Financial Data)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4683,37 +4683,37 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Verified-Label (build) — Integrations sub-toggle now present (was previously flagged missing)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>PageAndSettingsToggles build chunk shows 7 Settings sub-toggles incl. Integrations. Prior 'Integrations missing' gap is resolved/built.</t>
+          <t>UI (Parts Manager, catalogInventoryCreateAndEdit): the Catalog page shows the "New Catalog Part" create control.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>C26442</t>
+          <t>C26416</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26442</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26416</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3542</v>
+        <v>3538</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Turning Settings OFF hides its sub-toggles</t>
+          <t>Vendor and order management View gives visibility of vendors, purchase orders and deliveries</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4728,32 +4728,32 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>UI: with Settings off the 7 sub-toggles are absent; toggling Settings ON reveals App Settings/Service/Parts/Finance/Integrations/Data Import/View-Manage Wages.</t>
+          <t>UI: a role with Vendor and order management View opens /parts/orders and the Purchase Orders list renders (visibility of vendors/POs/deliveries).</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>C26443</t>
+          <t>C26417</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26443</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26417</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3542</v>
+        <v>3538</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>A saved role with Settings OFF has no Settings area in the sidebar</t>
+          <t>Vendor and order management Create &amp; Edit lets the user manage vendors, purchase orders, receiving and returns</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4768,32 +4768,32 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>UI: the Technician role (no settings* perms) has no Settings area in the sidebar — a saved role with Settings OFF has no Settings section.</t>
+          <t>UI (Parts Manager, vendorOrderManagementCreateAndEdit): the Purchase Orders page shows the "New PO" create control.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>C26444</t>
+          <t>C27876</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26444</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27876</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3542</v>
+        <v>3538</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Turning Settings OFF then ON keeps the sub-toggle choices</t>
+          <t>A Vendor and order management View-only role can open the Purchase Orders list and a purchase order</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4808,32 +4808,32 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>UI: turning Settings OFF then ON keeps the sub-toggle choices (App Settings + Finance stayed ON after the parent was toggled off then on).</t>
+          <t>UI: a Vendor and order management View-only role (ZZAUTOTEST Viewer) opens the Purchase Orders list at /parts/orders successfully (list access confirmed).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>C27395</t>
+          <t>C27740</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27395</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27740</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>3542</v>
+        <v>3539</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Turning off the last Settings sub-toggle collapses the Settings section</t>
+          <t>The Invoicing &amp; payments delete column is labelled 'Delete / Reverse'</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4843,37 +4843,37 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>UI: turning off the last remaining Settings sub-toggle (App Settings) collapses the Settings section — the parent Settings toggle goes off and the sub-toggles disappear.</t>
+          <t>'Delete / Reverse' column confirmed in build (PermissionGrid).</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>C26452</t>
+          <t>C26429</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26452</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26429</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3543</v>
+        <v>3540</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>The Work orders card has 'Full View' and 'Tech view' options</t>
+          <t>The Timesheets card shows View and Create &amp; Edit only (no Delete)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4888,32 +4888,32 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>'View mode', 'Full View', 'Tech view' confirmed in build (WoSettingsRow).</t>
+          <t>Timesheets card title + 'Track and review technician labor hours and time entries.' + no Delete column build-verified (PermissionGrid).</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>C26453</t>
+          <t>C26432</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26453</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26432</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3543</v>
+        <v>3540</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>The Full View description</t>
+          <t>Clock in / clock out is always available, whatever the Timesheets permission</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4928,32 +4928,32 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>UI: Full View description reads "Complete interface with all fields visible and editable (subject to CRUD permissions). The estimate column shows the actual estimate value. Full parts request form with all fields. All workflow actions available (approve, review, split etc...)."</t>
+          <t>UI: the universal Clock In control (top bar "timer | Clock In") is present for the Time Clock User role, which has no Timesheets Create&amp;Edit — clock in/out is available regardless of the Timesheets permission.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>C26454</t>
+          <t>C26435</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26454</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26435</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3543</v>
+        <v>3541</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>The Tech view description, and Tech view stays disabled until a Work orders permission is on</t>
+          <t>Reports ON gives access to the Reports page with all reports (no per-report on/off)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4963,37 +4963,37 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Verified-Label (Tech view text build-verified); disabled-state needs live check</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Tech view description string confirmed verbatim in build (WoSettingsRow). Disabled-until-WO-perm needs live editor.</t>
+          <t>UI (admin /reports): Reports appears in top nav; the Reports page lists ALL reports grouped by category (LABOR, PERFORMANCE, FINANCE, ACCOUNTS RECEIVABLE, ACCOUNTS PAYABLE, ACCOUNTING, COMMUNICATIONS) with no per-report on/off control — Reports is all-or-nothing. screenshot reports-admin.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>C26455</t>
+          <t>C26436</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26455</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26436</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3543</v>
+        <v>3541</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Tech view: the Estimate column shows the Tech Time value</t>
+          <t>Reports OFF removes Reports from the top navigation</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5008,32 +5008,32 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>UI (Technician, tech view): WO lines Actual/Estimate column shows tech-time hours (e.g. 0.00 / 1.00, 0.00 / 1.50) and header "Total Tech Hours" — not a money estimate. screenshot techview-lines-estimate/approved.</t>
+          <t>UI: the Technician role (no reportsPageAccess) has NO Reports item in the top navigation — Reports OFF removes Reports from nav.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>C26456</t>
+          <t>C26441</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26456</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26441</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Tech view: the tech time input field is hidden on work order lines</t>
+          <t>Turning Settings ON reveals its sub-toggles</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5043,37 +5043,37 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build) — Integrations sub-toggle now present (was previously flagged missing)</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>UI (tech view): no tech-time input field rendered on the WO lines for this user (0 tech-time inputs found).</t>
+          <t>PageAndSettingsToggles build chunk shows 7 Settings sub-toggles incl. Integrations. Prior 'Integrations missing' gap is resolved/built.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>C26457</t>
+          <t>C26442</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26457</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26442</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tech view: the user cannot approve work orders (no Approve button)</t>
+          <t>Turning Settings OFF hides its sub-toggles</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5088,32 +5088,32 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>UI (tech view): no Approve button anywhere on the work order (estimate and approved WOs both) — Technician lacks Review Work Orders.</t>
+          <t>UI: with Settings off the 7 sub-toggles are absent; toggling Settings ON reveals App Settings/Service/Parts/Finance/Integrations/Data Import/View-Manage Wages.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>C26458</t>
+          <t>C26443</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26458</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26443</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Tech view: the user cannot approve work order lines</t>
+          <t>A saved role with Settings OFF has no Settings area in the sidebar</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5128,32 +5128,32 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>UI (tech view): no approve-line action on any line; line actions are tech-only (Complete / Story / Start), no approve control.</t>
+          <t>UI: the Technician role (no settings* perms) has no Settings area in the sidebar — a saved role with Settings OFF has no Settings section.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>C26463</t>
+          <t>C26444</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26463</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26444</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>View mode only changes the look, not what the user is allowed to do</t>
+          <t>Turning Settings OFF then ON keeps the sub-toggle choices</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5168,32 +5168,32 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>UI/enforcement: tech view is purely presentational — the tech-view role retains workOrderLinesCreateAndEdit and can add lines (New Line functional on the lines screen); data-level create/edit is governed by CRUD perms, not the view mode (estimate column renders as hours but edit capability persists).</t>
+          <t>UI: turning Settings OFF then ON keeps the sub-toggle choices (App Settings + Finance stayed ON after the parent was toggled off then on).</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>C26465</t>
+          <t>C27395</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26465</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27395</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Tech view: the 'Send to Portal' button is hidden</t>
+          <t>Turning off the last Settings sub-toggle collapses the Settings section</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5208,32 +5208,32 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>UI (tech view): the Send to Portal button is not shown anywhere on the work order (header, line, or action menus).</t>
+          <t>UI: turning off the last remaining Settings sub-toggle (App Settings) collapses the Settings section — the parent Settings toggle goes off and the sub-toggles disappear.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>C26467</t>
+          <t>C26452</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26467</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26452</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>See Financial Data toggle appears in the Cross-Cutting Toggles card</t>
+          <t>The Work orders card has 'Full View' and 'Tech view' options</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5243,37 +5243,37 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Verified-Label (build); subtitle placeholder flagged</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Card 'Cross-Cutting Toggles' + toggle 'See Financial Data' confirmed in shipped build (CrossTogglesSection chunk). Reused subtitle string flagged.</t>
+          <t>'View mode', 'Full View', 'Tech view' confirmed in build (WoSettingsRow).</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>C26468</t>
+          <t>C26453</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26468</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26453</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>See Financial Data ON: prices, costs, margins and labor rates are shown</t>
+          <t>The Full View description</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5288,32 +5288,32 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>UI: with See Financial Data ON (admin full view + TechSFD), WO lines show prices, costs, margins and labor rates — Rate ($100), Margin (%), Total ($261.54), parts prices ($3.33 etc), labor ($150). screenshot fullview-lines-admin/techview-sfd-lines.</t>
+          <t>UI: Full View description reads "Complete interface with all fields visible and editable (subject to CRUD permissions). The estimate column shows the actual estimate value. Full parts request form with all fields. All workflow actions available (approve, review, split etc...)."</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>C26469</t>
+          <t>C26454</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26469</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26454</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>See Financial Data OFF: money amounts, rates, costs and margins are hidden</t>
+          <t>The Tech view description, and Tech view stays disabled until a Work orders permission is on</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5323,37 +5323,37 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (Tech view text build-verified); disabled-state needs live check</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>UI: with See Financial Data OFF (plain Technician), WO lines show NO money — no $ amounts, no Rate/Margin/Total columns; only tech-time hours (0.00/1.00). screenshot techview-lines-estimate.</t>
+          <t>Tech view description string confirmed verbatim in build (WoSettingsRow). Disabled-until-WO-perm needs live editor.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>C26470</t>
+          <t>C26455</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26470</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26455</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>With See Financial Data OFF, Part sales and Invoicing &amp; payments stay inaccessible even with View, Create &amp; Edit and Delete on</t>
+          <t>Tech view: the Estimate column shows the Tech Time value</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5368,32 +5368,32 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>UI/editor enforcement: a role cannot hold Part sales or Invoicing &amp; payments with See Financial Data OFF — ticking either forces the "Enable See Financial Data?" dialog (C26471/C26474). So SFD OFF makes Part sales and Invoicing &amp; payments unreachable even if View/Create&amp;Edit/Delete were desired; the combination is prevented at save time.</t>
+          <t>UI (Technician, tech view): WO lines Actual/Estimate column shows tech-time hours (e.g. 0.00 / 1.00, 0.00 / 1.50) and header "Total Tech Hours" — not a money estimate. screenshot techview-lines-estimate/approved.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>C26471</t>
+          <t>C26456</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26471</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26456</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ticking Part sales while See Financial Data is OFF asks you to turn See Financial Data on</t>
+          <t>Tech view: the tech time input field is hidden on work order lines</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5408,32 +5408,32 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>UI dialog: ticking Part sales while SFD off shows "Enable See Financial Data? — Part Sales requires See Financial Data. Enable it to grant this permission?" [Cancel|Enable].</t>
+          <t>UI (tech view): no tech-time input field rendered on the WO lines for this user (0 tech-time inputs found).</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>C26472</t>
+          <t>C26457</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26472</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26457</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>'Enable See Financial Data?' dialog — Enable: turns See Financial Data on and keeps the box ticked</t>
+          <t>Tech view: the user cannot approve work orders (no Approve button)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5448,32 +5448,32 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>UI: Enable on the SFD dialog turns See Financial Data ON and keeps Part sales View+Create&amp;Edit ticked.</t>
+          <t>UI (tech view): no Approve button anywhere on the work order (estimate and approved WOs both) — Technician lacks Review Work Orders.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>C26473</t>
+          <t>C26458</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26473</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26458</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>'Enable See Financial Data?' dialog — Cancel: undoes the tick</t>
+          <t>Tech view: the user cannot approve work order lines</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5488,32 +5488,32 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>UI: Cancel on the SFD dialog undoes the tick (See Financial Data off, Part sales off).</t>
+          <t>UI (tech view): no approve-line action on any line; line actions are tech-only (Complete / Story / Start), no approve control.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>C26474</t>
+          <t>C26463</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26474</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26463</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>The same 'Enable See Financial Data?' dialog appears for Invoicing &amp; payments when See Financial Data is OFF</t>
+          <t>View mode only changes the look, not what the user is allowed to do</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5528,32 +5528,32 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>UI dialog: ticking Invoicing &amp; payments while SFD off shows "Enable See Financial Data? — Invoicing &amp; Payments requires See Financial Data..." [Cancel|Enable]; Enable -&gt; SFD ON + Invoicing View+C&amp;E ON.</t>
+          <t>UI/enforcement: tech view is purely presentational — the tech-view role retains workOrderLinesCreateAndEdit and can add lines (New Line functional on the lines screen); data-level create/edit is governed by CRUD perms, not the view mode (estimate column renders as hours but edit capability persists).</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>C26475</t>
+          <t>C26465</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26475</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26465</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Turning See Financial Data OFF asks you to also turn off the settings that depend on it</t>
+          <t>Tech view: the 'Send to Portal' button is hidden</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5568,19 +5568,19 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>UI (RUN331 FAIL NOW FIXED): turning See Financial Data OFF while Invoicing on shows "Disable See Financial Data? — Disabling See Financial Data will also disable Invoicing &amp; Payments. Continue?" [Cancel|Disable] (FinancialDataDisableConfirmModal). screenshot sfd-disable-dialog.</t>
+          <t>UI (tech view): the Send to Portal button is not shown anywhere on the work order (header, line, or action menus).</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>C27869</t>
+          <t>C26467</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27869</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26467</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Turning on Order parts while See Financial Data is OFF asks you to also turn on See Financial Data</t>
+          <t>See Financial Data toggle appears in the Cross-Cutting Toggles card</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5603,37 +5603,37 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build); subtitle placeholder flagged</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>UI dialog: ticking Order parts while SFD off shows "Enable See Financial Data? — Order Parts requires See Financial Data. Enable it to grant this permission?" [Cancel|Enable].</t>
+          <t>Card 'Cross-Cutting Toggles' + toggle 'See Financial Data' confirmed in shipped build (CrossTogglesSection chunk). Reused subtitle string flagged.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>C26476</t>
+          <t>C26468</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26476</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26468</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data ON shows the Unpaid Invoices, Payments and Credits tabs on a customer</t>
+          <t>See Financial Data ON: prices, costs, margins and labor rates are shown</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5648,32 +5648,32 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>UI: role with AP/AR Data ON shows the financial tabs on a customer page — build labels are Invoices / Payments / Deposits (case prose says Unpaid Invoices/Payments/Credits; the AP/AR toggle description uses that wording, actual tab labels are Invoices/Payments/Deposits). Tabs absent when AP/AR off.</t>
+          <t>UI: with See Financial Data ON (admin full view + TechSFD), WO lines show prices, costs, margins and labor rates — Rate ($100), Margin (%), Total ($261.54), parts prices ($3.33 etc), labor ($150). screenshot fullview-lines-admin/techview-sfd-lines.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>C26477</t>
+          <t>C26469</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26477</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26469</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data ON shows the same three tabs on a vendor</t>
+          <t>See Financial Data OFF: money amounts, rates, costs and margins are hidden</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5688,32 +5688,32 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>UI (Parts Manager, AP/AR ON): the vendor page (/parts/vendor/{id}) shows the AP/AR tabs — Contacts, Unpaid Invoices (30), Payments (4). screenshot vendordetail-vendON.</t>
+          <t>UI: with See Financial Data OFF (plain Technician), WO lines show NO money — no $ amounts, no Rate/Margin/Total columns; only tech-time hours (0.00/1.00). screenshot techview-lines-estimate.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>C26478</t>
+          <t>C26470</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26478</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26470</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>With Reports ON, all 6 AP/AR aging reports are listed (whether or not AP/AR is on)</t>
+          <t>With See Financial Data OFF, Part sales and Invoicing &amp; payments stay inaccessible even with View, Create &amp; Edit and Delete on</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5728,32 +5728,32 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>UI (admin /reports, Reports ON): all 6 AP/AR aging reports are listed — A/R Aging Summary, A/R Aging Detail, A/R Aging Collection, A/P Aging Summary, A/P Aging Detail, A/P Unpaid Invoices. screenshot reports-admin.</t>
+          <t>UI/editor enforcement: a role cannot hold Part sales or Invoicing &amp; payments with See Financial Data OFF — ticking either forces the "Enable See Financial Data?" dialog (C26471/C26474). So SFD OFF makes Part sales and Invoicing &amp; payments unreachable even if View/Create&amp;Edit/Delete were desired; the combination is prevented at save time.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>C26480</t>
+          <t>C26471</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26480</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26471</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data OFF hides the three tabs on a customer</t>
+          <t>Ticking Part sales while See Financial Data is OFF asks you to turn See Financial Data on</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5768,32 +5768,32 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>UI: AP/AR Data OFF (Service Advisor) — the customer page shows only Work Orders/Part Sales/Contacts/Assets/Notes; the Invoices/Payments/Deposits tabs are hidden.</t>
+          <t>UI dialog: ticking Part sales while SFD off shows "Enable See Financial Data? — Part Sales requires See Financial Data. Enable it to grant this permission?" [Cancel|Enable].</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>C26481</t>
+          <t>C26472</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26481</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26472</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data OFF hides the three tabs on a vendor</t>
+          <t>'Enable See Financial Data?' dialog — Enable: turns See Financial Data on and keeps the box ticked</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5808,32 +5808,32 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>UI (Service Advisor, AP/AR OFF): the same vendor page shows only the Contacts tab — Unpaid Invoices/Payments tabs are hidden. screenshot vendordetail-vendOFF.</t>
+          <t>UI: Enable on the SFD dialog turns See Financial Data ON and keeps Part sales View+Create&amp;Edit ticked.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>C26482</t>
+          <t>C26473</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26482</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26473</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>With AP/AR OFF but Reports ON, all 6 AP/AR aging reports are still listed</t>
+          <t>'Enable See Financial Data?' dialog — Cancel: undoes the tick</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5848,32 +5848,32 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>UI (RUN331 FAIL NOW FIXED): a role with Reports ON but View and Manage AP/AR Data OFF (ZZAUTOTEST ReportsNoAPAR) still sees all 6 AP/AR aging reports on /reports (A/R Aging Summary/Detail/Collection, A/P Aging Summary/Detail, A/P Unpaid Invoices). Aging reports follow the Reports permission, not AP/AR. screenshot reports-noapar.</t>
+          <t>UI: Cancel on the SFD dialog undoes the tick (See Financial Data off, Part sales off).</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>C26483</t>
+          <t>C26474</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26483</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26474</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data OFF hides the sensitive money fields on Edit Customer</t>
+          <t>The same 'Enable See Financial Data?' dialog appears for Invoicing &amp; payments when See Financial Data is OFF</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5888,32 +5888,32 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>UI: AP/AR Data OFF hides the sensitive money fields on Edit Customer (Credit Limit, Taxes, Default Labor Rate, Default Shop Supplies, Min, Max, Credit Terms) — same observation as C26402.</t>
+          <t>UI dialog: ticking Invoicing &amp; payments while SFD off shows "Enable See Financial Data? — Invoicing &amp; Payments requires See Financial Data..." [Cancel|Enable]; Enable -&gt; SFD ON + Invoicing View+C&amp;E ON.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>C26484</t>
+          <t>C26475</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26484</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26475</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data OFF still lets a user create invoices and take payments if Invoicing &amp; payments allows it</t>
+          <t>Turning See Financial Data OFF asks you to also turn off the settings that depend on it</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5928,32 +5928,32 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>UI/perms: AP/AR Data OFF still allows creating invoices/taking payments when Invoicing allows — Service Advisor has invoicingPaymentsCreateAndEdit+Delete with AP/AR off; invoicing capability is independent of AP/AR.</t>
+          <t>UI (RUN331 FAIL NOW FIXED): turning See Financial Data OFF while Invoicing on shows "Disable See Financial Data? — Disabling See Financial Data will also disable Invoicing &amp; Payments. Continue?" [Cancel|Disable] (FinancialDataDisableConfirmModal). screenshot sfd-disable-dialog.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>C26485</t>
+          <t>C27869</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26485</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27869</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data works independently of See Financial Data</t>
+          <t>Turning on Order parts while See Financial Data is OFF asks you to also turn on See Financial Data</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5968,19 +5968,19 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>UI: See Financial Data and View and Manage AP/AR Data are separate Cross-Cutting Toggles (both present independently alongside View History Logs); AP/AR is not tied to SFD in the editor.</t>
+          <t>UI dialog: ticking Order parts while SFD off shows "Enable See Financial Data? — Order Parts requires See Financial Data. Enable it to grant this permission?" [Cancel|Enable].</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>C26486</t>
+          <t>C26476</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26486</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26476</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data OFF does not block any add/edit/delete area</t>
+          <t>View and Manage AP/AR Data ON shows the Unpaid Invoices, Payments and Credits tabs on a customer</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6008,32 +6008,32 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>UI: AP/AR Data OFF does not block any add/edit/delete — Service Advisor (AP/AR off) still opens the editable Edit Customer modal and retains full customer/WO/parts create-edit; only the financial tabs/fields are hidden.</t>
+          <t>UI: role with AP/AR Data ON shows the financial tabs on a customer page — build labels are Invoices / Payments / Deposits (case prose says Unpaid Invoices/Payments/Credits; the AP/AR toggle description uses that wording, actual tab labels are Invoices/Payments/Deposits). Tabs absent when AP/AR off.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>C26492</t>
+          <t>C26477</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26492</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26477</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>3547</v>
+        <v>3545</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Staff Page Role Assignment</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Changing a user's role logs them out immediately</t>
+          <t>View and Manage AP/AR Data ON shows the same three tabs on a vendor</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -6048,32 +6048,32 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>API/session: changing a user role logs them out immediately — the prior session is invalidated (409 Session has expired) right after the change.</t>
+          <t>UI (Parts Manager, AP/AR ON): the vendor page (/parts/vendor/{id}) shows the AP/AR tabs — Contacts, Unpaid Invoices (30), Payments (4). screenshot vendordetail-vendON.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>C26494</t>
+          <t>C26478</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26494</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26478</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3547</v>
+        <v>3545</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Staff Page Role Assignment</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>A logged-in user is logged out immediately when their role changes</t>
+          <t>With Reports ON, all 6 AP/AR aging reports are listed (whether or not AP/AR is on)</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6088,32 +6088,32 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>API/session: a logged-in user is logged out immediately when their role changes (session invalidated -&gt; 409 on next request).</t>
+          <t>UI (admin /reports, Reports ON): all 6 AP/AR aging reports are listed — A/R Aging Summary, A/R Aging Detail, A/R Aging Collection, A/P Aging Summary, A/P Aging Detail, A/P Unpaid Invoices. screenshot reports-admin.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>C26495</t>
+          <t>C26480</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26495</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26480</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Administrator: role permissions match the expected set</t>
+          <t>View and Manage AP/AR Data OFF hides the three tabs on a customer</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -6123,37 +6123,37 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Administrator permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI: AP/AR Data OFF (Service Advisor) — the customer page shows only Work Orders/Part Sales/Contacts/Assets/Notes; the Invoices/Payments/Deposits tabs are hidden.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>C26496</t>
+          <t>C26481</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26496</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26481</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Service Manager: role permissions match the expected set</t>
+          <t>View and Manage AP/AR Data OFF hides the three tabs on a vendor</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6163,37 +6163,37 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Service Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI (Service Advisor, AP/AR OFF): the same vendor page shows only the Contacts tab — Unpaid Invoices/Payments tabs are hidden. screenshot vendordetail-vendOFF.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>C26497</t>
+          <t>C26482</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26497</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26482</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Senior Service Advisor: role permissions match the expected set</t>
+          <t>With AP/AR OFF but Reports ON, all 6 AP/AR aging reports are still listed</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6203,37 +6203,37 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Senior Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI (RUN331 FAIL NOW FIXED): a role with Reports ON but View and Manage AP/AR Data OFF (ZZAUTOTEST ReportsNoAPAR) still sees all 6 AP/AR aging reports on /reports (A/R Aging Summary/Detail/Collection, A/P Aging Summary/Detail, A/P Unpaid Invoices). Aging reports follow the Reports permission, not AP/AR. screenshot reports-noapar.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>C26498</t>
+          <t>C26483</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26498</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26483</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Service Advisor: role permissions match the expected set</t>
+          <t>View and Manage AP/AR Data OFF hides the sensitive money fields on Edit Customer</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6243,37 +6243,37 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI: AP/AR Data OFF hides the sensitive money fields on Edit Customer (Credit Limit, Taxes, Default Labor Rate, Default Shop Supplies, Min, Max, Credit Terms) — same observation as C26402.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>C26499</t>
+          <t>C26484</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26499</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26484</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Foreman: role permissions match the expected set</t>
+          <t>View and Manage AP/AR Data OFF still lets a user create invoices and take payments if Invoicing &amp; payments allows it</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6283,37 +6283,37 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Foreman permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI/perms: AP/AR Data OFF still allows creating invoices/taking payments when Invoicing allows — Service Advisor has invoicingPaymentsCreateAndEdit+Delete with AP/AR off; invoicing capability is independent of AP/AR.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>C26500</t>
+          <t>C26485</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26500</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26485</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Technician: role permissions match the expected set</t>
+          <t>View and Manage AP/AR Data works independently of See Financial Data</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6323,37 +6323,37 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI: See Financial Data and View and Manage AP/AR Data are separate Cross-Cutting Toggles (both present independently alongside View History Logs); AP/AR is not tied to SFD in the editor.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>C26501</t>
+          <t>C26486</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26501</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26486</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Parts Manager: role permissions match the expected set</t>
+          <t>View and Manage AP/AR Data OFF does not block any add/edit/delete area</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6363,37 +6363,37 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Parts Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI: AP/AR Data OFF does not block any add/edit/delete — Service Advisor (AP/AR off) still opens the editable Edit Customer modal and retains full customer/WO/parts create-edit; only the financial tabs/fields are hidden.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>C26502</t>
+          <t>C26492</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26502</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26492</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Parts Technician: role permissions match the expected set</t>
+          <t>Changing a user's role logs them out immediately</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6403,37 +6403,37 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Parts Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>API/session: changing a user role logs them out immediately — the prior session is invalidated (409 Session has expired) right after the change.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>C26503</t>
+          <t>C26494</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26503</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26494</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Office User: role permissions match the expected set</t>
+          <t>A logged-in user is logged out immediately when their role changes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6443,24 +6443,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Office User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>API/session: a logged-in user is logged out immediately when their role changes (session invalidated -&gt; 409 on next request).</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>C26504</t>
+          <t>C26495</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26504</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26495</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Sales Representative: role permissions match the expected set</t>
+          <t>Administrator: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6488,19 +6488,19 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Sales Representative permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Administrator permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>C26505</t>
+          <t>C26496</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26505</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26496</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Time Clock User: role permissions match the expected set</t>
+          <t>Service Manager: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6528,19 +6528,19 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Time Clock User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Service Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>C26506</t>
+          <t>C26497</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26506</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26497</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Customer portal is on by default only for Service Advisor, Senior Service Advisor, Service Manager and Parts Manager (and Administrator)</t>
+          <t>Senior Service Advisor: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6563,37 +6563,37 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (matches live per-role customerPortalPageAccess)</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>customerPortalPageAccess per role confirmed live: on for Admin/SM/SSA/SA/PM; off for the rest (roles-matrix-2026-07-13).</t>
+          <t>Senior Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>C26510</t>
+          <t>C26498</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26510</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26498</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Legacy 'Admin / Administrator' users become 'Administrator' after migration</t>
+          <t>Service Advisor: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6603,37 +6603,37 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Live roles API: destination system role exists = "Admin" (build name; case prose says Administrator), isEditable=true, 89 users, 42 perms. Migration is a completed historical event; destination state verified (role present, editable with pencil, populated).</t>
+          <t>Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>C26511</t>
+          <t>C26499</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26511</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26499</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Legacy 'Office' users become 'Office User' after migration</t>
+          <t>Foreman: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6643,37 +6643,37 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Live roles API: "Office User" exists, isEditable=false (lock + eye only), 5 users, 23 perms — matches legacy Office -&gt; Office User destination.</t>
+          <t>Foreman permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>C26512</t>
+          <t>C26500</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26512</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26500</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Legacy 'Time Clock' users become 'Time Clock User' after migration</t>
+          <t>Technician: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6683,37 +6683,37 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Live roles API: "Time Clock User" exists, isEditable=false (lock + eye only), 11 users, 3 perms — matches legacy Time Clock -&gt; Time Clock User.</t>
+          <t>Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>C26513</t>
+          <t>C26501</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26513</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26501</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Legacy 'Service Manager' users become 'Service Manager' after migration</t>
+          <t>Parts Manager: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6723,37 +6723,37 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Live roles API: "Service Manager" exists, isEditable=true, 3 users, 35 perms.</t>
+          <t>Parts Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>C26514</t>
+          <t>C26502</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26514</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26502</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Legacy 'Senior Service Advisor' users become 'Senior Service Advisor' after migration</t>
+          <t>Parts Technician: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6763,37 +6763,37 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Live roles API: "Senior Service Advisor" exists, isEditable=true, 8 users, 32 perms.</t>
+          <t>Parts Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>C26515</t>
+          <t>C26503</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26515</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26503</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Legacy 'Service Advisor' users become 'Service Advisor' after migration</t>
+          <t>Office User: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6803,37 +6803,37 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Live roles API: "Service Advisor" exists, isEditable=true, 2 users, 26 perms.</t>
+          <t>Office User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>C26516</t>
+          <t>C26504</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26516</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26504</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Legacy 'Foreman' users become 'Foreman' after migration</t>
+          <t>Sales Representative: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6843,37 +6843,37 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Live roles API: "Foreman" exists, isEditable=true, 16 users, 23 perms.</t>
+          <t>Sales Representative permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>C26517</t>
+          <t>C26505</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26517</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26505</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Legacy 'Technician' users become 'Technician' after migration</t>
+          <t>Time Clock User: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6883,37 +6883,37 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Live roles API: "Technician" exists, isEditable=true, 66 users, 6 perms, view_mode tech (confirmed via role detail) — matches legacy Technician destination.</t>
+          <t>Time Clock User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>C26518</t>
+          <t>C26506</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26518</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26506</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Legacy 'Parts Manager' users become 'Parts Manager' after migration</t>
+          <t>Customer portal is on by default only for Service Advisor, Senior Service Advisor, Service Manager and Parts Manager (and Administrator)</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6923,24 +6923,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (matches live per-role customerPortalPageAccess)</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Live roles API: "Parts Manager" exists, isEditable=true, 4 users, 31 perms.</t>
+          <t>customerPortalPageAccess per role confirmed live: on for Admin/SM/SSA/SA/PM; off for the rest (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>C26519</t>
+          <t>C26510</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26519</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26510</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Legacy 'Parts Tech / Parts Technician' users become 'Parts Technician' after migration</t>
+          <t>Legacy 'Admin / Administrator' users become 'Administrator' after migration</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -6968,19 +6968,19 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Live roles API: "Parts Technician" exists, isEditable=true, 10 users, 19 perms — matches legacy Parts Tech -&gt; Parts Technician.</t>
+          <t>Live roles API: destination system role exists = "Admin" (build name; case prose says Administrator), isEditable=true, 89 users, 42 perms. Migration is a completed historical event; destination state verified (role present, editable with pencil, populated).</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>C26520</t>
+          <t>C26511</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26520</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26511</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Legacy 'Sales Representative' users become 'Sales Representative' after migration</t>
+          <t>Legacy 'Office' users become 'Office User' after migration</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -7008,19 +7008,19 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Live roles API: "Sales Representative" exists, isEditable=true, 15 users, 4 perms.</t>
+          <t>Live roles API: "Office User" exists, isEditable=false (lock + eye only), 5 users, 23 perms — matches legacy Office -&gt; Office User destination.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>C26525</t>
+          <t>C26512</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26525</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26512</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Changing a user's role logs that user out and forces them to log in again</t>
+          <t>Legacy 'Time Clock' users become 'Time Clock User' after migration</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -7048,32 +7048,32 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>UI/API: after an admin changed the Tech user role, the user existing session returned 409 "Session has expired." on the next call — the role change logs the user out and forces re-login.</t>
+          <t>Live roles API: "Time Clock User" exists, isEditable=false (lock + eye only), 11 users, 3 perms — matches legacy Time Clock -&gt; Time Clock User.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>C26528</t>
+          <t>C26513</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26528</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26513</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Staff Record Settings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>The universal clock in / out is available to any active staff member, whatever their role</t>
+          <t>Legacy 'Service Manager' users become 'Service Manager' after migration</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -7088,32 +7088,32 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>UI: the universal Clock In control appears in the top bar for every role observed (Admin, Technician, Time Clock User) — available to any active staff member whatever their role.</t>
+          <t>Live roles API: "Service Manager" exists, isEditable=true, 3 users, 35 perms.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>C26532</t>
+          <t>C26514</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26532</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26514</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Create success message wording</t>
+          <t>Legacy 'Senior Service Advisor' users become 'Senior Service Advisor' after migration</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -7123,37 +7123,37 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>'Role created successfully.' confirmed in build.</t>
+          <t>Live roles API: "Senior Service Advisor" exists, isEditable=true, 8 users, 32 perms.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>C26533</t>
+          <t>C26515</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26533</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26515</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Update success message wording</t>
+          <t>Legacy 'Service Advisor' users become 'Service Advisor' after migration</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -7163,37 +7163,37 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>'Role updated successfully.' confirmed in build.</t>
+          <t>Live roles API: "Service Advisor" exists, isEditable=true, 2 users, 26 perms.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>C26534</t>
+          <t>C26516</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26534</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26516</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Deleting a custom role with 0 users shows a confirmation dialog</t>
+          <t>Legacy 'Foreman' users become 'Foreman' after migration</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -7208,32 +7208,32 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>UI: deleting a 0-user custom role opens dialog "Confirmation — Are you sure you want to delete this role? This action cannot be undone." [Cancel|Delete]. screenshot delete-confirm-dialog.</t>
+          <t>Live roles API: "Foreman" exists, isEditable=true, 16 users, 23 perms.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>C26535</t>
+          <t>C26517</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26535</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26517</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Deleting a custom role that has users is blocked</t>
+          <t>Legacy 'Technician' users become 'Technician' after migration</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -7248,32 +7248,32 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>UI: a custom role with users (Parth Cust1, 1 user) has no Delete option in its 3-dot menu — deletion is blocked.</t>
+          <t>Live roles API: "Technician" exists, isEditable=true, 66 users, 6 perms, view_mode tech (confirmed via role detail) — matches legacy Technician destination.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>C26536</t>
+          <t>C26518</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26536</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26518</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Turning See Financial Data on shows a confirmation dialog</t>
+          <t>Legacy 'Parts Manager' users become 'Parts Manager' after migration</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -7283,37 +7283,37 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>'Enable See Financial Data?' + Cancel/Enable confirmed in build (FinancialDataConfirmModal).</t>
+          <t>Live roles API: "Parts Manager" exists, isEditable=true, 4 users, 31 perms.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>C26537</t>
+          <t>C26519</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26537</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26519</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Creating a role with no name is blocked with a required-field error</t>
+          <t>Legacy 'Parts Tech / Parts Technician' users become 'Parts Technician' after migration</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -7328,32 +7328,32 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>UI: creating a role with no name is blocked — Create disabled and inline "Role name is a required field" error when the field is touched/cleared.</t>
+          <t>Live roles API: "Parts Technician" exists, isEditable=true, 10 users, 19 perms — matches legacy Parts Tech -&gt; Parts Technician.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>C26538</t>
+          <t>C26520</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26538</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26520</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Creating a role with the same permissions as an existing role shows a 'similar role' warning</t>
+          <t>Legacy 'Sales Representative' users become 'Sales Representative' after migration</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -7368,32 +7368,32 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>UI: creating a role with the same permissions as an existing role shows "Similar role already exists" warning with "Create Anyway" (SimilarRoleWarningModal, keyed on identical permissions).</t>
+          <t>Live roles API: "Sales Representative" exists, isEditable=true, 15 users, 4 perms.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>C26542</t>
+          <t>C26525</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26542</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26525</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>3553</v>
+        <v>3549</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Cross-Permission Combinations</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>A system role cannot be deleted</t>
+          <t>Changing a user's role logs that user out and forces them to log in again</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -7403,37 +7403,37 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (all system roles deletable=false)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>deletable=false for all system roles (live roles API).</t>
+          <t>UI/API: after an admin changed the Tech user role, the user existing session returned 409 "Session has expired." on the next call — the role change logs the user out and forces re-login.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>C26543</t>
+          <t>C26528</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26543</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26528</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>3553</v>
+        <v>3550</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Cross-Permission Combinations</t>
+          <t>Staff Record Settings</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Only Office User and Time Clock User are non-editable; every other system role (including Administrator) is editable</t>
+          <t>The universal clock in / out is available to any active staff member, whatever their role</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -7443,37 +7443,37 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (editable flags match live)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Live roles API: Office User &amp; Time Clock User editable=false; all others (incl. Administrator) editable=true.</t>
+          <t>UI: the universal Clock In control appears in the top bar for every role observed (Admin, Technician, Time Clock User) — available to any active staff member whatever their role.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>C26549</t>
+          <t>C26532</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26549</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26532</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Cross-Permission Combinations</t>
+          <t>User Feedback Strings</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AP/AR OFF hides the sensitive customer fields on both the Edit Customer window and the customer overview</t>
+          <t>Create success message wording</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -7483,50 +7483,410 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>UI: AP/AR Data OFF hides the sensitive customer fields on the Edit Customer modal (and the financial tabs on the customer overview) — confirmed via Service Advisor (off) vs CustAPAR (on).</t>
+          <t>'Role created successfully.' confirmed in build.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
+          <t>C26533</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26533</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>3552</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>User Feedback Strings</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Update success message wording</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Verified-Label (build)</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>'Role updated successfully.' confirmed in build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>C26534</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26534</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>3552</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>User Feedback Strings</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Deleting a custom role with 0 users shows a confirmation dialog</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>UI: deleting a 0-user custom role opens dialog "Confirmation — Are you sure you want to delete this role? This action cannot be undone." [Cancel|Delete]. screenshot delete-confirm-dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>C26535</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26535</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>3552</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>User Feedback Strings</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Deleting a custom role that has users is blocked</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>UI: a custom role with users (Parth Cust1, 1 user) has no Delete option in its 3-dot menu — deletion is blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>C26536</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26536</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>3552</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>User Feedback Strings</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Turning See Financial Data on shows a confirmation dialog</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Verified-Label (build)</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>'Enable See Financial Data?' + Cancel/Enable confirmed in build (FinancialDataConfirmModal).</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>C26537</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26537</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>3552</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>User Feedback Strings</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Creating a role with no name is blocked with a required-field error</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>UI: creating a role with no name is blocked — Create disabled and inline "Role name is a required field" error when the field is touched/cleared.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>C26538</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26538</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>3552</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>User Feedback Strings</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Creating a role with the same permissions as an existing role shows a 'similar role' warning</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>UI: creating a role with the same permissions as an existing role shows "Similar role already exists" warning with "Create Anyway" (SimilarRoleWarningModal, keyed on identical permissions).</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>C26542</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26542</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>A system role cannot be deleted</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Roles-API-Verified (all system roles deletable=false)</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>deletable=false for all system roles (live roles API).</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>C26543</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26543</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Only Office User and Time Clock User are non-editable; every other system role (including Administrator) is editable</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Roles-API-Verified (editable flags match live)</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Live roles API: Office User &amp; Time Clock User editable=false; all others (incl. Administrator) editable=true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>C26549</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26549</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>AP/AR OFF hides the sensitive customer fields on both the Edit Customer window and the customer overview</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>UI: AP/AR Data OFF hides the sensitive customer fields on the Edit Customer modal (and the financial tabs on the customer overview) — confirmed via Service Advisor (off) vs CustAPAR (on).</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
           <t>C26551</t>
         </is>
       </c>
-      <c r="B159" s="4" t="inlineStr">
+      <c r="B168" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/26551</t>
         </is>
       </c>
-      <c r="C159" t="n">
+      <c r="C168" t="n">
         <v>3553</v>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="D168" t="inlineStr">
         <is>
           <t>Cross-Permission Combinations</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
+      <c r="E168" t="inlineStr">
         <is>
           <t>Universal clock in/out works even for a user whose role has (almost) no permissions</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
         <is>
           <t>UI: the Time Clock User role (only 3 perms: scheduleView/timesheetsView/workOrdersView) still shows the universal Clock In control — universal clock in is not gated by role/permissions.</t>
         </is>
@@ -7692,6 +8052,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B157" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B158" r:id="rId157"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B168" r:id="rId167"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7703,7 +8072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7841,12 +8210,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C26375</t>
+          <t>C26379</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26375</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26379</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -7859,7 +8228,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Work orders Create &amp; Edit lets the user create and change work orders</t>
+          <t>The Review work orders sub-toggle controls the Review action on work orders</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -7869,24 +8238,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: with woReviewWorkOrders the WO/line showed no explicit Review/Approve action (header menu: Audit Log/Add Fee-Discount; line menu: Add line note/Story history/Audit log). The Review action likely requires a submitted line-authorization state to appear; needs seeding that authorization workflow to show toggle on vs off.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Needs live UI + role edit.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C26376</t>
+          <t>C26380</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26376</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26380</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -7899,7 +8268,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Work orders Delete lets the user delete work orders</t>
+          <t>Pick parts needs only Work orders View, not Create &amp; Edit</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -7909,7 +8278,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: Technician (woPickParts + WO View, no C&amp;E) shows Complete/Start on lines but no Pick action was visible on the test WO (parts already picked/requested). Needs a seeded pending pickable part-request state to display and exercise the Pick action.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7921,12 +8290,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C26377</t>
+          <t>C27873</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26377</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27873</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -7939,7 +8308,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Work orders View OFF hides Work Orders from the top navigation</t>
+          <t>Edit/delete options on another user's customer note are hidden without the right permission</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -7949,24 +8318,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: needs a customer note authored by a DIFFERENT user, then observe edit/delete affordance hidden for a role lacking the note permission — requires seeding a note as user A and viewing as user B; not reachable with single Tech identity this pass.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded; customer notes governed by Customers permission (not WO Delete). API/element jargon stripped.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C26379</t>
+          <t>C29435</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26379</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29435</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -7979,7 +8348,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>The Review work orders sub-toggle controls the Review action on work orders</t>
+          <t>A Pick/Order Parts role can edit the Quantity on the Part Requests tab</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -7989,37 +8358,37 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: the Part Requests tab (Order-Parts role) shows a Quantity column, but the inline quantity-edit interaction could not be triggered in this harness (cell-click did not open an editable input). Needs manual confirm that qty is editable.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Needs live UI + role edit.</t>
+          <t>Reworded; element-id jargon stripped.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C26380</t>
+          <t>C26389</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26380</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26389</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3534</v>
+        <v>3535</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Work Orders Permissions</t>
+          <t>Work Order Lines Permissions</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pick parts needs only Work orders View, not Create &amp; Edit</t>
+          <t>Work order lines are visible whenever Work orders View is ON</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -8029,37 +8398,37 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role); no-WOL-View-column build-verified</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>WOL View comes from WO View (build-verified). Behavior needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C26381</t>
+          <t>C26390</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26381</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26390</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3534</v>
+        <v>3535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Work Orders Permissions</t>
+          <t>Work Order Lines Permissions</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Order parts needs Work orders View and See Financial Data (not Create &amp; Edit)</t>
+          <t>Work order lines Create &amp; Edit allows adding, editing, moving parts, authorizing and managing part requests</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -8074,32 +8443,32 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Order parts+SFD dependency consistent with build (Order-parts enable-SFD modal). Behavior needs live UI.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C26383</t>
+          <t>C26391</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26383</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26391</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3534</v>
+        <v>3535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Work Orders Permissions</t>
+          <t>Work Order Lines Permissions</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Without Create &amp; Edit, create/edit options are hidden on work orders</t>
+          <t>Work order lines Delete allows removing lines</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -8121,25 +8490,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C26384</t>
+          <t>C26392</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26384</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26392</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3534</v>
+        <v>3535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Work Orders Permissions</t>
+          <t>Work Order Lines Permissions</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Without Delete, no delete option is shown on a work order</t>
+          <t>Work orders View OFF makes work order lines unreachable</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -8161,25 +8530,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C26385</t>
+          <t>C26393</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26385</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26393</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3534</v>
+        <v>3535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Work Orders Permissions</t>
+          <t>Work Order Lines Permissions</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Creating a work order still works when Customers View is OFF</t>
+          <t>Work order lines are read-only when Create &amp; Edit is OFF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -8201,25 +8570,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C26386</t>
+          <t>C27271</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26386</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27271</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3534</v>
+        <v>3535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Work Orders Permissions</t>
+          <t>Work Order Lines Permissions</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>The customer name shows on the work order header even when Customers View is OFF</t>
+          <t>The Build Lines entry point is hidden for a Work Orders View-only role</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -8229,37 +8598,37 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role + ShopCoach on)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded; element-id jargon stripped. Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C27868</t>
+          <t>C27272</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27868</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27272</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3534</v>
+        <v>3535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Work Orders Permissions</t>
+          <t>Work Order Lines Permissions</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Order parts controls the work order Parts tab (on shows it, off hides it)</t>
+          <t>The Build Lines entry point is shown for a role with Work order lines Create &amp; Edit</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -8269,37 +8638,37 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role + ShopCoach on)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Consistent with build (Order parts gates WO Parts tab). Needs live UI.</t>
+          <t>Reworded; element-id jargon stripped. Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C27873</t>
+          <t>C27866</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27873</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27866</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3534</v>
+        <v>3535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Work Orders Permissions</t>
+          <t>Work Order Lines Permissions</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Edit/delete options on another user's customer note are hidden without the right permission</t>
+          <t>A default Technician (with Work order lines Create &amp; Edit) can bulk-complete another tech's line via Set Line Status</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -8309,37 +8678,37 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded roles + notes)</t>
+          <t>Blocked-UI (needs default Technician role + seeded WO line)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Reworded; customer notes governed by Customers permission (not WO Delete). API/element jargon stripped.</t>
+          <t>Reworded; SV-ref/URL/403 jargon stripped. Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C29435</t>
+          <t>C27870</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29435</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27870</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3534</v>
+        <v>3535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Work Orders Permissions</t>
+          <t>Work Order Lines Permissions</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>A Pick/Order Parts role can edit the Quantity on the Part Requests tab</t>
+          <t>Work order lines Create &amp; Edit lets the user mark a core OK/Not-OK and add line history</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -8349,37 +8718,37 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + WO)</t>
+          <t>Blocked-UI (needs seeded role + core part)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Reworded; element-id jargon stripped.</t>
+          <t>Needs live UI with a cored part.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C26389</t>
+          <t>C26395</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26389</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26395</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3535</v>
+        <v>3536</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Work Order Lines Permissions</t>
+          <t>Schedule Permissions</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Work order lines are visible whenever Work orders View is ON</t>
+          <t>Schedule Create &amp; Edit allows creating, changing and dragging appointments</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -8389,37 +8758,37 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); no-WOL-View-column build-verified</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>WOL View comes from WO View (build-verified). Behavior needs live UI.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C26390</t>
+          <t>C26396</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26390</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26396</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3535</v>
+        <v>3536</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Work Order Lines Permissions</t>
+          <t>Schedule Permissions</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Work order lines Create &amp; Edit allows adding, editing, moving parts, authorizing and managing part requests</t>
+          <t>Schedule Delete allows removing appointments</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -8441,25 +8810,25 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C26391</t>
+          <t>C27867</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26391</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27867</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3535</v>
+        <v>3536</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Work Order Lines Permissions</t>
+          <t>Schedule Permissions</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Work order lines Delete allows removing lines</t>
+          <t>A Schedule Create &amp; Edit only role can open 'Assign existing work order' and the unscheduled work order list loads</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -8469,37 +8838,37 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded Schedule-only role)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded; API endpoint jargon stripped. Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C26392</t>
+          <t>C26399</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26392</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26399</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3535</v>
+        <v>3537</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Work Order Lines Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Work orders View OFF makes work order lines unreachable</t>
+          <t>Customers Create &amp; Edit allows creating customers, contacts and vehicles</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -8521,25 +8890,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C26393</t>
+          <t>C26400</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26393</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26400</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3535</v>
+        <v>3537</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Work Order Lines Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Work order lines are read-only when Create &amp; Edit is OFF</t>
+          <t>Customers Delete removes the customer record</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -8561,25 +8930,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C27271</t>
+          <t>C26401</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27271</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26401</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3535</v>
+        <v>3537</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Work Order Lines Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>The Build Lines entry point is hidden for a Work Orders View-only role</t>
+          <t>Customers Delete does NOT let the user delete customer payments (that needs Invoicing &amp; payments Delete)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -8589,37 +8958,37 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + ShopCoach on)</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Reworded; element-id jargon stripped. Needs live UI.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C27272</t>
+          <t>C26405</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27272</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26405</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3535</v>
+        <v>3537</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Work Order Lines Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>The Build Lines entry point is shown for a role with Work order lines Create &amp; Edit</t>
+          <t>Customer names still show on work orders and invoices even when Customers is hidden</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -8629,37 +8998,37 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + ShopCoach on)</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Reworded; element-id jargon stripped. Needs live UI.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C27866</t>
+          <t>C26412</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27866</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26412</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3535</v>
+        <v>3538</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Work Order Lines Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>A default Technician (with Work order lines Create &amp; Edit) can bulk-complete another tech's line via Set Line Status</t>
+          <t>Part sales Delete lets the user delete part sales and reverse part sales invoices</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -8669,37 +9038,37 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs default Technician role + seeded WO line)</t>
+          <t>Blocked-UI: Part sales Delete affordance (delete/reverse a part sale) not located in this pass — the part-sale row menu did not open in the harness; needs the part-sale detail-page delete control with a with/without partSalesDelete contrast.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Reworded; SV-ref/URL/403 jargon stripped. Needs live UI.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C27870</t>
+          <t>C26415</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27870</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26415</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3535</v>
+        <v>3538</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Work Order Lines Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Work order lines Create &amp; Edit lets the user mark a core OK/Not-OK and add line history</t>
+          <t>Catalog and Inventory Delete removes catalog parts</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -8709,37 +9078,37 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + core part)</t>
+          <t>Blocked-UI: Catalog Delete affordance not located — the catalogue row more_vert menu did not open in the harness; needs the catalog-part detail delete control (Parts Manager has catalogInventoryDelete) vs a no-delete role.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Needs live UI with a cored part.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C26395</t>
+          <t>C26418</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26395</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26418</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3536</v>
+        <v>3538</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Schedule Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Schedule Create &amp; Edit allows creating, changing and dragging appointments</t>
+          <t>Vendor and order management Delete lets the user delete vendors and purchase orders and reverse vendor transactions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -8749,37 +9118,37 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: Vendor/PO Delete affordance (delete vendor/PO, reverse vendor txn) not located this pass; needs the vendor/PO detail delete control with/without vendorOrderManagementDelete.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Needs live UI; AP/AR dependency on the vendor Payments tab is build-observed.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C26396</t>
+          <t>C26419</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26396</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26419</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3536</v>
+        <v>3538</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Schedule Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Schedule Delete allows removing appointments</t>
+          <t>Returning a part to inventory (restocking) is controlled by Vendor and order management</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -8789,7 +9158,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: restocking (return part to inventory) control not reached — needs a WO/PO with a picked part to exercise the return-to-inventory action gated by Vendor and order management.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8801,25 +9170,25 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C27867</t>
+          <t>C26420</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27867</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26420</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3536</v>
+        <v>3539</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Schedule Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>A Schedule Create &amp; Edit only role can open 'Assign existing work order' and the unscheduled work order list loads</t>
+          <t>Invoicing &amp; payments View shows the Finance tab and lets the user see invoices</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -8829,37 +9198,37 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded Schedule-only role)</t>
+          <t>Blocked-UI: the Invoicing &amp; payments / Finance surface route was not confirmed (/invoices returned minimal content for the Viewer role). Follow-up: locate the Finance tab/invoices route and confirm invoicingPaymentsView access.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Reworded; API endpoint jargon stripped. Needs live UI.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C26399</t>
+          <t>C26421</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26399</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26421</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3537</v>
+        <v>3539</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Customers Create &amp; Edit allows creating customers, contacts and vehicles</t>
+          <t>Invoicing &amp; payments Create &amp; Edit lets the user create invoices and take payments</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -8881,25 +9250,25 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C26400</t>
+          <t>C26422</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26400</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26422</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3537</v>
+        <v>3539</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Customers Delete removes the customer record</t>
+          <t>Invoicing &amp; payments Delete lets the user delete payments and void transactions (but not reverse invoices)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -8921,25 +9290,25 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C26401</t>
+          <t>C26423</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26401</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26423</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3537</v>
+        <v>3539</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Customers Delete does NOT let the user delete customer payments (that needs Invoicing &amp; payments Delete)</t>
+          <t>Deleting a customer payment needs Invoicing &amp; payments Delete, not Customers Delete</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -8961,25 +9330,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>C26405</t>
+          <t>C26425</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26405</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26425</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3537</v>
+        <v>3539</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Customer names still show on work orders and invoices even when Customers is hidden</t>
+          <t>See Financial Data OFF makes Invoicing &amp; payments inaccessible even with View, Create &amp; Edit and Delete</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -9001,25 +9370,25 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>C26412</t>
+          <t>C26426</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26412</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26426</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3538</v>
+        <v>3539</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Part sales Delete lets the user delete part sales and reverse part sales invoices</t>
+          <t>Invoicing &amp; payments View OFF with See Financial Data ON: prices show but invoices are not reachable</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -9029,7 +9398,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Blocked-UI: Part sales Delete affordance (delete/reverse a part sale) not located in this pass — the part-sale row menu did not open in the harness; needs the part-sale detail-page delete control with a with/without partSalesDelete contrast.</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -9041,25 +9410,25 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>C26415</t>
+          <t>C26427</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26415</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26427</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3538</v>
+        <v>3539</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Catalog and Inventory Delete removes catalog parts</t>
+          <t>The Send to Terminal action needs Invoicing &amp; payments Create &amp; Edit</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -9069,7 +9438,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Blocked-UI: Catalog Delete affordance not located — the catalogue row more_vert menu did not open in the harness; needs the catalog-part detail delete control (Parts Manager has catalogInventoryDelete) vs a no-delete role.</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -9081,25 +9450,25 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>C26418</t>
+          <t>C26428</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26418</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26428</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3538</v>
+        <v>3539</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vendor and order management Delete lets the user delete vendors and purchase orders and reverse vendor transactions</t>
+          <t>Taking Deposits on a work order needs Invoicing &amp; payments Create &amp; Edit</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -9109,37 +9478,37 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Blocked-UI: Vendor/PO Delete affordance (delete vendor/PO, reverse vendor txn) not located this pass; needs the vendor/PO detail delete control with/without vendorOrderManagementDelete.</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Needs live UI; AP/AR dependency on the vendor Payments tab is build-observed.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C26419</t>
+          <t>C27871</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26419</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27871</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3538</v>
+        <v>3539</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Returning a part to inventory (restocking) is controlled by Vendor and order management</t>
+          <t>Deleting or cancelling a return is controlled by Invoicing &amp; payments Delete</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -9149,24 +9518,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Blocked-UI: restocking (return part to inventory) control not reached — needs a WO/PO with a picked part to exercise the return-to-inventory action gated by Vendor and order management.</t>
+          <t>Blocked-UI (needs seeded roles + returns)</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded; SV-ref/element-id jargon stripped.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C26420</t>
+          <t>C29434</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26420</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29434</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -9179,7 +9548,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Invoicing &amp; payments View shows the Finance tab and lets the user see invoices</t>
+          <t>Send to Terminal needs Invoicing &amp; payments Create &amp; Edit AND Customer portal ON</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -9189,24 +9558,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Blocked-UI: the Invoicing &amp; payments / Finance surface route was not confirmed (/invoices returned minimal content for the Viewer role). Follow-up: locate the Finance tab/invoices route and confirm invoicingPaymentsView access.</t>
+          <t>Blocked-UI (needs seeded roles + terminal)</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded; feature-flag/element-id/SV jargon stripped.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C26421</t>
+          <t>C29438</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26421</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29438</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -9219,7 +9588,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Invoicing &amp; payments Create &amp; Edit lets the user create invoices and take payments</t>
+          <t>Invoicing &amp; payments Create &amp; Edit gives the edit control on the work order Financial Info card</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -9229,37 +9598,37 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role + WO)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded; element-id/SV jargon stripped.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C26422</t>
+          <t>C26430</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26422</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26430</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Invoicing &amp; payments Delete lets the user delete payments and void transactions (but not reverse invoices)</t>
+          <t>Timesheets View only: timesheet entries are read-only</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -9274,32 +9643,32 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Read-only behavior needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C26423</t>
+          <t>C26431</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26423</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26431</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Deleting a customer payment needs Invoicing &amp; payments Delete, not Customers Delete</t>
+          <t>Timesheets Create &amp; Edit lets the user edit entries</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -9314,32 +9683,32 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Edit behavior needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C26425</t>
+          <t>C26433</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26425</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26433</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>See Financial Data OFF makes Invoicing &amp; payments inaccessible even with View, Create &amp; Edit and Delete</t>
+          <t>Timesheets View OFF with Reports ON: the timesheet activities report is still available</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -9354,32 +9723,32 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Report access needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C26426</t>
+          <t>C26434</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26426</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26434</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Invoicing &amp; payments View OFF with See Financial Data ON: prices show but invoices are not reachable</t>
+          <t>All Timesheets permissions OFF and Reports OFF: no timesheet navigation anywhere</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -9394,32 +9763,32 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Nav-hide needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C26427</t>
+          <t>C27394</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26427</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27394</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>The Send to Terminal action needs Invoicing &amp; payments Create &amp; Edit</t>
+          <t>A clock-capable role without Timesheets View can still see and open My Timesheets</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -9429,37 +9798,37 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded clock-capable role)</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded, jargon stripped; needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>C26428</t>
+          <t>C26437</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26428</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26437</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3539</v>
+        <v>3541</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Taking Deposits on a work order needs Invoicing &amp; payments Create &amp; Edit</t>
+          <t>Customer portal ON lets the user manage the customer portal</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -9469,37 +9838,37 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role); toggle label 'Customer portal' build-verified</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Toggle 'Customer portal' confirmed in build. Manage behavior needs live check.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>C27871</t>
+          <t>C26438</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27871</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26438</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3539</v>
+        <v>3541</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deleting or cancelling a return is controlled by Invoicing &amp; payments Delete</t>
+          <t>Customer portal OFF hides the customer portal from navigation</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -9509,37 +9878,37 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded roles + returns)</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Reworded; SV-ref/element-id jargon stripped.</t>
+          <t>Nav-hide needs live check.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>C29434</t>
+          <t>C26439</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29434</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26439</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3539</v>
+        <v>3541</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Send to Terminal needs Invoicing &amp; payments Create &amp; Edit AND Customer portal ON</t>
+          <t>Billing Portal ON lets the user manage the billing portal</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9549,37 +9918,37 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded roles + terminal)</t>
+          <t>Blocked-UI (needs seeded role); toggle label 'Billing Portal' build-verified</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Reworded; feature-flag/element-id/SV jargon stripped.</t>
+          <t>Toggle 'Billing Portal' confirmed in build. Manage behavior needs live check.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>C29438</t>
+          <t>C26440</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29438</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26440</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3539</v>
+        <v>3541</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Invoicing &amp; payments Create &amp; Edit gives the edit control on the work order Financial Info card</t>
+          <t>Billing Portal OFF hides the Billing Portal item in the Settings area</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9589,37 +9958,37 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + WO)</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Reworded; element-id/SV jargon stripped.</t>
+          <t>Nav-hide needs live check.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>C26430</t>
+          <t>C26445</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26430</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26445</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3540</v>
+        <v>3542</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Timesheets View only: timesheet entries are read-only</t>
+          <t>App Settings ON gives access to the admin pages</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9629,37 +9998,37 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role); page names build-verified</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Read-only behavior needs live UI.</t>
+          <t>App Settings gates Departments/Settings/Staff/Roles &amp; Permissions/Locations (build route metadata).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>C26431</t>
+          <t>C26446</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26431</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26446</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3540</v>
+        <v>3542</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Timesheets Create &amp; Edit lets the user edit entries</t>
+          <t>Service ON gives access to the Service configuration pages</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9669,37 +10038,37 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role); page names build-verified</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Edit behavior needs live UI.</t>
+          <t>Service gates Canned Lines/Inspection Templates/Labour Types/Vehicle Types (build route metadata).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>C26433</t>
+          <t>C26447</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26433</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26447</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3540</v>
+        <v>3542</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Timesheets View OFF with Reports ON: the timesheet activities report is still available</t>
+          <t>Parts ON gives access to the Parts configuration pages</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9709,37 +10078,37 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role); page names build-verified</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Report access needs live UI.</t>
+          <t>Parts gates Bins/Categories/Pricing (build route metadata).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C26434</t>
+          <t>C26448</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26434</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26448</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3540</v>
+        <v>3542</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>All Timesheets permissions OFF and Reports OFF: no timesheet navigation anywhere</t>
+          <t>Finance ON shows the Finance pages, and Integrations ON shows QuickBooks, IBS and Open API</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -9749,37 +10118,37 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role); page names build-verified</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Nav-hide needs live UI.</t>
+          <t>Finance gates Payment Methods/Taxes; Integrations gates IBS/Open API/QuickBooks (build route metadata).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C27394</t>
+          <t>C26449</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27394</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26449</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3540</v>
+        <v>3542</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>A clock-capable role without Timesheets View can still see and open My Timesheets</t>
+          <t>Data Import ON gives access to the Imports pages</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -9789,37 +10158,37 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded clock-capable role)</t>
+          <t>Blocked-UI (needs seeded role); page names build-verified</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Reworded, jargon stripped; needs live UI.</t>
+          <t>Data Import gates Contacts/Inventory/Invoices/Vehicles/Vendors Import (build route metadata).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>C26437</t>
+          <t>C26450</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26437</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26450</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3541</v>
+        <v>3542</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Customer portal ON lets the user manage the customer portal</t>
+          <t>View/Manage Wages ON lets the user manage wages</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -9829,37 +10198,37 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); toggle label 'Customer portal' build-verified</t>
+          <t>Blocked-UI (needs seeded role); toggle label 'View/Manage Wages' build-verified</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Toggle 'Customer portal' confirmed in build. Manage behavior needs live check.</t>
+          <t>Toggle 'View/Manage Wages' confirmed in build. Wage editing needs live check.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>C26438</t>
+          <t>C26451</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26438</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26451</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3541</v>
+        <v>3542</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Customer portal OFF hides the customer portal from navigation</t>
+          <t>The Settings sub-toggles work independently (Service on, Finance off)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -9874,32 +10243,32 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Nav-hide needs live check.</t>
+          <t>Needs live check.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>C26439</t>
+          <t>C29273</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26439</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29273</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3541</v>
+        <v>3542</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Billing Portal ON lets the user manage the billing portal</t>
+          <t>The Integrations admin pages depend on the Integrations sub-toggle, not on Finance</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -9909,37 +10278,37 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); toggle label 'Billing Portal' build-verified</t>
+          <t>Blocked-UI (needs two seeded roles)</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Toggle 'Billing Portal' confirmed in build. Manage behavior needs live check.</t>
+          <t>Steps-Separated case; reworded to layman, stripped element-id/URL jargon. Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C26440</t>
+          <t>C29274</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26440</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29274</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3541</v>
+        <v>3542</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Billing Portal OFF hides the Billing Portal item in the Settings area</t>
+          <t>The QuickBooks connection check does not run for roles without Integrations</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -9954,32 +10323,32 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Nav-hide needs live check.</t>
+          <t>Steps-Separated case; reworded to layman. Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C26445</t>
+          <t>C26460</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26445</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26460</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3542</v>
+        <v>3543</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>App Settings ON gives access to the admin pages</t>
+          <t>Tech view: the parts request form shows fewer fields</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -9989,37 +10358,37 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); page names build-verified</t>
+          <t>Blocked-UI: needs the New Part Request form opened in tech view vs full view to compare field counts; the lines screen is drivable but the request-form modal step was not reached this pass.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>App Settings gates Departments/Settings/Staff/Roles &amp; Permissions/Locations (build route metadata).</t>
+          <t>precise reason logged</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C26446</t>
+          <t>C26461</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26446</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26461</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3542</v>
+        <v>3543</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Service ON gives access to the Service configuration pages</t>
+          <t>Tech view: the user can add new work order lines but cannot edit existing ones</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -10029,37 +10398,37 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); page names build-verified</t>
+          <t>Blocked-UI: New Line (add) confirmed present in tech view, but the existing-line read-only lock was not directly exercised (would require attempting to edit a pending line inline). Precise follow-up: open a pending line editor as the tech.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Service gates Canned Lines/Inspection Templates/Labour Types/Vehicle Types (build route metadata).</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C26447</t>
+          <t>C26462</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26447</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26462</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3542</v>
+        <v>3543</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Parts ON gives access to the Parts configuration pages</t>
+          <t>Tech view: a line becomes read-only once its authorization is approved</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -10069,37 +10438,37 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); page names build-verified</t>
+          <t>Blocked-UI: approved-WO lines showed only tech status actions (Complete/Story/Start) with no edit control (consistent with read-only), but the pending-&gt;approved edit-lock transition was not directly exercised.</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Parts gates Bins/Categories/Pricing (build route metadata).</t>
+          <t>Needs live UI + a second user.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C26448</t>
+          <t>C26466</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26448</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26466</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3542</v>
+        <v>3543</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Finance ON shows the Finance pages, and Integrations ON shows QuickBooks, IBS and Open API</t>
+          <t>Full View: a user who can approve lines sees the 'Send to Portal' button</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -10109,37 +10478,37 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); page names build-verified</t>
+          <t>Blocked-UI: Send to Portal was NOT found on the full-view (admin) lines page body; it is likely in the WO header more_vert menu or gated by WO state — needs the header action menu expanded to confirm.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Finance gates Payment Methods/Taxes; Integrations gates IBS/Open API/QuickBooks (build route metadata).</t>
+          <t>Send-to-Portal flow needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C26449</t>
+          <t>C26479</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26449</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26479</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3542</v>
+        <v>3545</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Data Import ON gives access to the Imports pages</t>
+          <t>View and Manage AP/AR Data ON allows paying several invoices at once from the Unpaid Invoices tab</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -10149,37 +10518,37 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); page names build-verified</t>
+          <t>Blocked-UI (needs seeded role + live payment)</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Data Import gates Contacts/Inventory/Invoices/Vehicles/Vendors Import (build route metadata).</t>
+          <t>Bulk payment needs live UI + payment (create-customer-payment 500s intermittently per prior run).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C26450</t>
+          <t>C26488</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26450</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26488</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3542</v>
+        <v>3546</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>View History Logs</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>View/Manage Wages ON lets the user manage wages</t>
+          <t>View History Logs ON: work order history and line history are visible (work orders only)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -10189,37 +10558,37 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); toggle label 'View/Manage Wages' build-verified</t>
+          <t>Blocked-UI (needs seeded role); 'View History Logs' toggle build-verified</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Toggle 'View/Manage Wages' confirmed in build. Wage editing needs live check.</t>
+          <t>Cross-toggle 'View History Logs' confirmed in build. History visibility needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C26451</t>
+          <t>C26489</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26451</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26489</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3542</v>
+        <v>3546</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>View History Logs</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>The Settings sub-toggles work independently (Service on, Finance off)</t>
+          <t>View History Logs OFF: work order history and line history are hidden (work orders only)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -10229,37 +10598,37 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role); labels build-verified</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Needs live check.</t>
+          <t>viewHistoryLogs also gates the 'Part History' page under Parts (build route metadata). History-hide needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C29273</t>
+          <t>C26490</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29273</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26490</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3542</v>
+        <v>3547</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>The Integrations admin pages depend on the Integrations sub-toggle, not on Finance</t>
+          <t>The Staff role dropdown groups roles into System Roles and Custom Roles</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -10269,37 +10638,37 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs two seeded roles)</t>
+          <t>Blocked-UI: the Edit Staff Member Role dropdown (System/Custom grouping) was not reached — the staff row click opened Manage-staff-enrollments. Follow-up: locate the Edit Staff Member action, open the Role selector.</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Steps-Separated case; reworded to layman, stripped element-id/URL jargon. Needs live UI.</t>
+          <t>11 system roles confirmed in live roles list (was '12'). Grouping labels need live Staff page.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C29274</t>
+          <t>C26491</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29274</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26491</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3542</v>
+        <v>3547</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>The QuickBooks connection check does not run for roles without Integrations</t>
+          <t>The View Permissions button next to the role selector opens the Permission Summary</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -10309,37 +10678,37 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: View Permissions eye next to the staff Role selector not reached (same Edit-Staff-Member surface as C26490).</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Steps-Separated case; reworded to layman. Needs live UI.</t>
+          <t>'View Permissions' confirmed in build. Needs live Staff page.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C26460</t>
+          <t>C26493</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26460</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26493</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3543</v>
+        <v>3547</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Tech view: the parts request form shows fewer fields</t>
+          <t>If a role change fails, the user keeps their previous role</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -10349,37 +10718,37 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Blocked-UI: needs the New Part Request form opened in tech view vs full view to compare field counts; the lines screen is drivable but the request-form modal step was not reached this pass.</t>
+          <t>Blocked-UI: forcing a failed role change (to confirm the user keeps the prior role) requires inducing a server error on /change; not reproducible on demand this pass.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>precise reason logged</t>
+          <t>Failed-save path needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C26461</t>
+          <t>C26526</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26461</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26526</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3543</v>
+        <v>3550</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Staff Record Settings</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Tech view: the user can add new work order lines but cannot edit existing ones</t>
+          <t>Whether a technician can be scheduled depends on their department, not their role</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -10389,37 +10758,37 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Blocked-UI: New Line (add) confirmed present in tech view, but the existing-line read-only lock was not directly exercised (would require attempting to edit a pending line inline). Precise follow-up: open a pending line editor as the tech.</t>
+          <t>Blocked-UI (needs two seeded users + departments)</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Department-gated scheduling needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C26462</t>
+          <t>C26527</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26462</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26527</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3543</v>
+        <v>3550</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Staff Record Settings</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Tech view: a line becomes read-only once its authorization is approved</t>
+          <t>Clocking in on a work order line depends on the per-staff Time Clock setting</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -10429,37 +10798,37 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Blocked-UI: approved-WO lines showed only tech status actions (Complete/Story/Start) with no edit control (consistent with read-only), but the pending-&gt;approved edit-lock transition was not directly exercised.</t>
+          <t>Blocked-UI (needs two seeded users)</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Needs live UI + a second user.</t>
+          <t>Per-staff Time Clock gating needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C26466</t>
+          <t>C26539</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26466</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26539</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3543</v>
+        <v>3552</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>User Feedback Strings</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Full View: a user who can approve lines sees the 'Send to Portal' button</t>
+          <t>Reassigning a staff member's role updates the row with no success message (billing note in the window)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -10469,37 +10838,37 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Blocked-UI: Send to Portal was NOT found on the full-view (admin) lines page body; it is likely in the WO header more_vert menu or gated by WO state — needs the header action menu expanded to confirm.</t>
+          <t>Blocked-UI (needs live Staff page); billing note not re-captured this pass</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Send-to-Portal flow needs live UI.</t>
+          <t>No-toast-on-reassign + billing note need live Staff page (EditStaffMember chunk not fetched).</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C26479</t>
+          <t>C26540</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26479</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26540</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3545</v>
+        <v>3553</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>Cross-Permission Combinations</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data ON allows paying several invoices at once from the Unpaid Invoices tab</t>
+          <t>A role with all permissions off blocks the user from every feature</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -10509,37 +10878,37 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + live payment)</t>
+          <t>Blocked-UI (needs live role editor / roles list)</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Bulk payment needs live UI + payment (create-customer-payment 500s intermittently per prior run).</t>
+          <t>Needs seeded role.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>C26488</t>
+          <t>C26541</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26488</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26541</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3546</v>
+        <v>3553</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>View History Logs</t>
+          <t>Cross-Permission Combinations</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>View History Logs ON: work order history and line history are visible (work orders only)</t>
+          <t>A role with all permissions on behaves like Administrator but is still a custom role</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -10549,37 +10918,37 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); 'View History Logs' toggle build-verified</t>
+          <t>Blocked-UI (needs live role editor / roles list)</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Cross-toggle 'View History Logs' confirmed in build. History visibility needs live UI.</t>
+          <t>Needs seeded role.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C26489</t>
+          <t>C26544</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26489</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26544</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3546</v>
+        <v>3553</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>View History Logs</t>
+          <t>Cross-Permission Combinations</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>View History Logs OFF: work order history and line history are hidden (work orders only)</t>
+          <t>Being unable to open Customers does not stop a user from picking a customer when creating a work order</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -10589,37 +10958,37 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); labels build-verified</t>
+          <t>Blocked-UI (needs live role editor / roles list)</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>viewHistoryLogs also gates the 'Part History' page under Parts (build route metadata). History-hide needs live UI.</t>
+          <t>Needs seeded role.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C26490</t>
+          <t>C26545</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26490</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26545</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3547</v>
+        <v>3553</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Staff Page Role Assignment</t>
+          <t>Cross-Permission Combinations</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>The Staff role dropdown groups roles into System Roles and Custom Roles</t>
+          <t>A Page Access toggle that is off overrides the add/edit/delete boxes inside it</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -10629,37 +10998,37 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Blocked-UI: the Edit Staff Member Role dropdown (System/Custom grouping) was not reached — the staff row click opened Manage-staff-enrollments. Follow-up: locate the Edit Staff Member action, open the Role selector.</t>
+          <t>Blocked-UI (needs live role editor / roles list)</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>11 system roles confirmed in live roles list (was '12'). Grouping labels need live Staff page.</t>
+          <t>Needs seeded role.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>C26491</t>
+          <t>C26548</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26491</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26548</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>3547</v>
+        <v>3553</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Staff Page Role Assignment</t>
+          <t>Cross-Permission Combinations</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>The View Permissions button next to the role selector opens the Permission Summary</t>
+          <t>View off with Create &amp; Edit on is prevented by the tick-cascade</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -10669,37 +11038,37 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Blocked-UI: View Permissions eye next to the staff Role selector not reached (same Edit-Staff-Member surface as C26490).</t>
+          <t>Blocked-UI (needs live editor); cascade rule</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>'View Permissions' confirmed in build. Needs live Staff page.</t>
+          <t>Needs live editor; matches cascade rules.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>C26493</t>
+          <t>C26550</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26493</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26550</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3547</v>
+        <v>3553</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Staff Page Role Assignment</t>
+          <t>Cross-Permission Combinations</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>If a role change fails, the user keeps their previous role</t>
+          <t>The last Administrator cannot be left with zero users</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -10709,370 +11078,10 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Blocked-UI: forcing a failed role change (to confirm the user keeps the prior role) requires inducing a server error on /change; not reproducible on demand this pass.</t>
+          <t>Blocked-UI (needs live role editor / roles list)</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
-        <is>
-          <t>Failed-save path needs live UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>C26526</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26526</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>3550</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Staff Record Settings</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Whether a technician can be scheduled depends on their department, not their role</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs two seeded users + departments)</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Department-gated scheduling needs live UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>C26527</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26527</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>3550</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Staff Record Settings</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Clocking in on a work order line depends on the per-staff Time Clock setting</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs two seeded users)</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Per-staff Time Clock gating needs live UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>C26539</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26539</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>3552</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>User Feedback Strings</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Reassigning a staff member's role updates the row with no success message (billing note in the window)</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live Staff page); billing note not re-captured this pass</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>No-toast-on-reassign + billing note need live Staff page (EditStaffMember chunk not fetched).</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>C26540</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26540</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>A role with all permissions off blocks the user from every feature</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Needs seeded role.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>C26541</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26541</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>A role with all permissions on behaves like Administrator but is still a custom role</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Needs seeded role.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>C26544</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26544</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Being unable to open Customers does not stop a user from picking a customer when creating a work order</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Needs seeded role.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>C26545</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26545</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>A Page Access toggle that is off overrides the add/edit/delete boxes inside it</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Needs seeded role.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>C26548</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26548</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>View off with Create &amp; Edit on is prevented by the tick-cascade</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live editor); cascade rule</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Needs live editor; matches cascade rules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>C26550</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26550</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>The last Administrator cannot be left with zero users</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
         <is>
           <t>Needs live UI; invariant to confirm.</t>
         </is>
@@ -11154,15 +11163,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B84" r:id="rId83"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14454,17 +14454,17 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>UI (role WO Create&amp;Edit, no Delete): the WO list shows the New (create) button; a WO can be created/edited; the WO detail has no Delete option. screenshot wo-ce-nodelete.</t>
         </is>
       </c>
     </row>
@@ -14494,17 +14494,17 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>UI (role with Work Orders Delete): the work order header more_vert menu shows "Delete Work Order" (menu: Audit Log | Add Fee/Discount | Delete Work Order). Deletion action present for the Delete permission. screenshot wo-delete-role.</t>
         </is>
       </c>
     </row>
@@ -14534,17 +14534,17 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>UI (Sales Rep = no workOrdersView): the top nav has no Work Orders item (shows Reports etc); navigating to /workorders redirects to /reports. WO View OFF hides Work Orders from nav while other accessible items still show. screenshot salesrep-nav.</t>
         </is>
       </c>
     </row>
@@ -14619,7 +14619,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: with woReviewWorkOrders the WO/line showed no explicit Review/Approve action (header menu: Audit Log/Add Fee-Discount; line menu: Add line note/Story history/Audit log). The Review action likely requires a submitted line-authorization state to appear; needs seeding that authorization workflow to show toggle on vs off.</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -14659,7 +14659,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: Technician (woPickParts + WO View, no C&amp;E) shows Complete/Start on lines but no Pick action was visible on the test WO (parts already picked/requested). Needs a seeded pending pickable part-request state to display and exercise the Pick action.</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -14694,17 +14694,17 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Order parts+SFD dependency consistent with build (Order-parts enable-SFD modal). Behavior needs live UI.</t>
+          <t>UI (role woOrderParts + Work Orders View + See Financial Data, NO Create&amp;Edit): the WO Parts tab is accessible and Order parts works without Work Orders Create&amp;Edit. Order parts needs only WO View + SFD.</t>
         </is>
       </c>
     </row>
@@ -14774,17 +14774,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>UI (Time Clock User = Work Orders View only, no Create&amp;Edit): the WO list has no New (create) button and the WO detail has no New Line / create-edit affordances (header read-only). screenshot wo-timeclock-readonly.</t>
         </is>
       </c>
     </row>
@@ -14814,17 +14814,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>UI (role WO Create&amp;Edit WITHOUT Delete): the work order detail shows no Delete option anywhere (hasDelete=false).</t>
         </is>
       </c>
     </row>
@@ -14854,17 +14854,17 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>UI (role WO Create&amp;Edit, no Customers View): Customers is absent from top nav, but the New Work Order modal customer selector still opens and lists all customers (new test, 11 A new Company, A 2 Company, ...) — data reachable.</t>
         </is>
       </c>
     </row>
@@ -14894,17 +14894,17 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>UI (no Customers View): the customer name/contact shows on the work order header/detail even though Customers is hidden from nav (customer is part of the WO record).</t>
         </is>
       </c>
     </row>
@@ -15014,17 +15014,17 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Consistent with build (Order parts gates WO Parts tab). Needs live UI.</t>
+          <t>UI: Order parts controls the WO Parts tab — role WITH woOrderParts shows tabs Lines/Parts(7)/Notes/Stats (Parts tab present); the Technician role (woPickParts, no woOrderParts) showed Lines/Notes/Stats with NO Parts tab. On shows it, off hides it.</t>
         </is>
       </c>
     </row>
@@ -15059,7 +15059,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded roles + notes)</t>
+          <t>Blocked-UI: needs a customer note authored by a DIFFERENT user, then observe edit/delete affordance hidden for a role lacking the note permission — requires seeding a note as user A and viewing as user B; not reachable with single Tech identity this pass.</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -15099,7 +15099,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + WO)</t>
+          <t>Blocked-UI: the Part Requests tab (Order-Parts role) shows a Quantity column, but the inline quantity-edit interaction could not be triggered in this harness (cell-click did not open an editable input). Needs manual confirm that qty is editable.</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">

--- a/build/custom-roles-run/CustomRoles_WordingVIU_2026-07-13.xlsx
+++ b/build/custom-roles-run/CustomRoles_WordingVIU_2026-07-13.xlsx
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
         <v>1</v>
@@ -1157,7 +1157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H168"/>
+  <dimension ref="A1:H173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4815,12 +4815,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>C27740</t>
+          <t>C26420</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27740</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26420</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>The Invoicing &amp; payments delete column is labelled 'Delete / Reverse'</t>
+          <t>Invoicing &amp; payments View shows the Finance tab and lets the user see invoices</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4843,37 +4843,37 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>'Delete / Reverse' column confirmed in build (PermissionGrid).</t>
+          <t>UI (role Invoicing View + SFD, no C&amp;E/Delete): the WO Finance tab is shown and invoices can be opened; the Finance tab has NO create/edit/reverse buttons (view-only). screenshot inv-invView.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>C26429</t>
+          <t>C26421</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26429</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26421</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>The Timesheets card shows View and Create &amp; Edit only (no Delete)</t>
+          <t>Invoicing &amp; payments Create &amp; Edit lets the user create invoices and take payments</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4883,37 +4883,37 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Timesheets card title + 'Track and review technician labor hours and time entries.' + no Delete column build-verified (PermissionGrid).</t>
+          <t>UI (Service Advisor, Invoicing Create&amp;Edit): the WO Finance tab shows Create Invoice + Add Deposit actions (create invoices/take payments). screenshot inv-invCE.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>C26432</t>
+          <t>C26425</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26432</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26425</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Clock in / clock out is always available, whatever the Timesheets permission</t>
+          <t>See Financial Data OFF makes Invoicing &amp; payments inaccessible even with View, Create &amp; Edit and Delete</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4928,32 +4928,32 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>UI: the universal Clock In control (top bar "timer | Clock In") is present for the Time Clock User role, which has no Timesheets Create&amp;Edit — clock in/out is available regardless of the Timesheets permission.</t>
+          <t>UI/editor: See Financial Data OFF makes Invoicing &amp; payments inaccessible — SFD-off roles (e.g. Technician) show no Finance tab on the WO, and the editor forces SFD ON before Invoicing can be enabled (C26471/C26474). Invoicing is unreachable without SFD even with View/C&amp;E/Delete.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>C26435</t>
+          <t>C26426</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26435</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26426</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3541</v>
+        <v>3539</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Reports ON gives access to the Reports page with all reports (no per-report on/off)</t>
+          <t>Invoicing &amp; payments View OFF with See Financial Data ON: prices show but invoices are not reachable</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4968,32 +4968,32 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>UI (admin /reports): Reports appears in top nav; the Reports page lists ALL reports grouped by category (LABOR, PERFORMANCE, FINANCE, ACCOUNTS RECEIVABLE, ACCOUNTS PAYABLE, ACCOUNTING, COMMUNICATIONS) with no per-report on/off control — Reports is all-or-nothing. screenshot reports-admin.</t>
+          <t>UI (role SFD ON + WO C&amp;E, NO Invoicing View): the WO shows pricing/totals (SFD on) but the tabs are Lines/Notes/Stats — the Finance tab is hidden and invoices cannot be reached. screenshot inv-sfdNoInv.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>C26436</t>
+          <t>C26428</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26436</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26428</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3541</v>
+        <v>3539</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Reports OFF removes Reports from the top navigation</t>
+          <t>Taking Deposits on a work order needs Invoicing &amp; payments Create &amp; Edit</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5008,32 +5008,32 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>UI: the Technician role (no reportsPageAccess) has NO Reports item in the top navigation — Reports OFF removes Reports from nav.</t>
+          <t>UI: Taking Deposits needs Invoicing Create&amp;Edit — Add Deposit is shown for User B (Service Advisor, invoicing C&amp;E) and NOT shown for User A (Invoicing View-only).</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>C26441</t>
+          <t>C27740</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26441</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27740</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3542</v>
+        <v>3539</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Turning Settings ON reveals its sub-toggles</t>
+          <t>The Invoicing &amp; payments delete column is labelled 'Delete / Reverse'</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5043,37 +5043,37 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Verified-Label (build) — Integrations sub-toggle now present (was previously flagged missing)</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>PageAndSettingsToggles build chunk shows 7 Settings sub-toggles incl. Integrations. Prior 'Integrations missing' gap is resolved/built.</t>
+          <t>'Delete / Reverse' column confirmed in build (PermissionGrid).</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>C26442</t>
+          <t>C26429</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26442</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26429</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3542</v>
+        <v>3540</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Turning Settings OFF hides its sub-toggles</t>
+          <t>The Timesheets card shows View and Create &amp; Edit only (no Delete)</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5083,37 +5083,37 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>UI: with Settings off the 7 sub-toggles are absent; toggling Settings ON reveals App Settings/Service/Parts/Finance/Integrations/Data Import/View-Manage Wages.</t>
+          <t>Timesheets card title + 'Track and review technician labor hours and time entries.' + no Delete column build-verified (PermissionGrid).</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>C26443</t>
+          <t>C26432</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26443</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26432</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>3542</v>
+        <v>3540</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>A saved role with Settings OFF has no Settings area in the sidebar</t>
+          <t>Clock in / clock out is always available, whatever the Timesheets permission</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5128,32 +5128,32 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>UI: the Technician role (no settings* perms) has no Settings area in the sidebar — a saved role with Settings OFF has no Settings section.</t>
+          <t>UI: the universal Clock In control (top bar "timer | Clock In") is present for the Time Clock User role, which has no Timesheets Create&amp;Edit — clock in/out is available regardless of the Timesheets permission.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>C26444</t>
+          <t>C26435</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26444</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26435</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Turning Settings OFF then ON keeps the sub-toggle choices</t>
+          <t>Reports ON gives access to the Reports page with all reports (no per-report on/off)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5168,32 +5168,32 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>UI: turning Settings OFF then ON keeps the sub-toggle choices (App Settings + Finance stayed ON after the parent was toggled off then on).</t>
+          <t>UI (admin /reports): Reports appears in top nav; the Reports page lists ALL reports grouped by category (LABOR, PERFORMANCE, FINANCE, ACCOUNTS RECEIVABLE, ACCOUNTS PAYABLE, ACCOUNTING, COMMUNICATIONS) with no per-report on/off control — Reports is all-or-nothing. screenshot reports-admin.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>C27395</t>
+          <t>C26436</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27395</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26436</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Turning off the last Settings sub-toggle collapses the Settings section</t>
+          <t>Reports OFF removes Reports from the top navigation</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5208,32 +5208,32 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>UI: turning off the last remaining Settings sub-toggle (App Settings) collapses the Settings section — the parent Settings toggle goes off and the sub-toggles disappear.</t>
+          <t>UI: the Technician role (no reportsPageAccess) has NO Reports item in the top navigation — Reports OFF removes Reports from nav.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>C26452</t>
+          <t>C26441</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26452</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26441</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>The Work orders card has 'Full View' and 'Tech view' options</t>
+          <t>Turning Settings ON reveals its sub-toggles</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5243,37 +5243,37 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>Verified-Label (build) — Integrations sub-toggle now present (was previously flagged missing)</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>'View mode', 'Full View', 'Tech view' confirmed in build (WoSettingsRow).</t>
+          <t>PageAndSettingsToggles build chunk shows 7 Settings sub-toggles incl. Integrations. Prior 'Integrations missing' gap is resolved/built.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>C26453</t>
+          <t>C26442</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26453</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26442</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>The Full View description</t>
+          <t>Turning Settings OFF hides its sub-toggles</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5288,32 +5288,32 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>UI: Full View description reads "Complete interface with all fields visible and editable (subject to CRUD permissions). The estimate column shows the actual estimate value. Full parts request form with all fields. All workflow actions available (approve, review, split etc...)."</t>
+          <t>UI: with Settings off the 7 sub-toggles are absent; toggling Settings ON reveals App Settings/Service/Parts/Finance/Integrations/Data Import/View-Manage Wages.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>C26454</t>
+          <t>C26443</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26454</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26443</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>The Tech view description, and Tech view stays disabled until a Work orders permission is on</t>
+          <t>A saved role with Settings OFF has no Settings area in the sidebar</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5323,37 +5323,37 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Verified-Label (Tech view text build-verified); disabled-state needs live check</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Tech view description string confirmed verbatim in build (WoSettingsRow). Disabled-until-WO-perm needs live editor.</t>
+          <t>UI: the Technician role (no settings* perms) has no Settings area in the sidebar — a saved role with Settings OFF has no Settings section.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>C26455</t>
+          <t>C26444</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26455</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26444</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Tech view: the Estimate column shows the Tech Time value</t>
+          <t>Turning Settings OFF then ON keeps the sub-toggle choices</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5368,32 +5368,32 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>UI (Technician, tech view): WO lines Actual/Estimate column shows tech-time hours (e.g. 0.00 / 1.00, 0.00 / 1.50) and header "Total Tech Hours" — not a money estimate. screenshot techview-lines-estimate/approved.</t>
+          <t>UI: turning Settings OFF then ON keeps the sub-toggle choices (App Settings + Finance stayed ON after the parent was toggled off then on).</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>C26456</t>
+          <t>C27395</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26456</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27395</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Tech view: the tech time input field is hidden on work order lines</t>
+          <t>Turning off the last Settings sub-toggle collapses the Settings section</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5408,19 +5408,19 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>UI (tech view): no tech-time input field rendered on the WO lines for this user (0 tech-time inputs found).</t>
+          <t>UI: turning off the last remaining Settings sub-toggle (App Settings) collapses the Settings section — the parent Settings toggle goes off and the sub-toggles disappear.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>C26457</t>
+          <t>C26452</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26457</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26452</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Tech view: the user cannot approve work orders (no Approve button)</t>
+          <t>The Work orders card has 'Full View' and 'Tech view' options</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5443,24 +5443,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>UI (tech view): no Approve button anywhere on the work order (estimate and approved WOs both) — Technician lacks Review Work Orders.</t>
+          <t>'View mode', 'Full View', 'Tech view' confirmed in build (WoSettingsRow).</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>C26458</t>
+          <t>C26453</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26458</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26453</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Tech view: the user cannot approve work order lines</t>
+          <t>The Full View description</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5488,19 +5488,19 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>UI (tech view): no approve-line action on any line; line actions are tech-only (Complete / Story / Start), no approve control.</t>
+          <t>UI: Full View description reads "Complete interface with all fields visible and editable (subject to CRUD permissions). The estimate column shows the actual estimate value. Full parts request form with all fields. All workflow actions available (approve, review, split etc...)."</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>C26463</t>
+          <t>C26454</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26463</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26454</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>View mode only changes the look, not what the user is allowed to do</t>
+          <t>The Tech view description, and Tech view stays disabled until a Work orders permission is on</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5523,24 +5523,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (Tech view text build-verified); disabled-state needs live check</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>UI/enforcement: tech view is purely presentational — the tech-view role retains workOrderLinesCreateAndEdit and can add lines (New Line functional on the lines screen); data-level create/edit is governed by CRUD perms, not the view mode (estimate column renders as hours but edit capability persists).</t>
+          <t>Tech view description string confirmed verbatim in build (WoSettingsRow). Disabled-until-WO-perm needs live editor.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>C26465</t>
+          <t>C26455</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26465</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26455</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Tech view: the 'Send to Portal' button is hidden</t>
+          <t>Tech view: the Estimate column shows the Tech Time value</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5568,32 +5568,32 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>UI (tech view): the Send to Portal button is not shown anywhere on the work order (header, line, or action menus).</t>
+          <t>UI (Technician, tech view): WO lines Actual/Estimate column shows tech-time hours (e.g. 0.00 / 1.00, 0.00 / 1.50) and header "Total Tech Hours" — not a money estimate. screenshot techview-lines-estimate/approved.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>C26467</t>
+          <t>C26456</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26467</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26456</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>See Financial Data toggle appears in the Cross-Cutting Toggles card</t>
+          <t>Tech view: the tech time input field is hidden on work order lines</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5603,37 +5603,37 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Verified-Label (build); subtitle placeholder flagged</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Card 'Cross-Cutting Toggles' + toggle 'See Financial Data' confirmed in shipped build (CrossTogglesSection chunk). Reused subtitle string flagged.</t>
+          <t>UI (tech view): no tech-time input field rendered on the WO lines for this user (0 tech-time inputs found).</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>C26468</t>
+          <t>C26457</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26468</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26457</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>See Financial Data ON: prices, costs, margins and labor rates are shown</t>
+          <t>Tech view: the user cannot approve work orders (no Approve button)</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5648,32 +5648,32 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>UI: with See Financial Data ON (admin full view + TechSFD), WO lines show prices, costs, margins and labor rates — Rate ($100), Margin (%), Total ($261.54), parts prices ($3.33 etc), labor ($150). screenshot fullview-lines-admin/techview-sfd-lines.</t>
+          <t>UI (tech view): no Approve button anywhere on the work order (estimate and approved WOs both) — Technician lacks Review Work Orders.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>C26469</t>
+          <t>C26458</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26469</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26458</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>See Financial Data OFF: money amounts, rates, costs and margins are hidden</t>
+          <t>Tech view: the user cannot approve work order lines</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5688,32 +5688,32 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>UI: with See Financial Data OFF (plain Technician), WO lines show NO money — no $ amounts, no Rate/Margin/Total columns; only tech-time hours (0.00/1.00). screenshot techview-lines-estimate.</t>
+          <t>UI (tech view): no approve-line action on any line; line actions are tech-only (Complete / Story / Start), no approve control.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>C26470</t>
+          <t>C26463</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26470</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26463</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>With See Financial Data OFF, Part sales and Invoicing &amp; payments stay inaccessible even with View, Create &amp; Edit and Delete on</t>
+          <t>View mode only changes the look, not what the user is allowed to do</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5728,32 +5728,32 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>UI/editor enforcement: a role cannot hold Part sales or Invoicing &amp; payments with See Financial Data OFF — ticking either forces the "Enable See Financial Data?" dialog (C26471/C26474). So SFD OFF makes Part sales and Invoicing &amp; payments unreachable even if View/Create&amp;Edit/Delete were desired; the combination is prevented at save time.</t>
+          <t>UI/enforcement: tech view is purely presentational — the tech-view role retains workOrderLinesCreateAndEdit and can add lines (New Line functional on the lines screen); data-level create/edit is governed by CRUD perms, not the view mode (estimate column renders as hours but edit capability persists).</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>C26471</t>
+          <t>C26465</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26471</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26465</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ticking Part sales while See Financial Data is OFF asks you to turn See Financial Data on</t>
+          <t>Tech view: the 'Send to Portal' button is hidden</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5768,19 +5768,19 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>UI dialog: ticking Part sales while SFD off shows "Enable See Financial Data? — Part Sales requires See Financial Data. Enable it to grant this permission?" [Cancel|Enable].</t>
+          <t>UI (tech view): the Send to Portal button is not shown anywhere on the work order (header, line, or action menus).</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>C26472</t>
+          <t>C26467</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26472</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26467</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>'Enable See Financial Data?' dialog — Enable: turns See Financial Data on and keeps the box ticked</t>
+          <t>See Financial Data toggle appears in the Cross-Cutting Toggles card</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5803,24 +5803,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build); subtitle placeholder flagged</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>UI: Enable on the SFD dialog turns See Financial Data ON and keeps Part sales View+Create&amp;Edit ticked.</t>
+          <t>Card 'Cross-Cutting Toggles' + toggle 'See Financial Data' confirmed in shipped build (CrossTogglesSection chunk). Reused subtitle string flagged.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>C26473</t>
+          <t>C26468</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26473</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26468</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>'Enable See Financial Data?' dialog — Cancel: undoes the tick</t>
+          <t>See Financial Data ON: prices, costs, margins and labor rates are shown</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5848,19 +5848,19 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>UI: Cancel on the SFD dialog undoes the tick (See Financial Data off, Part sales off).</t>
+          <t>UI: with See Financial Data ON (admin full view + TechSFD), WO lines show prices, costs, margins and labor rates — Rate ($100), Margin (%), Total ($261.54), parts prices ($3.33 etc), labor ($150). screenshot fullview-lines-admin/techview-sfd-lines.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>C26474</t>
+          <t>C26469</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26474</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26469</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>The same 'Enable See Financial Data?' dialog appears for Invoicing &amp; payments when See Financial Data is OFF</t>
+          <t>See Financial Data OFF: money amounts, rates, costs and margins are hidden</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5888,19 +5888,19 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>UI dialog: ticking Invoicing &amp; payments while SFD off shows "Enable See Financial Data? — Invoicing &amp; Payments requires See Financial Data..." [Cancel|Enable]; Enable -&gt; SFD ON + Invoicing View+C&amp;E ON.</t>
+          <t>UI: with See Financial Data OFF (plain Technician), WO lines show NO money — no $ amounts, no Rate/Margin/Total columns; only tech-time hours (0.00/1.00). screenshot techview-lines-estimate.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>C26475</t>
+          <t>C26470</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26475</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26470</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Turning See Financial Data OFF asks you to also turn off the settings that depend on it</t>
+          <t>With See Financial Data OFF, Part sales and Invoicing &amp; payments stay inaccessible even with View, Create &amp; Edit and Delete on</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5928,19 +5928,19 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>UI (RUN331 FAIL NOW FIXED): turning See Financial Data OFF while Invoicing on shows "Disable See Financial Data? — Disabling See Financial Data will also disable Invoicing &amp; Payments. Continue?" [Cancel|Disable] (FinancialDataDisableConfirmModal). screenshot sfd-disable-dialog.</t>
+          <t>UI/editor enforcement: a role cannot hold Part sales or Invoicing &amp; payments with See Financial Data OFF — ticking either forces the "Enable See Financial Data?" dialog (C26471/C26474). So SFD OFF makes Part sales and Invoicing &amp; payments unreachable even if View/Create&amp;Edit/Delete were desired; the combination is prevented at save time.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>C27869</t>
+          <t>C26471</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27869</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26471</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Turning on Order parts while See Financial Data is OFF asks you to also turn on See Financial Data</t>
+          <t>Ticking Part sales while See Financial Data is OFF asks you to turn See Financial Data on</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5968,32 +5968,32 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>UI dialog: ticking Order parts while SFD off shows "Enable See Financial Data? — Order Parts requires See Financial Data. Enable it to grant this permission?" [Cancel|Enable].</t>
+          <t>UI dialog: ticking Part sales while SFD off shows "Enable See Financial Data? — Part Sales requires See Financial Data. Enable it to grant this permission?" [Cancel|Enable].</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>C26476</t>
+          <t>C26472</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26476</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26472</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data ON shows the Unpaid Invoices, Payments and Credits tabs on a customer</t>
+          <t>'Enable See Financial Data?' dialog — Enable: turns See Financial Data on and keeps the box ticked</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6008,32 +6008,32 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>UI: role with AP/AR Data ON shows the financial tabs on a customer page — build labels are Invoices / Payments / Deposits (case prose says Unpaid Invoices/Payments/Credits; the AP/AR toggle description uses that wording, actual tab labels are Invoices/Payments/Deposits). Tabs absent when AP/AR off.</t>
+          <t>UI: Enable on the SFD dialog turns See Financial Data ON and keeps Part sales View+Create&amp;Edit ticked.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>C26477</t>
+          <t>C26473</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26477</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26473</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data ON shows the same three tabs on a vendor</t>
+          <t>'Enable See Financial Data?' dialog — Cancel: undoes the tick</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -6048,32 +6048,32 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>UI (Parts Manager, AP/AR ON): the vendor page (/parts/vendor/{id}) shows the AP/AR tabs — Contacts, Unpaid Invoices (30), Payments (4). screenshot vendordetail-vendON.</t>
+          <t>UI: Cancel on the SFD dialog undoes the tick (See Financial Data off, Part sales off).</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>C26478</t>
+          <t>C26474</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26478</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26474</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>With Reports ON, all 6 AP/AR aging reports are listed (whether or not AP/AR is on)</t>
+          <t>The same 'Enable See Financial Data?' dialog appears for Invoicing &amp; payments when See Financial Data is OFF</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6088,32 +6088,32 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>UI (admin /reports, Reports ON): all 6 AP/AR aging reports are listed — A/R Aging Summary, A/R Aging Detail, A/R Aging Collection, A/P Aging Summary, A/P Aging Detail, A/P Unpaid Invoices. screenshot reports-admin.</t>
+          <t>UI dialog: ticking Invoicing &amp; payments while SFD off shows "Enable See Financial Data? — Invoicing &amp; Payments requires See Financial Data..." [Cancel|Enable]; Enable -&gt; SFD ON + Invoicing View+C&amp;E ON.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>C26480</t>
+          <t>C26475</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26480</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26475</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data OFF hides the three tabs on a customer</t>
+          <t>Turning See Financial Data OFF asks you to also turn off the settings that depend on it</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -6128,32 +6128,32 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>UI: AP/AR Data OFF (Service Advisor) — the customer page shows only Work Orders/Part Sales/Contacts/Assets/Notes; the Invoices/Payments/Deposits tabs are hidden.</t>
+          <t>UI (RUN331 FAIL NOW FIXED): turning See Financial Data OFF while Invoicing on shows "Disable See Financial Data? — Disabling See Financial Data will also disable Invoicing &amp; Payments. Continue?" [Cancel|Disable] (FinancialDataDisableConfirmModal). screenshot sfd-disable-dialog.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>C26481</t>
+          <t>C27869</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26481</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27869</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data OFF hides the three tabs on a vendor</t>
+          <t>Turning on Order parts while See Financial Data is OFF asks you to also turn on See Financial Data</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6168,19 +6168,19 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>UI (Service Advisor, AP/AR OFF): the same vendor page shows only the Contacts tab — Unpaid Invoices/Payments tabs are hidden. screenshot vendordetail-vendOFF.</t>
+          <t>UI dialog: ticking Order parts while SFD off shows "Enable See Financial Data? — Order Parts requires See Financial Data. Enable it to grant this permission?" [Cancel|Enable].</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>C26482</t>
+          <t>C26476</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26482</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26476</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>With AP/AR OFF but Reports ON, all 6 AP/AR aging reports are still listed</t>
+          <t>View and Manage AP/AR Data ON shows the Unpaid Invoices, Payments and Credits tabs on a customer</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6208,19 +6208,19 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>UI (RUN331 FAIL NOW FIXED): a role with Reports ON but View and Manage AP/AR Data OFF (ZZAUTOTEST ReportsNoAPAR) still sees all 6 AP/AR aging reports on /reports (A/R Aging Summary/Detail/Collection, A/P Aging Summary/Detail, A/P Unpaid Invoices). Aging reports follow the Reports permission, not AP/AR. screenshot reports-noapar.</t>
+          <t>UI: role with AP/AR Data ON shows the financial tabs on a customer page — build labels are Invoices / Payments / Deposits (case prose says Unpaid Invoices/Payments/Credits; the AP/AR toggle description uses that wording, actual tab labels are Invoices/Payments/Deposits). Tabs absent when AP/AR off.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>C26483</t>
+          <t>C26477</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26483</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26477</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data OFF hides the sensitive money fields on Edit Customer</t>
+          <t>View and Manage AP/AR Data ON shows the same three tabs on a vendor</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6248,19 +6248,19 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>UI: AP/AR Data OFF hides the sensitive money fields on Edit Customer (Credit Limit, Taxes, Default Labor Rate, Default Shop Supplies, Min, Max, Credit Terms) — same observation as C26402.</t>
+          <t>UI (Parts Manager, AP/AR ON): the vendor page (/parts/vendor/{id}) shows the AP/AR tabs — Contacts, Unpaid Invoices (30), Payments (4). screenshot vendordetail-vendON.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>C26484</t>
+          <t>C26478</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26484</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26478</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data OFF still lets a user create invoices and take payments if Invoicing &amp; payments allows it</t>
+          <t>With Reports ON, all 6 AP/AR aging reports are listed (whether or not AP/AR is on)</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6288,19 +6288,19 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>UI/perms: AP/AR Data OFF still allows creating invoices/taking payments when Invoicing allows — Service Advisor has invoicingPaymentsCreateAndEdit+Delete with AP/AR off; invoicing capability is independent of AP/AR.</t>
+          <t>UI (admin /reports, Reports ON): all 6 AP/AR aging reports are listed — A/R Aging Summary, A/R Aging Detail, A/R Aging Collection, A/P Aging Summary, A/P Aging Detail, A/P Unpaid Invoices. screenshot reports-admin.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>C26485</t>
+          <t>C26480</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26485</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26480</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data works independently of See Financial Data</t>
+          <t>View and Manage AP/AR Data OFF hides the three tabs on a customer</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6328,19 +6328,19 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>UI: See Financial Data and View and Manage AP/AR Data are separate Cross-Cutting Toggles (both present independently alongside View History Logs); AP/AR is not tied to SFD in the editor.</t>
+          <t>UI: AP/AR Data OFF (Service Advisor) — the customer page shows only Work Orders/Part Sales/Contacts/Assets/Notes; the Invoices/Payments/Deposits tabs are hidden.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>C26486</t>
+          <t>C26481</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26486</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26481</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data OFF does not block any add/edit/delete area</t>
+          <t>View and Manage AP/AR Data OFF hides the three tabs on a vendor</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6368,32 +6368,32 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>UI: AP/AR Data OFF does not block any add/edit/delete — Service Advisor (AP/AR off) still opens the editable Edit Customer modal and retains full customer/WO/parts create-edit; only the financial tabs/fields are hidden.</t>
+          <t>UI (Service Advisor, AP/AR OFF): the same vendor page shows only the Contacts tab — Unpaid Invoices/Payments tabs are hidden. screenshot vendordetail-vendOFF.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>C26492</t>
+          <t>C26482</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26492</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26482</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3547</v>
+        <v>3545</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Staff Page Role Assignment</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Changing a user's role logs them out immediately</t>
+          <t>With AP/AR OFF but Reports ON, all 6 AP/AR aging reports are still listed</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6408,32 +6408,32 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>API/session: changing a user role logs them out immediately — the prior session is invalidated (409 Session has expired) right after the change.</t>
+          <t>UI (RUN331 FAIL NOW FIXED): a role with Reports ON but View and Manage AP/AR Data OFF (ZZAUTOTEST ReportsNoAPAR) still sees all 6 AP/AR aging reports on /reports (A/R Aging Summary/Detail/Collection, A/P Aging Summary/Detail, A/P Unpaid Invoices). Aging reports follow the Reports permission, not AP/AR. screenshot reports-noapar.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>C26494</t>
+          <t>C26483</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26494</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26483</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>3547</v>
+        <v>3545</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Staff Page Role Assignment</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>A logged-in user is logged out immediately when their role changes</t>
+          <t>View and Manage AP/AR Data OFF hides the sensitive money fields on Edit Customer</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6448,32 +6448,32 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>API/session: a logged-in user is logged out immediately when their role changes (session invalidated -&gt; 409 on next request).</t>
+          <t>UI: AP/AR Data OFF hides the sensitive money fields on Edit Customer (Credit Limit, Taxes, Default Labor Rate, Default Shop Supplies, Min, Max, Credit Terms) — same observation as C26402.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>C26495</t>
+          <t>C26484</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26495</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26484</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Administrator: role permissions match the expected set</t>
+          <t>View and Manage AP/AR Data OFF still lets a user create invoices and take payments if Invoicing &amp; payments allows it</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6483,37 +6483,37 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Administrator permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI/perms: AP/AR Data OFF still allows creating invoices/taking payments when Invoicing allows — Service Advisor has invoicingPaymentsCreateAndEdit+Delete with AP/AR off; invoicing capability is independent of AP/AR.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>C26496</t>
+          <t>C26485</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26496</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26485</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Service Manager: role permissions match the expected set</t>
+          <t>View and Manage AP/AR Data works independently of See Financial Data</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6523,37 +6523,37 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Service Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI: See Financial Data and View and Manage AP/AR Data are separate Cross-Cutting Toggles (both present independently alongside View History Logs); AP/AR is not tied to SFD in the editor.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>C26497</t>
+          <t>C26486</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26497</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26486</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Senior Service Advisor: role permissions match the expected set</t>
+          <t>View and Manage AP/AR Data OFF does not block any add/edit/delete area</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6563,37 +6563,37 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Senior Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI: AP/AR Data OFF does not block any add/edit/delete — Service Advisor (AP/AR off) still opens the editable Edit Customer modal and retains full customer/WO/parts create-edit; only the financial tabs/fields are hidden.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>C26498</t>
+          <t>C26492</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26498</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26492</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Service Advisor: role permissions match the expected set</t>
+          <t>Changing a user's role logs them out immediately</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6603,37 +6603,37 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>API/session: changing a user role logs them out immediately — the prior session is invalidated (409 Session has expired) right after the change.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>C26499</t>
+          <t>C26494</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26499</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26494</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Foreman: role permissions match the expected set</t>
+          <t>A logged-in user is logged out immediately when their role changes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6643,24 +6643,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Foreman permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>API/session: a logged-in user is logged out immediately when their role changes (session invalidated -&gt; 409 on next request).</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>C26500</t>
+          <t>C26495</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26500</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26495</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Technician: role permissions match the expected set</t>
+          <t>Administrator: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6688,19 +6688,19 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Administrator permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>C26501</t>
+          <t>C26496</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26501</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26496</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Parts Manager: role permissions match the expected set</t>
+          <t>Service Manager: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6728,19 +6728,19 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Parts Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Service Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>C26502</t>
+          <t>C26497</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26502</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26497</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Parts Technician: role permissions match the expected set</t>
+          <t>Senior Service Advisor: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6768,19 +6768,19 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Parts Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Senior Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>C26503</t>
+          <t>C26498</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26503</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26498</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Office User: role permissions match the expected set</t>
+          <t>Service Advisor: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6808,19 +6808,19 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Office User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>C26504</t>
+          <t>C26499</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26504</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26499</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Sales Representative: role permissions match the expected set</t>
+          <t>Foreman: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6848,19 +6848,19 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Sales Representative permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Foreman permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>C26505</t>
+          <t>C26500</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26505</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26500</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Time Clock User: role permissions match the expected set</t>
+          <t>Technician: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6888,19 +6888,19 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Time Clock User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>C26506</t>
+          <t>C26501</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26506</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26501</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Customer portal is on by default only for Service Advisor, Senior Service Advisor, Service Manager and Parts Manager (and Administrator)</t>
+          <t>Parts Manager: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6923,37 +6923,37 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (matches live per-role customerPortalPageAccess)</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>customerPortalPageAccess per role confirmed live: on for Admin/SM/SSA/SA/PM; off for the rest (roles-matrix-2026-07-13).</t>
+          <t>Parts Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>C26510</t>
+          <t>C26502</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26510</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26502</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Legacy 'Admin / Administrator' users become 'Administrator' after migration</t>
+          <t>Parts Technician: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -6963,37 +6963,37 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Live roles API: destination system role exists = "Admin" (build name; case prose says Administrator), isEditable=true, 89 users, 42 perms. Migration is a completed historical event; destination state verified (role present, editable with pencil, populated).</t>
+          <t>Parts Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>C26511</t>
+          <t>C26503</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26511</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26503</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Legacy 'Office' users become 'Office User' after migration</t>
+          <t>Office User: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -7003,37 +7003,37 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Live roles API: "Office User" exists, isEditable=false (lock + eye only), 5 users, 23 perms — matches legacy Office -&gt; Office User destination.</t>
+          <t>Office User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>C26512</t>
+          <t>C26504</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26512</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26504</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Legacy 'Time Clock' users become 'Time Clock User' after migration</t>
+          <t>Sales Representative: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -7043,37 +7043,37 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Live roles API: "Time Clock User" exists, isEditable=false (lock + eye only), 11 users, 3 perms — matches legacy Time Clock -&gt; Time Clock User.</t>
+          <t>Sales Representative permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>C26513</t>
+          <t>C26505</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26513</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26505</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Legacy 'Service Manager' users become 'Service Manager' after migration</t>
+          <t>Time Clock User: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -7083,37 +7083,37 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Live roles API: "Service Manager" exists, isEditable=true, 3 users, 35 perms.</t>
+          <t>Time Clock User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>C26514</t>
+          <t>C26506</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26514</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26506</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Legacy 'Senior Service Advisor' users become 'Senior Service Advisor' after migration</t>
+          <t>Customer portal is on by default only for Service Advisor, Senior Service Advisor, Service Manager and Parts Manager (and Administrator)</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -7123,24 +7123,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (matches live per-role customerPortalPageAccess)</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Live roles API: "Senior Service Advisor" exists, isEditable=true, 8 users, 32 perms.</t>
+          <t>customerPortalPageAccess per role confirmed live: on for Admin/SM/SSA/SA/PM; off for the rest (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>C26515</t>
+          <t>C26510</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26515</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26510</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Legacy 'Service Advisor' users become 'Service Advisor' after migration</t>
+          <t>Legacy 'Admin / Administrator' users become 'Administrator' after migration</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -7168,19 +7168,19 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Live roles API: "Service Advisor" exists, isEditable=true, 2 users, 26 perms.</t>
+          <t>Live roles API: destination system role exists = "Admin" (build name; case prose says Administrator), isEditable=true, 89 users, 42 perms. Migration is a completed historical event; destination state verified (role present, editable with pencil, populated).</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>C26516</t>
+          <t>C26511</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26516</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26511</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Legacy 'Foreman' users become 'Foreman' after migration</t>
+          <t>Legacy 'Office' users become 'Office User' after migration</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -7208,19 +7208,19 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Live roles API: "Foreman" exists, isEditable=true, 16 users, 23 perms.</t>
+          <t>Live roles API: "Office User" exists, isEditable=false (lock + eye only), 5 users, 23 perms — matches legacy Office -&gt; Office User destination.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>C26517</t>
+          <t>C26512</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26517</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26512</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Legacy 'Technician' users become 'Technician' after migration</t>
+          <t>Legacy 'Time Clock' users become 'Time Clock User' after migration</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -7248,19 +7248,19 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Live roles API: "Technician" exists, isEditable=true, 66 users, 6 perms, view_mode tech (confirmed via role detail) — matches legacy Technician destination.</t>
+          <t>Live roles API: "Time Clock User" exists, isEditable=false (lock + eye only), 11 users, 3 perms — matches legacy Time Clock -&gt; Time Clock User.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>C26518</t>
+          <t>C26513</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26518</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26513</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Legacy 'Parts Manager' users become 'Parts Manager' after migration</t>
+          <t>Legacy 'Service Manager' users become 'Service Manager' after migration</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -7288,19 +7288,19 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Live roles API: "Parts Manager" exists, isEditable=true, 4 users, 31 perms.</t>
+          <t>Live roles API: "Service Manager" exists, isEditable=true, 3 users, 35 perms.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>C26519</t>
+          <t>C26514</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26519</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26514</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Legacy 'Parts Tech / Parts Technician' users become 'Parts Technician' after migration</t>
+          <t>Legacy 'Senior Service Advisor' users become 'Senior Service Advisor' after migration</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -7328,19 +7328,19 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Live roles API: "Parts Technician" exists, isEditable=true, 10 users, 19 perms — matches legacy Parts Tech -&gt; Parts Technician.</t>
+          <t>Live roles API: "Senior Service Advisor" exists, isEditable=true, 8 users, 32 perms.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>C26520</t>
+          <t>C26515</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26520</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26515</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Legacy 'Sales Representative' users become 'Sales Representative' after migration</t>
+          <t>Legacy 'Service Advisor' users become 'Service Advisor' after migration</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -7368,19 +7368,19 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Live roles API: "Sales Representative" exists, isEditable=true, 15 users, 4 perms.</t>
+          <t>Live roles API: "Service Advisor" exists, isEditable=true, 2 users, 26 perms.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>C26525</t>
+          <t>C26516</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26525</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26516</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Changing a user's role logs that user out and forces them to log in again</t>
+          <t>Legacy 'Foreman' users become 'Foreman' after migration</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -7408,32 +7408,32 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>UI/API: after an admin changed the Tech user role, the user existing session returned 409 "Session has expired." on the next call — the role change logs the user out and forces re-login.</t>
+          <t>Live roles API: "Foreman" exists, isEditable=true, 16 users, 23 perms.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>C26528</t>
+          <t>C26517</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26528</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26517</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Staff Record Settings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>The universal clock in / out is available to any active staff member, whatever their role</t>
+          <t>Legacy 'Technician' users become 'Technician' after migration</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -7448,32 +7448,32 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>UI: the universal Clock In control appears in the top bar for every role observed (Admin, Technician, Time Clock User) — available to any active staff member whatever their role.</t>
+          <t>Live roles API: "Technician" exists, isEditable=true, 66 users, 6 perms, view_mode tech (confirmed via role detail) — matches legacy Technician destination.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>C26532</t>
+          <t>C26518</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26532</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26518</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Create success message wording</t>
+          <t>Legacy 'Parts Manager' users become 'Parts Manager' after migration</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -7483,37 +7483,37 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>'Role created successfully.' confirmed in build.</t>
+          <t>Live roles API: "Parts Manager" exists, isEditable=true, 4 users, 31 perms.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>C26533</t>
+          <t>C26519</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26533</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26519</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Update success message wording</t>
+          <t>Legacy 'Parts Tech / Parts Technician' users become 'Parts Technician' after migration</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -7523,37 +7523,37 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>'Role updated successfully.' confirmed in build.</t>
+          <t>Live roles API: "Parts Technician" exists, isEditable=true, 10 users, 19 perms — matches legacy Parts Tech -&gt; Parts Technician.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>C26534</t>
+          <t>C26520</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26534</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26520</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Deleting a custom role with 0 users shows a confirmation dialog</t>
+          <t>Legacy 'Sales Representative' users become 'Sales Representative' after migration</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -7568,32 +7568,32 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>UI: deleting a 0-user custom role opens dialog "Confirmation — Are you sure you want to delete this role? This action cannot be undone." [Cancel|Delete]. screenshot delete-confirm-dialog.</t>
+          <t>Live roles API: "Sales Representative" exists, isEditable=true, 15 users, 4 perms.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>C26535</t>
+          <t>C26525</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26535</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26525</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Deleting a custom role that has users is blocked</t>
+          <t>Changing a user's role logs that user out and forces them to log in again</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -7608,32 +7608,32 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>UI: a custom role with users (Parth Cust1, 1 user) has no Delete option in its 3-dot menu — deletion is blocked.</t>
+          <t>UI/API: after an admin changed the Tech user role, the user existing session returned 409 "Session has expired." on the next call — the role change logs the user out and forces re-login.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>C26536</t>
+          <t>C26528</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26536</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26528</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>3552</v>
+        <v>3550</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Staff Record Settings</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Turning See Financial Data on shows a confirmation dialog</t>
+          <t>The universal clock in / out is available to any active staff member, whatever their role</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -7643,24 +7643,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>'Enable See Financial Data?' + Cancel/Enable confirmed in build (FinancialDataConfirmModal).</t>
+          <t>UI: the universal Clock In control appears in the top bar for every role observed (Admin, Technician, Time Clock User) — available to any active staff member whatever their role.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>C26537</t>
+          <t>C26532</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26537</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26532</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -7673,7 +7673,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Creating a role with no name is blocked with a required-field error</t>
+          <t>Create success message wording</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -7683,24 +7683,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>UI: creating a role with no name is blocked — Create disabled and inline "Role name is a required field" error when the field is touched/cleared.</t>
+          <t>'Role created successfully.' confirmed in build.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>C26538</t>
+          <t>C26533</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26538</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26533</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Creating a role with the same permissions as an existing role shows a 'similar role' warning</t>
+          <t>Update success message wording</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -7723,37 +7723,37 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>UI: creating a role with the same permissions as an existing role shows "Similar role already exists" warning with "Create Anyway" (SimilarRoleWarningModal, keyed on identical permissions).</t>
+          <t>'Role updated successfully.' confirmed in build.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>C26542</t>
+          <t>C26534</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26542</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26534</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Cross-Permission Combinations</t>
+          <t>User Feedback Strings</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>A system role cannot be deleted</t>
+          <t>Deleting a custom role with 0 users shows a confirmation dialog</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -7763,37 +7763,37 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (all system roles deletable=false)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>deletable=false for all system roles (live roles API).</t>
+          <t>UI: deleting a 0-user custom role opens dialog "Confirmation — Are you sure you want to delete this role? This action cannot be undone." [Cancel|Delete]. screenshot delete-confirm-dialog.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>C26543</t>
+          <t>C26535</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26543</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26535</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Cross-Permission Combinations</t>
+          <t>User Feedback Strings</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Only Office User and Time Clock User are non-editable; every other system role (including Administrator) is editable</t>
+          <t>Deleting a custom role that has users is blocked</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -7803,37 +7803,37 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (editable flags match live)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Live roles API: Office User &amp; Time Clock User editable=false; all others (incl. Administrator) editable=true.</t>
+          <t>UI: a custom role with users (Parth Cust1, 1 user) has no Delete option in its 3-dot menu — deletion is blocked.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>C26549</t>
+          <t>C26536</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26549</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26536</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Cross-Permission Combinations</t>
+          <t>User Feedback Strings</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AP/AR OFF hides the sensitive customer fields on both the Edit Customer window and the customer overview</t>
+          <t>Turning See Financial Data on shows a confirmation dialog</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -7843,50 +7843,250 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>UI: AP/AR Data OFF hides the sensitive customer fields on the Edit Customer modal (and the financial tabs on the customer overview) — confirmed via Service Advisor (off) vs CustAPAR (on).</t>
+          <t>'Enable See Financial Data?' + Cancel/Enable confirmed in build (FinancialDataConfirmModal).</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
+          <t>C26537</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26537</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>3552</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>User Feedback Strings</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Creating a role with no name is blocked with a required-field error</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>UI: creating a role with no name is blocked — Create disabled and inline "Role name is a required field" error when the field is touched/cleared.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>C26538</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26538</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>3552</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>User Feedback Strings</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Creating a role with the same permissions as an existing role shows a 'similar role' warning</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>UI: creating a role with the same permissions as an existing role shows "Similar role already exists" warning with "Create Anyway" (SimilarRoleWarningModal, keyed on identical permissions).</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>C26542</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26542</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>A system role cannot be deleted</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Roles-API-Verified (all system roles deletable=false)</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>deletable=false for all system roles (live roles API).</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>C26543</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26543</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Only Office User and Time Clock User are non-editable; every other system role (including Administrator) is editable</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Roles-API-Verified (editable flags match live)</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Live roles API: Office User &amp; Time Clock User editable=false; all others (incl. Administrator) editable=true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>C26549</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26549</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>AP/AR OFF hides the sensitive customer fields on both the Edit Customer window and the customer overview</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>UI: AP/AR Data OFF hides the sensitive customer fields on the Edit Customer modal (and the financial tabs on the customer overview) — confirmed via Service Advisor (off) vs CustAPAR (on).</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
           <t>C26551</t>
         </is>
       </c>
-      <c r="B168" s="4" t="inlineStr">
+      <c r="B173" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/26551</t>
         </is>
       </c>
-      <c r="C168" t="n">
+      <c r="C173" t="n">
         <v>3553</v>
       </c>
-      <c r="D168" t="inlineStr">
+      <c r="D173" t="inlineStr">
         <is>
           <t>Cross-Permission Combinations</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
+      <c r="E173" t="inlineStr">
         <is>
           <t>Universal clock in/out works even for a user whose role has (almost) no permissions</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
         <is>
           <t>UI: the Time Clock User role (only 3 perms: scheduleView/timesheetsView/workOrdersView) still shows the universal Clock In control — universal clock in is not gated by role/permissions.</t>
         </is>
@@ -8061,6 +8261,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B166" r:id="rId165"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B167" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B173" r:id="rId172"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8072,7 +8277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9170,12 +9375,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C26420</t>
+          <t>C26422</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26420</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26422</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -9188,7 +9393,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Invoicing &amp; payments View shows the Finance tab and lets the user see invoices</t>
+          <t>Invoicing &amp; payments Delete lets the user delete payments and void transactions (but not reverse invoices)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -9198,7 +9403,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Blocked-UI: the Invoicing &amp; payments / Finance surface route was not confirmed (/invoices returned minimal content for the Viewer role). Follow-up: locate the Finance tab/invoices route and confirm invoicingPaymentsView access.</t>
+          <t>Blocked-UI: per-payment delete/void affordance not located on the WO Finance tab in the harness (payment rows/menus did not expose a delete/void control); needs the invoice-&gt;payment detail view with a with/without invoicingPaymentsDelete contrast.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -9210,12 +9415,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C26421</t>
+          <t>C26423</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26421</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26423</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -9228,7 +9433,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Invoicing &amp; payments Create &amp; Edit lets the user create invoices and take payments</t>
+          <t>Deleting a customer payment needs Invoicing &amp; payments Delete, not Customers Delete</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -9238,7 +9443,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: deleting a customer payment (gated by Invoicing Delete not Customers Delete) needs the payment delete control located; the Finance-tab payment row menu was not reachable this pass.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -9250,12 +9455,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C26422</t>
+          <t>C26427</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26422</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26427</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -9268,7 +9473,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Invoicing &amp; payments Delete lets the user delete payments and void transactions (but not reverse invoices)</t>
+          <t>The Send to Terminal action needs Invoicing &amp; payments Create &amp; Edit</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -9278,7 +9483,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: Send to Terminal was not shown at the WO Finance-tab level even for a role with Invoicing C&amp;E + Customer Portal (Service Advisor); it appears within the take-payment flow on an open invoice — needs seeding an open invoice + entering the payment dialog.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -9290,12 +9495,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C26423</t>
+          <t>C27871</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26423</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27871</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -9308,7 +9513,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deleting a customer payment needs Invoicing &amp; payments Delete, not Customers Delete</t>
+          <t>Deleting or cancelling a return is controlled by Invoicing &amp; payments Delete</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -9318,24 +9523,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: deleting/cancelling a return (gated by Invoicing Delete) needs a part return seeded first (create return via admin) then observe the delete/cancel gate; return flow not seeded this pass.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded; SV-ref/element-id jargon stripped.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>C26425</t>
+          <t>C29434</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26425</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29434</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -9348,7 +9553,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>See Financial Data OFF makes Invoicing &amp; payments inaccessible even with View, Create &amp; Edit and Delete</t>
+          <t>Send to Terminal needs Invoicing &amp; payments Create &amp; Edit AND Customer portal ON</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -9358,24 +9563,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: same as C26427 — Send to Terminal (needs Invoicing C&amp;E AND Customer Portal) is in the payment dialog, not reached; needs an open invoice + payment flow to observe both-gates.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded; feature-flag/element-id/SV jargon stripped.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>C26426</t>
+          <t>C29438</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26426</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29438</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -9388,7 +9593,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Invoicing &amp; payments View OFF with See Financial Data ON: prices show but invoices are not reachable</t>
+          <t>Invoicing &amp; payments Create &amp; Edit gives the edit control on the work order Financial Info card</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -9398,37 +9603,37 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: the WO Financial Info card is present but no edit control was detected for either an Invoicing-C&amp;E role or a view-only role on a PAID WO (balance $0, editing locked). Needs an open/unpaid WO with a balance to observe the C&amp;E edit control.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded; element-id/SV jargon stripped.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>C26427</t>
+          <t>C26430</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26427</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26430</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>The Send to Terminal action needs Invoicing &amp; payments Create &amp; Edit</t>
+          <t>Timesheets View only: timesheet entries are read-only</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -9443,32 +9648,32 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Read-only behavior needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>C26428</t>
+          <t>C26431</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26428</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26431</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Taking Deposits on a work order needs Invoicing &amp; payments Create &amp; Edit</t>
+          <t>Timesheets Create &amp; Edit lets the user edit entries</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -9483,32 +9688,32 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Edit behavior needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C27871</t>
+          <t>C26433</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27871</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26433</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Deleting or cancelling a return is controlled by Invoicing &amp; payments Delete</t>
+          <t>Timesheets View OFF with Reports ON: the timesheet activities report is still available</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -9518,37 +9723,37 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded roles + returns)</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Reworded; SV-ref/element-id jargon stripped.</t>
+          <t>Report access needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C29434</t>
+          <t>C26434</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29434</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26434</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Send to Terminal needs Invoicing &amp; payments Create &amp; Edit AND Customer portal ON</t>
+          <t>All Timesheets permissions OFF and Reports OFF: no timesheet navigation anywhere</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -9558,37 +9763,37 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded roles + terminal)</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Reworded; feature-flag/element-id/SV jargon stripped.</t>
+          <t>Nav-hide needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C29438</t>
+          <t>C27394</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29438</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27394</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Invoicing &amp; payments Create &amp; Edit gives the edit control on the work order Financial Info card</t>
+          <t>A clock-capable role without Timesheets View can still see and open My Timesheets</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -9598,37 +9803,37 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + WO)</t>
+          <t>Blocked-UI (needs seeded clock-capable role)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Reworded; element-id/SV jargon stripped.</t>
+          <t>Reworded, jargon stripped; needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C26430</t>
+          <t>C26437</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26430</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26437</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3540</v>
+        <v>3541</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Timesheets View only: timesheet entries are read-only</t>
+          <t>Customer portal ON lets the user manage the customer portal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -9638,37 +9843,37 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role); toggle label 'Customer portal' build-verified</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Read-only behavior needs live UI.</t>
+          <t>Toggle 'Customer portal' confirmed in build. Manage behavior needs live check.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C26431</t>
+          <t>C26438</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26431</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26438</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3540</v>
+        <v>3541</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Timesheets Create &amp; Edit lets the user edit entries</t>
+          <t>Customer portal OFF hides the customer portal from navigation</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -9683,32 +9888,32 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Edit behavior needs live UI.</t>
+          <t>Nav-hide needs live check.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C26433</t>
+          <t>C26439</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26433</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26439</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3540</v>
+        <v>3541</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Timesheets View OFF with Reports ON: the timesheet activities report is still available</t>
+          <t>Billing Portal ON lets the user manage the billing portal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -9718,37 +9923,37 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role); toggle label 'Billing Portal' build-verified</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Report access needs live UI.</t>
+          <t>Toggle 'Billing Portal' confirmed in build. Manage behavior needs live check.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C26434</t>
+          <t>C26440</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26434</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26440</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3540</v>
+        <v>3541</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>All Timesheets permissions OFF and Reports OFF: no timesheet navigation anywhere</t>
+          <t>Billing Portal OFF hides the Billing Portal item in the Settings area</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -9763,32 +9968,32 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Nav-hide needs live UI.</t>
+          <t>Nav-hide needs live check.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C27394</t>
+          <t>C26445</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27394</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26445</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3540</v>
+        <v>3542</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>A clock-capable role without Timesheets View can still see and open My Timesheets</t>
+          <t>App Settings ON gives access to the admin pages</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -9798,37 +10003,37 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded clock-capable role)</t>
+          <t>Blocked-UI (needs seeded role); page names build-verified</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Reworded, jargon stripped; needs live UI.</t>
+          <t>App Settings gates Departments/Settings/Staff/Roles &amp; Permissions/Locations (build route metadata).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>C26437</t>
+          <t>C26446</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26437</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26446</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3541</v>
+        <v>3542</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Customer portal ON lets the user manage the customer portal</t>
+          <t>Service ON gives access to the Service configuration pages</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -9838,37 +10043,37 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); toggle label 'Customer portal' build-verified</t>
+          <t>Blocked-UI (needs seeded role); page names build-verified</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Toggle 'Customer portal' confirmed in build. Manage behavior needs live check.</t>
+          <t>Service gates Canned Lines/Inspection Templates/Labour Types/Vehicle Types (build route metadata).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>C26438</t>
+          <t>C26447</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26438</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26447</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3541</v>
+        <v>3542</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Customer portal OFF hides the customer portal from navigation</t>
+          <t>Parts ON gives access to the Parts configuration pages</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -9878,37 +10083,37 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role); page names build-verified</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Nav-hide needs live check.</t>
+          <t>Parts gates Bins/Categories/Pricing (build route metadata).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>C26439</t>
+          <t>C26448</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26439</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26448</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3541</v>
+        <v>3542</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Billing Portal ON lets the user manage the billing portal</t>
+          <t>Finance ON shows the Finance pages, and Integrations ON shows QuickBooks, IBS and Open API</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9918,37 +10123,37 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); toggle label 'Billing Portal' build-verified</t>
+          <t>Blocked-UI (needs seeded role); page names build-verified</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Toggle 'Billing Portal' confirmed in build. Manage behavior needs live check.</t>
+          <t>Finance gates Payment Methods/Taxes; Integrations gates IBS/Open API/QuickBooks (build route metadata).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>C26440</t>
+          <t>C26449</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26440</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26449</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3541</v>
+        <v>3542</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Billing Portal OFF hides the Billing Portal item in the Settings area</t>
+          <t>Data Import ON gives access to the Imports pages</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9958,24 +10163,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role); page names build-verified</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Nav-hide needs live check.</t>
+          <t>Data Import gates Contacts/Inventory/Invoices/Vehicles/Vendors Import (build route metadata).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>C26445</t>
+          <t>C26450</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26445</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26450</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -9988,7 +10193,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>App Settings ON gives access to the admin pages</t>
+          <t>View/Manage Wages ON lets the user manage wages</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9998,24 +10203,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); page names build-verified</t>
+          <t>Blocked-UI (needs seeded role); toggle label 'View/Manage Wages' build-verified</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>App Settings gates Departments/Settings/Staff/Roles &amp; Permissions/Locations (build route metadata).</t>
+          <t>Toggle 'View/Manage Wages' confirmed in build. Wage editing needs live check.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>C26446</t>
+          <t>C26451</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26446</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26451</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -10028,7 +10233,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Service ON gives access to the Service configuration pages</t>
+          <t>The Settings sub-toggles work independently (Service on, Finance off)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -10038,24 +10243,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); page names build-verified</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Service gates Canned Lines/Inspection Templates/Labour Types/Vehicle Types (build route metadata).</t>
+          <t>Needs live check.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>C26447</t>
+          <t>C29273</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26447</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29273</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -10068,7 +10273,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Parts ON gives access to the Parts configuration pages</t>
+          <t>The Integrations admin pages depend on the Integrations sub-toggle, not on Finance</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -10078,24 +10283,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); page names build-verified</t>
+          <t>Blocked-UI (needs two seeded roles)</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Parts gates Bins/Categories/Pricing (build route metadata).</t>
+          <t>Steps-Separated case; reworded to layman, stripped element-id/URL jargon. Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C26448</t>
+          <t>C29274</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26448</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29274</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -10108,7 +10313,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Finance ON shows the Finance pages, and Integrations ON shows QuickBooks, IBS and Open API</t>
+          <t>The QuickBooks connection check does not run for roles without Integrations</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10118,37 +10323,37 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); page names build-verified</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Finance gates Payment Methods/Taxes; Integrations gates IBS/Open API/QuickBooks (build route metadata).</t>
+          <t>Steps-Separated case; reworded to layman. Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C26449</t>
+          <t>C26460</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26449</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26460</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3542</v>
+        <v>3543</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Data Import ON gives access to the Imports pages</t>
+          <t>Tech view: the parts request form shows fewer fields</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10158,37 +10363,37 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); page names build-verified</t>
+          <t>Blocked-UI: needs the New Part Request form opened in tech view vs full view to compare field counts; the lines screen is drivable but the request-form modal step was not reached this pass.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Data Import gates Contacts/Inventory/Invoices/Vehicles/Vendors Import (build route metadata).</t>
+          <t>precise reason logged</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>C26450</t>
+          <t>C26461</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26450</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26461</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3542</v>
+        <v>3543</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>View/Manage Wages ON lets the user manage wages</t>
+          <t>Tech view: the user can add new work order lines but cannot edit existing ones</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10198,37 +10403,37 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); toggle label 'View/Manage Wages' build-verified</t>
+          <t>Blocked-UI: New Line (add) confirmed present in tech view, but the existing-line read-only lock was not directly exercised (would require attempting to edit a pending line inline). Precise follow-up: open a pending line editor as the tech.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Toggle 'View/Manage Wages' confirmed in build. Wage editing needs live check.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>C26451</t>
+          <t>C26462</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26451</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26462</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3542</v>
+        <v>3543</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>The Settings sub-toggles work independently (Service on, Finance off)</t>
+          <t>Tech view: a line becomes read-only once its authorization is approved</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10238,37 +10443,37 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: approved-WO lines showed only tech status actions (Complete/Story/Start) with no edit control (consistent with read-only), but the pending-&gt;approved edit-lock transition was not directly exercised.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Needs live check.</t>
+          <t>Needs live UI + a second user.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>C29273</t>
+          <t>C26466</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29273</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26466</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3542</v>
+        <v>3543</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>The Integrations admin pages depend on the Integrations sub-toggle, not on Finance</t>
+          <t>Full View: a user who can approve lines sees the 'Send to Portal' button</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10278,37 +10483,37 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs two seeded roles)</t>
+          <t>Blocked-UI: Send to Portal was NOT found on the full-view (admin) lines page body; it is likely in the WO header more_vert menu or gated by WO state — needs the header action menu expanded to confirm.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Steps-Separated case; reworded to layman, stripped element-id/URL jargon. Needs live UI.</t>
+          <t>Send-to-Portal flow needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C29274</t>
+          <t>C26479</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29274</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26479</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3542</v>
+        <v>3545</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>The QuickBooks connection check does not run for roles without Integrations</t>
+          <t>View and Manage AP/AR Data ON allows paying several invoices at once from the Unpaid Invoices tab</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10318,37 +10523,37 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role + live payment)</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Steps-Separated case; reworded to layman. Needs live UI.</t>
+          <t>Bulk payment needs live UI + payment (create-customer-payment 500s intermittently per prior run).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C26460</t>
+          <t>C26488</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26460</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26488</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3543</v>
+        <v>3546</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>View History Logs</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Tech view: the parts request form shows fewer fields</t>
+          <t>View History Logs ON: work order history and line history are visible (work orders only)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -10358,37 +10563,37 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Blocked-UI: needs the New Part Request form opened in tech view vs full view to compare field counts; the lines screen is drivable but the request-form modal step was not reached this pass.</t>
+          <t>Blocked-UI (needs seeded role); 'View History Logs' toggle build-verified</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>precise reason logged</t>
+          <t>Cross-toggle 'View History Logs' confirmed in build. History visibility needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C26461</t>
+          <t>C26489</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26461</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26489</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3543</v>
+        <v>3546</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>View History Logs</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Tech view: the user can add new work order lines but cannot edit existing ones</t>
+          <t>View History Logs OFF: work order history and line history are hidden (work orders only)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -10398,37 +10603,37 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Blocked-UI: New Line (add) confirmed present in tech view, but the existing-line read-only lock was not directly exercised (would require attempting to edit a pending line inline). Precise follow-up: open a pending line editor as the tech.</t>
+          <t>Blocked-UI (needs seeded role); labels build-verified</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>viewHistoryLogs also gates the 'Part History' page under Parts (build route metadata). History-hide needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C26462</t>
+          <t>C26490</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26462</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26490</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3543</v>
+        <v>3547</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Tech view: a line becomes read-only once its authorization is approved</t>
+          <t>The Staff role dropdown groups roles into System Roles and Custom Roles</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -10438,37 +10643,37 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Blocked-UI: approved-WO lines showed only tech status actions (Complete/Story/Start) with no edit control (consistent with read-only), but the pending-&gt;approved edit-lock transition was not directly exercised.</t>
+          <t>Blocked-UI: the Edit Staff Member Role dropdown (System/Custom grouping) was not reached — the staff row click opened Manage-staff-enrollments. Follow-up: locate the Edit Staff Member action, open the Role selector.</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Needs live UI + a second user.</t>
+          <t>11 system roles confirmed in live roles list (was '12'). Grouping labels need live Staff page.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C26466</t>
+          <t>C26491</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26466</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26491</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3543</v>
+        <v>3547</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Full View: a user who can approve lines sees the 'Send to Portal' button</t>
+          <t>The View Permissions button next to the role selector opens the Permission Summary</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -10478,37 +10683,37 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Blocked-UI: Send to Portal was NOT found on the full-view (admin) lines page body; it is likely in the WO header more_vert menu or gated by WO state — needs the header action menu expanded to confirm.</t>
+          <t>Blocked-UI: View Permissions eye next to the staff Role selector not reached (same Edit-Staff-Member surface as C26490).</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Send-to-Portal flow needs live UI.</t>
+          <t>'View Permissions' confirmed in build. Needs live Staff page.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C26479</t>
+          <t>C26493</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26479</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26493</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3545</v>
+        <v>3547</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data ON allows paying several invoices at once from the Unpaid Invoices tab</t>
+          <t>If a role change fails, the user keeps their previous role</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -10518,37 +10723,37 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + live payment)</t>
+          <t>Blocked-UI: forcing a failed role change (to confirm the user keeps the prior role) requires inducing a server error on /change; not reproducible on demand this pass.</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Bulk payment needs live UI + payment (create-customer-payment 500s intermittently per prior run).</t>
+          <t>Failed-save path needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C26488</t>
+          <t>C26526</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26488</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26526</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3546</v>
+        <v>3550</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>View History Logs</t>
+          <t>Staff Record Settings</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>View History Logs ON: work order history and line history are visible (work orders only)</t>
+          <t>Whether a technician can be scheduled depends on their department, not their role</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -10558,37 +10763,37 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); 'View History Logs' toggle build-verified</t>
+          <t>Blocked-UI (needs two seeded users + departments)</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Cross-toggle 'View History Logs' confirmed in build. History visibility needs live UI.</t>
+          <t>Department-gated scheduling needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C26489</t>
+          <t>C26527</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26489</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26527</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3546</v>
+        <v>3550</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>View History Logs</t>
+          <t>Staff Record Settings</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>View History Logs OFF: work order history and line history are hidden (work orders only)</t>
+          <t>Clocking in on a work order line depends on the per-staff Time Clock setting</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -10598,37 +10803,37 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); labels build-verified</t>
+          <t>Blocked-UI (needs two seeded users)</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>viewHistoryLogs also gates the 'Part History' page under Parts (build route metadata). History-hide needs live UI.</t>
+          <t>Per-staff Time Clock gating needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C26490</t>
+          <t>C26539</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26490</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26539</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3547</v>
+        <v>3552</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Staff Page Role Assignment</t>
+          <t>User Feedback Strings</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>The Staff role dropdown groups roles into System Roles and Custom Roles</t>
+          <t>Reassigning a staff member's role updates the row with no success message (billing note in the window)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -10638,37 +10843,37 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Blocked-UI: the Edit Staff Member Role dropdown (System/Custom grouping) was not reached — the staff row click opened Manage-staff-enrollments. Follow-up: locate the Edit Staff Member action, open the Role selector.</t>
+          <t>Blocked-UI (needs live Staff page); billing note not re-captured this pass</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>11 system roles confirmed in live roles list (was '12'). Grouping labels need live Staff page.</t>
+          <t>No-toast-on-reassign + billing note need live Staff page (EditStaffMember chunk not fetched).</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C26491</t>
+          <t>C26540</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26491</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26540</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3547</v>
+        <v>3553</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Staff Page Role Assignment</t>
+          <t>Cross-Permission Combinations</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>The View Permissions button next to the role selector opens the Permission Summary</t>
+          <t>A role with all permissions off blocks the user from every feature</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -10678,37 +10883,37 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Blocked-UI: View Permissions eye next to the staff Role selector not reached (same Edit-Staff-Member surface as C26490).</t>
+          <t>Blocked-UI (needs live role editor / roles list)</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>'View Permissions' confirmed in build. Needs live Staff page.</t>
+          <t>Needs seeded role.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C26493</t>
+          <t>C26541</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26493</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26541</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3547</v>
+        <v>3553</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Staff Page Role Assignment</t>
+          <t>Cross-Permission Combinations</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>If a role change fails, the user keeps their previous role</t>
+          <t>A role with all permissions on behaves like Administrator but is still a custom role</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -10718,37 +10923,37 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Blocked-UI: forcing a failed role change (to confirm the user keeps the prior role) requires inducing a server error on /change; not reproducible on demand this pass.</t>
+          <t>Blocked-UI (needs live role editor / roles list)</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Failed-save path needs live UI.</t>
+          <t>Needs seeded role.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C26526</t>
+          <t>C26544</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26526</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26544</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3550</v>
+        <v>3553</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Staff Record Settings</t>
+          <t>Cross-Permission Combinations</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Whether a technician can be scheduled depends on their department, not their role</t>
+          <t>Being unable to open Customers does not stop a user from picking a customer when creating a work order</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -10758,37 +10963,37 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs two seeded users + departments)</t>
+          <t>Blocked-UI (needs live role editor / roles list)</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Department-gated scheduling needs live UI.</t>
+          <t>Needs seeded role.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C26527</t>
+          <t>C26545</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26527</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26545</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3550</v>
+        <v>3553</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Staff Record Settings</t>
+          <t>Cross-Permission Combinations</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Clocking in on a work order line depends on the per-staff Time Clock setting</t>
+          <t>A Page Access toggle that is off overrides the add/edit/delete boxes inside it</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -10798,37 +11003,37 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs two seeded users)</t>
+          <t>Blocked-UI (needs live role editor / roles list)</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Per-staff Time Clock gating needs live UI.</t>
+          <t>Needs seeded role.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C26539</t>
+          <t>C26548</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26539</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26548</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3552</v>
+        <v>3553</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Cross-Permission Combinations</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Reassigning a staff member's role updates the row with no success message (billing note in the window)</t>
+          <t>View off with Create &amp; Edit on is prevented by the tick-cascade</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -10838,24 +11043,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs live Staff page); billing note not re-captured this pass</t>
+          <t>Blocked-UI (needs live editor); cascade rule</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>No-toast-on-reassign + billing note need live Staff page (EditStaffMember chunk not fetched).</t>
+          <t>Needs live editor; matches cascade rules.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C26540</t>
+          <t>C26550</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26540</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26550</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -10868,7 +11073,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>A role with all permissions off blocks the user from every feature</t>
+          <t>The last Administrator cannot be left with zero users</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -10882,206 +11087,6 @@
         </is>
       </c>
       <c r="H70" t="inlineStr">
-        <is>
-          <t>Needs seeded role.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>C26541</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26541</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>A role with all permissions on behaves like Administrator but is still a custom role</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Needs seeded role.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>C26544</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26544</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Being unable to open Customers does not stop a user from picking a customer when creating a work order</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Needs seeded role.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>C26545</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26545</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>A Page Access toggle that is off overrides the add/edit/delete boxes inside it</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Needs seeded role.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>C26548</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26548</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>View off with Create &amp; Edit on is prevented by the tick-cascade</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live editor); cascade rule</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Needs live editor; matches cascade rules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>C26550</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26550</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>The last Administrator cannot be left with zero users</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
         <is>
           <t>Needs live UI; invariant to confirm.</t>
         </is>
@@ -11158,11 +11163,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B69" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B75" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16614,17 +16614,17 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Blocked-UI: the Invoicing &amp; payments / Finance surface route was not confirmed (/invoices returned minimal content for the Viewer role). Follow-up: locate the Finance tab/invoices route and confirm invoicingPaymentsView access.</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>UI (role Invoicing View + SFD, no C&amp;E/Delete): the WO Finance tab is shown and invoices can be opened; the Finance tab has NO create/edit/reverse buttons (view-only). screenshot inv-invView.</t>
         </is>
       </c>
     </row>
@@ -16654,17 +16654,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>UI (Service Advisor, Invoicing Create&amp;Edit): the WO Finance tab shows Create Invoice + Add Deposit actions (create invoices/take payments). screenshot inv-invCE.</t>
         </is>
       </c>
     </row>
@@ -16699,7 +16699,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: per-payment delete/void affordance not located on the WO Finance tab in the harness (payment rows/menus did not expose a delete/void control); needs the invoice-&gt;payment detail view with a with/without invoicingPaymentsDelete contrast.</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -16739,7 +16739,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: deleting a customer payment (gated by Invoicing Delete not Customers Delete) needs the payment delete control located; the Finance-tab payment row menu was not reachable this pass.</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -16814,17 +16814,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>UI/editor: See Financial Data OFF makes Invoicing &amp; payments inaccessible — SFD-off roles (e.g. Technician) show no Finance tab on the WO, and the editor forces SFD ON before Invoicing can be enabled (C26471/C26474). Invoicing is unreachable without SFD even with View/C&amp;E/Delete.</t>
         </is>
       </c>
     </row>
@@ -16854,17 +16854,17 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>UI (role SFD ON + WO C&amp;E, NO Invoicing View): the WO shows pricing/totals (SFD on) but the tabs are Lines/Notes/Stats — the Finance tab is hidden and invoices cannot be reached. screenshot inv-sfdNoInv.</t>
         </is>
       </c>
     </row>
@@ -16899,7 +16899,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: Send to Terminal was not shown at the WO Finance-tab level even for a role with Invoicing C&amp;E + Customer Portal (Service Advisor); it appears within the take-payment flow on an open invoice — needs seeding an open invoice + entering the payment dialog.</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -16934,17 +16934,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>UI: Taking Deposits needs Invoicing Create&amp;Edit — Add Deposit is shown for User B (Service Advisor, invoicing C&amp;E) and NOT shown for User A (Invoicing View-only).</t>
         </is>
       </c>
     </row>
@@ -17019,7 +17019,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded roles + returns)</t>
+          <t>Blocked-UI: deleting/cancelling a return (gated by Invoicing Delete) needs a part return seeded first (create return via admin) then observe the delete/cancel gate; return flow not seeded this pass.</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -17059,7 +17059,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded roles + terminal)</t>
+          <t>Blocked-UI: same as C26427 — Send to Terminal (needs Invoicing C&amp;E AND Customer Portal) is in the payment dialog, not reached; needs an open invoice + payment flow to observe both-gates.</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -17099,7 +17099,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + WO)</t>
+          <t>Blocked-UI: the WO Financial Info card is present but no edit control was detected for either an Invoicing-C&amp;E role or a view-only role on a PAID WO (balance $0, editing locked). Needs an open/unpaid WO with a balance to observe the C&amp;E edit control.</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">

--- a/build/custom-roles-run/CustomRoles_WordingVIU_2026-07-13.xlsx
+++ b/build/custom-roles-run/CustomRoles_WordingVIU_2026-07-13.xlsx
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>172</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">
@@ -735,10 +735,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -889,10 +889,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1157,7 +1157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H173"/>
+  <dimension ref="A1:H187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4135,25 +4135,25 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>C26394</t>
+          <t>C26389</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26394</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26389</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Schedule Permissions</t>
+          <t>Work Order Lines Permissions</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Schedule View shows the calendar with all technicians</t>
+          <t>Work order lines are visible whenever Work orders View is ON</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4168,32 +4168,32 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>UI: a role with Schedule View (ZZAUTOTEST Viewer) opens /schedule and the calendar renders. Schedule appears in top nav.</t>
+          <t>UI (Time Clock User = WO View only): work order lines are visible (line items/labor/parts) but there is no New Line/add option and no edit controls — lines visible whenever WO View is on. screenshot wol-tcuLines.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>C26397</t>
+          <t>C26390</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26397</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26390</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Schedule Permissions</t>
+          <t>Work Order Lines Permissions</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Schedule View OFF hides Schedule from the top navigation</t>
+          <t>Work order lines Create &amp; Edit allows adding, editing, moving parts, authorizing and managing part requests</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4208,32 +4208,32 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>UI: the WOCust custom role (no scheduleView) has NO Schedule item in the top navigation — Schedule View OFF hides Schedule from nav.</t>
+          <t>UI (role WO View + Work order lines Create&amp;Edit): the lines screen shows New Line + Build Lines — the user can add/edit lines (add and line management affordances present). screenshot wol-wolce.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>C26398</t>
+          <t>C26392</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26398</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26392</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3537</v>
+        <v>3535</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Work Order Lines Permissions</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Customers View gives access to customer records, contacts, vehicles and history</t>
+          <t>Work orders View OFF makes work order lines unreachable</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4248,32 +4248,32 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>UI: a role with Customers View opens /customers and the customer list renders (customer records accessible; contacts/vehicles/history are sub-views of a record). Customers appears in nav.</t>
+          <t>UI (Sales Rep = no workOrdersView): Work Orders is hidden from nav and /workorders redirects to /reports, so no work order (and therefore no work order lines) is reachable. WO View OFF makes WO lines unreachable.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>C26402</t>
+          <t>C26393</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26402</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26393</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>3537</v>
+        <v>3535</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Work Order Lines Permissions</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AP/AR OFF hides the 7 sensitive customer fields on Edit Customer</t>
+          <t>Work order lines are read-only when Create &amp; Edit is OFF</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4288,32 +4288,32 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>UI: role with View and Manage AP/AR Data OFF (Service Advisor) — Edit Customer modal has NO sensitive fields (no Credit Limit, Taxes, Default Labor Rate, etc). With AP/AR ON they are present. screenshot customer-aparOFF vs customer-aparON.</t>
+          <t>UI (WO View only, no WOL Create&amp;Edit): no Add line option and existing line fields are read-only (no New Line, no edit affordances). screenshot wol-tcuLines.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>C26403</t>
+          <t>C27271</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26403</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27271</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3537</v>
+        <v>3535</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Work Order Lines Permissions</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AP/AR ON shows the 7 sensitive customer fields on Edit Customer</t>
+          <t>The Build Lines entry point is hidden for a Work Orders View-only role</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4328,32 +4328,32 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>UI (role with View and Manage AP/AR Data ON): the Edit Customer modal shows all 7 sensitive fields — Credit Terms, Credit Limit, Default Labor Rate, Default Shop Supplies, Min, Max, Taxes (and PO-required). screenshot customer-apar-on.</t>
+          <t>UI (WO View-only role): the Build Lines entry point is not shown (buildLines=false).</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>C26404</t>
+          <t>C27272</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26404</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27272</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3537</v>
+        <v>3535</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Work Order Lines Permissions</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Customers View OFF hides Customers from the top navigation</t>
+          <t>The Build Lines entry point is shown for a role with Work order lines Create &amp; Edit</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4368,32 +4368,32 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>UI: the Time Clock User role (no customersView) shows top nav Work Orders | Schedule only — no Customers entry. Customers View OFF hides Customers from the top navigation.</t>
+          <t>UI (role with Work order lines Create&amp;Edit): the Build Lines entry point is shown (Build Lines button present).</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>C26406</t>
+          <t>C26394</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26406</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26394</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3538</v>
+        <v>3536</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Schedule Permissions</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Turning Parts Department ON shows exactly 3 child cards</t>
+          <t>Schedule View shows the calendar with all technicians</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4403,37 +4403,37 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Parts Department children + descriptions build-verified (PermissionGrid).</t>
+          <t>UI: a role with Schedule View (ZZAUTOTEST Viewer) opens /schedule and the calendar renders. Schedule appears in top nav.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>C26407</t>
+          <t>C26397</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26407</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26397</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3538</v>
+        <v>3536</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Schedule Permissions</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Turning Parts Department OFF hides the 3 child cards</t>
+          <t>Schedule View OFF hides Schedule from the top navigation</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4448,32 +4448,32 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>UI: on blank form the 3 child cards (Part sales/Catalog and Inventory/Vendor and order management) are absent; toggling Parts Department ON reveals all 3.</t>
+          <t>UI: the WOCust custom role (no scheduleView) has NO Schedule item in the top navigation — Schedule View OFF hides Schedule from nav.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>C26408</t>
+          <t>C26398</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26408</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26398</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>A saved role with Parts Department OFF hides the Parts navigation and its pages</t>
+          <t>Customers View gives access to customer records, contacts, vehicles and history</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4488,32 +4488,32 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>UI: the Technician role (no Parts Department perms) has NO Parts item in the top navigation — Parts Department OFF hides the Parts navigation.</t>
+          <t>UI: a role with Customers View opens /customers and the customer list renders (customer records accessible; contacts/vehicles/history are sub-views of a record). Customers appears in nav.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>C26409</t>
+          <t>C26402</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26409</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26402</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Turning Parts Department OFF then ON keeps the 3 child card choices</t>
+          <t>AP/AR OFF hides the 7 sensitive customer fields on Edit Customer</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4528,32 +4528,32 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>UI: Parts Department OFF hides 3 children then ON again retains prior child choices (Part sales Delete + Catalog Delete stayed ON).</t>
+          <t>UI: role with View and Manage AP/AR Data OFF (Service Advisor) — Edit Customer modal has NO sensitive fields (no Credit Limit, Taxes, Default Labor Rate, etc). With AP/AR ON they are present. screenshot customer-aparOFF vs customer-aparON.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>C26410</t>
+          <t>C26403</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26410</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26403</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Part sales View gives read access to part sales records</t>
+          <t>AP/AR ON shows the 7 sensitive customer fields on Edit Customer</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4568,32 +4568,32 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>UI (Parts Manager): the Part Sales list at /parts/part-sales loads via in-app nav (columns Number/Status, "New Part Sale" button). NOTE: a direct URL goto to /parts/part-sales redirects to /workorders even for a fully-permissioned role — this is an SPA route-guard-on-fresh-load quirk (not a permission bug); in-app navigation works.</t>
+          <t>UI (role with View and Manage AP/AR Data ON): the Edit Customer modal shows all 7 sensitive fields — Credit Terms, Credit Limit, Default Labor Rate, Default Shop Supplies, Min, Max, Taxes (and PO-required). screenshot customer-apar-on.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>C26411</t>
+          <t>C26404</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26411</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26404</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Part sales Create &amp; Edit lets the user create part sales, returns and transactions</t>
+          <t>Customers View OFF hides Customers from the top navigation</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4608,19 +4608,19 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>UI (Parts Manager, partSalesCreateAndEdit): the Part Sales page shows the "New Part Sale" create control.</t>
+          <t>UI: the Time Clock User role (no customersView) shows top nav Work Orders | Schedule only — no Customers entry. Customers View OFF hides Customers from the top navigation.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>C26413</t>
+          <t>C26406</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26413</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26406</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Catalog and Inventory View gives read access to the catalog and inventory</t>
+          <t>Turning Parts Department ON shows exactly 3 child cards</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4643,24 +4643,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>UI: a role with Catalog and Inventory View opens /parts/parts-catalogue and the catalogue renders (read access to the catalog).</t>
+          <t>Parts Department children + descriptions build-verified (PermissionGrid).</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>C26414</t>
+          <t>C26407</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26414</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26407</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Catalog and Inventory Create &amp; Edit lets the user create/edit items and make adjustments (cost/price shown only with See Financial Data)</t>
+          <t>Turning Parts Department OFF hides the 3 child cards</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4688,19 +4688,19 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>UI (Parts Manager, catalogInventoryCreateAndEdit): the Catalog page shows the "New Catalog Part" create control.</t>
+          <t>UI: on blank form the 3 child cards (Part sales/Catalog and Inventory/Vendor and order management) are absent; toggling Parts Department ON reveals all 3.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>C26416</t>
+          <t>C26408</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26416</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26408</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Vendor and order management View gives visibility of vendors, purchase orders and deliveries</t>
+          <t>A saved role with Parts Department OFF hides the Parts navigation and its pages</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4728,19 +4728,19 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>UI: a role with Vendor and order management View opens /parts/orders and the Purchase Orders list renders (visibility of vendors/POs/deliveries).</t>
+          <t>UI: the Technician role (no Parts Department perms) has NO Parts item in the top navigation — Parts Department OFF hides the Parts navigation.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>C26417</t>
+          <t>C26409</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26417</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26409</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Vendor and order management Create &amp; Edit lets the user manage vendors, purchase orders, receiving and returns</t>
+          <t>Turning Parts Department OFF then ON keeps the 3 child card choices</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4768,19 +4768,19 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>UI (Parts Manager, vendorOrderManagementCreateAndEdit): the Purchase Orders page shows the "New PO" create control.</t>
+          <t>UI: Parts Department OFF hides 3 children then ON again retains prior child choices (Part sales Delete + Catalog Delete stayed ON).</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>C27876</t>
+          <t>C26410</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27876</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26410</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>A Vendor and order management View-only role can open the Purchase Orders list and a purchase order</t>
+          <t>Part sales View gives read access to part sales records</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4808,32 +4808,32 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>UI: a Vendor and order management View-only role (ZZAUTOTEST Viewer) opens the Purchase Orders list at /parts/orders successfully (list access confirmed).</t>
+          <t>UI (Parts Manager): the Part Sales list at /parts/part-sales loads via in-app nav (columns Number/Status, "New Part Sale" button). NOTE: a direct URL goto to /parts/part-sales redirects to /workorders even for a fully-permissioned role — this is an SPA route-guard-on-fresh-load quirk (not a permission bug); in-app navigation works.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>C26420</t>
+          <t>C26411</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26420</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26411</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Invoicing &amp; payments View shows the Finance tab and lets the user see invoices</t>
+          <t>Part sales Create &amp; Edit lets the user create part sales, returns and transactions</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4848,32 +4848,32 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>UI (role Invoicing View + SFD, no C&amp;E/Delete): the WO Finance tab is shown and invoices can be opened; the Finance tab has NO create/edit/reverse buttons (view-only). screenshot inv-invView.</t>
+          <t>UI (Parts Manager, partSalesCreateAndEdit): the Part Sales page shows the "New Part Sale" create control.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>C26421</t>
+          <t>C26413</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26421</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26413</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Invoicing &amp; payments Create &amp; Edit lets the user create invoices and take payments</t>
+          <t>Catalog and Inventory View gives read access to the catalog and inventory</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4888,32 +4888,32 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>UI (Service Advisor, Invoicing Create&amp;Edit): the WO Finance tab shows Create Invoice + Add Deposit actions (create invoices/take payments). screenshot inv-invCE.</t>
+          <t>UI: a role with Catalog and Inventory View opens /parts/parts-catalogue and the catalogue renders (read access to the catalog).</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>C26425</t>
+          <t>C26414</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26425</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26414</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>See Financial Data OFF makes Invoicing &amp; payments inaccessible even with View, Create &amp; Edit and Delete</t>
+          <t>Catalog and Inventory Create &amp; Edit lets the user create/edit items and make adjustments (cost/price shown only with See Financial Data)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4928,32 +4928,32 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>UI/editor: See Financial Data OFF makes Invoicing &amp; payments inaccessible — SFD-off roles (e.g. Technician) show no Finance tab on the WO, and the editor forces SFD ON before Invoicing can be enabled (C26471/C26474). Invoicing is unreachable without SFD even with View/C&amp;E/Delete.</t>
+          <t>UI (Parts Manager, catalogInventoryCreateAndEdit): the Catalog page shows the "New Catalog Part" create control.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>C26426</t>
+          <t>C26416</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26426</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26416</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Invoicing &amp; payments View OFF with See Financial Data ON: prices show but invoices are not reachable</t>
+          <t>Vendor and order management View gives visibility of vendors, purchase orders and deliveries</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4968,32 +4968,32 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>UI (role SFD ON + WO C&amp;E, NO Invoicing View): the WO shows pricing/totals (SFD on) but the tabs are Lines/Notes/Stats — the Finance tab is hidden and invoices cannot be reached. screenshot inv-sfdNoInv.</t>
+          <t>UI: a role with Vendor and order management View opens /parts/orders and the Purchase Orders list renders (visibility of vendors/POs/deliveries).</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>C26428</t>
+          <t>C26417</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26428</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26417</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Taking Deposits on a work order needs Invoicing &amp; payments Create &amp; Edit</t>
+          <t>Vendor and order management Create &amp; Edit lets the user manage vendors, purchase orders, receiving and returns</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5008,32 +5008,32 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>UI: Taking Deposits needs Invoicing Create&amp;Edit — Add Deposit is shown for User B (Service Advisor, invoicing C&amp;E) and NOT shown for User A (Invoicing View-only).</t>
+          <t>UI (Parts Manager, vendorOrderManagementCreateAndEdit): the Purchase Orders page shows the "New PO" create control.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>C27740</t>
+          <t>C27876</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27740</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27876</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>The Invoicing &amp; payments delete column is labelled 'Delete / Reverse'</t>
+          <t>A Vendor and order management View-only role can open the Purchase Orders list and a purchase order</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5043,37 +5043,37 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>'Delete / Reverse' column confirmed in build (PermissionGrid).</t>
+          <t>UI: a Vendor and order management View-only role (ZZAUTOTEST Viewer) opens the Purchase Orders list at /parts/orders successfully (list access confirmed).</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>C26429</t>
+          <t>C26420</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26429</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26420</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>The Timesheets card shows View and Create &amp; Edit only (no Delete)</t>
+          <t>Invoicing &amp; payments View shows the Finance tab and lets the user see invoices</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5083,37 +5083,37 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Timesheets card title + 'Track and review technician labor hours and time entries.' + no Delete column build-verified (PermissionGrid).</t>
+          <t>UI (role Invoicing View + SFD, no C&amp;E/Delete): the WO Finance tab is shown and invoices can be opened; the Finance tab has NO create/edit/reverse buttons (view-only). screenshot inv-invView.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>C26432</t>
+          <t>C26421</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26432</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26421</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Clock in / clock out is always available, whatever the Timesheets permission</t>
+          <t>Invoicing &amp; payments Create &amp; Edit lets the user create invoices and take payments</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5128,32 +5128,32 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>UI: the universal Clock In control (top bar "timer | Clock In") is present for the Time Clock User role, which has no Timesheets Create&amp;Edit — clock in/out is available regardless of the Timesheets permission.</t>
+          <t>UI (Service Advisor, Invoicing Create&amp;Edit): the WO Finance tab shows Create Invoice + Add Deposit actions (create invoices/take payments). screenshot inv-invCE.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>C26435</t>
+          <t>C26425</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26435</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26425</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3541</v>
+        <v>3539</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Reports ON gives access to the Reports page with all reports (no per-report on/off)</t>
+          <t>See Financial Data OFF makes Invoicing &amp; payments inaccessible even with View, Create &amp; Edit and Delete</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5168,32 +5168,32 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>UI (admin /reports): Reports appears in top nav; the Reports page lists ALL reports grouped by category (LABOR, PERFORMANCE, FINANCE, ACCOUNTS RECEIVABLE, ACCOUNTS PAYABLE, ACCOUNTING, COMMUNICATIONS) with no per-report on/off control — Reports is all-or-nothing. screenshot reports-admin.</t>
+          <t>UI/editor: See Financial Data OFF makes Invoicing &amp; payments inaccessible — SFD-off roles (e.g. Technician) show no Finance tab on the WO, and the editor forces SFD ON before Invoicing can be enabled (C26471/C26474). Invoicing is unreachable without SFD even with View/C&amp;E/Delete.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>C26436</t>
+          <t>C26426</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26436</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26426</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>3541</v>
+        <v>3539</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Reports OFF removes Reports from the top navigation</t>
+          <t>Invoicing &amp; payments View OFF with See Financial Data ON: prices show but invoices are not reachable</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5208,32 +5208,32 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>UI: the Technician role (no reportsPageAccess) has NO Reports item in the top navigation — Reports OFF removes Reports from nav.</t>
+          <t>UI (role SFD ON + WO C&amp;E, NO Invoicing View): the WO shows pricing/totals (SFD on) but the tabs are Lines/Notes/Stats — the Finance tab is hidden and invoices cannot be reached. screenshot inv-sfdNoInv.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>C26441</t>
+          <t>C26428</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26441</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26428</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3542</v>
+        <v>3539</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Turning Settings ON reveals its sub-toggles</t>
+          <t>Taking Deposits on a work order needs Invoicing &amp; payments Create &amp; Edit</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5243,37 +5243,37 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Verified-Label (build) — Integrations sub-toggle now present (was previously flagged missing)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>PageAndSettingsToggles build chunk shows 7 Settings sub-toggles incl. Integrations. Prior 'Integrations missing' gap is resolved/built.</t>
+          <t>UI: Taking Deposits needs Invoicing Create&amp;Edit — Add Deposit is shown for User B (Service Advisor, invoicing C&amp;E) and NOT shown for User A (Invoicing View-only).</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>C26442</t>
+          <t>C27740</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26442</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27740</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>3542</v>
+        <v>3539</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Turning Settings OFF hides its sub-toggles</t>
+          <t>The Invoicing &amp; payments delete column is labelled 'Delete / Reverse'</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5283,37 +5283,37 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>UI: with Settings off the 7 sub-toggles are absent; toggling Settings ON reveals App Settings/Service/Parts/Finance/Integrations/Data Import/View-Manage Wages.</t>
+          <t>'Delete / Reverse' column confirmed in build (PermissionGrid).</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>C26443</t>
+          <t>C26429</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26443</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26429</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>3542</v>
+        <v>3540</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>A saved role with Settings OFF has no Settings area in the sidebar</t>
+          <t>The Timesheets card shows View and Create &amp; Edit only (no Delete)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5323,37 +5323,37 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>UI: the Technician role (no settings* perms) has no Settings area in the sidebar — a saved role with Settings OFF has no Settings section.</t>
+          <t>Timesheets card title + 'Track and review technician labor hours and time entries.' + no Delete column build-verified (PermissionGrid).</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>C26444</t>
+          <t>C26432</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26444</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26432</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3542</v>
+        <v>3540</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Turning Settings OFF then ON keeps the sub-toggle choices</t>
+          <t>Clock in / clock out is always available, whatever the Timesheets permission</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5368,32 +5368,32 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>UI: turning Settings OFF then ON keeps the sub-toggle choices (App Settings + Finance stayed ON after the parent was toggled off then on).</t>
+          <t>UI: the universal Clock In control (top bar "timer | Clock In") is present for the Time Clock User role, which has no Timesheets Create&amp;Edit — clock in/out is available regardless of the Timesheets permission.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>C27395</t>
+          <t>C26435</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27395</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26435</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Turning off the last Settings sub-toggle collapses the Settings section</t>
+          <t>Reports ON gives access to the Reports page with all reports (no per-report on/off)</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5408,32 +5408,32 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>UI: turning off the last remaining Settings sub-toggle (App Settings) collapses the Settings section — the parent Settings toggle goes off and the sub-toggles disappear.</t>
+          <t>UI (admin /reports): Reports appears in top nav; the Reports page lists ALL reports grouped by category (LABOR, PERFORMANCE, FINANCE, ACCOUNTS RECEIVABLE, ACCOUNTS PAYABLE, ACCOUNTING, COMMUNICATIONS) with no per-report on/off control — Reports is all-or-nothing. screenshot reports-admin.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>C26452</t>
+          <t>C26436</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26452</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26436</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>3543</v>
+        <v>3541</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>The Work orders card has 'Full View' and 'Tech view' options</t>
+          <t>Reports OFF removes Reports from the top navigation</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5443,37 +5443,37 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>'View mode', 'Full View', 'Tech view' confirmed in build (WoSettingsRow).</t>
+          <t>UI: the Technician role (no reportsPageAccess) has NO Reports item in the top navigation — Reports OFF removes Reports from nav.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>C26453</t>
+          <t>C26441</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26453</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26441</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>The Full View description</t>
+          <t>Turning Settings ON reveals its sub-toggles</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5483,37 +5483,37 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build) — Integrations sub-toggle now present (was previously flagged missing)</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>UI: Full View description reads "Complete interface with all fields visible and editable (subject to CRUD permissions). The estimate column shows the actual estimate value. Full parts request form with all fields. All workflow actions available (approve, review, split etc...)."</t>
+          <t>PageAndSettingsToggles build chunk shows 7 Settings sub-toggles incl. Integrations. Prior 'Integrations missing' gap is resolved/built.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>C26454</t>
+          <t>C26442</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26454</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26442</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>The Tech view description, and Tech view stays disabled until a Work orders permission is on</t>
+          <t>Turning Settings OFF hides its sub-toggles</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5523,37 +5523,37 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Verified-Label (Tech view text build-verified); disabled-state needs live check</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Tech view description string confirmed verbatim in build (WoSettingsRow). Disabled-until-WO-perm needs live editor.</t>
+          <t>UI: with Settings off the 7 sub-toggles are absent; toggling Settings ON reveals App Settings/Service/Parts/Finance/Integrations/Data Import/View-Manage Wages.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>C26455</t>
+          <t>C26443</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26455</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26443</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Tech view: the Estimate column shows the Tech Time value</t>
+          <t>A saved role with Settings OFF has no Settings area in the sidebar</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5568,32 +5568,32 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>UI (Technician, tech view): WO lines Actual/Estimate column shows tech-time hours (e.g. 0.00 / 1.00, 0.00 / 1.50) and header "Total Tech Hours" — not a money estimate. screenshot techview-lines-estimate/approved.</t>
+          <t>UI: the Technician role (no settings* perms) has no Settings area in the sidebar — a saved role with Settings OFF has no Settings section.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>C26456</t>
+          <t>C26444</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26456</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26444</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Tech view: the tech time input field is hidden on work order lines</t>
+          <t>Turning Settings OFF then ON keeps the sub-toggle choices</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5608,32 +5608,32 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>UI (tech view): no tech-time input field rendered on the WO lines for this user (0 tech-time inputs found).</t>
+          <t>UI: turning Settings OFF then ON keeps the sub-toggle choices (App Settings + Finance stayed ON after the parent was toggled off then on).</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>C26457</t>
+          <t>C26445</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26457</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26445</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Tech view: the user cannot approve work orders (no Approve button)</t>
+          <t>App Settings ON gives access to the admin pages</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5648,32 +5648,32 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>UI (tech view): no Approve button anywhere on the work order (estimate and approved WOs both) — Technician lacks Review Work Orders.</t>
+          <t>UI (role settingsApp): the SETTINGS admin group is present — Settings, Staff, Roles &amp; Permissions, Locations, Departments. screenshot settings-SetX.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>C26458</t>
+          <t>C26446</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26458</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26446</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Tech view: the user cannot approve work order lines</t>
+          <t>Service ON gives access to the Service configuration pages</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5688,32 +5688,32 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>UI (tech view): no approve-line action on any line; line actions are tech-only (Complete / Story / Start), no approve control.</t>
+          <t>UI (role settingsService): the SERVICE group is present — Labor Rates, Canned Lines, Asset Types, Inspection Templates. screenshot settings-SetX.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>C26463</t>
+          <t>C26447</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26463</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26447</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>View mode only changes the look, not what the user is allowed to do</t>
+          <t>Parts ON gives access to the Parts configuration pages</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5728,32 +5728,32 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>UI/enforcement: tech view is purely presentational — the tech-view role retains workOrderLinesCreateAndEdit and can add lines (New Line functional on the lines screen); data-level create/edit is governed by CRUD perms, not the view mode (estimate column renders as hours but edit capability persists).</t>
+          <t>UI (role settingsParts): the PARTS config group is present — Pricing, Bin Locations, Categories. screenshot settings-SetX.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>C26465</t>
+          <t>C26448</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26465</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26448</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Tech view: the 'Send to Portal' button is hidden</t>
+          <t>Finance ON shows the Finance pages, and Integrations ON shows QuickBooks, IBS and Open API</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5768,32 +5768,32 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>UI (tech view): the Send to Portal button is not shown anywhere on the work order (header, line, or action menus).</t>
+          <t>UI: Finance ON shows the FINANCE group (Payment Methods, Taxes) [SetFin]; Integrations ON shows the INTEGRATIONS group (IBS, Open API; QuickBooks gated under Integrations) [SetAppIntg]. Roles without each toggle lack the respective group. screenshot settings-SetFin/settings-SetAppIntg.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>C26467</t>
+          <t>C26449</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26467</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26449</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>3544</v>
+        <v>3542</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>See Financial Data toggle appears in the Cross-Cutting Toggles card</t>
+          <t>Data Import ON gives access to the Imports pages</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5803,37 +5803,37 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Verified-Label (build); subtitle placeholder flagged</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Card 'Cross-Cutting Toggles' + toggle 'See Financial Data' confirmed in shipped build (CrossTogglesSection chunk). Reused subtitle string flagged.</t>
+          <t>UI (role settingsDataImport): the IMPORTS group is present — Contacts, Assets, Vendors, Inventory, Invoices. screenshot settings-SetX.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>C26468</t>
+          <t>C26451</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26468</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26451</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>3544</v>
+        <v>3542</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>See Financial Data ON: prices, costs, margins and labor rates are shown</t>
+          <t>The Settings sub-toggles work independently (Service on, Finance off)</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5848,32 +5848,32 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>UI: with See Financial Data ON (admin full view + TechSFD), WO lines show prices, costs, margins and labor rates — Rate ($100), Margin (%), Total ($261.54), parts prices ($3.33 etc), labor ($150). screenshot fullview-lines-admin/techview-sfd-lines.</t>
+          <t>UI (role with Service ON, Finance OFF = SetX): the SERVICE pages show and there is NO FINANCE group — the Settings sub-toggles work independently.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>C26469</t>
+          <t>C27395</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26469</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27395</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>3544</v>
+        <v>3542</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>See Financial Data OFF: money amounts, rates, costs and margins are hidden</t>
+          <t>Turning off the last Settings sub-toggle collapses the Settings section</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5888,32 +5888,32 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>UI: with See Financial Data OFF (plain Technician), WO lines show NO money — no $ amounts, no Rate/Margin/Total columns; only tech-time hours (0.00/1.00). screenshot techview-lines-estimate.</t>
+          <t>UI: turning off the last remaining Settings sub-toggle (App Settings) collapses the Settings section — the parent Settings toggle goes off and the sub-toggles disappear.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>C26470</t>
+          <t>C29273</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26470</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29273</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>3544</v>
+        <v>3542</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>With See Financial Data OFF, Part sales and Invoicing &amp; payments stay inaccessible even with View, Create &amp; Edit and Delete on</t>
+          <t>The Integrations admin pages depend on the Integrations sub-toggle, not on Finance</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5928,32 +5928,32 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>UI/editor enforcement: a role cannot hold Part sales or Invoicing &amp; payments with See Financial Data OFF — ticking either forces the "Enable See Financial Data?" dialog (C26471/C26474). So SFD OFF makes Part sales and Invoicing &amp; payments unreachable even if View/Create&amp;Edit/Delete were desired; the combination is prevented at save time.</t>
+          <t>UI: a Finance-only role (settingsFinance, no settingsIntegrations = SetFin) shows the FINANCE group (Payment Methods, Taxes) but NO INTEGRATIONS group (no IBS/Open API/QuickBooks) — Integrations admin pages depend on the Integrations sub-toggle, not on Finance. screenshot settings-SetFin.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>C26471</t>
+          <t>C29274</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26471</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29274</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>3544</v>
+        <v>3542</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ticking Part sales while See Financial Data is OFF asks you to turn See Financial Data on</t>
+          <t>The QuickBooks connection check does not run for roles without Integrations</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5968,32 +5968,32 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>UI dialog: ticking Part sales while SFD off shows "Enable See Financial Data? — Part Sales requires See Financial Data. Enable it to grant this permission?" [Cancel|Enable].</t>
+          <t>UI (inference from gating): QuickBooks lives under the INTEGRATIONS group which is only shown for roles with settingsIntegrations (present for SetAppIntg, absent for SetX/SetFin). Roles without Integrations never reach the QuickBooks surface, so the QuickBooks connection check is not triggered for them. (The background check API call itself is not directly observable in the harness; verified via the Integrations gating.)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>C26472</t>
+          <t>C26452</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26472</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26452</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>'Enable See Financial Data?' dialog — Enable: turns See Financial Data on and keeps the box ticked</t>
+          <t>The Work orders card has 'Full View' and 'Tech view' options</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6003,37 +6003,37 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>UI: Enable on the SFD dialog turns See Financial Data ON and keeps Part sales View+Create&amp;Edit ticked.</t>
+          <t>'View mode', 'Full View', 'Tech view' confirmed in build (WoSettingsRow).</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>C26473</t>
+          <t>C26453</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26473</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26453</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>'Enable See Financial Data?' dialog — Cancel: undoes the tick</t>
+          <t>The Full View description</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -6048,32 +6048,32 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>UI: Cancel on the SFD dialog undoes the tick (See Financial Data off, Part sales off).</t>
+          <t>UI: Full View description reads "Complete interface with all fields visible and editable (subject to CRUD permissions). The estimate column shows the actual estimate value. Full parts request form with all fields. All workflow actions available (approve, review, split etc...)."</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>C26474</t>
+          <t>C26454</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26474</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26454</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>The same 'Enable See Financial Data?' dialog appears for Invoicing &amp; payments when See Financial Data is OFF</t>
+          <t>The Tech view description, and Tech view stays disabled until a Work orders permission is on</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6083,37 +6083,37 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (Tech view text build-verified); disabled-state needs live check</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>UI dialog: ticking Invoicing &amp; payments while SFD off shows "Enable See Financial Data? — Invoicing &amp; Payments requires See Financial Data..." [Cancel|Enable]; Enable -&gt; SFD ON + Invoicing View+C&amp;E ON.</t>
+          <t>Tech view description string confirmed verbatim in build (WoSettingsRow). Disabled-until-WO-perm needs live editor.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>C26475</t>
+          <t>C26455</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26475</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26455</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Turning See Financial Data OFF asks you to also turn off the settings that depend on it</t>
+          <t>Tech view: the Estimate column shows the Tech Time value</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -6128,32 +6128,32 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>UI (RUN331 FAIL NOW FIXED): turning See Financial Data OFF while Invoicing on shows "Disable See Financial Data? — Disabling See Financial Data will also disable Invoicing &amp; Payments. Continue?" [Cancel|Disable] (FinancialDataDisableConfirmModal). screenshot sfd-disable-dialog.</t>
+          <t>UI (Technician, tech view): WO lines Actual/Estimate column shows tech-time hours (e.g. 0.00 / 1.00, 0.00 / 1.50) and header "Total Tech Hours" — not a money estimate. screenshot techview-lines-estimate/approved.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>C27869</t>
+          <t>C26456</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27869</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26456</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Turning on Order parts while See Financial Data is OFF asks you to also turn on See Financial Data</t>
+          <t>Tech view: the tech time input field is hidden on work order lines</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6168,32 +6168,32 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>UI dialog: ticking Order parts while SFD off shows "Enable See Financial Data? — Order Parts requires See Financial Data. Enable it to grant this permission?" [Cancel|Enable].</t>
+          <t>UI (tech view): no tech-time input field rendered on the WO lines for this user (0 tech-time inputs found).</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>C26476</t>
+          <t>C26457</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26476</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26457</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>3545</v>
+        <v>3543</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data ON shows the Unpaid Invoices, Payments and Credits tabs on a customer</t>
+          <t>Tech view: the user cannot approve work orders (no Approve button)</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6208,32 +6208,32 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>UI: role with AP/AR Data ON shows the financial tabs on a customer page — build labels are Invoices / Payments / Deposits (case prose says Unpaid Invoices/Payments/Credits; the AP/AR toggle description uses that wording, actual tab labels are Invoices/Payments/Deposits). Tabs absent when AP/AR off.</t>
+          <t>UI (tech view): no Approve button anywhere on the work order (estimate and approved WOs both) — Technician lacks Review Work Orders.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>C26477</t>
+          <t>C26458</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26477</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26458</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>3545</v>
+        <v>3543</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data ON shows the same three tabs on a vendor</t>
+          <t>Tech view: the user cannot approve work order lines</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6248,32 +6248,32 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>UI (Parts Manager, AP/AR ON): the vendor page (/parts/vendor/{id}) shows the AP/AR tabs — Contacts, Unpaid Invoices (30), Payments (4). screenshot vendordetail-vendON.</t>
+          <t>UI (tech view): no approve-line action on any line; line actions are tech-only (Complete / Story / Start), no approve control.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>C26478</t>
+          <t>C26463</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26478</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26463</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>3545</v>
+        <v>3543</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>With Reports ON, all 6 AP/AR aging reports are listed (whether or not AP/AR is on)</t>
+          <t>View mode only changes the look, not what the user is allowed to do</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6288,32 +6288,32 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>UI (admin /reports, Reports ON): all 6 AP/AR aging reports are listed — A/R Aging Summary, A/R Aging Detail, A/R Aging Collection, A/P Aging Summary, A/P Aging Detail, A/P Unpaid Invoices. screenshot reports-admin.</t>
+          <t>UI/enforcement: tech view is purely presentational — the tech-view role retains workOrderLinesCreateAndEdit and can add lines (New Line functional on the lines screen); data-level create/edit is governed by CRUD perms, not the view mode (estimate column renders as hours but edit capability persists).</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>C26480</t>
+          <t>C26465</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26480</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26465</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>3545</v>
+        <v>3543</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data OFF hides the three tabs on a customer</t>
+          <t>Tech view: the 'Send to Portal' button is hidden</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6328,32 +6328,32 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>UI: AP/AR Data OFF (Service Advisor) — the customer page shows only Work Orders/Part Sales/Contacts/Assets/Notes; the Invoices/Payments/Deposits tabs are hidden.</t>
+          <t>UI (tech view): the Send to Portal button is not shown anywhere on the work order (header, line, or action menus).</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>C26481</t>
+          <t>C26467</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26481</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26467</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data OFF hides the three tabs on a vendor</t>
+          <t>See Financial Data toggle appears in the Cross-Cutting Toggles card</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6363,37 +6363,37 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build); subtitle placeholder flagged</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>UI (Service Advisor, AP/AR OFF): the same vendor page shows only the Contacts tab — Unpaid Invoices/Payments tabs are hidden. screenshot vendordetail-vendOFF.</t>
+          <t>Card 'Cross-Cutting Toggles' + toggle 'See Financial Data' confirmed in shipped build (CrossTogglesSection chunk). Reused subtitle string flagged.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>C26482</t>
+          <t>C26468</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26482</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26468</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>With AP/AR OFF but Reports ON, all 6 AP/AR aging reports are still listed</t>
+          <t>See Financial Data ON: prices, costs, margins and labor rates are shown</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6408,32 +6408,32 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>UI (RUN331 FAIL NOW FIXED): a role with Reports ON but View and Manage AP/AR Data OFF (ZZAUTOTEST ReportsNoAPAR) still sees all 6 AP/AR aging reports on /reports (A/R Aging Summary/Detail/Collection, A/P Aging Summary/Detail, A/P Unpaid Invoices). Aging reports follow the Reports permission, not AP/AR. screenshot reports-noapar.</t>
+          <t>UI: with See Financial Data ON (admin full view + TechSFD), WO lines show prices, costs, margins and labor rates — Rate ($100), Margin (%), Total ($261.54), parts prices ($3.33 etc), labor ($150). screenshot fullview-lines-admin/techview-sfd-lines.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>C26483</t>
+          <t>C26469</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26483</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26469</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data OFF hides the sensitive money fields on Edit Customer</t>
+          <t>See Financial Data OFF: money amounts, rates, costs and margins are hidden</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6448,32 +6448,32 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>UI: AP/AR Data OFF hides the sensitive money fields on Edit Customer (Credit Limit, Taxes, Default Labor Rate, Default Shop Supplies, Min, Max, Credit Terms) — same observation as C26402.</t>
+          <t>UI: with See Financial Data OFF (plain Technician), WO lines show NO money — no $ amounts, no Rate/Margin/Total columns; only tech-time hours (0.00/1.00). screenshot techview-lines-estimate.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>C26484</t>
+          <t>C26470</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26484</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26470</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data OFF still lets a user create invoices and take payments if Invoicing &amp; payments allows it</t>
+          <t>With See Financial Data OFF, Part sales and Invoicing &amp; payments stay inaccessible even with View, Create &amp; Edit and Delete on</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6488,32 +6488,32 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>UI/perms: AP/AR Data OFF still allows creating invoices/taking payments when Invoicing allows — Service Advisor has invoicingPaymentsCreateAndEdit+Delete with AP/AR off; invoicing capability is independent of AP/AR.</t>
+          <t>UI/editor enforcement: a role cannot hold Part sales or Invoicing &amp; payments with See Financial Data OFF — ticking either forces the "Enable See Financial Data?" dialog (C26471/C26474). So SFD OFF makes Part sales and Invoicing &amp; payments unreachable even if View/Create&amp;Edit/Delete were desired; the combination is prevented at save time.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>C26485</t>
+          <t>C26471</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26485</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26471</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data works independently of See Financial Data</t>
+          <t>Ticking Part sales while See Financial Data is OFF asks you to turn See Financial Data on</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6528,32 +6528,32 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>UI: See Financial Data and View and Manage AP/AR Data are separate Cross-Cutting Toggles (both present independently alongside View History Logs); AP/AR is not tied to SFD in the editor.</t>
+          <t>UI dialog: ticking Part sales while SFD off shows "Enable See Financial Data? — Part Sales requires See Financial Data. Enable it to grant this permission?" [Cancel|Enable].</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>C26486</t>
+          <t>C26472</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26486</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26472</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data OFF does not block any add/edit/delete area</t>
+          <t>'Enable See Financial Data?' dialog — Enable: turns See Financial Data on and keeps the box ticked</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6568,32 +6568,32 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>UI: AP/AR Data OFF does not block any add/edit/delete — Service Advisor (AP/AR off) still opens the editable Edit Customer modal and retains full customer/WO/parts create-edit; only the financial tabs/fields are hidden.</t>
+          <t>UI: Enable on the SFD dialog turns See Financial Data ON and keeps Part sales View+Create&amp;Edit ticked.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>C26492</t>
+          <t>C26473</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26492</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26473</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>3547</v>
+        <v>3544</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Staff Page Role Assignment</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Changing a user's role logs them out immediately</t>
+          <t>'Enable See Financial Data?' dialog — Cancel: undoes the tick</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6608,32 +6608,32 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>API/session: changing a user role logs them out immediately — the prior session is invalidated (409 Session has expired) right after the change.</t>
+          <t>UI: Cancel on the SFD dialog undoes the tick (See Financial Data off, Part sales off).</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>C26494</t>
+          <t>C26474</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26494</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26474</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>3547</v>
+        <v>3544</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Staff Page Role Assignment</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>A logged-in user is logged out immediately when their role changes</t>
+          <t>The same 'Enable See Financial Data?' dialog appears for Invoicing &amp; payments when See Financial Data is OFF</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6648,32 +6648,32 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>API/session: a logged-in user is logged out immediately when their role changes (session invalidated -&gt; 409 on next request).</t>
+          <t>UI dialog: ticking Invoicing &amp; payments while SFD off shows "Enable See Financial Data? — Invoicing &amp; Payments requires See Financial Data..." [Cancel|Enable]; Enable -&gt; SFD ON + Invoicing View+C&amp;E ON.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>C26495</t>
+          <t>C26475</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26495</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26475</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>3548</v>
+        <v>3544</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Administrator: role permissions match the expected set</t>
+          <t>Turning See Financial Data OFF asks you to also turn off the settings that depend on it</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6683,37 +6683,37 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Administrator permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI (RUN331 FAIL NOW FIXED): turning See Financial Data OFF while Invoicing on shows "Disable See Financial Data? — Disabling See Financial Data will also disable Invoicing &amp; Payments. Continue?" [Cancel|Disable] (FinancialDataDisableConfirmModal). screenshot sfd-disable-dialog.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>C26496</t>
+          <t>C27869</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26496</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27869</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>3548</v>
+        <v>3544</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Service Manager: role permissions match the expected set</t>
+          <t>Turning on Order parts while See Financial Data is OFF asks you to also turn on See Financial Data</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6723,37 +6723,37 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Service Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI dialog: ticking Order parts while SFD off shows "Enable See Financial Data? — Order Parts requires See Financial Data. Enable it to grant this permission?" [Cancel|Enable].</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>C26497</t>
+          <t>C26476</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26497</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26476</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Senior Service Advisor: role permissions match the expected set</t>
+          <t>View and Manage AP/AR Data ON shows the Unpaid Invoices, Payments and Credits tabs on a customer</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6763,37 +6763,37 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Senior Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI: role with AP/AR Data ON shows the financial tabs on a customer page — build labels are Invoices / Payments / Deposits (case prose says Unpaid Invoices/Payments/Credits; the AP/AR toggle description uses that wording, actual tab labels are Invoices/Payments/Deposits). Tabs absent when AP/AR off.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>C26498</t>
+          <t>C26477</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26498</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26477</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Service Advisor: role permissions match the expected set</t>
+          <t>View and Manage AP/AR Data ON shows the same three tabs on a vendor</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6803,37 +6803,37 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI (Parts Manager, AP/AR ON): the vendor page (/parts/vendor/{id}) shows the AP/AR tabs — Contacts, Unpaid Invoices (30), Payments (4). screenshot vendordetail-vendON.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>C26499</t>
+          <t>C26478</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26499</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26478</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Foreman: role permissions match the expected set</t>
+          <t>With Reports ON, all 6 AP/AR aging reports are listed (whether or not AP/AR is on)</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6843,37 +6843,37 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Foreman permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI (admin /reports, Reports ON): all 6 AP/AR aging reports are listed — A/R Aging Summary, A/R Aging Detail, A/R Aging Collection, A/P Aging Summary, A/P Aging Detail, A/P Unpaid Invoices. screenshot reports-admin.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>C26500</t>
+          <t>C26480</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26500</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26480</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Technician: role permissions match the expected set</t>
+          <t>View and Manage AP/AR Data OFF hides the three tabs on a customer</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6883,37 +6883,37 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI: AP/AR Data OFF (Service Advisor) — the customer page shows only Work Orders/Part Sales/Contacts/Assets/Notes; the Invoices/Payments/Deposits tabs are hidden.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>C26501</t>
+          <t>C26481</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26501</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26481</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Parts Manager: role permissions match the expected set</t>
+          <t>View and Manage AP/AR Data OFF hides the three tabs on a vendor</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6923,37 +6923,37 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Parts Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI (Service Advisor, AP/AR OFF): the same vendor page shows only the Contacts tab — Unpaid Invoices/Payments tabs are hidden. screenshot vendordetail-vendOFF.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>C26502</t>
+          <t>C26482</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26502</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26482</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Parts Technician: role permissions match the expected set</t>
+          <t>With AP/AR OFF but Reports ON, all 6 AP/AR aging reports are still listed</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -6963,37 +6963,37 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Parts Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI (RUN331 FAIL NOW FIXED): a role with Reports ON but View and Manage AP/AR Data OFF (ZZAUTOTEST ReportsNoAPAR) still sees all 6 AP/AR aging reports on /reports (A/R Aging Summary/Detail/Collection, A/P Aging Summary/Detail, A/P Unpaid Invoices). Aging reports follow the Reports permission, not AP/AR. screenshot reports-noapar.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>C26503</t>
+          <t>C26483</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26503</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26483</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Office User: role permissions match the expected set</t>
+          <t>View and Manage AP/AR Data OFF hides the sensitive money fields on Edit Customer</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -7003,37 +7003,37 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Office User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI: AP/AR Data OFF hides the sensitive money fields on Edit Customer (Credit Limit, Taxes, Default Labor Rate, Default Shop Supplies, Min, Max, Credit Terms) — same observation as C26402.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>C26504</t>
+          <t>C26484</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26504</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26484</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Sales Representative: role permissions match the expected set</t>
+          <t>View and Manage AP/AR Data OFF still lets a user create invoices and take payments if Invoicing &amp; payments allows it</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -7043,37 +7043,37 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Sales Representative permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI/perms: AP/AR Data OFF still allows creating invoices/taking payments when Invoicing allows — Service Advisor has invoicingPaymentsCreateAndEdit+Delete with AP/AR off; invoicing capability is independent of AP/AR.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>C26505</t>
+          <t>C26485</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26505</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26485</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Time Clock User: role permissions match the expected set</t>
+          <t>View and Manage AP/AR Data works independently of See Financial Data</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -7083,37 +7083,37 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Time Clock User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI: See Financial Data and View and Manage AP/AR Data are separate Cross-Cutting Toggles (both present independently alongside View History Logs); AP/AR is not tied to SFD in the editor.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>C26506</t>
+          <t>C26486</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26506</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26486</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Customer portal is on by default only for Service Advisor, Senior Service Advisor, Service Manager and Parts Manager (and Administrator)</t>
+          <t>View and Manage AP/AR Data OFF does not block any add/edit/delete area</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -7123,37 +7123,37 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (matches live per-role customerPortalPageAccess)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>customerPortalPageAccess per role confirmed live: on for Admin/SM/SSA/SA/PM; off for the rest (roles-matrix-2026-07-13).</t>
+          <t>UI: AP/AR Data OFF does not block any add/edit/delete — Service Advisor (AP/AR off) still opens the editable Edit Customer modal and retains full customer/WO/parts create-edit; only the financial tabs/fields are hidden.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>C26510</t>
+          <t>C26492</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26510</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26492</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>3549</v>
+        <v>3547</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Legacy 'Admin / Administrator' users become 'Administrator' after migration</t>
+          <t>Changing a user's role logs them out immediately</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -7168,32 +7168,32 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Live roles API: destination system role exists = "Admin" (build name; case prose says Administrator), isEditable=true, 89 users, 42 perms. Migration is a completed historical event; destination state verified (role present, editable with pencil, populated).</t>
+          <t>API/session: changing a user role logs them out immediately — the prior session is invalidated (409 Session has expired) right after the change.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>C26511</t>
+          <t>C26494</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26511</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26494</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>3549</v>
+        <v>3547</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Legacy 'Office' users become 'Office User' after migration</t>
+          <t>A logged-in user is logged out immediately when their role changes</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -7208,32 +7208,32 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Live roles API: "Office User" exists, isEditable=false (lock + eye only), 5 users, 23 perms — matches legacy Office -&gt; Office User destination.</t>
+          <t>API/session: a logged-in user is logged out immediately when their role changes (session invalidated -&gt; 409 on next request).</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>C26512</t>
+          <t>C26495</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26512</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26495</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Legacy 'Time Clock' users become 'Time Clock User' after migration</t>
+          <t>Administrator: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -7243,37 +7243,37 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Live roles API: "Time Clock User" exists, isEditable=false (lock + eye only), 11 users, 3 perms — matches legacy Time Clock -&gt; Time Clock User.</t>
+          <t>Administrator permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>C26513</t>
+          <t>C26496</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26513</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26496</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Legacy 'Service Manager' users become 'Service Manager' after migration</t>
+          <t>Service Manager: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -7283,37 +7283,37 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Live roles API: "Service Manager" exists, isEditable=true, 3 users, 35 perms.</t>
+          <t>Service Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>C26514</t>
+          <t>C26497</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26514</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26497</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Legacy 'Senior Service Advisor' users become 'Senior Service Advisor' after migration</t>
+          <t>Senior Service Advisor: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -7323,37 +7323,37 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Live roles API: "Senior Service Advisor" exists, isEditable=true, 8 users, 32 perms.</t>
+          <t>Senior Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>C26515</t>
+          <t>C26498</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26515</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26498</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Legacy 'Service Advisor' users become 'Service Advisor' after migration</t>
+          <t>Service Advisor: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -7363,37 +7363,37 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Live roles API: "Service Advisor" exists, isEditable=true, 2 users, 26 perms.</t>
+          <t>Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>C26516</t>
+          <t>C26499</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26516</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26499</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Legacy 'Foreman' users become 'Foreman' after migration</t>
+          <t>Foreman: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -7403,37 +7403,37 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Live roles API: "Foreman" exists, isEditable=true, 16 users, 23 perms.</t>
+          <t>Foreman permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>C26517</t>
+          <t>C26500</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26517</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26500</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Legacy 'Technician' users become 'Technician' after migration</t>
+          <t>Technician: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -7443,37 +7443,37 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Live roles API: "Technician" exists, isEditable=true, 66 users, 6 perms, view_mode tech (confirmed via role detail) — matches legacy Technician destination.</t>
+          <t>Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>C26518</t>
+          <t>C26501</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26518</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26501</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Legacy 'Parts Manager' users become 'Parts Manager' after migration</t>
+          <t>Parts Manager: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -7483,37 +7483,37 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Live roles API: "Parts Manager" exists, isEditable=true, 4 users, 31 perms.</t>
+          <t>Parts Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>C26519</t>
+          <t>C26502</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26519</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26502</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Legacy 'Parts Tech / Parts Technician' users become 'Parts Technician' after migration</t>
+          <t>Parts Technician: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -7523,37 +7523,37 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Live roles API: "Parts Technician" exists, isEditable=true, 10 users, 19 perms — matches legacy Parts Tech -&gt; Parts Technician.</t>
+          <t>Parts Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>C26520</t>
+          <t>C26503</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26520</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26503</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Legacy 'Sales Representative' users become 'Sales Representative' after migration</t>
+          <t>Office User: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -7563,37 +7563,37 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Live roles API: "Sales Representative" exists, isEditable=true, 15 users, 4 perms.</t>
+          <t>Office User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>C26525</t>
+          <t>C26504</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26525</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26504</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Changing a user's role logs that user out and forces them to log in again</t>
+          <t>Sales Representative: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -7603,37 +7603,37 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>UI/API: after an admin changed the Tech user role, the user existing session returned 409 "Session has expired." on the next call — the role change logs the user out and forces re-login.</t>
+          <t>Sales Representative permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>C26528</t>
+          <t>C26505</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26528</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26505</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>3550</v>
+        <v>3548</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Staff Record Settings</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>The universal clock in / out is available to any active staff member, whatever their role</t>
+          <t>Time Clock User: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -7643,37 +7643,37 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>UI: the universal Clock In control appears in the top bar for every role observed (Admin, Technician, Time Clock User) — available to any active staff member whatever their role.</t>
+          <t>Time Clock User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>C26532</t>
+          <t>C26506</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26532</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26506</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>3552</v>
+        <v>3548</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Create success message wording</t>
+          <t>Customer portal is on by default only for Service Advisor, Senior Service Advisor, Service Manager and Parts Manager (and Administrator)</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -7683,37 +7683,37 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>Roles-API-Verified (matches live per-role customerPortalPageAccess)</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>'Role created successfully.' confirmed in build.</t>
+          <t>customerPortalPageAccess per role confirmed live: on for Admin/SM/SSA/SA/PM; off for the rest (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>C26533</t>
+          <t>C26510</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26533</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26510</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Update success message wording</t>
+          <t>Legacy 'Admin / Administrator' users become 'Administrator' after migration</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -7723,37 +7723,37 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>'Role updated successfully.' confirmed in build.</t>
+          <t>Live roles API: destination system role exists = "Admin" (build name; case prose says Administrator), isEditable=true, 89 users, 42 perms. Migration is a completed historical event; destination state verified (role present, editable with pencil, populated).</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>C26534</t>
+          <t>C26511</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26534</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26511</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Deleting a custom role with 0 users shows a confirmation dialog</t>
+          <t>Legacy 'Office' users become 'Office User' after migration</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -7768,32 +7768,32 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>UI: deleting a 0-user custom role opens dialog "Confirmation — Are you sure you want to delete this role? This action cannot be undone." [Cancel|Delete]. screenshot delete-confirm-dialog.</t>
+          <t>Live roles API: "Office User" exists, isEditable=false (lock + eye only), 5 users, 23 perms — matches legacy Office -&gt; Office User destination.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>C26535</t>
+          <t>C26512</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26535</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26512</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Deleting a custom role that has users is blocked</t>
+          <t>Legacy 'Time Clock' users become 'Time Clock User' after migration</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -7808,32 +7808,32 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>UI: a custom role with users (Parth Cust1, 1 user) has no Delete option in its 3-dot menu — deletion is blocked.</t>
+          <t>Live roles API: "Time Clock User" exists, isEditable=false (lock + eye only), 11 users, 3 perms — matches legacy Time Clock -&gt; Time Clock User.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>C26536</t>
+          <t>C26513</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26536</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26513</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Turning See Financial Data on shows a confirmation dialog</t>
+          <t>Legacy 'Service Manager' users become 'Service Manager' after migration</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -7843,37 +7843,37 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>'Enable See Financial Data?' + Cancel/Enable confirmed in build (FinancialDataConfirmModal).</t>
+          <t>Live roles API: "Service Manager" exists, isEditable=true, 3 users, 35 perms.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>C26537</t>
+          <t>C26514</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26537</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26514</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Creating a role with no name is blocked with a required-field error</t>
+          <t>Legacy 'Senior Service Advisor' users become 'Senior Service Advisor' after migration</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -7888,32 +7888,32 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>UI: creating a role with no name is blocked — Create disabled and inline "Role name is a required field" error when the field is touched/cleared.</t>
+          <t>Live roles API: "Senior Service Advisor" exists, isEditable=true, 8 users, 32 perms.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>C26538</t>
+          <t>C26515</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26538</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26515</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Creating a role with the same permissions as an existing role shows a 'similar role' warning</t>
+          <t>Legacy 'Service Advisor' users become 'Service Advisor' after migration</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -7928,32 +7928,32 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>UI: creating a role with the same permissions as an existing role shows "Similar role already exists" warning with "Create Anyway" (SimilarRoleWarningModal, keyed on identical permissions).</t>
+          <t>Live roles API: "Service Advisor" exists, isEditable=true, 2 users, 26 perms.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>C26542</t>
+          <t>C26516</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26542</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26516</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>3553</v>
+        <v>3549</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Cross-Permission Combinations</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>A system role cannot be deleted</t>
+          <t>Legacy 'Foreman' users become 'Foreman' after migration</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -7963,37 +7963,37 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (all system roles deletable=false)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>deletable=false for all system roles (live roles API).</t>
+          <t>Live roles API: "Foreman" exists, isEditable=true, 16 users, 23 perms.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>C26543</t>
+          <t>C26517</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26543</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26517</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>3553</v>
+        <v>3549</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Cross-Permission Combinations</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Only Office User and Time Clock User are non-editable; every other system role (including Administrator) is editable</t>
+          <t>Legacy 'Technician' users become 'Technician' after migration</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -8003,37 +8003,37 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (editable flags match live)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Live roles API: Office User &amp; Time Clock User editable=false; all others (incl. Administrator) editable=true.</t>
+          <t>Live roles API: "Technician" exists, isEditable=true, 66 users, 6 perms, view_mode tech (confirmed via role detail) — matches legacy Technician destination.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>C26549</t>
+          <t>C26518</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26549</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26518</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>3553</v>
+        <v>3549</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Cross-Permission Combinations</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AP/AR OFF hides the sensitive customer fields on both the Edit Customer window and the customer overview</t>
+          <t>Legacy 'Parts Manager' users become 'Parts Manager' after migration</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -8048,45 +8048,605 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>UI: AP/AR Data OFF hides the sensitive customer fields on the Edit Customer modal (and the financial tabs on the customer overview) — confirmed via Service Advisor (off) vs CustAPAR (on).</t>
+          <t>Live roles API: "Parts Manager" exists, isEditable=true, 4 users, 31 perms.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
+          <t>C26519</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26519</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>3549</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Legacy 'Parts Tech / Parts Technician' users become 'Parts Technician' after migration</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Live roles API: "Parts Technician" exists, isEditable=true, 10 users, 19 perms — matches legacy Parts Tech -&gt; Parts Technician.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>C26520</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26520</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>3549</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Legacy 'Sales Representative' users become 'Sales Representative' after migration</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Live roles API: "Sales Representative" exists, isEditable=true, 15 users, 4 perms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>C26525</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26525</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>3549</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Changing a user's role logs that user out and forces them to log in again</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>UI/API: after an admin changed the Tech user role, the user existing session returned 409 "Session has expired." on the next call — the role change logs the user out and forces re-login.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>C26528</t>
+        </is>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26528</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>3550</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Staff Record Settings</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>The universal clock in / out is available to any active staff member, whatever their role</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>UI: the universal Clock In control appears in the top bar for every role observed (Admin, Technician, Time Clock User) — available to any active staff member whatever their role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>C26532</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26532</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>3552</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>User Feedback Strings</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Create success message wording</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Verified-Label (build)</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>'Role created successfully.' confirmed in build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>C26533</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26533</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>3552</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>User Feedback Strings</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Update success message wording</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Verified-Label (build)</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>'Role updated successfully.' confirmed in build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>C26534</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26534</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>3552</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>User Feedback Strings</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Deleting a custom role with 0 users shows a confirmation dialog</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>UI: deleting a 0-user custom role opens dialog "Confirmation — Are you sure you want to delete this role? This action cannot be undone." [Cancel|Delete]. screenshot delete-confirm-dialog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>C26535</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26535</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>3552</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>User Feedback Strings</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Deleting a custom role that has users is blocked</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>UI: a custom role with users (Parth Cust1, 1 user) has no Delete option in its 3-dot menu — deletion is blocked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>C26536</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26536</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>3552</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>User Feedback Strings</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Turning See Financial Data on shows a confirmation dialog</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Verified-Label (build)</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>'Enable See Financial Data?' + Cancel/Enable confirmed in build (FinancialDataConfirmModal).</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>C26537</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26537</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>3552</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>User Feedback Strings</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Creating a role with no name is blocked with a required-field error</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>UI: creating a role with no name is blocked — Create disabled and inline "Role name is a required field" error when the field is touched/cleared.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>C26538</t>
+        </is>
+      </c>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26538</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>3552</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>User Feedback Strings</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Creating a role with the same permissions as an existing role shows a 'similar role' warning</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>UI: creating a role with the same permissions as an existing role shows "Similar role already exists" warning with "Create Anyway" (SimilarRoleWarningModal, keyed on identical permissions).</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>C26542</t>
+        </is>
+      </c>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26542</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>A system role cannot be deleted</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Roles-API-Verified (all system roles deletable=false)</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>deletable=false for all system roles (live roles API).</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>C26543</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26543</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Only Office User and Time Clock User are non-editable; every other system role (including Administrator) is editable</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Roles-API-Verified (editable flags match live)</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Live roles API: Office User &amp; Time Clock User editable=false; all others (incl. Administrator) editable=true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>C26549</t>
+        </is>
+      </c>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26549</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>AP/AR OFF hides the sensitive customer fields on both the Edit Customer window and the customer overview</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>UI: AP/AR Data OFF hides the sensitive customer fields on the Edit Customer modal (and the financial tabs on the customer overview) — confirmed via Service Advisor (off) vs CustAPAR (on).</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
           <t>C26551</t>
         </is>
       </c>
-      <c r="B173" s="4" t="inlineStr">
+      <c r="B187" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/26551</t>
         </is>
       </c>
-      <c r="C173" t="n">
+      <c r="C187" t="n">
         <v>3553</v>
       </c>
-      <c r="D173" t="inlineStr">
+      <c r="D187" t="inlineStr">
         <is>
           <t>Cross-Permission Combinations</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
+      <c r="E187" t="inlineStr">
         <is>
           <t>Universal clock in/out works even for a user whose role has (almost) no permissions</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
         <is>
           <t>UI: the Time Clock User role (only 3 perms: scheduleView/timesheetsView/workOrdersView) still shows the universal Clock In control — universal clock in is not gated by role/permissions.</t>
         </is>
@@ -8266,6 +8826,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B171" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B172" r:id="rId171"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B187" r:id="rId186"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8277,7 +8851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8575,12 +9149,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C26389</t>
+          <t>C26391</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26389</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26391</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -8593,7 +9167,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Work order lines are visible whenever Work orders View is ON</t>
+          <t>Work order lines Delete allows removing lines</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -8603,24 +9177,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); no-WOL-View-column build-verified</t>
+          <t>Blocked-UI: WOL Delete role shows line-selection checkboxes but no line delete/remove button was exposed (selecting a line revealed no bulk-delete control; no per-line delete icon). Line-delete affordance not reachable in the harness; needs the expanded-line editor delete control or the line-delete endpoint confirmed.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>WOL View comes from WO View (build-verified). Behavior needs live UI.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C26390</t>
+          <t>C27866</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26390</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27866</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -8633,7 +9207,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Work order lines Create &amp; Edit allows adding, editing, moving parts, authorizing and managing part requests</t>
+          <t>A default Technician (with Work order lines Create &amp; Edit) can bulk-complete another tech's line via Set Line Status</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -8643,24 +9217,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: needs multiple lines assigned to a DIFFERENT technician plus the Set Line Status bulk control; Set Line Status was not present on the test WO for the Technician role. Requires seeding another tech-s lines + reaching the bulk Set Line Status action.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded; SV-ref/URL/403 jargon stripped. Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C26391</t>
+          <t>C27870</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26391</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27870</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -8673,7 +9247,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Work order lines Delete allows removing lines</t>
+          <t>Work order lines Create &amp; Edit lets the user mark a core OK/Not-OK and add line history</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -8683,37 +9257,37 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: needs a work order line with a cored part to expose the core OK/Not-OK control; no cored-part line was present on the test WOs. Requires seeding a core part on a line (New Part Request with a cored catalog PN) then observe the core control + line history for a WOL C&amp;E role.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Needs live UI with a cored part.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C26392</t>
+          <t>C26395</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26392</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26395</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3535</v>
+        <v>3536</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Work Order Lines Permissions</t>
+          <t>Schedule Permissions</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Work orders View OFF makes work order lines unreachable</t>
+          <t>Schedule Create &amp; Edit allows creating, changing and dragging appointments</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -8735,25 +9309,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C26393</t>
+          <t>C26396</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26393</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26396</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3535</v>
+        <v>3536</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Work Order Lines Permissions</t>
+          <t>Schedule Permissions</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Work order lines are read-only when Create &amp; Edit is OFF</t>
+          <t>Schedule Delete allows removing appointments</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -8775,25 +9349,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C27271</t>
+          <t>C27867</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27271</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27867</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3535</v>
+        <v>3536</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Work Order Lines Permissions</t>
+          <t>Schedule Permissions</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>The Build Lines entry point is hidden for a Work Orders View-only role</t>
+          <t>A Schedule Create &amp; Edit only role can open 'Assign existing work order' and the unscheduled work order list loads</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -8803,37 +9377,37 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + ShopCoach on)</t>
+          <t>Blocked-UI (needs seeded Schedule-only role)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Reworded; element-id jargon stripped. Needs live UI.</t>
+          <t>Reworded; API endpoint jargon stripped. Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C27272</t>
+          <t>C26399</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27272</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26399</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3535</v>
+        <v>3537</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Work Order Lines Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>The Build Lines entry point is shown for a role with Work order lines Create &amp; Edit</t>
+          <t>Customers Create &amp; Edit allows creating customers, contacts and vehicles</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -8843,37 +9417,37 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + ShopCoach on)</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Reworded; element-id jargon stripped. Needs live UI.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C27866</t>
+          <t>C26400</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27866</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26400</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3535</v>
+        <v>3537</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Work Order Lines Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>A default Technician (with Work order lines Create &amp; Edit) can bulk-complete another tech's line via Set Line Status</t>
+          <t>Customers Delete removes the customer record</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -8883,37 +9457,37 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs default Technician role + seeded WO line)</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Reworded; SV-ref/URL/403 jargon stripped. Needs live UI.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C27870</t>
+          <t>C26401</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27870</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26401</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3535</v>
+        <v>3537</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Work Order Lines Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Work order lines Create &amp; Edit lets the user mark a core OK/Not-OK and add line history</t>
+          <t>Customers Delete does NOT let the user delete customer payments (that needs Invoicing &amp; payments Delete)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -8923,37 +9497,37 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + core part)</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Needs live UI with a cored part.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C26395</t>
+          <t>C26405</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26395</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26405</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3536</v>
+        <v>3537</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Schedule Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Schedule Create &amp; Edit allows creating, changing and dragging appointments</t>
+          <t>Customer names still show on work orders and invoices even when Customers is hidden</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -8975,25 +9549,25 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C26396</t>
+          <t>C26412</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26396</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26412</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3536</v>
+        <v>3538</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Schedule Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Schedule Delete allows removing appointments</t>
+          <t>Part sales Delete lets the user delete part sales and reverse part sales invoices</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -9003,7 +9577,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: Part sales Delete affordance (delete/reverse a part sale) not located in this pass — the part-sale row menu did not open in the harness; needs the part-sale detail-page delete control with a with/without partSalesDelete contrast.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -9015,25 +9589,25 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C27867</t>
+          <t>C26415</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27867</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26415</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3536</v>
+        <v>3538</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Schedule Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>A Schedule Create &amp; Edit only role can open 'Assign existing work order' and the unscheduled work order list loads</t>
+          <t>Catalog and Inventory Delete removes catalog parts</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -9043,37 +9617,37 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded Schedule-only role)</t>
+          <t>Blocked-UI: Catalog Delete affordance not located — the catalogue row more_vert menu did not open in the harness; needs the catalog-part detail delete control (Parts Manager has catalogInventoryDelete) vs a no-delete role.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Reworded; API endpoint jargon stripped. Needs live UI.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C26399</t>
+          <t>C26418</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26399</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26418</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3537</v>
+        <v>3538</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Customers Create &amp; Edit allows creating customers, contacts and vehicles</t>
+          <t>Vendor and order management Delete lets the user delete vendors and purchase orders and reverse vendor transactions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -9083,37 +9657,37 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: Vendor/PO Delete affordance (delete vendor/PO, reverse vendor txn) not located this pass; needs the vendor/PO detail delete control with/without vendorOrderManagementDelete.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Needs live UI; AP/AR dependency on the vendor Payments tab is build-observed.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C26400</t>
+          <t>C26419</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26400</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26419</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3537</v>
+        <v>3538</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Customers Delete removes the customer record</t>
+          <t>Returning a part to inventory (restocking) is controlled by Vendor and order management</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -9123,7 +9697,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: restocking (return part to inventory) control not reached — needs a WO/PO with a picked part to exercise the return-to-inventory action gated by Vendor and order management.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -9135,25 +9709,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C26401</t>
+          <t>C26422</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26401</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26422</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3537</v>
+        <v>3539</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Customers Delete does NOT let the user delete customer payments (that needs Invoicing &amp; payments Delete)</t>
+          <t>Invoicing &amp; payments Delete lets the user delete payments and void transactions (but not reverse invoices)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -9163,7 +9737,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: per-payment delete/void affordance not located on the WO Finance tab in the harness (payment rows/menus did not expose a delete/void control); needs the invoice-&gt;payment detail view with a with/without invoicingPaymentsDelete contrast.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -9175,25 +9749,25 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C26405</t>
+          <t>C26423</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26405</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26423</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3537</v>
+        <v>3539</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Customer names still show on work orders and invoices even when Customers is hidden</t>
+          <t>Deleting a customer payment needs Invoicing &amp; payments Delete, not Customers Delete</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -9203,7 +9777,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: deleting a customer payment (gated by Invoicing Delete not Customers Delete) needs the payment delete control located; the Finance-tab payment row menu was not reachable this pass.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -9215,25 +9789,25 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C26412</t>
+          <t>C26427</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26412</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26427</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3538</v>
+        <v>3539</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Part sales Delete lets the user delete part sales and reverse part sales invoices</t>
+          <t>The Send to Terminal action needs Invoicing &amp; payments Create &amp; Edit</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -9243,7 +9817,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Blocked-UI: Part sales Delete affordance (delete/reverse a part sale) not located in this pass — the part-sale row menu did not open in the harness; needs the part-sale detail-page delete control with a with/without partSalesDelete contrast.</t>
+          <t>Blocked-UI: Send to Terminal was not shown at the WO Finance-tab level even for a role with Invoicing C&amp;E + Customer Portal (Service Advisor); it appears within the take-payment flow on an open invoice — needs seeding an open invoice + entering the payment dialog.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -9255,25 +9829,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C26415</t>
+          <t>C27871</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26415</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27871</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3538</v>
+        <v>3539</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Catalog and Inventory Delete removes catalog parts</t>
+          <t>Deleting or cancelling a return is controlled by Invoicing &amp; payments Delete</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -9283,37 +9857,37 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Blocked-UI: Catalog Delete affordance not located — the catalogue row more_vert menu did not open in the harness; needs the catalog-part detail delete control (Parts Manager has catalogInventoryDelete) vs a no-delete role.</t>
+          <t>Blocked-UI: deleting/cancelling a return (gated by Invoicing Delete) needs a part return seeded first (create return via admin) then observe the delete/cancel gate; return flow not seeded this pass.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded; SV-ref/element-id jargon stripped.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C26418</t>
+          <t>C29434</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26418</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29434</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3538</v>
+        <v>3539</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vendor and order management Delete lets the user delete vendors and purchase orders and reverse vendor transactions</t>
+          <t>Send to Terminal needs Invoicing &amp; payments Create &amp; Edit AND Customer portal ON</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -9323,37 +9897,37 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Blocked-UI: Vendor/PO Delete affordance (delete vendor/PO, reverse vendor txn) not located this pass; needs the vendor/PO detail delete control with/without vendorOrderManagementDelete.</t>
+          <t>Blocked-UI: same as C26427 — Send to Terminal (needs Invoicing C&amp;E AND Customer Portal) is in the payment dialog, not reached; needs an open invoice + payment flow to observe both-gates.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Needs live UI; AP/AR dependency on the vendor Payments tab is build-observed.</t>
+          <t>Reworded; feature-flag/element-id/SV jargon stripped.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C26419</t>
+          <t>C29438</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26419</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29438</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3538</v>
+        <v>3539</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Returning a part to inventory (restocking) is controlled by Vendor and order management</t>
+          <t>Invoicing &amp; payments Create &amp; Edit gives the edit control on the work order Financial Info card</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -9363,37 +9937,37 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Blocked-UI: restocking (return part to inventory) control not reached — needs a WO/PO with a picked part to exercise the return-to-inventory action gated by Vendor and order management.</t>
+          <t>Blocked-UI: the WO Financial Info card is present but no edit control was detected for either an Invoicing-C&amp;E role or a view-only role on a PAID WO (balance $0, editing locked). Needs an open/unpaid WO with a balance to observe the C&amp;E edit control.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded; element-id/SV jargon stripped.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C26422</t>
+          <t>C26430</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26422</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26430</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Invoicing &amp; payments Delete lets the user delete payments and void transactions (but not reverse invoices)</t>
+          <t>Timesheets View only: timesheet entries are read-only</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -9403,37 +9977,37 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Blocked-UI: per-payment delete/void affordance not located on the WO Finance tab in the harness (payment rows/menus did not expose a delete/void control); needs the invoice-&gt;payment detail view with a with/without invoicingPaymentsDelete contrast.</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Read-only behavior needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C26423</t>
+          <t>C26431</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26423</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26431</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deleting a customer payment needs Invoicing &amp; payments Delete, not Customers Delete</t>
+          <t>Timesheets Create &amp; Edit lets the user edit entries</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -9443,37 +10017,37 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Blocked-UI: deleting a customer payment (gated by Invoicing Delete not Customers Delete) needs the payment delete control located; the Finance-tab payment row menu was not reachable this pass.</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Edit behavior needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C26427</t>
+          <t>C26433</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26427</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26433</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>The Send to Terminal action needs Invoicing &amp; payments Create &amp; Edit</t>
+          <t>Timesheets View OFF with Reports ON: the timesheet activities report is still available</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -9483,37 +10057,37 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Blocked-UI: Send to Terminal was not shown at the WO Finance-tab level even for a role with Invoicing C&amp;E + Customer Portal (Service Advisor); it appears within the take-payment flow on an open invoice — needs seeding an open invoice + entering the payment dialog.</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Report access needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C27871</t>
+          <t>C26434</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27871</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26434</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deleting or cancelling a return is controlled by Invoicing &amp; payments Delete</t>
+          <t>All Timesheets permissions OFF and Reports OFF: no timesheet navigation anywhere</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -9523,37 +10097,37 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Blocked-UI: deleting/cancelling a return (gated by Invoicing Delete) needs a part return seeded first (create return via admin) then observe the delete/cancel gate; return flow not seeded this pass.</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Reworded; SV-ref/element-id jargon stripped.</t>
+          <t>Nav-hide needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>C29434</t>
+          <t>C27394</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29434</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27394</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Send to Terminal needs Invoicing &amp; payments Create &amp; Edit AND Customer portal ON</t>
+          <t>A clock-capable role without Timesheets View can still see and open My Timesheets</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -9563,37 +10137,37 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Blocked-UI: same as C26427 — Send to Terminal (needs Invoicing C&amp;E AND Customer Portal) is in the payment dialog, not reached; needs an open invoice + payment flow to observe both-gates.</t>
+          <t>Blocked-UI (needs seeded clock-capable role)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Reworded; feature-flag/element-id/SV jargon stripped.</t>
+          <t>Reworded, jargon stripped; needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>C29438</t>
+          <t>C26437</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29438</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26437</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3539</v>
+        <v>3541</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Invoicing &amp; payments Create &amp; Edit gives the edit control on the work order Financial Info card</t>
+          <t>Customer portal ON lets the user manage the customer portal</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -9603,37 +10177,37 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Blocked-UI: the WO Financial Info card is present but no edit control was detected for either an Invoicing-C&amp;E role or a view-only role on a PAID WO (balance $0, editing locked). Needs an open/unpaid WO with a balance to observe the C&amp;E edit control.</t>
+          <t>Blocked-UI (needs seeded role); toggle label 'Customer portal' build-verified</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Reworded; element-id/SV jargon stripped.</t>
+          <t>Toggle 'Customer portal' confirmed in build. Manage behavior needs live check.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>C26430</t>
+          <t>C26438</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26430</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26438</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3540</v>
+        <v>3541</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Timesheets View only: timesheet entries are read-only</t>
+          <t>Customer portal OFF hides the customer portal from navigation</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -9648,32 +10222,32 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Read-only behavior needs live UI.</t>
+          <t>Nav-hide needs live check.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>C26431</t>
+          <t>C26439</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26431</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26439</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3540</v>
+        <v>3541</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Timesheets Create &amp; Edit lets the user edit entries</t>
+          <t>Billing Portal ON lets the user manage the billing portal</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -9683,37 +10257,37 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role); toggle label 'Billing Portal' build-verified</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Edit behavior needs live UI.</t>
+          <t>Toggle 'Billing Portal' confirmed in build. Manage behavior needs live check.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C26433</t>
+          <t>C26440</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26433</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26440</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3540</v>
+        <v>3541</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Timesheets View OFF with Reports ON: the timesheet activities report is still available</t>
+          <t>Billing Portal OFF hides the Billing Portal item in the Settings area</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -9728,32 +10302,32 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Report access needs live UI.</t>
+          <t>Nav-hide needs live check.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C26434</t>
+          <t>C26450</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26434</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26450</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3540</v>
+        <v>3542</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>All Timesheets permissions OFF and Reports OFF: no timesheet navigation anywhere</t>
+          <t>View/Manage Wages ON lets the user manage wages</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -9763,37 +10337,37 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: wage rate fields live on the Edit Staff Member profile, which is not reachable in this harness (the staff row action opens Manage-staff-enrollments, not the profile/wage editor — same limitation as C26356/C26490/C26491). Role has settingsWages; needs the staff profile editor opened (real browser) to confirm wage fields shown/editable.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Nav-hide needs live UI.</t>
+          <t>Toggle 'View/Manage Wages' confirmed in build. Wage editing needs live check.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C27394</t>
+          <t>C26460</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27394</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26460</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3540</v>
+        <v>3543</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>A clock-capable role without Timesheets View can still see and open My Timesheets</t>
+          <t>Tech view: the parts request form shows fewer fields</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -9803,37 +10377,37 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded clock-capable role)</t>
+          <t>Blocked-UI: needs the New Part Request form opened in tech view vs full view to compare field counts; the lines screen is drivable but the request-form modal step was not reached this pass.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Reworded, jargon stripped; needs live UI.</t>
+          <t>precise reason logged</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C26437</t>
+          <t>C26461</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26437</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26461</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3541</v>
+        <v>3543</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Customer portal ON lets the user manage the customer portal</t>
+          <t>Tech view: the user can add new work order lines but cannot edit existing ones</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -9843,37 +10417,37 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); toggle label 'Customer portal' build-verified</t>
+          <t>Blocked-UI: New Line (add) confirmed present in tech view, but the existing-line read-only lock was not directly exercised (would require attempting to edit a pending line inline). Precise follow-up: open a pending line editor as the tech.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Toggle 'Customer portal' confirmed in build. Manage behavior needs live check.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C26438</t>
+          <t>C26462</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26438</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26462</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3541</v>
+        <v>3543</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Customer portal OFF hides the customer portal from navigation</t>
+          <t>Tech view: a line becomes read-only once its authorization is approved</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -9883,37 +10457,37 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: approved-WO lines showed only tech status actions (Complete/Story/Start) with no edit control (consistent with read-only), but the pending-&gt;approved edit-lock transition was not directly exercised.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Nav-hide needs live check.</t>
+          <t>Needs live UI + a second user.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C26439</t>
+          <t>C26466</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26439</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26466</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3541</v>
+        <v>3543</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Billing Portal ON lets the user manage the billing portal</t>
+          <t>Full View: a user who can approve lines sees the 'Send to Portal' button</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -9923,37 +10497,37 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); toggle label 'Billing Portal' build-verified</t>
+          <t>Blocked-UI: Send to Portal was NOT found on the full-view (admin) lines page body; it is likely in the WO header more_vert menu or gated by WO state — needs the header action menu expanded to confirm.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Toggle 'Billing Portal' confirmed in build. Manage behavior needs live check.</t>
+          <t>Send-to-Portal flow needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C26440</t>
+          <t>C26479</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26440</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26479</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3541</v>
+        <v>3545</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Billing Portal OFF hides the Billing Portal item in the Settings area</t>
+          <t>View and Manage AP/AR Data ON allows paying several invoices at once from the Unpaid Invoices tab</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -9963,37 +10537,37 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role + live payment)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Nav-hide needs live check.</t>
+          <t>Bulk payment needs live UI + payment (create-customer-payment 500s intermittently per prior run).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C26445</t>
+          <t>C26488</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26445</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26488</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3542</v>
+        <v>3546</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>View History Logs</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>App Settings ON gives access to the admin pages</t>
+          <t>View History Logs ON: work order history and line history are visible (work orders only)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -10003,37 +10577,37 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); page names build-verified</t>
+          <t>Blocked-UI (needs seeded role); 'View History Logs' toggle build-verified</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>App Settings gates Departments/Settings/Staff/Roles &amp; Permissions/Locations (build route metadata).</t>
+          <t>Cross-toggle 'View History Logs' confirmed in build. History visibility needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>C26446</t>
+          <t>C26489</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26446</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26489</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3542</v>
+        <v>3546</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>View History Logs</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Service ON gives access to the Service configuration pages</t>
+          <t>View History Logs OFF: work order history and line history are hidden (work orders only)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -10043,37 +10617,37 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); page names build-verified</t>
+          <t>Blocked-UI (needs seeded role); labels build-verified</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Service gates Canned Lines/Inspection Templates/Labour Types/Vehicle Types (build route metadata).</t>
+          <t>viewHistoryLogs also gates the 'Part History' page under Parts (build route metadata). History-hide needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>C26447</t>
+          <t>C26490</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26447</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26490</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3542</v>
+        <v>3547</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Parts ON gives access to the Parts configuration pages</t>
+          <t>The Staff role dropdown groups roles into System Roles and Custom Roles</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -10083,37 +10657,37 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); page names build-verified</t>
+          <t>Blocked-UI: the Edit Staff Member Role dropdown (System/Custom grouping) was not reached — the staff row click opened Manage-staff-enrollments. Follow-up: locate the Edit Staff Member action, open the Role selector.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Parts gates Bins/Categories/Pricing (build route metadata).</t>
+          <t>11 system roles confirmed in live roles list (was '12'). Grouping labels need live Staff page.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>C26448</t>
+          <t>C26491</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26448</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26491</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3542</v>
+        <v>3547</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Finance ON shows the Finance pages, and Integrations ON shows QuickBooks, IBS and Open API</t>
+          <t>The View Permissions button next to the role selector opens the Permission Summary</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -10123,37 +10697,37 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); page names build-verified</t>
+          <t>Blocked-UI: View Permissions eye next to the staff Role selector not reached (same Edit-Staff-Member surface as C26490).</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Finance gates Payment Methods/Taxes; Integrations gates IBS/Open API/QuickBooks (build route metadata).</t>
+          <t>'View Permissions' confirmed in build. Needs live Staff page.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>C26449</t>
+          <t>C26493</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26449</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26493</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3542</v>
+        <v>3547</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Data Import ON gives access to the Imports pages</t>
+          <t>If a role change fails, the user keeps their previous role</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -10163,37 +10737,37 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); page names build-verified</t>
+          <t>Blocked-UI: forcing a failed role change (to confirm the user keeps the prior role) requires inducing a server error on /change; not reproducible on demand this pass.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Data Import gates Contacts/Inventory/Invoices/Vehicles/Vendors Import (build route metadata).</t>
+          <t>Failed-save path needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>C26450</t>
+          <t>C26526</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26450</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26526</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3542</v>
+        <v>3550</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Staff Record Settings</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>View/Manage Wages ON lets the user manage wages</t>
+          <t>Whether a technician can be scheduled depends on their department, not their role</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -10203,37 +10777,37 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); toggle label 'View/Manage Wages' build-verified</t>
+          <t>Blocked-UI (needs two seeded users + departments)</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Toggle 'View/Manage Wages' confirmed in build. Wage editing needs live check.</t>
+          <t>Department-gated scheduling needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>C26451</t>
+          <t>C26527</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26451</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26527</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3542</v>
+        <v>3550</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Staff Record Settings</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>The Settings sub-toggles work independently (Service on, Finance off)</t>
+          <t>Clocking in on a work order line depends on the per-staff Time Clock setting</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -10243,37 +10817,37 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs two seeded users)</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Needs live check.</t>
+          <t>Per-staff Time Clock gating needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>C29273</t>
+          <t>C26539</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29273</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26539</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3542</v>
+        <v>3552</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>User Feedback Strings</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>The Integrations admin pages depend on the Integrations sub-toggle, not on Finance</t>
+          <t>Reassigning a staff member's role updates the row with no success message (billing note in the window)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -10283,37 +10857,37 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs two seeded roles)</t>
+          <t>Blocked-UI (needs live Staff page); billing note not re-captured this pass</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Steps-Separated case; reworded to layman, stripped element-id/URL jargon. Needs live UI.</t>
+          <t>No-toast-on-reassign + billing note need live Staff page (EditStaffMember chunk not fetched).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C29274</t>
+          <t>C26540</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29274</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26540</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3542</v>
+        <v>3553</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Cross-Permission Combinations</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>The QuickBooks connection check does not run for roles without Integrations</t>
+          <t>A role with all permissions off blocks the user from every feature</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10323,37 +10897,37 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs live role editor / roles list)</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Steps-Separated case; reworded to layman. Needs live UI.</t>
+          <t>Needs seeded role.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C26460</t>
+          <t>C26541</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26460</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26541</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3543</v>
+        <v>3553</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Cross-Permission Combinations</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Tech view: the parts request form shows fewer fields</t>
+          <t>A role with all permissions on behaves like Administrator but is still a custom role</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10363,37 +10937,37 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Blocked-UI: needs the New Part Request form opened in tech view vs full view to compare field counts; the lines screen is drivable but the request-form modal step was not reached this pass.</t>
+          <t>Blocked-UI (needs live role editor / roles list)</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>precise reason logged</t>
+          <t>Needs seeded role.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>C26461</t>
+          <t>C26544</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26461</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26544</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3543</v>
+        <v>3553</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Cross-Permission Combinations</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Tech view: the user can add new work order lines but cannot edit existing ones</t>
+          <t>Being unable to open Customers does not stop a user from picking a customer when creating a work order</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10403,37 +10977,37 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Blocked-UI: New Line (add) confirmed present in tech view, but the existing-line read-only lock was not directly exercised (would require attempting to edit a pending line inline). Precise follow-up: open a pending line editor as the tech.</t>
+          <t>Blocked-UI (needs live role editor / roles list)</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Needs seeded role.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>C26462</t>
+          <t>C26545</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26462</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26545</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3543</v>
+        <v>3553</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Cross-Permission Combinations</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tech view: a line becomes read-only once its authorization is approved</t>
+          <t>A Page Access toggle that is off overrides the add/edit/delete boxes inside it</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10443,37 +11017,37 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Blocked-UI: approved-WO lines showed only tech status actions (Complete/Story/Start) with no edit control (consistent with read-only), but the pending-&gt;approved edit-lock transition was not directly exercised.</t>
+          <t>Blocked-UI (needs live role editor / roles list)</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Needs live UI + a second user.</t>
+          <t>Needs seeded role.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>C26466</t>
+          <t>C26548</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26466</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26548</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3543</v>
+        <v>3553</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Cross-Permission Combinations</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Full View: a user who can approve lines sees the 'Send to Portal' button</t>
+          <t>View off with Create &amp; Edit on is prevented by the tick-cascade</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10483,37 +11057,37 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Blocked-UI: Send to Portal was NOT found on the full-view (admin) lines page body; it is likely in the WO header more_vert menu or gated by WO state — needs the header action menu expanded to confirm.</t>
+          <t>Blocked-UI (needs live editor); cascade rule</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Send-to-Portal flow needs live UI.</t>
+          <t>Needs live editor; matches cascade rules.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C26479</t>
+          <t>C26550</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26479</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26550</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3545</v>
+        <v>3553</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>Cross-Permission Combinations</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data ON allows paying several invoices at once from the Unpaid Invoices tab</t>
+          <t>The last Administrator cannot be left with zero users</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10523,570 +11097,10 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + live payment)</t>
+          <t>Blocked-UI (needs live role editor / roles list)</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
-        <is>
-          <t>Bulk payment needs live UI + payment (create-customer-payment 500s intermittently per prior run).</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>C26488</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26488</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>3546</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>View History Logs</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>View History Logs ON: work order history and line history are visible (work orders only)</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs seeded role); 'View History Logs' toggle build-verified</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Cross-toggle 'View History Logs' confirmed in build. History visibility needs live UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>C26489</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26489</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>3546</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>View History Logs</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>View History Logs OFF: work order history and line history are hidden (work orders only)</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs seeded role); labels build-verified</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>viewHistoryLogs also gates the 'Part History' page under Parts (build route metadata). History-hide needs live UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>C26490</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26490</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>3547</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Staff Page Role Assignment</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>The Staff role dropdown groups roles into System Roles and Custom Roles</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Blocked-UI: the Edit Staff Member Role dropdown (System/Custom grouping) was not reached — the staff row click opened Manage-staff-enrollments. Follow-up: locate the Edit Staff Member action, open the Role selector.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>11 system roles confirmed in live roles list (was '12'). Grouping labels need live Staff page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>C26491</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26491</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>3547</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Staff Page Role Assignment</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>The View Permissions button next to the role selector opens the Permission Summary</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Blocked-UI: View Permissions eye next to the staff Role selector not reached (same Edit-Staff-Member surface as C26490).</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>'View Permissions' confirmed in build. Needs live Staff page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>C26493</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26493</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>3547</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Staff Page Role Assignment</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>If a role change fails, the user keeps their previous role</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Blocked-UI: forcing a failed role change (to confirm the user keeps the prior role) requires inducing a server error on /change; not reproducible on demand this pass.</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Failed-save path needs live UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>C26526</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26526</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>3550</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Staff Record Settings</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Whether a technician can be scheduled depends on their department, not their role</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs two seeded users + departments)</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Department-gated scheduling needs live UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>C26527</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26527</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>3550</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Staff Record Settings</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Clocking in on a work order line depends on the per-staff Time Clock setting</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs two seeded users)</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Per-staff Time Clock gating needs live UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>C26539</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26539</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>3552</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>User Feedback Strings</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Reassigning a staff member's role updates the row with no success message (billing note in the window)</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live Staff page); billing note not re-captured this pass</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>No-toast-on-reassign + billing note need live Staff page (EditStaffMember chunk not fetched).</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>C26540</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26540</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>A role with all permissions off blocks the user from every feature</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Needs seeded role.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>C26541</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26541</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>A role with all permissions on behaves like Administrator but is still a custom role</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Needs seeded role.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>C26544</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26544</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Being unable to open Customers does not stop a user from picking a customer when creating a work order</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Needs seeded role.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>C26545</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26545</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>A Page Access toggle that is off overrides the add/edit/delete boxes inside it</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Needs seeded role.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>C26548</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26548</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>View off with Create &amp; Edit on is prevented by the tick-cascade</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live editor); cascade rule</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Needs live editor; matches cascade rules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>C26550</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26550</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>The last Administrator cannot be left with zero users</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
         <is>
           <t>Needs live UI; invariant to confirm.</t>
         </is>
@@ -11149,20 +11163,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B70" r:id="rId69"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15134,17 +15134,17 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); no-WOL-View-column build-verified</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>WOL View comes from WO View (build-verified). Behavior needs live UI.</t>
+          <t>UI (Time Clock User = WO View only): work order lines are visible (line items/labor/parts) but there is no New Line/add option and no edit controls — lines visible whenever WO View is on. screenshot wol-tcuLines.</t>
         </is>
       </c>
     </row>
@@ -15174,17 +15174,17 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>UI (role WO View + Work order lines Create&amp;Edit): the lines screen shows New Line + Build Lines — the user can add/edit lines (add and line management affordances present). screenshot wol-wolce.</t>
         </is>
       </c>
     </row>
@@ -15219,7 +15219,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: WOL Delete role shows line-selection checkboxes but no line delete/remove button was exposed (selecting a line revealed no bulk-delete control; no per-line delete icon). Line-delete affordance not reachable in the harness; needs the expanded-line editor delete control or the line-delete endpoint confirmed.</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -15254,17 +15254,17 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>UI (Sales Rep = no workOrdersView): Work Orders is hidden from nav and /workorders redirects to /reports, so no work order (and therefore no work order lines) is reachable. WO View OFF makes WO lines unreachable.</t>
         </is>
       </c>
     </row>
@@ -15294,17 +15294,17 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>UI (WO View only, no WOL Create&amp;Edit): no Add line option and existing line fields are read-only (no New Line, no edit affordances). screenshot wol-tcuLines.</t>
         </is>
       </c>
     </row>
@@ -15334,17 +15334,17 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + ShopCoach on)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Reworded; element-id jargon stripped. Needs live UI.</t>
+          <t>UI (WO View-only role): the Build Lines entry point is not shown (buildLines=false).</t>
         </is>
       </c>
     </row>
@@ -15374,17 +15374,17 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + ShopCoach on)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Reworded; element-id jargon stripped. Needs live UI.</t>
+          <t>UI (role with Work order lines Create&amp;Edit): the Build Lines entry point is shown (Build Lines button present).</t>
         </is>
       </c>
     </row>
@@ -15419,7 +15419,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs default Technician role + seeded WO line)</t>
+          <t>Blocked-UI: needs multiple lines assigned to a DIFFERENT technician plus the Set Line Status bulk control; Set Line Status was not present on the test WO for the Technician role. Requires seeding another tech-s lines + reaching the bulk Set Line Status action.</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -15459,7 +15459,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + core part)</t>
+          <t>Blocked-UI: needs a work order line with a cored part to expose the core OK/Not-OK control; no cored-part line was present on the test WOs. Requires seeding a core part on a line (New Part Request with a cored catalog PN) then observe the core control + line history for a WOL C&amp;E role.</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -17814,17 +17814,17 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); page names build-verified</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>App Settings gates Departments/Settings/Staff/Roles &amp; Permissions/Locations (build route metadata).</t>
+          <t>UI (role settingsApp): the SETTINGS admin group is present — Settings, Staff, Roles &amp; Permissions, Locations, Departments. screenshot settings-SetX.</t>
         </is>
       </c>
     </row>
@@ -17854,17 +17854,17 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); page names build-verified</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Service gates Canned Lines/Inspection Templates/Labour Types/Vehicle Types (build route metadata).</t>
+          <t>UI (role settingsService): the SERVICE group is present — Labor Rates, Canned Lines, Asset Types, Inspection Templates. screenshot settings-SetX.</t>
         </is>
       </c>
     </row>
@@ -17894,17 +17894,17 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); page names build-verified</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Parts gates Bins/Categories/Pricing (build route metadata).</t>
+          <t>UI (role settingsParts): the PARTS config group is present — Pricing, Bin Locations, Categories. screenshot settings-SetX.</t>
         </is>
       </c>
     </row>
@@ -17934,17 +17934,17 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); page names build-verified</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Finance gates Payment Methods/Taxes; Integrations gates IBS/Open API/QuickBooks (build route metadata).</t>
+          <t>UI: Finance ON shows the FINANCE group (Payment Methods, Taxes) [SetFin]; Integrations ON shows the INTEGRATIONS group (IBS, Open API; QuickBooks gated under Integrations) [SetAppIntg]. Roles without each toggle lack the respective group. screenshot settings-SetFin/settings-SetAppIntg.</t>
         </is>
       </c>
     </row>
@@ -17974,17 +17974,17 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); page names build-verified</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Data Import gates Contacts/Inventory/Invoices/Vehicles/Vendors Import (build route metadata).</t>
+          <t>UI (role settingsDataImport): the IMPORTS group is present — Contacts, Assets, Vendors, Inventory, Invoices. screenshot settings-SetX.</t>
         </is>
       </c>
     </row>
@@ -18019,7 +18019,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); toggle label 'View/Manage Wages' build-verified</t>
+          <t>Blocked-UI: wage rate fields live on the Edit Staff Member profile, which is not reachable in this harness (the staff row action opens Manage-staff-enrollments, not the profile/wage editor — same limitation as C26356/C26490/C26491). Role has settingsWages; needs the staff profile editor opened (real browser) to confirm wage fields shown/editable.</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -18054,17 +18054,17 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Needs live check.</t>
+          <t>UI (role with Service ON, Finance OFF = SetX): the SERVICE pages show and there is NO FINANCE group — the Settings sub-toggles work independently.</t>
         </is>
       </c>
     </row>
@@ -18134,17 +18134,17 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs two seeded roles)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Steps-Separated case; reworded to layman, stripped element-id/URL jargon. Needs live UI.</t>
+          <t>UI: a Finance-only role (settingsFinance, no settingsIntegrations = SetFin) shows the FINANCE group (Payment Methods, Taxes) but NO INTEGRATIONS group (no IBS/Open API/QuickBooks) — Integrations admin pages depend on the Integrations sub-toggle, not on Finance. screenshot settings-SetFin.</t>
         </is>
       </c>
     </row>
@@ -18174,17 +18174,17 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Steps-Separated case; reworded to layman. Needs live UI.</t>
+          <t>UI (inference from gating): QuickBooks lives under the INTEGRATIONS group which is only shown for roles with settingsIntegrations (present for SetAppIntg, absent for SetX/SetFin). Roles without Integrations never reach the QuickBooks surface, so the QuickBooks connection check is not triggered for them. (The background check API call itself is not directly observable in the harness; verified via the Integrations gating.)</t>
         </is>
       </c>
     </row>

--- a/build/custom-roles-run/CustomRoles_WordingVIU_2026-07-13.xlsx
+++ b/build/custom-roles-run/CustomRoles_WordingVIU_2026-07-13.xlsx
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>186</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -977,10 +977,10 @@
         </is>
       </c>
       <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="n">
         <v>0</v>
-      </c>
-      <c r="C33" t="n">
-        <v>2</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -1157,7 +1157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H187"/>
+  <dimension ref="A1:H198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5335,12 +5335,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>C26432</t>
+          <t>C26430</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26432</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26430</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Clock in / clock out is always available, whatever the Timesheets permission</t>
+          <t>Timesheets View only: timesheet entries are read-only</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5368,32 +5368,32 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>UI: the universal Clock In control (top bar "timer | Clock In") is present for the Time Clock User role, which has no Timesheets Create&amp;Edit — clock in/out is available regardless of the Timesheets permission.</t>
+          <t>UI (Time Clock User = timesheetsView only): the WO Timesheets tab shows entries but has no edit/add/delete affordances (read-only). screenshot ts-TCUview.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>C26435</t>
+          <t>C26432</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26435</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26432</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Reports ON gives access to the Reports page with all reports (no per-report on/off)</t>
+          <t>Clock in / clock out is always available, whatever the Timesheets permission</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5408,32 +5408,32 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>UI (admin /reports): Reports appears in top nav; the Reports page lists ALL reports grouped by category (LABOR, PERFORMANCE, FINANCE, ACCOUNTS RECEIVABLE, ACCOUNTS PAYABLE, ACCOUNTING, COMMUNICATIONS) with no per-report on/off control — Reports is all-or-nothing. screenshot reports-admin.</t>
+          <t>UI: the universal Clock In control (top bar "timer | Clock In") is present for the Time Clock User role, which has no Timesheets Create&amp;Edit — clock in/out is available regardless of the Timesheets permission.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>C26436</t>
+          <t>C26433</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26436</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26433</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Reports OFF removes Reports from the top navigation</t>
+          <t>Timesheets View OFF with Reports ON: the timesheet activities report is still available</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5448,32 +5448,32 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>UI: the Technician role (no reportsPageAccess) has NO Reports item in the top navigation — Reports OFF removes Reports from nav.</t>
+          <t>UI: a Reports-on role without Timesheets View (ZZAUTOTEST ReportsNoAPAR, round 5) still shows the Timesheet Activities report under LABOR on /reports — the timesheet activities report follows the Reports permission, available even with Timesheets View off. screenshot reports-noapar.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>C26441</t>
+          <t>C26434</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26441</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26434</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>3542</v>
+        <v>3540</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Turning Settings ON reveals its sub-toggles</t>
+          <t>All Timesheets permissions OFF and Reports OFF: no timesheet navigation anywhere</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5483,37 +5483,37 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Verified-Label (build) — Integrations sub-toggle now present (was previously flagged missing)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>PageAndSettingsToggles build chunk shows 7 Settings sub-toggles incl. Integrations. Prior 'Integrations missing' gap is resolved/built.</t>
+          <t>UI: a role with no timesheetsView and no reportsPageAccess (e.g. HistOn: woView+SFD+histlogs) has NO Timesheets tab on the work order and no Timesheet Activities report — no timesheet access anywhere. (Time Clock User, which has timesheetsView, DOES show a Timesheets tab, confirming the gate.)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>C26442</t>
+          <t>C27394</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26442</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27394</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>3542</v>
+        <v>3540</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Turning Settings OFF hides its sub-toggles</t>
+          <t>A clock-capable role without Timesheets View can still see and open My Timesheets</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5528,32 +5528,32 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>UI: with Settings off the 7 sub-toggles are absent; toggling Settings ON reveals App Settings/Service/Parts/Finance/Integrations/Data Import/View-Manage Wages.</t>
+          <t>UI (Technician = clockable, NO timesheetsView): /timesheets is accessible (not restricted) and shows the user My Timesheets entries — a clock-capable role without Timesheets View can still see and open My Timesheets. screenshot myts-tech.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>C26443</t>
+          <t>C26435</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26443</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26435</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>A saved role with Settings OFF has no Settings area in the sidebar</t>
+          <t>Reports ON gives access to the Reports page with all reports (no per-report on/off)</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5568,32 +5568,32 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>UI: the Technician role (no settings* perms) has no Settings area in the sidebar — a saved role with Settings OFF has no Settings section.</t>
+          <t>UI (admin /reports): Reports appears in top nav; the Reports page lists ALL reports grouped by category (LABOR, PERFORMANCE, FINANCE, ACCOUNTS RECEIVABLE, ACCOUNTS PAYABLE, ACCOUNTING, COMMUNICATIONS) with no per-report on/off control — Reports is all-or-nothing. screenshot reports-admin.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>C26444</t>
+          <t>C26436</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26444</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26436</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Turning Settings OFF then ON keeps the sub-toggle choices</t>
+          <t>Reports OFF removes Reports from the top navigation</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5608,19 +5608,19 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>UI: turning Settings OFF then ON keeps the sub-toggle choices (App Settings + Finance stayed ON after the parent was toggled off then on).</t>
+          <t>UI: the Technician role (no reportsPageAccess) has NO Reports item in the top navigation — Reports OFF removes Reports from nav.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>C26445</t>
+          <t>C26441</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26445</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26441</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>App Settings ON gives access to the admin pages</t>
+          <t>Turning Settings ON reveals its sub-toggles</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5643,24 +5643,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build) — Integrations sub-toggle now present (was previously flagged missing)</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>UI (role settingsApp): the SETTINGS admin group is present — Settings, Staff, Roles &amp; Permissions, Locations, Departments. screenshot settings-SetX.</t>
+          <t>PageAndSettingsToggles build chunk shows 7 Settings sub-toggles incl. Integrations. Prior 'Integrations missing' gap is resolved/built.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>C26446</t>
+          <t>C26442</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26446</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26442</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Service ON gives access to the Service configuration pages</t>
+          <t>Turning Settings OFF hides its sub-toggles</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5688,19 +5688,19 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>UI (role settingsService): the SERVICE group is present — Labor Rates, Canned Lines, Asset Types, Inspection Templates. screenshot settings-SetX.</t>
+          <t>UI: with Settings off the 7 sub-toggles are absent; toggling Settings ON reveals App Settings/Service/Parts/Finance/Integrations/Data Import/View-Manage Wages.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>C26447</t>
+          <t>C26443</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26447</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26443</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Parts ON gives access to the Parts configuration pages</t>
+          <t>A saved role with Settings OFF has no Settings area in the sidebar</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5728,19 +5728,19 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>UI (role settingsParts): the PARTS config group is present — Pricing, Bin Locations, Categories. screenshot settings-SetX.</t>
+          <t>UI: the Technician role (no settings* perms) has no Settings area in the sidebar — a saved role with Settings OFF has no Settings section.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>C26448</t>
+          <t>C26444</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26448</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26444</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Finance ON shows the Finance pages, and Integrations ON shows QuickBooks, IBS and Open API</t>
+          <t>Turning Settings OFF then ON keeps the sub-toggle choices</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5768,19 +5768,19 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>UI: Finance ON shows the FINANCE group (Payment Methods, Taxes) [SetFin]; Integrations ON shows the INTEGRATIONS group (IBS, Open API; QuickBooks gated under Integrations) [SetAppIntg]. Roles without each toggle lack the respective group. screenshot settings-SetFin/settings-SetAppIntg.</t>
+          <t>UI: turning Settings OFF then ON keeps the sub-toggle choices (App Settings + Finance stayed ON after the parent was toggled off then on).</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>C26449</t>
+          <t>C26445</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26449</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26445</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Data Import ON gives access to the Imports pages</t>
+          <t>App Settings ON gives access to the admin pages</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5808,19 +5808,19 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>UI (role settingsDataImport): the IMPORTS group is present — Contacts, Assets, Vendors, Inventory, Invoices. screenshot settings-SetX.</t>
+          <t>UI (role settingsApp): the SETTINGS admin group is present — Settings, Staff, Roles &amp; Permissions, Locations, Departments. screenshot settings-SetX.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>C26451</t>
+          <t>C26446</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26451</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26446</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>The Settings sub-toggles work independently (Service on, Finance off)</t>
+          <t>Service ON gives access to the Service configuration pages</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5848,19 +5848,19 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>UI (role with Service ON, Finance OFF = SetX): the SERVICE pages show and there is NO FINANCE group — the Settings sub-toggles work independently.</t>
+          <t>UI (role settingsService): the SERVICE group is present — Labor Rates, Canned Lines, Asset Types, Inspection Templates. screenshot settings-SetX.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>C27395</t>
+          <t>C26447</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27395</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26447</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Turning off the last Settings sub-toggle collapses the Settings section</t>
+          <t>Parts ON gives access to the Parts configuration pages</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5888,19 +5888,19 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>UI: turning off the last remaining Settings sub-toggle (App Settings) collapses the Settings section — the parent Settings toggle goes off and the sub-toggles disappear.</t>
+          <t>UI (role settingsParts): the PARTS config group is present — Pricing, Bin Locations, Categories. screenshot settings-SetX.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>C29273</t>
+          <t>C26448</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29273</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26448</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>The Integrations admin pages depend on the Integrations sub-toggle, not on Finance</t>
+          <t>Finance ON shows the Finance pages, and Integrations ON shows QuickBooks, IBS and Open API</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5928,19 +5928,19 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>UI: a Finance-only role (settingsFinance, no settingsIntegrations = SetFin) shows the FINANCE group (Payment Methods, Taxes) but NO INTEGRATIONS group (no IBS/Open API/QuickBooks) — Integrations admin pages depend on the Integrations sub-toggle, not on Finance. screenshot settings-SetFin.</t>
+          <t>UI: Finance ON shows the FINANCE group (Payment Methods, Taxes) [SetFin]; Integrations ON shows the INTEGRATIONS group (IBS, Open API; QuickBooks gated under Integrations) [SetAppIntg]. Roles without each toggle lack the respective group. screenshot settings-SetFin/settings-SetAppIntg.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>C29274</t>
+          <t>C26449</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29274</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26449</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>The QuickBooks connection check does not run for roles without Integrations</t>
+          <t>Data Import ON gives access to the Imports pages</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5968,32 +5968,32 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>UI (inference from gating): QuickBooks lives under the INTEGRATIONS group which is only shown for roles with settingsIntegrations (present for SetAppIntg, absent for SetX/SetFin). Roles without Integrations never reach the QuickBooks surface, so the QuickBooks connection check is not triggered for them. (The background check API call itself is not directly observable in the harness; verified via the Integrations gating.)</t>
+          <t>UI (role settingsDataImport): the IMPORTS group is present — Contacts, Assets, Vendors, Inventory, Invoices. screenshot settings-SetX.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>C26452</t>
+          <t>C26451</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26452</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26451</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>The Work orders card has 'Full View' and 'Tech view' options</t>
+          <t>The Settings sub-toggles work independently (Service on, Finance off)</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6003,37 +6003,37 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>'View mode', 'Full View', 'Tech view' confirmed in build (WoSettingsRow).</t>
+          <t>UI (role with Service ON, Finance OFF = SetX): the SERVICE pages show and there is NO FINANCE group — the Settings sub-toggles work independently.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>C26453</t>
+          <t>C27395</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26453</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27395</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>The Full View description</t>
+          <t>Turning off the last Settings sub-toggle collapses the Settings section</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -6048,32 +6048,32 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>UI: Full View description reads "Complete interface with all fields visible and editable (subject to CRUD permissions). The estimate column shows the actual estimate value. Full parts request form with all fields. All workflow actions available (approve, review, split etc...)."</t>
+          <t>UI: turning off the last remaining Settings sub-toggle (App Settings) collapses the Settings section — the parent Settings toggle goes off and the sub-toggles disappear.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>C26454</t>
+          <t>C29273</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26454</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29273</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>The Tech view description, and Tech view stays disabled until a Work orders permission is on</t>
+          <t>The Integrations admin pages depend on the Integrations sub-toggle, not on Finance</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6083,37 +6083,37 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Verified-Label (Tech view text build-verified); disabled-state needs live check</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Tech view description string confirmed verbatim in build (WoSettingsRow). Disabled-until-WO-perm needs live editor.</t>
+          <t>UI: a Finance-only role (settingsFinance, no settingsIntegrations = SetFin) shows the FINANCE group (Payment Methods, Taxes) but NO INTEGRATIONS group (no IBS/Open API/QuickBooks) — Integrations admin pages depend on the Integrations sub-toggle, not on Finance. screenshot settings-SetFin.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>C26455</t>
+          <t>C29274</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26455</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29274</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Tech view: the Estimate column shows the Tech Time value</t>
+          <t>The QuickBooks connection check does not run for roles without Integrations</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -6128,19 +6128,19 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>UI (Technician, tech view): WO lines Actual/Estimate column shows tech-time hours (e.g. 0.00 / 1.00, 0.00 / 1.50) and header "Total Tech Hours" — not a money estimate. screenshot techview-lines-estimate/approved.</t>
+          <t>UI (inference from gating): QuickBooks lives under the INTEGRATIONS group which is only shown for roles with settingsIntegrations (present for SetAppIntg, absent for SetX/SetFin). Roles without Integrations never reach the QuickBooks surface, so the QuickBooks connection check is not triggered for them. (The background check API call itself is not directly observable in the harness; verified via the Integrations gating.)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>C26456</t>
+          <t>C26452</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26456</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26452</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Tech view: the tech time input field is hidden on work order lines</t>
+          <t>The Work orders card has 'Full View' and 'Tech view' options</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6163,24 +6163,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>UI (tech view): no tech-time input field rendered on the WO lines for this user (0 tech-time inputs found).</t>
+          <t>'View mode', 'Full View', 'Tech view' confirmed in build (WoSettingsRow).</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>C26457</t>
+          <t>C26453</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26457</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26453</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Tech view: the user cannot approve work orders (no Approve button)</t>
+          <t>The Full View description</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6208,19 +6208,19 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>UI (tech view): no Approve button anywhere on the work order (estimate and approved WOs both) — Technician lacks Review Work Orders.</t>
+          <t>UI: Full View description reads "Complete interface with all fields visible and editable (subject to CRUD permissions). The estimate column shows the actual estimate value. Full parts request form with all fields. All workflow actions available (approve, review, split etc...)."</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>C26458</t>
+          <t>C26454</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26458</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26454</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Tech view: the user cannot approve work order lines</t>
+          <t>The Tech view description, and Tech view stays disabled until a Work orders permission is on</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6243,24 +6243,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (Tech view text build-verified); disabled-state needs live check</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>UI (tech view): no approve-line action on any line; line actions are tech-only (Complete / Story / Start), no approve control.</t>
+          <t>Tech view description string confirmed verbatim in build (WoSettingsRow). Disabled-until-WO-perm needs live editor.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>C26463</t>
+          <t>C26455</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26463</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26455</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>View mode only changes the look, not what the user is allowed to do</t>
+          <t>Tech view: the Estimate column shows the Tech Time value</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6288,19 +6288,19 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>UI/enforcement: tech view is purely presentational — the tech-view role retains workOrderLinesCreateAndEdit and can add lines (New Line functional on the lines screen); data-level create/edit is governed by CRUD perms, not the view mode (estimate column renders as hours but edit capability persists).</t>
+          <t>UI (Technician, tech view): WO lines Actual/Estimate column shows tech-time hours (e.g. 0.00 / 1.00, 0.00 / 1.50) and header "Total Tech Hours" — not a money estimate. screenshot techview-lines-estimate/approved.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>C26465</t>
+          <t>C26456</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26465</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26456</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Tech view: the 'Send to Portal' button is hidden</t>
+          <t>Tech view: the tech time input field is hidden on work order lines</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6328,32 +6328,32 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>UI (tech view): the Send to Portal button is not shown anywhere on the work order (header, line, or action menus).</t>
+          <t>UI (tech view): no tech-time input field rendered on the WO lines for this user (0 tech-time inputs found).</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>C26467</t>
+          <t>C26457</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26467</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26457</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>See Financial Data toggle appears in the Cross-Cutting Toggles card</t>
+          <t>Tech view: the user cannot approve work orders (no Approve button)</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6363,37 +6363,37 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Verified-Label (build); subtitle placeholder flagged</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Card 'Cross-Cutting Toggles' + toggle 'See Financial Data' confirmed in shipped build (CrossTogglesSection chunk). Reused subtitle string flagged.</t>
+          <t>UI (tech view): no Approve button anywhere on the work order (estimate and approved WOs both) — Technician lacks Review Work Orders.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>C26468</t>
+          <t>C26458</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26468</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26458</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>See Financial Data ON: prices, costs, margins and labor rates are shown</t>
+          <t>Tech view: the user cannot approve work order lines</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6408,32 +6408,32 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>UI: with See Financial Data ON (admin full view + TechSFD), WO lines show prices, costs, margins and labor rates — Rate ($100), Margin (%), Total ($261.54), parts prices ($3.33 etc), labor ($150). screenshot fullview-lines-admin/techview-sfd-lines.</t>
+          <t>UI (tech view): no approve-line action on any line; line actions are tech-only (Complete / Story / Start), no approve control.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>C26469</t>
+          <t>C26463</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26469</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26463</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>See Financial Data OFF: money amounts, rates, costs and margins are hidden</t>
+          <t>View mode only changes the look, not what the user is allowed to do</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6448,32 +6448,32 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>UI: with See Financial Data OFF (plain Technician), WO lines show NO money — no $ amounts, no Rate/Margin/Total columns; only tech-time hours (0.00/1.00). screenshot techview-lines-estimate.</t>
+          <t>UI/enforcement: tech view is purely presentational — the tech-view role retains workOrderLinesCreateAndEdit and can add lines (New Line functional on the lines screen); data-level create/edit is governed by CRUD perms, not the view mode (estimate column renders as hours but edit capability persists).</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>C26470</t>
+          <t>C26465</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26470</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26465</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>With See Financial Data OFF, Part sales and Invoicing &amp; payments stay inaccessible even with View, Create &amp; Edit and Delete on</t>
+          <t>Tech view: the 'Send to Portal' button is hidden</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6488,19 +6488,19 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>UI/editor enforcement: a role cannot hold Part sales or Invoicing &amp; payments with See Financial Data OFF — ticking either forces the "Enable See Financial Data?" dialog (C26471/C26474). So SFD OFF makes Part sales and Invoicing &amp; payments unreachable even if View/Create&amp;Edit/Delete were desired; the combination is prevented at save time.</t>
+          <t>UI (tech view): the Send to Portal button is not shown anywhere on the work order (header, line, or action menus).</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>C26471</t>
+          <t>C26467</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26471</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26467</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Ticking Part sales while See Financial Data is OFF asks you to turn See Financial Data on</t>
+          <t>See Financial Data toggle appears in the Cross-Cutting Toggles card</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6523,24 +6523,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build); subtitle placeholder flagged</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>UI dialog: ticking Part sales while SFD off shows "Enable See Financial Data? — Part Sales requires See Financial Data. Enable it to grant this permission?" [Cancel|Enable].</t>
+          <t>Card 'Cross-Cutting Toggles' + toggle 'See Financial Data' confirmed in shipped build (CrossTogglesSection chunk). Reused subtitle string flagged.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>C26472</t>
+          <t>C26468</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26472</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26468</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>'Enable See Financial Data?' dialog — Enable: turns See Financial Data on and keeps the box ticked</t>
+          <t>See Financial Data ON: prices, costs, margins and labor rates are shown</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6568,19 +6568,19 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>UI: Enable on the SFD dialog turns See Financial Data ON and keeps Part sales View+Create&amp;Edit ticked.</t>
+          <t>UI: with See Financial Data ON (admin full view + TechSFD), WO lines show prices, costs, margins and labor rates — Rate ($100), Margin (%), Total ($261.54), parts prices ($3.33 etc), labor ($150). screenshot fullview-lines-admin/techview-sfd-lines.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>C26473</t>
+          <t>C26469</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26473</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26469</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>'Enable See Financial Data?' dialog — Cancel: undoes the tick</t>
+          <t>See Financial Data OFF: money amounts, rates, costs and margins are hidden</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6608,19 +6608,19 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>UI: Cancel on the SFD dialog undoes the tick (See Financial Data off, Part sales off).</t>
+          <t>UI: with See Financial Data OFF (plain Technician), WO lines show NO money — no $ amounts, no Rate/Margin/Total columns; only tech-time hours (0.00/1.00). screenshot techview-lines-estimate.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>C26474</t>
+          <t>C26470</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26474</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26470</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>The same 'Enable See Financial Data?' dialog appears for Invoicing &amp; payments when See Financial Data is OFF</t>
+          <t>With See Financial Data OFF, Part sales and Invoicing &amp; payments stay inaccessible even with View, Create &amp; Edit and Delete on</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6648,19 +6648,19 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>UI dialog: ticking Invoicing &amp; payments while SFD off shows "Enable See Financial Data? — Invoicing &amp; Payments requires See Financial Data..." [Cancel|Enable]; Enable -&gt; SFD ON + Invoicing View+C&amp;E ON.</t>
+          <t>UI/editor enforcement: a role cannot hold Part sales or Invoicing &amp; payments with See Financial Data OFF — ticking either forces the "Enable See Financial Data?" dialog (C26471/C26474). So SFD OFF makes Part sales and Invoicing &amp; payments unreachable even if View/Create&amp;Edit/Delete were desired; the combination is prevented at save time.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>C26475</t>
+          <t>C26471</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26475</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26471</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -6673,7 +6673,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Turning See Financial Data OFF asks you to also turn off the settings that depend on it</t>
+          <t>Ticking Part sales while See Financial Data is OFF asks you to turn See Financial Data on</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6688,19 +6688,19 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>UI (RUN331 FAIL NOW FIXED): turning See Financial Data OFF while Invoicing on shows "Disable See Financial Data? — Disabling See Financial Data will also disable Invoicing &amp; Payments. Continue?" [Cancel|Disable] (FinancialDataDisableConfirmModal). screenshot sfd-disable-dialog.</t>
+          <t>UI dialog: ticking Part sales while SFD off shows "Enable See Financial Data? — Part Sales requires See Financial Data. Enable it to grant this permission?" [Cancel|Enable].</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>C27869</t>
+          <t>C26472</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27869</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26472</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Turning on Order parts while See Financial Data is OFF asks you to also turn on See Financial Data</t>
+          <t>'Enable See Financial Data?' dialog — Enable: turns See Financial Data on and keeps the box ticked</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6728,32 +6728,32 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>UI dialog: ticking Order parts while SFD off shows "Enable See Financial Data? — Order Parts requires See Financial Data. Enable it to grant this permission?" [Cancel|Enable].</t>
+          <t>UI: Enable on the SFD dialog turns See Financial Data ON and keeps Part sales View+Create&amp;Edit ticked.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>C26476</t>
+          <t>C26473</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26476</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26473</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data ON shows the Unpaid Invoices, Payments and Credits tabs on a customer</t>
+          <t>'Enable See Financial Data?' dialog — Cancel: undoes the tick</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6768,32 +6768,32 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>UI: role with AP/AR Data ON shows the financial tabs on a customer page — build labels are Invoices / Payments / Deposits (case prose says Unpaid Invoices/Payments/Credits; the AP/AR toggle description uses that wording, actual tab labels are Invoices/Payments/Deposits). Tabs absent when AP/AR off.</t>
+          <t>UI: Cancel on the SFD dialog undoes the tick (See Financial Data off, Part sales off).</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>C26477</t>
+          <t>C26474</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26477</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26474</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data ON shows the same three tabs on a vendor</t>
+          <t>The same 'Enable See Financial Data?' dialog appears for Invoicing &amp; payments when See Financial Data is OFF</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6808,32 +6808,32 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>UI (Parts Manager, AP/AR ON): the vendor page (/parts/vendor/{id}) shows the AP/AR tabs — Contacts, Unpaid Invoices (30), Payments (4). screenshot vendordetail-vendON.</t>
+          <t>UI dialog: ticking Invoicing &amp; payments while SFD off shows "Enable See Financial Data? — Invoicing &amp; Payments requires See Financial Data..." [Cancel|Enable]; Enable -&gt; SFD ON + Invoicing View+C&amp;E ON.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>C26478</t>
+          <t>C26475</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26478</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26475</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>With Reports ON, all 6 AP/AR aging reports are listed (whether or not AP/AR is on)</t>
+          <t>Turning See Financial Data OFF asks you to also turn off the settings that depend on it</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6848,32 +6848,32 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>UI (admin /reports, Reports ON): all 6 AP/AR aging reports are listed — A/R Aging Summary, A/R Aging Detail, A/R Aging Collection, A/P Aging Summary, A/P Aging Detail, A/P Unpaid Invoices. screenshot reports-admin.</t>
+          <t>UI (RUN331 FAIL NOW FIXED): turning See Financial Data OFF while Invoicing on shows "Disable See Financial Data? — Disabling See Financial Data will also disable Invoicing &amp; Payments. Continue?" [Cancel|Disable] (FinancialDataDisableConfirmModal). screenshot sfd-disable-dialog.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>C26480</t>
+          <t>C27869</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26480</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27869</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data OFF hides the three tabs on a customer</t>
+          <t>Turning on Order parts while See Financial Data is OFF asks you to also turn on See Financial Data</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6888,19 +6888,19 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>UI: AP/AR Data OFF (Service Advisor) — the customer page shows only Work Orders/Part Sales/Contacts/Assets/Notes; the Invoices/Payments/Deposits tabs are hidden.</t>
+          <t>UI dialog: ticking Order parts while SFD off shows "Enable See Financial Data? — Order Parts requires See Financial Data. Enable it to grant this permission?" [Cancel|Enable].</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>C26481</t>
+          <t>C26476</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26481</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26476</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data OFF hides the three tabs on a vendor</t>
+          <t>View and Manage AP/AR Data ON shows the Unpaid Invoices, Payments and Credits tabs on a customer</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6928,19 +6928,19 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>UI (Service Advisor, AP/AR OFF): the same vendor page shows only the Contacts tab — Unpaid Invoices/Payments tabs are hidden. screenshot vendordetail-vendOFF.</t>
+          <t>UI: role with AP/AR Data ON shows the financial tabs on a customer page — build labels are Invoices / Payments / Deposits (case prose says Unpaid Invoices/Payments/Credits; the AP/AR toggle description uses that wording, actual tab labels are Invoices/Payments/Deposits). Tabs absent when AP/AR off.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>C26482</t>
+          <t>C26477</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26482</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26477</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>With AP/AR OFF but Reports ON, all 6 AP/AR aging reports are still listed</t>
+          <t>View and Manage AP/AR Data ON shows the same three tabs on a vendor</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -6968,19 +6968,19 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>UI (RUN331 FAIL NOW FIXED): a role with Reports ON but View and Manage AP/AR Data OFF (ZZAUTOTEST ReportsNoAPAR) still sees all 6 AP/AR aging reports on /reports (A/R Aging Summary/Detail/Collection, A/P Aging Summary/Detail, A/P Unpaid Invoices). Aging reports follow the Reports permission, not AP/AR. screenshot reports-noapar.</t>
+          <t>UI (Parts Manager, AP/AR ON): the vendor page (/parts/vendor/{id}) shows the AP/AR tabs — Contacts, Unpaid Invoices (30), Payments (4). screenshot vendordetail-vendON.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>C26483</t>
+          <t>C26478</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26483</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26478</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data OFF hides the sensitive money fields on Edit Customer</t>
+          <t>With Reports ON, all 6 AP/AR aging reports are listed (whether or not AP/AR is on)</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -7008,19 +7008,19 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>UI: AP/AR Data OFF hides the sensitive money fields on Edit Customer (Credit Limit, Taxes, Default Labor Rate, Default Shop Supplies, Min, Max, Credit Terms) — same observation as C26402.</t>
+          <t>UI (admin /reports, Reports ON): all 6 AP/AR aging reports are listed — A/R Aging Summary, A/R Aging Detail, A/R Aging Collection, A/P Aging Summary, A/P Aging Detail, A/P Unpaid Invoices. screenshot reports-admin.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>C26484</t>
+          <t>C26480</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26484</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26480</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data OFF still lets a user create invoices and take payments if Invoicing &amp; payments allows it</t>
+          <t>View and Manage AP/AR Data OFF hides the three tabs on a customer</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -7048,19 +7048,19 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>UI/perms: AP/AR Data OFF still allows creating invoices/taking payments when Invoicing allows — Service Advisor has invoicingPaymentsCreateAndEdit+Delete with AP/AR off; invoicing capability is independent of AP/AR.</t>
+          <t>UI: AP/AR Data OFF (Service Advisor) — the customer page shows only Work Orders/Part Sales/Contacts/Assets/Notes; the Invoices/Payments/Deposits tabs are hidden.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>C26485</t>
+          <t>C26481</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26485</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26481</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data works independently of See Financial Data</t>
+          <t>View and Manage AP/AR Data OFF hides the three tabs on a vendor</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -7088,19 +7088,19 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>UI: See Financial Data and View and Manage AP/AR Data are separate Cross-Cutting Toggles (both present independently alongside View History Logs); AP/AR is not tied to SFD in the editor.</t>
+          <t>UI (Service Advisor, AP/AR OFF): the same vendor page shows only the Contacts tab — Unpaid Invoices/Payments tabs are hidden. screenshot vendordetail-vendOFF.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>C26486</t>
+          <t>C26482</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26486</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26482</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data OFF does not block any add/edit/delete area</t>
+          <t>With AP/AR OFF but Reports ON, all 6 AP/AR aging reports are still listed</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -7128,32 +7128,32 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>UI: AP/AR Data OFF does not block any add/edit/delete — Service Advisor (AP/AR off) still opens the editable Edit Customer modal and retains full customer/WO/parts create-edit; only the financial tabs/fields are hidden.</t>
+          <t>UI (RUN331 FAIL NOW FIXED): a role with Reports ON but View and Manage AP/AR Data OFF (ZZAUTOTEST ReportsNoAPAR) still sees all 6 AP/AR aging reports on /reports (A/R Aging Summary/Detail/Collection, A/P Aging Summary/Detail, A/P Unpaid Invoices). Aging reports follow the Reports permission, not AP/AR. screenshot reports-noapar.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>C26492</t>
+          <t>C26483</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26492</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26483</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>3547</v>
+        <v>3545</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Staff Page Role Assignment</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Changing a user's role logs them out immediately</t>
+          <t>View and Manage AP/AR Data OFF hides the sensitive money fields on Edit Customer</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -7168,32 +7168,32 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>API/session: changing a user role logs them out immediately — the prior session is invalidated (409 Session has expired) right after the change.</t>
+          <t>UI: AP/AR Data OFF hides the sensitive money fields on Edit Customer (Credit Limit, Taxes, Default Labor Rate, Default Shop Supplies, Min, Max, Credit Terms) — same observation as C26402.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>C26494</t>
+          <t>C26484</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26494</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26484</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>3547</v>
+        <v>3545</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Staff Page Role Assignment</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>A logged-in user is logged out immediately when their role changes</t>
+          <t>View and Manage AP/AR Data OFF still lets a user create invoices and take payments if Invoicing &amp; payments allows it</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -7208,32 +7208,32 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>API/session: a logged-in user is logged out immediately when their role changes (session invalidated -&gt; 409 on next request).</t>
+          <t>UI/perms: AP/AR Data OFF still allows creating invoices/taking payments when Invoicing allows — Service Advisor has invoicingPaymentsCreateAndEdit+Delete with AP/AR off; invoicing capability is independent of AP/AR.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>C26495</t>
+          <t>C26485</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26495</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26485</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Administrator: role permissions match the expected set</t>
+          <t>View and Manage AP/AR Data works independently of See Financial Data</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -7243,37 +7243,37 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Administrator permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI: See Financial Data and View and Manage AP/AR Data are separate Cross-Cutting Toggles (both present independently alongside View History Logs); AP/AR is not tied to SFD in the editor.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>C26496</t>
+          <t>C26486</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26496</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26486</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Service Manager: role permissions match the expected set</t>
+          <t>View and Manage AP/AR Data OFF does not block any add/edit/delete area</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -7283,37 +7283,37 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Service Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI: AP/AR Data OFF does not block any add/edit/delete — Service Advisor (AP/AR off) still opens the editable Edit Customer modal and retains full customer/WO/parts create-edit; only the financial tabs/fields are hidden.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>C26497</t>
+          <t>C26488</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26497</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26488</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>3548</v>
+        <v>3546</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View History Logs</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Senior Service Advisor: role permissions match the expected set</t>
+          <t>View History Logs ON: work order history and line history are visible (work orders only)</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -7323,37 +7323,37 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Senior Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI (role with View History Logs ON): the WO detail shows the History (15) tab exposing work order + line history/change events. screenshot hist-HistOn.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>C26498</t>
+          <t>C26489</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26498</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26489</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>3548</v>
+        <v>3546</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View History Logs</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Service Advisor: role permissions match the expected set</t>
+          <t>View History Logs OFF: work order history and line history are hidden (work orders only)</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -7363,37 +7363,37 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI (role with View History Logs OFF = Time Clock User): the WO detail has NO History tab (Lines/Notes/Timesheets/Stats only) — work order and line history are hidden. screenshot hist-HistOff.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>C26499</t>
+          <t>C26492</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26499</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26492</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Foreman: role permissions match the expected set</t>
+          <t>Changing a user's role logs them out immediately</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -7403,37 +7403,37 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Foreman permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>API/session: changing a user role logs them out immediately — the prior session is invalidated (409 Session has expired) right after the change.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>C26500</t>
+          <t>C26494</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26500</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26494</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Technician: role permissions match the expected set</t>
+          <t>A logged-in user is logged out immediately when their role changes</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -7443,24 +7443,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>API/session: a logged-in user is logged out immediately when their role changes (session invalidated -&gt; 409 on next request).</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>C26501</t>
+          <t>C26495</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26501</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26495</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -7473,7 +7473,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Parts Manager: role permissions match the expected set</t>
+          <t>Administrator: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -7488,19 +7488,19 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Parts Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Administrator permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>C26502</t>
+          <t>C26496</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26502</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26496</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Parts Technician: role permissions match the expected set</t>
+          <t>Service Manager: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -7528,19 +7528,19 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Parts Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Service Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>C26503</t>
+          <t>C26497</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26503</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26497</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Office User: role permissions match the expected set</t>
+          <t>Senior Service Advisor: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -7568,19 +7568,19 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Office User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Senior Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>C26504</t>
+          <t>C26498</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26504</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26498</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Sales Representative: role permissions match the expected set</t>
+          <t>Service Advisor: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -7608,19 +7608,19 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Sales Representative permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>C26505</t>
+          <t>C26499</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26505</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26499</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Time Clock User: role permissions match the expected set</t>
+          <t>Foreman: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -7648,19 +7648,19 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Time Clock User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Foreman permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>C26506</t>
+          <t>C26500</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26506</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26500</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -7673,7 +7673,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Customer portal is on by default only for Service Advisor, Senior Service Advisor, Service Manager and Parts Manager (and Administrator)</t>
+          <t>Technician: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -7683,37 +7683,37 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (matches live per-role customerPortalPageAccess)</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>customerPortalPageAccess per role confirmed live: on for Admin/SM/SSA/SA/PM; off for the rest (roles-matrix-2026-07-13).</t>
+          <t>Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>C26510</t>
+          <t>C26501</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26510</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26501</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Legacy 'Admin / Administrator' users become 'Administrator' after migration</t>
+          <t>Parts Manager: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -7723,37 +7723,37 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Live roles API: destination system role exists = "Admin" (build name; case prose says Administrator), isEditable=true, 89 users, 42 perms. Migration is a completed historical event; destination state verified (role present, editable with pencil, populated).</t>
+          <t>Parts Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>C26511</t>
+          <t>C26502</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26511</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26502</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Legacy 'Office' users become 'Office User' after migration</t>
+          <t>Parts Technician: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -7763,37 +7763,37 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Live roles API: "Office User" exists, isEditable=false (lock + eye only), 5 users, 23 perms — matches legacy Office -&gt; Office User destination.</t>
+          <t>Parts Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>C26512</t>
+          <t>C26503</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26512</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26503</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Legacy 'Time Clock' users become 'Time Clock User' after migration</t>
+          <t>Office User: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -7803,37 +7803,37 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Live roles API: "Time Clock User" exists, isEditable=false (lock + eye only), 11 users, 3 perms — matches legacy Time Clock -&gt; Time Clock User.</t>
+          <t>Office User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>C26513</t>
+          <t>C26504</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26513</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26504</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Legacy 'Service Manager' users become 'Service Manager' after migration</t>
+          <t>Sales Representative: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -7843,37 +7843,37 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Live roles API: "Service Manager" exists, isEditable=true, 3 users, 35 perms.</t>
+          <t>Sales Representative permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>C26514</t>
+          <t>C26505</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26514</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26505</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Legacy 'Senior Service Advisor' users become 'Senior Service Advisor' after migration</t>
+          <t>Time Clock User: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -7883,37 +7883,37 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Live roles API: "Senior Service Advisor" exists, isEditable=true, 8 users, 32 perms.</t>
+          <t>Time Clock User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>C26515</t>
+          <t>C26506</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26515</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26506</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Legacy 'Service Advisor' users become 'Service Advisor' after migration</t>
+          <t>Customer portal is on by default only for Service Advisor, Senior Service Advisor, Service Manager and Parts Manager (and Administrator)</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -7923,24 +7923,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (matches live per-role customerPortalPageAccess)</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Live roles API: "Service Advisor" exists, isEditable=true, 2 users, 26 perms.</t>
+          <t>customerPortalPageAccess per role confirmed live: on for Admin/SM/SSA/SA/PM; off for the rest (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>C26516</t>
+          <t>C26510</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26516</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26510</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Legacy 'Foreman' users become 'Foreman' after migration</t>
+          <t>Legacy 'Admin / Administrator' users become 'Administrator' after migration</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -7968,19 +7968,19 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Live roles API: "Foreman" exists, isEditable=true, 16 users, 23 perms.</t>
+          <t>Live roles API: destination system role exists = "Admin" (build name; case prose says Administrator), isEditable=true, 89 users, 42 perms. Migration is a completed historical event; destination state verified (role present, editable with pencil, populated).</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>C26517</t>
+          <t>C26511</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26517</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26511</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Legacy 'Technician' users become 'Technician' after migration</t>
+          <t>Legacy 'Office' users become 'Office User' after migration</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -8008,19 +8008,19 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Live roles API: "Technician" exists, isEditable=true, 66 users, 6 perms, view_mode tech (confirmed via role detail) — matches legacy Technician destination.</t>
+          <t>Live roles API: "Office User" exists, isEditable=false (lock + eye only), 5 users, 23 perms — matches legacy Office -&gt; Office User destination.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>C26518</t>
+          <t>C26512</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26518</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26512</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Legacy 'Parts Manager' users become 'Parts Manager' after migration</t>
+          <t>Legacy 'Time Clock' users become 'Time Clock User' after migration</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -8048,19 +8048,19 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Live roles API: "Parts Manager" exists, isEditable=true, 4 users, 31 perms.</t>
+          <t>Live roles API: "Time Clock User" exists, isEditable=false (lock + eye only), 11 users, 3 perms — matches legacy Time Clock -&gt; Time Clock User.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>C26519</t>
+          <t>C26513</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26519</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26513</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Legacy 'Parts Tech / Parts Technician' users become 'Parts Technician' after migration</t>
+          <t>Legacy 'Service Manager' users become 'Service Manager' after migration</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -8088,19 +8088,19 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Live roles API: "Parts Technician" exists, isEditable=true, 10 users, 19 perms — matches legacy Parts Tech -&gt; Parts Technician.</t>
+          <t>Live roles API: "Service Manager" exists, isEditable=true, 3 users, 35 perms.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>C26520</t>
+          <t>C26514</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26520</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26514</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Legacy 'Sales Representative' users become 'Sales Representative' after migration</t>
+          <t>Legacy 'Senior Service Advisor' users become 'Senior Service Advisor' after migration</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -8128,19 +8128,19 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Live roles API: "Sales Representative" exists, isEditable=true, 15 users, 4 perms.</t>
+          <t>Live roles API: "Senior Service Advisor" exists, isEditable=true, 8 users, 32 perms.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>C26525</t>
+          <t>C26515</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26525</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26515</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Changing a user's role logs that user out and forces them to log in again</t>
+          <t>Legacy 'Service Advisor' users become 'Service Advisor' after migration</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -8168,32 +8168,32 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>UI/API: after an admin changed the Tech user role, the user existing session returned 409 "Session has expired." on the next call — the role change logs the user out and forces re-login.</t>
+          <t>Live roles API: "Service Advisor" exists, isEditable=true, 2 users, 26 perms.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>C26528</t>
+          <t>C26516</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26528</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26516</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Staff Record Settings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>The universal clock in / out is available to any active staff member, whatever their role</t>
+          <t>Legacy 'Foreman' users become 'Foreman' after migration</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -8208,32 +8208,32 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>UI: the universal Clock In control appears in the top bar for every role observed (Admin, Technician, Time Clock User) — available to any active staff member whatever their role.</t>
+          <t>Live roles API: "Foreman" exists, isEditable=true, 16 users, 23 perms.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>C26532</t>
+          <t>C26517</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26532</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26517</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Create success message wording</t>
+          <t>Legacy 'Technician' users become 'Technician' after migration</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -8243,37 +8243,37 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>'Role created successfully.' confirmed in build.</t>
+          <t>Live roles API: "Technician" exists, isEditable=true, 66 users, 6 perms, view_mode tech (confirmed via role detail) — matches legacy Technician destination.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>C26533</t>
+          <t>C26518</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26533</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26518</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Update success message wording</t>
+          <t>Legacy 'Parts Manager' users become 'Parts Manager' after migration</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -8283,37 +8283,37 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>'Role updated successfully.' confirmed in build.</t>
+          <t>Live roles API: "Parts Manager" exists, isEditable=true, 4 users, 31 perms.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>C26534</t>
+          <t>C26519</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26534</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26519</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Deleting a custom role with 0 users shows a confirmation dialog</t>
+          <t>Legacy 'Parts Tech / Parts Technician' users become 'Parts Technician' after migration</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -8328,32 +8328,32 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>UI: deleting a 0-user custom role opens dialog "Confirmation — Are you sure you want to delete this role? This action cannot be undone." [Cancel|Delete]. screenshot delete-confirm-dialog.</t>
+          <t>Live roles API: "Parts Technician" exists, isEditable=true, 10 users, 19 perms — matches legacy Parts Tech -&gt; Parts Technician.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>C26535</t>
+          <t>C26520</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26535</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26520</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Deleting a custom role that has users is blocked</t>
+          <t>Legacy 'Sales Representative' users become 'Sales Representative' after migration</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -8368,32 +8368,32 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>UI: a custom role with users (Parth Cust1, 1 user) has no Delete option in its 3-dot menu — deletion is blocked.</t>
+          <t>Live roles API: "Sales Representative" exists, isEditable=true, 15 users, 4 perms.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>C26536</t>
+          <t>C26525</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26536</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26525</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Turning See Financial Data on shows a confirmation dialog</t>
+          <t>Changing a user's role logs that user out and forces them to log in again</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -8403,37 +8403,37 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>'Enable See Financial Data?' + Cancel/Enable confirmed in build (FinancialDataConfirmModal).</t>
+          <t>UI/API: after an admin changed the Tech user role, the user existing session returned 409 "Session has expired." on the next call — the role change logs the user out and forces re-login.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>C26537</t>
+          <t>C26528</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26537</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26528</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>3552</v>
+        <v>3550</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Staff Record Settings</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Creating a role with no name is blocked with a required-field error</t>
+          <t>The universal clock in / out is available to any active staff member, whatever their role</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -8448,19 +8448,19 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>UI: creating a role with no name is blocked — Create disabled and inline "Role name is a required field" error when the field is touched/cleared.</t>
+          <t>UI: the universal Clock In control appears in the top bar for every role observed (Admin, Technician, Time Clock User) — available to any active staff member whatever their role.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>C26538</t>
+          <t>C26532</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26538</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26532</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Creating a role with the same permissions as an existing role shows a 'similar role' warning</t>
+          <t>Create success message wording</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -8483,37 +8483,37 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>UI: creating a role with the same permissions as an existing role shows "Similar role already exists" warning with "Create Anyway" (SimilarRoleWarningModal, keyed on identical permissions).</t>
+          <t>'Role created successfully.' confirmed in build.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>C26542</t>
+          <t>C26533</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26542</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26533</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Cross-Permission Combinations</t>
+          <t>User Feedback Strings</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>A system role cannot be deleted</t>
+          <t>Update success message wording</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -8523,37 +8523,37 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (all system roles deletable=false)</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>deletable=false for all system roles (live roles API).</t>
+          <t>'Role updated successfully.' confirmed in build.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>C26543</t>
+          <t>C26534</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26543</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26534</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Cross-Permission Combinations</t>
+          <t>User Feedback Strings</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Only Office User and Time Clock User are non-editable; every other system role (including Administrator) is editable</t>
+          <t>Deleting a custom role with 0 users shows a confirmation dialog</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -8563,37 +8563,37 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (editable flags match live)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Live roles API: Office User &amp; Time Clock User editable=false; all others (incl. Administrator) editable=true.</t>
+          <t>UI: deleting a 0-user custom role opens dialog "Confirmation — Are you sure you want to delete this role? This action cannot be undone." [Cancel|Delete]. screenshot delete-confirm-dialog.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>C26549</t>
+          <t>C26535</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26549</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26535</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Cross-Permission Combinations</t>
+          <t>User Feedback Strings</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AP/AR OFF hides the sensitive customer fields on both the Edit Customer window and the customer overview</t>
+          <t>Deleting a custom role that has users is blocked</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -8608,45 +8608,485 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>UI: AP/AR Data OFF hides the sensitive customer fields on the Edit Customer modal (and the financial tabs on the customer overview) — confirmed via Service Advisor (off) vs CustAPAR (on).</t>
+          <t>UI: a custom role with users (Parth Cust1, 1 user) has no Delete option in its 3-dot menu — deletion is blocked.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
+          <t>C26536</t>
+        </is>
+      </c>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26536</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>3552</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>User Feedback Strings</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Turning See Financial Data on shows a confirmation dialog</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Verified-Label (build)</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>'Enable See Financial Data?' + Cancel/Enable confirmed in build (FinancialDataConfirmModal).</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>C26537</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26537</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>3552</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>User Feedback Strings</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Creating a role with no name is blocked with a required-field error</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>UI: creating a role with no name is blocked — Create disabled and inline "Role name is a required field" error when the field is touched/cleared.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>C26538</t>
+        </is>
+      </c>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26538</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>3552</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>User Feedback Strings</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Creating a role with the same permissions as an existing role shows a 'similar role' warning</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>UI: creating a role with the same permissions as an existing role shows "Similar role already exists" warning with "Create Anyway" (SimilarRoleWarningModal, keyed on identical permissions).</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>C26540</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26540</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>A role with all permissions off blocks the user from every feature</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>UI: a near-minimal custom role (only scheduleView) shows a minimal nav (just Schedule + Clock In); navigating to /reports or /administration/staff is refused and redirects to /schedule. (A truly all-off role cannot be saved — Create is disabled at zero perms, C26335 — so the practical minimum is one feature perm; that user is blocked from every other feature.) screenshot xperm-MinRole.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>C26541</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26541</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>A role with all permissions on behaves like Administrator but is still a custom role</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>UI: an all-permissions custom role (42 perms, all cross-toggles on, type Custom) behaves like Administrator — full nav (Work Orders/Schedule/Customers/Parts/Reports), /reports and /administration/staff accessible — yet it is a Custom role (created via Create Custom Role). screenshot xperm-AllOn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>C26542</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26542</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>A system role cannot be deleted</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Roles-API-Verified (all system roles deletable=false)</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>deletable=false for all system roles (live roles API).</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>C26543</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26543</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Only Office User and Time Clock User are non-editable; every other system role (including Administrator) is editable</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Roles-API-Verified (editable flags match live)</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Live roles API: Office User &amp; Time Clock User editable=false; all others (incl. Administrator) editable=true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>C26544</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26544</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Being unable to open Customers does not stop a user from picking a customer when creating a work order</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>UI: verified via C26385 — a role with Work Orders Create&amp;Edit but NO Customers View cannot open Customers (hidden from nav), yet the New Work Order customer picker still opens and lists existing customers, so a customer can be selected when creating a WO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>C26545</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26545</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>A Page Access toggle that is off overrides the add/edit/delete boxes inside it</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>UI: a Page Access toggle that is off overrides inner boxes — a role without reportsPageAccess has no Reports nav entry and /reports is refused (redirects away); a role with Parts Department off hides its 3 child cards (C26407). The Page Access toggle is checked first regardless of inner add/edit/delete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>C26548</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26548</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>View off with Create &amp; Edit on is prevented by the tick-cascade</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>UI/editor: View-off + Create&amp;Edit-on cannot be saved — the tick-cascade (verified C26360/C26362/C26363) auto-ticks View when Create&amp;Edit is ticked, and unticks Create&amp;Edit+Delete when View is unticked, so that invalid combination is impossible in the editor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>C26549</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26549</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>AP/AR OFF hides the sensitive customer fields on both the Edit Customer window and the customer overview</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>UI: AP/AR Data OFF hides the sensitive customer fields on the Edit Customer modal (and the financial tabs on the customer overview) — confirmed via Service Advisor (off) vs CustAPAR (on).</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
           <t>C26551</t>
         </is>
       </c>
-      <c r="B187" s="4" t="inlineStr">
+      <c r="B198" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/26551</t>
         </is>
       </c>
-      <c r="C187" t="n">
+      <c r="C198" t="n">
         <v>3553</v>
       </c>
-      <c r="D187" t="inlineStr">
+      <c r="D198" t="inlineStr">
         <is>
           <t>Cross-Permission Combinations</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
+      <c r="E198" t="inlineStr">
         <is>
           <t>Universal clock in/out works even for a user whose role has (almost) no permissions</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
         <is>
           <t>UI: the Time Clock User role (only 3 perms: scheduleView/timesheetsView/workOrdersView) still shows the universal Clock In control — universal clock in is not gated by role/permissions.</t>
         </is>
@@ -8840,6 +9280,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B185" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B186" r:id="rId185"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B198" r:id="rId197"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8851,7 +9302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9297,7 +9748,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: the Schedule calendar renders for a scheduleCreateAndEdit role, but creating/dragging/editing an appointment requires real calendar drag/slot mouse interaction that does not trigger headless (Schedule button + calendar-cell clicks opened no create dialog); appointment CRUD API endpoint not exposed at standard paths. Needs a real browser.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -9337,7 +9788,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: appointment delete requires selecting an existing appointment on the calendar (drag/slot interaction) which is not triggerable headless; same calendar-automation limitation as C26395.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -9377,7 +9828,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded Schedule-only role)</t>
+          <t>Blocked-UI: the Assign existing work order dialog / unscheduled WO list could not be opened headless (Schedule button + calendar clicks opened no dialog); needs the calendar create-entry interaction in a real browser.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9949,12 +10400,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C26430</t>
+          <t>C26431</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26430</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26431</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -9967,7 +10418,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Timesheets View only: timesheet entries are read-only</t>
+          <t>Timesheets Create &amp; Edit lets the user edit entries</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -9977,37 +10428,37 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: the timesheet entry EDIT affordance was not reachable in the harness for a timesheetsCreateAndEdit role — the WO Timesheets tab is a summary (no edit for view or C&amp;E) and the /timesheets page exposed no per-row edit control/dialog/menu on click. Needs the timesheet entry editor (real browser) to confirm edit works; view-only read-only is confirmed (C26430).</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Read-only behavior needs live UI.</t>
+          <t>Edit behavior needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C26431</t>
+          <t>C26437</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26431</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26437</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3540</v>
+        <v>3541</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Timesheets Create &amp; Edit lets the user edit entries</t>
+          <t>Customer portal ON lets the user manage the customer portal</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -10017,37 +10468,37 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role); toggle label 'Customer portal' build-verified</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Edit behavior needs live UI.</t>
+          <t>Toggle 'Customer portal' confirmed in build. Manage behavior needs live check.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C26433</t>
+          <t>C26438</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26433</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26438</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3540</v>
+        <v>3541</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Timesheets View OFF with Reports ON: the timesheet activities report is still available</t>
+          <t>Customer portal OFF hides the customer portal from navigation</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -10062,32 +10513,32 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Report access needs live UI.</t>
+          <t>Nav-hide needs live check.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C26434</t>
+          <t>C26439</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26434</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26439</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3540</v>
+        <v>3541</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>All Timesheets permissions OFF and Reports OFF: no timesheet navigation anywhere</t>
+          <t>Billing Portal ON lets the user manage the billing portal</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -10097,37 +10548,37 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role); toggle label 'Billing Portal' build-verified</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Nav-hide needs live UI.</t>
+          <t>Toggle 'Billing Portal' confirmed in build. Manage behavior needs live check.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>C27394</t>
+          <t>C26440</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27394</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26440</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3540</v>
+        <v>3541</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>A clock-capable role without Timesheets View can still see and open My Timesheets</t>
+          <t>Billing Portal OFF hides the Billing Portal item in the Settings area</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -10137,37 +10588,37 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded clock-capable role)</t>
+          <t>Blocked-UI (needs seeded role)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Reworded, jargon stripped; needs live UI.</t>
+          <t>Nav-hide needs live check.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>C26437</t>
+          <t>C26450</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26437</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26450</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3541</v>
+        <v>3542</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Customer portal ON lets the user manage the customer portal</t>
+          <t>View/Manage Wages ON lets the user manage wages</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -10177,37 +10628,37 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); toggle label 'Customer portal' build-verified</t>
+          <t>Blocked-UI: wage rate fields live on the Edit Staff Member profile, which is not reachable in this harness (the staff row action opens Manage-staff-enrollments, not the profile/wage editor — same limitation as C26356/C26490/C26491). Role has settingsWages; needs the staff profile editor opened (real browser) to confirm wage fields shown/editable.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Toggle 'Customer portal' confirmed in build. Manage behavior needs live check.</t>
+          <t>Toggle 'View/Manage Wages' confirmed in build. Wage editing needs live check.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>C26438</t>
+          <t>C26460</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26438</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26460</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3541</v>
+        <v>3543</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Customer portal OFF hides the customer portal from navigation</t>
+          <t>Tech view: the parts request form shows fewer fields</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -10217,37 +10668,37 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: needs the New Part Request form opened in tech view vs full view to compare field counts; the lines screen is drivable but the request-form modal step was not reached this pass.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Nav-hide needs live check.</t>
+          <t>precise reason logged</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>C26439</t>
+          <t>C26461</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26439</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26461</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3541</v>
+        <v>3543</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Billing Portal ON lets the user manage the billing portal</t>
+          <t>Tech view: the user can add new work order lines but cannot edit existing ones</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -10257,37 +10708,37 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); toggle label 'Billing Portal' build-verified</t>
+          <t>Blocked-UI: New Line (add) confirmed present in tech view, but the existing-line read-only lock was not directly exercised (would require attempting to edit a pending line inline). Precise follow-up: open a pending line editor as the tech.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Toggle 'Billing Portal' confirmed in build. Manage behavior needs live check.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C26440</t>
+          <t>C26462</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26440</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26462</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3541</v>
+        <v>3543</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Billing Portal OFF hides the Billing Portal item in the Settings area</t>
+          <t>Tech view: a line becomes read-only once its authorization is approved</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -10297,37 +10748,37 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: approved-WO lines showed only tech status actions (Complete/Story/Start) with no edit control (consistent with read-only), but the pending-&gt;approved edit-lock transition was not directly exercised.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Nav-hide needs live check.</t>
+          <t>Needs live UI + a second user.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C26450</t>
+          <t>C26466</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26450</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26466</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3542</v>
+        <v>3543</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>View/Manage Wages ON lets the user manage wages</t>
+          <t>Full View: a user who can approve lines sees the 'Send to Portal' button</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -10337,37 +10788,37 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Blocked-UI: wage rate fields live on the Edit Staff Member profile, which is not reachable in this harness (the staff row action opens Manage-staff-enrollments, not the profile/wage editor — same limitation as C26356/C26490/C26491). Role has settingsWages; needs the staff profile editor opened (real browser) to confirm wage fields shown/editable.</t>
+          <t>Blocked-UI: Send to Portal was NOT found on the full-view (admin) lines page body; it is likely in the WO header more_vert menu or gated by WO state — needs the header action menu expanded to confirm.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Toggle 'View/Manage Wages' confirmed in build. Wage editing needs live check.</t>
+          <t>Send-to-Portal flow needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C26460</t>
+          <t>C26479</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26460</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26479</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3543</v>
+        <v>3545</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tech view: the parts request form shows fewer fields</t>
+          <t>View and Manage AP/AR Data ON allows paying several invoices at once from the Unpaid Invoices tab</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -10377,37 +10828,37 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Blocked-UI: needs the New Part Request form opened in tech view vs full view to compare field counts; the lines screen is drivable but the request-form modal step was not reached this pass.</t>
+          <t>Blocked-UI (needs seeded role + live payment)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>precise reason logged</t>
+          <t>Bulk payment needs live UI + payment (create-customer-payment 500s intermittently per prior run).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C26461</t>
+          <t>C26490</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26461</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26490</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3543</v>
+        <v>3547</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tech view: the user can add new work order lines but cannot edit existing ones</t>
+          <t>The Staff role dropdown groups roles into System Roles and Custom Roles</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -10417,37 +10868,37 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Blocked-UI: New Line (add) confirmed present in tech view, but the existing-line read-only lock was not directly exercised (would require attempting to edit a pending line inline). Precise follow-up: open a pending line editor as the tech.</t>
+          <t>Blocked-UI: the Edit Staff Member Role dropdown (System/Custom grouping) was not reached — the staff row click opened Manage-staff-enrollments. Follow-up: locate the Edit Staff Member action, open the Role selector.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>11 system roles confirmed in live roles list (was '12'). Grouping labels need live Staff page.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C26462</t>
+          <t>C26491</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26462</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26491</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3543</v>
+        <v>3547</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tech view: a line becomes read-only once its authorization is approved</t>
+          <t>The View Permissions button next to the role selector opens the Permission Summary</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -10457,37 +10908,37 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Blocked-UI: approved-WO lines showed only tech status actions (Complete/Story/Start) with no edit control (consistent with read-only), but the pending-&gt;approved edit-lock transition was not directly exercised.</t>
+          <t>Blocked-UI: View Permissions eye next to the staff Role selector not reached (same Edit-Staff-Member surface as C26490).</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Needs live UI + a second user.</t>
+          <t>'View Permissions' confirmed in build. Needs live Staff page.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C26466</t>
+          <t>C26493</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26466</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26493</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3543</v>
+        <v>3547</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Full View: a user who can approve lines sees the 'Send to Portal' button</t>
+          <t>If a role change fails, the user keeps their previous role</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -10497,37 +10948,37 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Blocked-UI: Send to Portal was NOT found on the full-view (admin) lines page body; it is likely in the WO header more_vert menu or gated by WO state — needs the header action menu expanded to confirm.</t>
+          <t>Blocked-UI: forcing a failed role change (to confirm the user keeps the prior role) requires inducing a server error on /change; not reproducible on demand this pass.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Send-to-Portal flow needs live UI.</t>
+          <t>Failed-save path needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C26479</t>
+          <t>C26526</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26479</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26526</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3545</v>
+        <v>3550</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>Staff Record Settings</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data ON allows paying several invoices at once from the Unpaid Invoices tab</t>
+          <t>Whether a technician can be scheduled depends on their department, not their role</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -10537,37 +10988,37 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + live payment)</t>
+          <t>Blocked-UI (needs two seeded users + departments)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Bulk payment needs live UI + payment (create-customer-payment 500s intermittently per prior run).</t>
+          <t>Department-gated scheduling needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C26488</t>
+          <t>C26527</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26488</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26527</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3546</v>
+        <v>3550</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>View History Logs</t>
+          <t>Staff Record Settings</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>View History Logs ON: work order history and line history are visible (work orders only)</t>
+          <t>Clocking in on a work order line depends on the per-staff Time Clock setting</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -10577,37 +11028,37 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); 'View History Logs' toggle build-verified</t>
+          <t>Blocked-UI (needs two seeded users)</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Cross-toggle 'View History Logs' confirmed in build. History visibility needs live UI.</t>
+          <t>Per-staff Time Clock gating needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>C26489</t>
+          <t>C26539</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26489</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26539</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3546</v>
+        <v>3552</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>View History Logs</t>
+          <t>User Feedback Strings</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>View History Logs OFF: work order history and line history are hidden (work orders only)</t>
+          <t>Reassigning a staff member's role updates the row with no success message (billing note in the window)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -10617,37 +11068,37 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); labels build-verified</t>
+          <t>Blocked-UI (needs live Staff page); billing note not re-captured this pass</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>viewHistoryLogs also gates the 'Part History' page under Parts (build route metadata). History-hide needs live UI.</t>
+          <t>No-toast-on-reassign + billing note need live Staff page (EditStaffMember chunk not fetched).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>C26490</t>
+          <t>C26550</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26490</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26550</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3547</v>
+        <v>3553</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Staff Page Role Assignment</t>
+          <t>Cross-Permission Combinations</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>The Staff role dropdown groups roles into System Roles and Custom Roles</t>
+          <t>The last Administrator cannot be left with zero users</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -10657,450 +11108,10 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Blocked-UI: the Edit Staff Member Role dropdown (System/Custom grouping) was not reached — the staff row click opened Manage-staff-enrollments. Follow-up: locate the Edit Staff Member action, open the Role selector.</t>
+          <t>Blocked-UI: cannot test the last-Administrator guard on shared staging — the org has 89 users on the Admin role, so the single-last-admin state cannot be created without mass-reassigning real users (destructive/irreversible on a shared env). Product rule; needs an isolated org or DB-level setup. Route to product team to confirm the rule exists.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
-        <is>
-          <t>11 system roles confirmed in live roles list (was '12'). Grouping labels need live Staff page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>C26491</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26491</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>3547</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Staff Page Role Assignment</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>The View Permissions button next to the role selector opens the Permission Summary</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Blocked-UI: View Permissions eye next to the staff Role selector not reached (same Edit-Staff-Member surface as C26490).</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>'View Permissions' confirmed in build. Needs live Staff page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>C26493</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26493</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>3547</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Staff Page Role Assignment</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>If a role change fails, the user keeps their previous role</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Blocked-UI: forcing a failed role change (to confirm the user keeps the prior role) requires inducing a server error on /change; not reproducible on demand this pass.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Failed-save path needs live UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>C26526</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26526</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>3550</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Staff Record Settings</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Whether a technician can be scheduled depends on their department, not their role</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs two seeded users + departments)</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Department-gated scheduling needs live UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>C26527</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26527</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>3550</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Staff Record Settings</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Clocking in on a work order line depends on the per-staff Time Clock setting</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs two seeded users)</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Per-staff Time Clock gating needs live UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>C26539</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26539</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>3552</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>User Feedback Strings</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Reassigning a staff member's role updates the row with no success message (billing note in the window)</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live Staff page); billing note not re-captured this pass</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>No-toast-on-reassign + billing note need live Staff page (EditStaffMember chunk not fetched).</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>C26540</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26540</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>A role with all permissions off blocks the user from every feature</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Needs seeded role.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>C26541</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26541</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>A role with all permissions on behaves like Administrator but is still a custom role</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Needs seeded role.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>C26544</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26544</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Being unable to open Customers does not stop a user from picking a customer when creating a work order</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Needs seeded role.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>C26545</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26545</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>A Page Access toggle that is off overrides the add/edit/delete boxes inside it</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Needs seeded role.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>C26548</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26548</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>View off with Create &amp; Edit on is prevented by the tick-cascade</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live editor); cascade rule</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Needs live editor; matches cascade rules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>C26550</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26550</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>The last Administrator cannot be left with zero users</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
         <is>
           <t>Needs live UI; invariant to confirm.</t>
         </is>
@@ -11152,17 +11163,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B54" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15539,7 +15539,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: the Schedule calendar renders for a scheduleCreateAndEdit role, but creating/dragging/editing an appointment requires real calendar drag/slot mouse interaction that does not trigger headless (Schedule button + calendar-cell clicks opened no create dialog); appointment CRUD API endpoint not exposed at standard paths. Needs a real browser.</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -15579,7 +15579,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: appointment delete requires selecting an existing appointment on the calendar (drag/slot interaction) which is not triggerable headless; same calendar-automation limitation as C26395.</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -15659,7 +15659,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded Schedule-only role)</t>
+          <t>Blocked-UI: the Assign existing work order dialog / unscheduled WO list could not be opened headless (Schedule button + calendar clicks opened no dialog); needs the calendar create-entry interaction in a real browser.</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -17174,17 +17174,17 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Read-only behavior needs live UI.</t>
+          <t>UI (Time Clock User = timesheetsView only): the WO Timesheets tab shows entries but has no edit/add/delete affordances (read-only). screenshot ts-TCUview.</t>
         </is>
       </c>
     </row>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: the timesheet entry EDIT affordance was not reachable in the harness for a timesheetsCreateAndEdit role — the WO Timesheets tab is a summary (no edit for view or C&amp;E) and the /timesheets page exposed no per-row edit control/dialog/menu on click. Needs the timesheet entry editor (real browser) to confirm edit works; view-only read-only is confirmed (C26430).</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -17294,17 +17294,17 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Report access needs live UI.</t>
+          <t>UI: a Reports-on role without Timesheets View (ZZAUTOTEST ReportsNoAPAR, round 5) still shows the Timesheet Activities report under LABOR on /reports — the timesheet activities report follows the Reports permission, available even with Timesheets View off. screenshot reports-noapar.</t>
         </is>
       </c>
     </row>
@@ -17334,17 +17334,17 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Nav-hide needs live UI.</t>
+          <t>UI: a role with no timesheetsView and no reportsPageAccess (e.g. HistOn: woView+SFD+histlogs) has NO Timesheets tab on the work order and no Timesheet Activities report — no timesheet access anywhere. (Time Clock User, which has timesheetsView, DOES show a Timesheets tab, confirming the gate.)</t>
         </is>
       </c>
     </row>
@@ -17374,17 +17374,17 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded clock-capable role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Reworded, jargon stripped; needs live UI.</t>
+          <t>UI (Technician = clockable, NO timesheetsView): /timesheets is accessible (not restricted) and shows the user My Timesheets entries — a clock-capable role without Timesheets View can still see and open My Timesheets. screenshot myts-tech.</t>
         </is>
       </c>
     </row>
@@ -19654,17 +19654,17 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); 'View History Logs' toggle build-verified</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Cross-toggle 'View History Logs' confirmed in build. History visibility needs live UI.</t>
+          <t>UI (role with View History Logs ON): the WO detail shows the History (15) tab exposing work order + line history/change events. screenshot hist-HistOn.</t>
         </is>
       </c>
     </row>
@@ -19694,17 +19694,17 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); labels build-verified</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>viewHistoryLogs also gates the 'Part History' page under Parts (build route metadata). History-hide needs live UI.</t>
+          <t>UI (role with View History Logs OFF = Time Clock User): the WO detail has NO History tab (Lines/Notes/Timesheets/Stats only) — work order and line history are hidden. screenshot hist-HistOff.</t>
         </is>
       </c>
     </row>
@@ -21454,17 +21454,17 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Needs seeded role.</t>
+          <t>UI: a near-minimal custom role (only scheduleView) shows a minimal nav (just Schedule + Clock In); navigating to /reports or /administration/staff is refused and redirects to /schedule. (A truly all-off role cannot be saved — Create is disabled at zero perms, C26335 — so the practical minimum is one feature perm; that user is blocked from every other feature.) screenshot xperm-MinRole.</t>
         </is>
       </c>
     </row>
@@ -21494,17 +21494,17 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Needs seeded role.</t>
+          <t>UI: an all-permissions custom role (42 perms, all cross-toggles on, type Custom) behaves like Administrator — full nav (Work Orders/Schedule/Customers/Parts/Reports), /reports and /administration/staff accessible — yet it is a Custom role (created via Create Custom Role). screenshot xperm-AllOn.</t>
         </is>
       </c>
     </row>
@@ -21614,17 +21614,17 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Needs seeded role.</t>
+          <t>UI: verified via C26385 — a role with Work Orders Create&amp;Edit but NO Customers View cannot open Customers (hidden from nav), yet the New Work Order customer picker still opens and lists existing customers, so a customer can be selected when creating a WO.</t>
         </is>
       </c>
     </row>
@@ -21654,17 +21654,17 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Needs seeded role.</t>
+          <t>UI: a Page Access toggle that is off overrides inner boxes — a role without reportsPageAccess has no Reports nav entry and /reports is refused (redirects away); a role with Parts Department off hides its 3 child cards (C26407). The Page Access toggle is checked first regardless of inner add/edit/delete.</t>
         </is>
       </c>
     </row>
@@ -21694,17 +21694,17 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs live editor); cascade rule</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Needs live editor; matches cascade rules.</t>
+          <t>UI/editor: View-off + Create&amp;Edit-on cannot be saved — the tick-cascade (verified C26360/C26362/C26363) auto-ticks View when Create&amp;Edit is ticked, and unticks Create&amp;Edit+Delete when View is unticked, so that invalid combination is impossible in the editor.</t>
         </is>
       </c>
     </row>
@@ -21779,7 +21779,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs live role editor / roles list)</t>
+          <t>Blocked-UI: cannot test the last-Administrator guard on shared staging — the org has 89 users on the Admin role, so the single-last-admin state cannot be created without mass-reassigning real users (destructive/irreversible on a shared env). Product rule; needs an isolated org or DB-level setup. Route to product team to confirm the rule exists.</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">

--- a/build/custom-roles-run/CustomRoles_WordingVIU_2026-07-13.xlsx
+++ b/build/custom-roles-run/CustomRoles_WordingVIU_2026-07-13.xlsx
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -581,10 +581,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -779,10 +779,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
         <v>2</v>
@@ -1157,7 +1157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H198"/>
+  <dimension ref="A1:H204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1575,12 +1575,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C26318</t>
+          <t>C26317</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26318</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26317</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Locations appears under the Settings area</t>
+          <t>Roles &amp; Permissions is hidden for users without the App Settings sub-toggle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1608,19 +1608,19 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>UI: Locations appears under the SETTINGS area in the sidebar (SETTINGS &gt; Settings/Staff/Roles &amp; Permissions/Locations/Departments/Taxes).</t>
+          <t>UI: a role with a Settings sub-toggle but WITHOUT App Settings (ZZAUTOTEST SetFin = settingsFinance only, round 6) shows a Settings area with only its Finance items (Payment Methods, Taxes) and NO Roles &amp; Permissions / Staff entries — Roles &amp; Permissions is hidden for users without the App Settings sub-toggle. screenshot settings-SetFin.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C26319</t>
+          <t>C26318</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26319</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26318</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>The roles list has a Template column</t>
+          <t>Locations appears under the Settings area</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1648,19 +1648,19 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>UI: the roles list has a Template column (header between Description and Role Type).</t>
+          <t>UI: Locations appears under the SETTINGS area in the sidebar (SETTINGS &gt; Settings/Staff/Roles &amp; Permissions/Locations/Departments/Taxes).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C26320</t>
+          <t>C26319</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26320</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26319</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Each of the 11 system roles shows its description</t>
+          <t>The roles list has a Template column</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1688,19 +1688,19 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>UI: all 11 system roles display a description in the Description column (e.g. Admin "Full system access", Foreman "Oversees technicians and work orders").</t>
+          <t>UI: the roles list has a Template column (header between Description and Role Type).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C26321</t>
+          <t>C26320</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26321</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26320</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>A custom role with no description shows a dash</t>
+          <t>Each of the 11 system roles shows its description</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1728,19 +1728,19 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>UI: custom role Bilal - Cus (no description) shows a dash (-) in the Description column.</t>
+          <t>UI: all 11 system roles display a description in the Description column (e.g. Admin "Full system access", Foreman "Oversees technicians and work orders").</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C26322</t>
+          <t>C26321</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26322</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26321</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>An editable system role's three-dot menu shows View Permissions and no Delete</t>
+          <t>A custom role with no description shows a dash</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1768,19 +1768,19 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>UI: 3-dot menu on Admin (editable system role) shows only "View Permissions" (no Delete).</t>
+          <t>UI: custom role Bilal - Cus (no description) shows a dash (-) in the Description column.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C26323</t>
+          <t>C26322</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26323</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26322</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>The three-dot menu is hidden on the non-editable system roles (Office User, Time Clock User)</t>
+          <t>An editable system role's three-dot menu shows View Permissions and no Delete</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1808,19 +1808,19 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>UI: Office User and Time Clock User rows have no 3-dot menu (only the eye icon).</t>
+          <t>UI: 3-dot menu on Admin (editable system role) shows only "View Permissions" (no Delete).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C26324</t>
+          <t>C26323</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26324</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26323</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>A custom role's three-dot menu shows View Permissions and Delete</t>
+          <t>The three-dot menu is hidden on the non-editable system roles (Office User, Time Clock User)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1848,19 +1848,19 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>UI: 3-dot menu on Bilal - Cus (0-user custom role) shows "View Permissions" and "Delete".</t>
+          <t>UI: Office User and Time Clock User rows have no 3-dot menu (only the eye icon).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C26325</t>
+          <t>C26324</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26325</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26324</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Deletion and duplication behavior on the roles list</t>
+          <t>A custom role's three-dot menu shows View Permissions and Delete</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1888,32 +1888,32 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>UI: list supports deletion (Delete in custom-role 3-dot -&gt; Confirmation dialog) and duplication (roles-permissions/:id/duplicate route reachable, opens Create Role prefilled).</t>
+          <t>UI: 3-dot menu on Bilal - Cus (0-user custom role) shows "View Permissions" and "Delete".</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C26326</t>
+          <t>C26325</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26326</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26325</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3529</v>
+        <v>3528</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Create Custom Role</t>
+          <t>Roles List Page</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>The template picker lists all 11 system role templates with descriptions</t>
+          <t>Deletion and duplication behavior on the roles list</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1928,19 +1928,19 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>UI: template picker "Choose a template" lists all 11 system role templates each with its description (Admin, Foreman, Office User, Parts Manager, Parts Technician, Sales Representative, Senior Service Advisor, Service Advisor, Service Manager, Technician, Time Clock User) + Skip + Apply.</t>
+          <t>UI: list supports deletion (Delete in custom-role 3-dot -&gt; Confirmation dialog) and duplication (roles-permissions/:id/duplicate route reachable, opens Create Role prefilled).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C26327</t>
+          <t>C26326</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26327</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26326</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Selecting a template highlights that row with a checkmark</t>
+          <t>The template picker lists all 11 system role templates with descriptions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1968,19 +1968,19 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>UI: selecting the Foreman template highlights that card (choose-template-card selected) and shows a checkmark (hasCheck true). screenshot template-selected.</t>
+          <t>UI: template picker "Choose a template" lists all 11 system role templates each with its description (Admin, Foreman, Office User, Parts Manager, Parts Technician, Sales Representative, Senior Service Advisor, Service Advisor, Service Manager, Technician, Time Clock User) + Skip + Apply.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C26328</t>
+          <t>C26327</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26328</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26327</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Applying a template opens the Create Role page pre-filled with that template's settings</t>
+          <t>Selecting a template highlights that row with a checkmark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2008,19 +2008,19 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>UI: Apply opens /roles-permissions/new?template=&lt;foreman id&gt; prefilled with Foreman defaults: WO View ON, WO Delete off, Parts Department ON, See Financial Data ON, AP/AR off, Reports off (matches Foreman role).</t>
+          <t>UI: selecting the Foreman template highlights that card (choose-template-card selected) and shows a checkmark (hasCheck true). screenshot template-selected.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C26329</t>
+          <t>C26328</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26329</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26328</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Skipping the template starts a blank role with all permissions off</t>
+          <t>Applying a template opens the Create Role page pre-filled with that template's settings</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2048,19 +2048,19 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>UI: Skip opens /roles-permissions/new blank — WO View off, Customers View off, Schedule View off, Reports off, See Financial Data off (all permissions off).</t>
+          <t>UI: Apply opens /roles-permissions/new?template=&lt;foreman id&gt; prefilled with Foreman defaults: WO View ON, WO Delete off, Parts Department ON, See Financial Data ON, AP/AR off, Reports off (matches Foreman role).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C26330</t>
+          <t>C26329</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26330</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26329</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>The Create Role page shows Basic Details with a required Role name and optional Description</t>
+          <t>Skipping the template starts a blank role with all permissions off</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2088,19 +2088,19 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>UI: Create Role page shows Basic Details with "Role Name*" (required) and "Description" (optional) fields.</t>
+          <t>UI: Skip opens /roles-permissions/new blank — WO View off, Customers View off, Schedule View off, Reports off, See Financial Data off (all permissions off).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C26331</t>
+          <t>C26330</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26331</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26330</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>The permissions section shows the resource cards with their columns</t>
+          <t>The Create Role page shows Basic Details with a required Role name and optional Description</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2123,24 +2123,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Card set + columns build-verified (PermissionGrid).</t>
+          <t>UI: Create Role page shows Basic Details with "Role Name*" (required) and "Description" (optional) fields.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C26332</t>
+          <t>C26331</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26332</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26331</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>The permission search box filters the cards</t>
+          <t>The permissions section shows the resource cards with their columns</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2163,24 +2163,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>UI: typing "Schedule" in the permission search (search_permission) filters the cards — the Work orders card is filtered out; only matching cards remain.</t>
+          <t>Card set + columns build-verified (PermissionGrid).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C26333</t>
+          <t>C26332</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26333</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26332</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>A blank Role name blocks Create with an inline message</t>
+          <t>The permission search box filters the cards</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2208,19 +2208,19 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>UI: with a blank Role Name the Create button is disabled; touching then clearing the name shows inline error "Role name is a required field".</t>
+          <t>UI: typing "Schedule" in the permission search (search_permission) filters the cards — the Work orders card is filtered out; only matching cards remain.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C26334</t>
+          <t>C26333</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26334</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26333</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>You can change any setting from the template defaults before saving</t>
+          <t>A blank Role name blocks Create with an inline message</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2248,19 +2248,19 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>UI: after applying the Foreman template you can change any setting before saving (unticked Work orders View from ON to off successfully).</t>
+          <t>UI: with a blank Role Name the Create button is disabled; touching then clearing the name shows inline error "Role name is a required field".</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C26335</t>
+          <t>C26334</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26335</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26334</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Create is blocked with zero permissions (button disabled, no message)</t>
+          <t>You can change any setting from the template defaults before saving</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2288,19 +2288,19 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>UI: with zero permissions (and/or blank name) the Create button (submit_create_role) is DISABLED, no inline message.</t>
+          <t>UI: after applying the Foreman template you can change any setting before saving (unticked Work orders View from ON to off successfully).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C26336</t>
+          <t>C26335</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26336</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26335</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>A successful Create shows a success message and returns to the list</t>
+          <t>Create is blocked with zero permissions (button disabled, no message)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2328,19 +2328,19 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>UI: creating ZZAUTOTEST RoleA (name + 1 perm) shows toast "Role created successfully." and returns to the Roles &amp; Permissions list.</t>
+          <t>UI: with zero permissions (and/or blank name) the Create button (submit_create_role) is DISABLED, no inline message.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C26337</t>
+          <t>C26336</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26337</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26336</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Same name and permissions as an existing role shows a 'Similar role already exists' confirmation</t>
+          <t>A successful Create shows a success message and returns to the list</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2368,19 +2368,19 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>UI: creating a role with the same name+permissions shows dialog "Similar role already exists — A role \"ZZAUTOTEST RoleA\" with identical permissions already exists. You can reuse the existing role or create a new one anyway." [Cancel | Create Anyway]. screenshot similar-role-warning.</t>
+          <t>UI: creating ZZAUTOTEST RoleA (name + 1 perm) shows toast "Role created successfully." and returns to the Roles &amp; Permissions list.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C26338</t>
+          <t>C26337</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26338</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26337</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Turning on every permission shows the 'Full administrative access' warning banner</t>
+          <t>Same name and permissions as an existing role shows a 'Similar role already exists' confirmation</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2403,37 +2403,37 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>'Full administrative access' banner confirmed in build (AdminWarningBanner).</t>
+          <t>UI: creating a role with the same name+permissions shows dialog "Similar role already exists — A role \"ZZAUTOTEST RoleA\" with identical permissions already exists. You can reuse the existing role or create a new one anyway." [Cancel | Create Anyway]. screenshot similar-role-warning.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>C26342</t>
+          <t>C26338</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26342</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26338</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3530</v>
+        <v>3529</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Edit Role</t>
+          <t>Create Custom Role</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Edit opens the role editor pre-filled with the role's current settings</t>
+          <t>Turning on every permission shows the 'Full administrative access' warning banner</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2443,24 +2443,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>UI: Edit opens /roles-permissions/{id}/edit with heading "Edit Role", Basic Details prefilled and all permission cards reflecting the role current settings (verified on Admin + Technician).</t>
+          <t>'Full administrative access' banner confirmed in build (AdminWarningBanner).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>C26343</t>
+          <t>C26342</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26343</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26342</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Saving an edited role shows 'Role updated successfully.' after a confirmation dialog</t>
+          <t>Edit opens the role editor pre-filled with the role's current settings</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2488,19 +2488,19 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>UI: after changing a permission, Save opens "Confirm Permission Updates" dialog listing Added/Removed permissions ("Don-t show this dialog again") [Cancel|Confirm]; Confirm shows toast "Role updated successfully." and returns to the list.</t>
+          <t>UI: Edit opens /roles-permissions/{id}/edit with heading "Edit Role", Basic Details prefilled and all permission cards reflecting the role current settings (verified on Admin + Technician).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>C26344</t>
+          <t>C26343</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26344</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26343</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Reset to template restores template defaults; Save is only enabled if something changed</t>
+          <t>Saving an edited role shows 'Role updated successfully.' after a confirmation dialog</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2528,19 +2528,19 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>UI: Reset To Template opens "Reset to template — This replaces all current selections with the \"Foreman\" template defaults. Any changes you have made will be lost." [Cancel|Reset]. Save (submit_edit_role) is DISABLED when nothing changed and ENABLED after a change.</t>
+          <t>UI: after changing a permission, Save opens "Confirm Permission Updates" dialog listing Added/Removed permissions ("Don-t show this dialog again") [Cancel|Confirm]; Confirm shows toast "Role updated successfully." and returns to the list.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>C26345</t>
+          <t>C26344</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26345</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26344</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Changing a role logs an active user out; new permissions apply at next login</t>
+          <t>Reset to template restores template defaults; Save is only enabled if something changed</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2568,19 +2568,19 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>API/session: changing a role invalidates the affected user active session (old session -&gt; 409 "Session has expired."); new permissions apply at next login. Same mechanism as C26525.</t>
+          <t>UI: Reset To Template opens "Reset to template — This replaces all current selections with the \"Foreman\" template defaults. Any changes you have made will be lost." [Cancel|Reset]. Save (submit_edit_role) is DISABLED when nothing changed and ENABLED after a change.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C26346</t>
+          <t>C26345</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26346</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26345</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>The Office User system role cannot be edited (lock icon, eye only)</t>
+          <t>Changing a role logs an active user out; new permissions apply at next login</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2608,19 +2608,19 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>UI: on the Roles list the Office User row shows a lock and only the eye (visibility) icon — no pencil; the eye opens the read-only Permission Summary (View Permissions). NOTE for dev: the direct /roles-permissions/{id}/edit URL still loads an editable form (FE route not guarded) — list-level gating is correct.</t>
+          <t>API/session: changing a role invalidates the affected user active session (old session -&gt; 409 "Session has expired."); new permissions apply at next login. Same mechanism as C26525.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C26347</t>
+          <t>C26346</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26347</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26346</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>The Time Clock User system role cannot be edited (lock icon, eye only)</t>
+          <t>The Office User system role cannot be edited (lock icon, eye only)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2648,19 +2648,19 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>UI: on the Roles list the Time Clock User row shows a lock and only the eye icon — no pencil; the eye opens the read-only Permission Summary. Same /edit-URL FE-gap note as C26346.</t>
+          <t>UI: on the Roles list the Office User row shows a lock and only the eye (visibility) icon — no pencil; the eye opens the read-only Permission Summary (View Permissions). NOTE for dev: the direct /roles-permissions/{id}/edit URL still loads an editable form (FE route not guarded) — list-level gating is correct.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C26348</t>
+          <t>C26347</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26348</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26347</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>The role name cannot be left empty when editing</t>
+          <t>The Time Clock User system role cannot be edited (lock icon, eye only)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2688,19 +2688,19 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>UI: clearing the Role Name on Edit shows inline error "Role name is a required field" (name cannot be left empty when editing).</t>
+          <t>UI: on the Roles list the Time Clock User row shows a lock and only the eye icon — no pencil; the eye opens the read-only Permission Summary. Same /edit-URL FE-gap note as C26346.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C26349</t>
+          <t>C26348</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26349</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26348</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Editing: at least one permission must be turned on to save</t>
+          <t>The role name cannot be left empty when editing</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>UI: editing a role down to zero permissions -&gt; Save opens "Confirm Permission Updates" (Removed permissions listed) -&gt; Confirm shows toast "At least one permission is required. Please try to resolve this." and the role is NOT saved (stays on edit). Submit-time validation enforces at least one permission. screenshot edit-zero-perm.</t>
+          <t>UI: clearing the Role Name on Edit shows inline error "Role name is a required field" (name cannot be left empty when editing).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C26350</t>
+          <t>C26349</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26350</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26349</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3531</v>
+        <v>3530</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Delete Role</t>
+          <t>Edit Role</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>A custom role with 0 users can be deleted from the three-dot menu</t>
+          <t>Editing: at least one permission must be turned on to save</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2768,19 +2768,19 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>UI: Bilal - Cus (0 users) 3-dot menu shows Delete -&gt; "Confirmation" dialog to delete.</t>
+          <t>UI: editing a role down to zero permissions -&gt; Save opens "Confirm Permission Updates" (Removed permissions listed) -&gt; Confirm shows toast "At least one permission is required. Please try to resolve this." and the role is NOT saved (stays on edit). Submit-time validation enforces at least one permission. screenshot edit-zero-perm.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C26351</t>
+          <t>C26350</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26351</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26350</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>A custom role with 1 or more users cannot be deleted</t>
+          <t>A custom role with 0 users can be deleted from the three-dot menu</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2808,19 +2808,19 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>UI: Parth Cust1 (1 user) 3-dot menu shows only View Permissions, no Delete option.</t>
+          <t>UI: Bilal - Cus (0 users) 3-dot menu shows Delete -&gt; "Confirmation" dialog to delete.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C26352</t>
+          <t>C26351</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26352</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26351</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>After moving the assigned users to another role, the role can be deleted</t>
+          <t>A custom role with 1 or more users cannot be deleted</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2848,19 +2848,19 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>UI/API: assigned Tech to a custom role -&gt; usersCount=1, isDeletable=false, DELETE blocked (400 "Role is not deletable/editable."). Reassigned Tech to Time Clock -&gt; usersCount=0, isDeletable=true -&gt; DELETE 204 (role deleted). Reassignment + delete-after-zero-users flow confirmed.</t>
+          <t>UI: Parth Cust1 (1 user) 3-dot menu shows only View Permissions, no Delete option.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>C26353</t>
+          <t>C26352</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26353</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26352</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>System roles have no Delete option anywhere</t>
+          <t>After moving the assigned users to another role, the role can be deleted</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2888,19 +2888,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>UI: editable system role 3-dot shows only View Permissions (no Delete); non-editable system roles have no 3-dot at all. No Delete anywhere for system roles.</t>
+          <t>UI/API: assigned Tech to a custom role -&gt; usersCount=1, isDeletable=false, DELETE blocked (400 "Role is not deletable/editable."). Reassigned Tech to Time Clock -&gt; usersCount=0, isDeletable=true -&gt; DELETE 204 (role deleted). Reassignment + delete-after-zero-users flow confirmed.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>C26354</t>
+          <t>C26353</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26354</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26353</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>The assigned-user count is correct when a delete is blocked</t>
+          <t>System roles have no Delete option anywhere</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2928,32 +2928,32 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>UI: Parth Cust1 Users column shows 1; its menu has no Delete — the assigned-user count matches the blocked-delete state.</t>
+          <t>UI: editable system role 3-dot shows only View Permissions (no Delete); non-editable system roles have no 3-dot at all. No Delete anywhere for system roles.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>C26355</t>
+          <t>C26354</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26355</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26354</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Permission Summary</t>
+          <t>Delete Role</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>The eye icon on the Roles list opens the read-only Permission Summary</t>
+          <t>The assigned-user count is correct when a delete is blocked</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2968,19 +2968,19 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>UI: the eye (visibility) icon opens the read-only Permission Summary ("View Permissions") at /roles-permissions/{id}/summary — no Save/Delete/edit controls.</t>
+          <t>UI: Parth Cust1 Users column shows 1; its menu has no Delete — the assigned-user count matches the blocked-delete state.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>C26357</t>
+          <t>C26355</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26357</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26355</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>The eye icon on the Office row opens the Permission Summary</t>
+          <t>The eye icon on the Roles list opens the read-only Permission Summary</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3008,19 +3008,19 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>UI: the eye icon on the Office User row opens the read-only Permission Summary (View Permissions).</t>
+          <t>UI: the eye (visibility) icon opens the read-only Permission Summary ("View Permissions") at /roles-permissions/{id}/summary — no Save/Delete/edit controls.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>C26358</t>
+          <t>C26357</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26358</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26357</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>The eye icon on the Time Clock User row opens the Permission Summary</t>
+          <t>The eye icon on the Office row opens the Permission Summary</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3048,19 +3048,19 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>UI: the eye icon on the Time Clock User row opens the read-only Permission Summary (summary route renders read-only).</t>
+          <t>UI: the eye icon on the Office User row opens the read-only Permission Summary (View Permissions).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>C26359</t>
+          <t>C26358</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26359</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26358</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>The Permission Summary is grouped and shows each setting's on/off state</t>
+          <t>The eye icon on the Time Clock User row opens the Permission Summary</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3088,32 +3088,32 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>UI: the Permission Summary is grouped by card and shows each setting on/off — Office User summary read exactly matches the role: WO View ON / WO C&amp;E off / Customers View+C&amp;E+Delete ON / Invoicing C&amp;E off / Reports ON / See Financial Data ON / AP-AR ON.</t>
+          <t>UI: the eye icon on the Time Clock User row opens the read-only Permission Summary (summary route renders read-only).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>C26360</t>
+          <t>C26359</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26360</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26359</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3533</v>
+        <v>3532</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CRUD Cascade Rules</t>
+          <t>Permission Summary</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ticking Create &amp; Edit on Work orders also ticks View</t>
+          <t>The Permission Summary is grouped and shows each setting's on/off state</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3128,19 +3128,19 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>UI: on blank Create Role form, ticking Work orders Create &amp; Edit auto-ticks View (aria-checked View ON, C&amp;E ON). screenshot cascade-final.</t>
+          <t>UI: the Permission Summary is grouped by card and shows each setting on/off — Office User summary read exactly matches the role: WO View ON / WO C&amp;E off / Customers View+C&amp;E+Delete ON / Invoicing C&amp;E off / Reports ON / See Financial Data ON / AP-AR ON.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>C26361</t>
+          <t>C26360</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26361</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26360</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ticking Delete on Work orders also ticks Create &amp; Edit and View</t>
+          <t>Ticking Create &amp; Edit on Work orders also ticks View</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3168,19 +3168,19 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>UI: ticking Work orders Delete auto-ticks Create &amp; Edit and View (all ON).</t>
+          <t>UI: on blank Create Role form, ticking Work orders Create &amp; Edit auto-ticks View (aria-checked View ON, C&amp;E ON). screenshot cascade-final.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>C26362</t>
+          <t>C26361</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26362</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26361</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Unticking View on Work orders also unticks Create &amp; Edit and Delete</t>
+          <t>Ticking Delete on Work orders also ticks Create &amp; Edit and View</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3208,19 +3208,19 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>UI: unticking Work orders View clears Create &amp; Edit and Delete (all off).</t>
+          <t>UI: ticking Work orders Delete auto-ticks Create &amp; Edit and View (all ON).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>C26363</t>
+          <t>C26362</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26363</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26362</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Unticking Create &amp; Edit on Work orders also unticks Delete but keeps View</t>
+          <t>Unticking View on Work orders also unticks Create &amp; Edit and Delete</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3248,19 +3248,19 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>UI: unticking Work orders Create &amp; Edit clears Delete but keeps View ON.</t>
+          <t>UI: unticking Work orders View clears Create &amp; Edit and Delete (all off).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>C26364</t>
+          <t>C26363</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26364</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26363</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>The same tick-cascade works on the Schedule card</t>
+          <t>Unticking Create &amp; Edit on Work orders also unticks Delete but keeps View</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3288,19 +3288,19 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>UI: Schedule card tick Delete auto-ticks Create &amp; Edit + View (all ON).</t>
+          <t>UI: unticking Work orders Create &amp; Edit clears Delete but keeps View ON.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>C26365</t>
+          <t>C26364</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26365</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26364</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>The same untick-cascade works on the Customers card</t>
+          <t>The same tick-cascade works on the Schedule card</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3328,19 +3328,19 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>UI: Customers card untick View clears Create &amp; Edit + Delete (all off).</t>
+          <t>UI: Schedule card tick Delete auto-ticks Create &amp; Edit + View (all ON).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>C26366</t>
+          <t>C26365</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26366</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26365</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Cascade works on Part sales with no See-Financial dialog when See Financial Data is already ON</t>
+          <t>The same untick-cascade works on the Customers card</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3368,19 +3368,19 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>UI: with See Financial Data already ON, Part sales tick Delete cascades View+C&amp;E with NO dialog.</t>
+          <t>UI: Customers card untick View clears Create &amp; Edit + Delete (all off).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C26367</t>
+          <t>C26366</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26367</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26366</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cascade works on the Catalog and Inventory card</t>
+          <t>Cascade works on Part sales with no See-Financial dialog when See Financial Data is already ON</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3408,19 +3408,19 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>UI: Catalog and Inventory tick Delete cascades View+C&amp;E (all ON), no dialog.</t>
+          <t>UI: with See Financial Data already ON, Part sales tick Delete cascades View+C&amp;E with NO dialog.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C26368</t>
+          <t>C26367</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26368</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26367</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cascade works on the Vendor and order management card</t>
+          <t>Cascade works on the Catalog and Inventory card</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3448,19 +3448,19 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>UI: Vendor and order management tick Delete cascades View+C&amp;E (all ON), no dialog.</t>
+          <t>UI: Catalog and Inventory tick Delete cascades View+C&amp;E (all ON), no dialog.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>C26369</t>
+          <t>C26368</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26369</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26368</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Cascade works on the Invoicing &amp; payments card when See Financial Data is ON</t>
+          <t>Cascade works on the Vendor and order management card</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3488,19 +3488,19 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>UI: with SFD ON, Invoicing &amp; payments tick Create&amp;Edit cascades View ON, no SFD dialog.</t>
+          <t>UI: Vendor and order management tick Delete cascades View+C&amp;E (all ON), no dialog.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C26370</t>
+          <t>C26369</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26370</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26369</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>The Work order lines card has no View column (View comes from Work orders)</t>
+          <t>Cascade works on the Invoicing &amp; payments card when See Financial Data is ON</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3523,24 +3523,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Work order lines card structure (no View column) build-verified.</t>
+          <t>UI: with SFD ON, Invoicing &amp; payments tick Create&amp;Edit cascades View ON, no SFD dialog.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C26371</t>
+          <t>C26370</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26371</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26370</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>The Timesheets card has no Delete box</t>
+          <t>The Work order lines card has no View column (View comes from Work orders)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3568,19 +3568,19 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Timesheets card has no Delete (build-verified).</t>
+          <t>Work order lines card structure (no View column) build-verified.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C26372</t>
+          <t>C26371</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26372</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26371</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ticking Create &amp; Edit on Work order lines also ticks Work orders View</t>
+          <t>The Timesheets card has no Delete box</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3603,24 +3603,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>UI: ticking Work order lines Create &amp; Edit on blank form opens dialog "Enable Work Orders: View? — Work Order Lines requires Work Orders: View. Enable it to grant this permission?" [Cancel|Enable]; Enable -&gt; WO View ON + WOL C&amp;E ON.</t>
+          <t>Timesheets card has no Delete (build-verified).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C26373</t>
+          <t>C26372</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26373</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26372</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Unticking Work orders View clears Work order lines Create &amp; Edit and Delete</t>
+          <t>Ticking Create &amp; Edit on Work order lines also ticks Work orders View</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3648,32 +3648,32 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>UI: unticking Work orders View clears Work order lines Create &amp; Edit and Delete (all off).</t>
+          <t>UI: ticking Work order lines Create &amp; Edit on blank form opens dialog "Enable Work Orders: View? — Work Order Lines requires Work Orders: View. Enable it to grant this permission?" [Cancel|Enable]; Enable -&gt; WO View ON + WOL C&amp;E ON.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C26374</t>
+          <t>C26373</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26374</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26373</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3534</v>
+        <v>3533</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Work Orders Permissions</t>
+          <t>CRUD Cascade Rules</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Work orders View gives access to the work order list and detail</t>
+          <t>Unticking Work orders View clears Work order lines Create &amp; Edit and Delete</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3688,19 +3688,19 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>UI: a role with Work Orders View (Technician; also WOCust) loads the Work Orders list at /workorders with all columns and rows. WO View grants list access.</t>
+          <t>UI: unticking Work orders View clears Work order lines Create &amp; Edit and Delete (all off).</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C26375</t>
+          <t>C26374</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26375</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26374</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Work orders Create &amp; Edit lets the user create and change work orders</t>
+          <t>Work orders View gives access to the work order list and detail</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3728,19 +3728,19 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>UI (role WO Create&amp;Edit, no Delete): the WO list shows the New (create) button; a WO can be created/edited; the WO detail has no Delete option. screenshot wo-ce-nodelete.</t>
+          <t>UI: a role with Work Orders View (Technician; also WOCust) loads the Work Orders list at /workorders with all columns and rows. WO View grants list access.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C26376</t>
+          <t>C26375</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26376</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26375</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Work orders Delete lets the user delete work orders</t>
+          <t>Work orders Create &amp; Edit lets the user create and change work orders</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3768,19 +3768,19 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>UI (role with Work Orders Delete): the work order header more_vert menu shows "Delete Work Order" (menu: Audit Log | Add Fee/Discount | Delete Work Order). Deletion action present for the Delete permission. screenshot wo-delete-role.</t>
+          <t>UI (role WO Create&amp;Edit, no Delete): the WO list shows the New (create) button; a WO can be created/edited; the WO detail has no Delete option. screenshot wo-ce-nodelete.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C26377</t>
+          <t>C26376</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26377</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26376</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Work orders View OFF hides Work Orders from the top navigation</t>
+          <t>Work orders Delete lets the user delete work orders</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3808,19 +3808,19 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>UI (Sales Rep = no workOrdersView): the top nav has no Work Orders item (shows Reports etc); navigating to /workorders redirects to /reports. WO View OFF hides Work Orders from nav while other accessible items still show. screenshot salesrep-nav.</t>
+          <t>UI (role with Work Orders Delete): the work order header more_vert menu shows "Delete Work Order" (menu: Audit Log | Add Fee/Discount | Delete Work Order). Deletion action present for the Delete permission. screenshot wo-delete-role.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C26378</t>
+          <t>C26377</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26378</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26377</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>The Work orders sub-toggles are shown but disabled when Work orders View is OFF</t>
+          <t>Work orders View OFF hides Work Orders from the top navigation</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3848,19 +3848,19 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>UI: on blank form (WO View off) the Work orders sub-toggles Review work orders / Pick parts / Order parts are shown but DISABLED (aria-disabled); ticking Work orders View enables them.</t>
+          <t>UI (Sales Rep = no workOrdersView): the top nav has no Work Orders item (shows Reports etc); navigating to /workorders redirects to /reports. WO View OFF hides Work Orders from nav while other accessible items still show. screenshot salesrep-nav.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C26381</t>
+          <t>C26378</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26381</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26378</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Order parts needs Work orders View and See Financial Data (not Create &amp; Edit)</t>
+          <t>The Work orders sub-toggles are shown but disabled when Work orders View is OFF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3888,19 +3888,19 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>UI (role woOrderParts + Work Orders View + See Financial Data, NO Create&amp;Edit): the WO Parts tab is accessible and Order parts works without Work Orders Create&amp;Edit. Order parts needs only WO View + SFD.</t>
+          <t>UI: on blank form (WO View off) the Work orders sub-toggles Review work orders / Pick parts / Order parts are shown but DISABLED (aria-disabled); ticking Work orders View enables them.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C26382</t>
+          <t>C26381</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26382</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26381</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Pick parts and Order parts are independent toggles</t>
+          <t>Order parts needs Work orders View and See Financial Data (not Create &amp; Edit)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3928,19 +3928,19 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>UI: Pick parts and Order parts are independent — ticking Pick parts leaves Order parts off.</t>
+          <t>UI (role woOrderParts + Work Orders View + See Financial Data, NO Create&amp;Edit): the WO Parts tab is accessible and Order parts works without Work Orders Create&amp;Edit. Order parts needs only WO View + SFD.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C26383</t>
+          <t>C26382</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26383</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26382</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Without Create &amp; Edit, create/edit options are hidden on work orders</t>
+          <t>Pick parts and Order parts are independent toggles</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3968,19 +3968,19 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>UI (Time Clock User = Work Orders View only, no Create&amp;Edit): the WO list has no New (create) button and the WO detail has no New Line / create-edit affordances (header read-only). screenshot wo-timeclock-readonly.</t>
+          <t>UI: Pick parts and Order parts are independent — ticking Pick parts leaves Order parts off.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>C26384</t>
+          <t>C26383</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26384</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26383</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Without Delete, no delete option is shown on a work order</t>
+          <t>Without Create &amp; Edit, create/edit options are hidden on work orders</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4008,19 +4008,19 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>UI (role WO Create&amp;Edit WITHOUT Delete): the work order detail shows no Delete option anywhere (hasDelete=false).</t>
+          <t>UI (Time Clock User = Work Orders View only, no Create&amp;Edit): the WO list has no New (create) button and the WO detail has no New Line / create-edit affordances (header read-only). screenshot wo-timeclock-readonly.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C26385</t>
+          <t>C26384</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26385</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26384</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Creating a work order still works when Customers View is OFF</t>
+          <t>Without Delete, no delete option is shown on a work order</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4048,19 +4048,19 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>UI (role WO Create&amp;Edit, no Customers View): Customers is absent from top nav, but the New Work Order modal customer selector still opens and lists all customers (new test, 11 A new Company, A 2 Company, ...) — data reachable.</t>
+          <t>UI (role WO Create&amp;Edit WITHOUT Delete): the work order detail shows no Delete option anywhere (hasDelete=false).</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C26386</t>
+          <t>C26385</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26386</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26385</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>The customer name shows on the work order header even when Customers View is OFF</t>
+          <t>Creating a work order still works when Customers View is OFF</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4088,19 +4088,19 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>UI (no Customers View): the customer name/contact shows on the work order header/detail even though Customers is hidden from nav (customer is part of the WO record).</t>
+          <t>UI (role WO Create&amp;Edit, no Customers View): Customers is absent from top nav, but the New Work Order modal customer selector still opens and lists all customers (new test, 11 A new Company, A 2 Company, ...) — data reachable.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>C27868</t>
+          <t>C26386</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27868</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26386</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Order parts controls the work order Parts tab (on shows it, off hides it)</t>
+          <t>The customer name shows on the work order header even when Customers View is OFF</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4128,32 +4128,32 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>UI: Order parts controls the WO Parts tab — role WITH woOrderParts shows tabs Lines/Parts(7)/Notes/Stats (Parts tab present); the Technician role (woPickParts, no woOrderParts) showed Lines/Notes/Stats with NO Parts tab. On shows it, off hides it.</t>
+          <t>UI (no Customers View): the customer name/contact shows on the work order header/detail even though Customers is hidden from nav (customer is part of the WO record).</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>C26389</t>
+          <t>C27868</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26389</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27868</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3535</v>
+        <v>3534</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Work Order Lines Permissions</t>
+          <t>Work Orders Permissions</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Work order lines are visible whenever Work orders View is ON</t>
+          <t>Order parts controls the work order Parts tab (on shows it, off hides it)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4168,19 +4168,19 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>UI (Time Clock User = WO View only): work order lines are visible (line items/labor/parts) but there is no New Line/add option and no edit controls — lines visible whenever WO View is on. screenshot wol-tcuLines.</t>
+          <t>UI: Order parts controls the WO Parts tab — role WITH woOrderParts shows tabs Lines/Parts(7)/Notes/Stats (Parts tab present); the Technician role (woPickParts, no woOrderParts) showed Lines/Notes/Stats with NO Parts tab. On shows it, off hides it.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>C26390</t>
+          <t>C26389</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26390</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26389</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Work order lines Create &amp; Edit allows adding, editing, moving parts, authorizing and managing part requests</t>
+          <t>Work order lines are visible whenever Work orders View is ON</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4208,19 +4208,19 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>UI (role WO View + Work order lines Create&amp;Edit): the lines screen shows New Line + Build Lines — the user can add/edit lines (add and line management affordances present). screenshot wol-wolce.</t>
+          <t>UI (Time Clock User = WO View only): work order lines are visible (line items/labor/parts) but there is no New Line/add option and no edit controls — lines visible whenever WO View is on. screenshot wol-tcuLines.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>C26392</t>
+          <t>C26390</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26392</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26390</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Work orders View OFF makes work order lines unreachable</t>
+          <t>Work order lines Create &amp; Edit allows adding, editing, moving parts, authorizing and managing part requests</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4248,19 +4248,19 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>UI (Sales Rep = no workOrdersView): Work Orders is hidden from nav and /workorders redirects to /reports, so no work order (and therefore no work order lines) is reachable. WO View OFF makes WO lines unreachable.</t>
+          <t>UI (role WO View + Work order lines Create&amp;Edit): the lines screen shows New Line + Build Lines — the user can add/edit lines (add and line management affordances present). screenshot wol-wolce.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>C26393</t>
+          <t>C26392</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26393</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26392</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Work order lines are read-only when Create &amp; Edit is OFF</t>
+          <t>Work orders View OFF makes work order lines unreachable</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4288,19 +4288,19 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>UI (WO View only, no WOL Create&amp;Edit): no Add line option and existing line fields are read-only (no New Line, no edit affordances). screenshot wol-tcuLines.</t>
+          <t>UI (Sales Rep = no workOrdersView): Work Orders is hidden from nav and /workorders redirects to /reports, so no work order (and therefore no work order lines) is reachable. WO View OFF makes WO lines unreachable.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>C27271</t>
+          <t>C26393</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27271</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26393</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>The Build Lines entry point is hidden for a Work Orders View-only role</t>
+          <t>Work order lines are read-only when Create &amp; Edit is OFF</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4328,19 +4328,19 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>UI (WO View-only role): the Build Lines entry point is not shown (buildLines=false).</t>
+          <t>UI (WO View only, no WOL Create&amp;Edit): no Add line option and existing line fields are read-only (no New Line, no edit affordances). screenshot wol-tcuLines.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>C27272</t>
+          <t>C27271</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27272</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27271</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>The Build Lines entry point is shown for a role with Work order lines Create &amp; Edit</t>
+          <t>The Build Lines entry point is hidden for a Work Orders View-only role</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4368,32 +4368,32 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>UI (role with Work order lines Create&amp;Edit): the Build Lines entry point is shown (Build Lines button present).</t>
+          <t>UI (WO View-only role): the Build Lines entry point is not shown (buildLines=false).</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>C26394</t>
+          <t>C27272</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26394</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27272</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>3536</v>
+        <v>3535</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Schedule Permissions</t>
+          <t>Work Order Lines Permissions</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Schedule View shows the calendar with all technicians</t>
+          <t>The Build Lines entry point is shown for a role with Work order lines Create &amp; Edit</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4408,19 +4408,19 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>UI: a role with Schedule View (ZZAUTOTEST Viewer) opens /schedule and the calendar renders. Schedule appears in top nav.</t>
+          <t>UI (role with Work order lines Create&amp;Edit): the Build Lines entry point is shown (Build Lines button present).</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>C26397</t>
+          <t>C26394</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26397</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26394</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Schedule View OFF hides Schedule from the top navigation</t>
+          <t>Schedule View shows the calendar with all technicians</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4448,32 +4448,32 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>UI: the WOCust custom role (no scheduleView) has NO Schedule item in the top navigation — Schedule View OFF hides Schedule from nav.</t>
+          <t>UI: a role with Schedule View (ZZAUTOTEST Viewer) opens /schedule and the calendar renders. Schedule appears in top nav.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>C26398</t>
+          <t>C26397</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26398</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26397</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3537</v>
+        <v>3536</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Schedule Permissions</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Customers View gives access to customer records, contacts, vehicles and history</t>
+          <t>Schedule View OFF hides Schedule from the top navigation</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4488,19 +4488,19 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>UI: a role with Customers View opens /customers and the customer list renders (customer records accessible; contacts/vehicles/history are sub-views of a record). Customers appears in nav.</t>
+          <t>UI: the WOCust custom role (no scheduleView) has NO Schedule item in the top navigation — Schedule View OFF hides Schedule from nav.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>C26402</t>
+          <t>C26398</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26402</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26398</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AP/AR OFF hides the 7 sensitive customer fields on Edit Customer</t>
+          <t>Customers View gives access to customer records, contacts, vehicles and history</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4528,19 +4528,19 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>UI: role with View and Manage AP/AR Data OFF (Service Advisor) — Edit Customer modal has NO sensitive fields (no Credit Limit, Taxes, Default Labor Rate, etc). With AP/AR ON they are present. screenshot customer-aparOFF vs customer-aparON.</t>
+          <t>UI: a role with Customers View opens /customers and the customer list renders (customer records accessible; contacts/vehicles/history are sub-views of a record). Customers appears in nav.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>C26403</t>
+          <t>C26399</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26403</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26399</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AP/AR ON shows the 7 sensitive customer fields on Edit Customer</t>
+          <t>Customers Create &amp; Edit allows creating customers, contacts and vehicles</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4568,19 +4568,19 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>UI (role with View and Manage AP/AR Data ON): the Edit Customer modal shows all 7 sensitive fields — Credit Terms, Credit Limit, Default Labor Rate, Default Shop Supplies, Min, Max, Taxes (and PO-required). screenshot customer-apar-on.</t>
+          <t>UI (role with Customers Create&amp;Edit = Service Advisor): the /customers list shows the New Customer create control; a customer without customersDelete shows no Delete. Create customers/contacts/vehicles is enabled by Customers Create&amp;Edit. screenshot cust-SAce.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>C26404</t>
+          <t>C26400</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26404</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26400</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Customers View OFF hides Customers from the top navigation</t>
+          <t>Customers Delete removes the customer record</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4608,32 +4608,32 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>UI: the Time Clock User role (no customersView) shows top nav Work Orders | Schedule only — no Customers entry. Customers View OFF hides Customers from the top navigation.</t>
+          <t>UI (role with Customers Delete): the Edit Customer modal shows a Delete button -&gt; Confirmation dialog "Are you sure you want to delete this company?" [Cancel|Delete] -&gt; confirming removes the customer and returns to /customers. Verified end-to-end on a seeded ZZAUTOTEST customer (created then deleted). screenshot cust-delete2.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>C26406</t>
+          <t>C26402</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26406</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26402</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Turning Parts Department ON shows exactly 3 child cards</t>
+          <t>AP/AR OFF hides the 7 sensitive customer fields on Edit Customer</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4643,37 +4643,37 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Parts Department children + descriptions build-verified (PermissionGrid).</t>
+          <t>UI: role with View and Manage AP/AR Data OFF (Service Advisor) — Edit Customer modal has NO sensitive fields (no Credit Limit, Taxes, Default Labor Rate, etc). With AP/AR ON they are present. screenshot customer-aparOFF vs customer-aparON.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>C26407</t>
+          <t>C26403</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26407</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26403</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Turning Parts Department OFF hides the 3 child cards</t>
+          <t>AP/AR ON shows the 7 sensitive customer fields on Edit Customer</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4688,32 +4688,32 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>UI: on blank form the 3 child cards (Part sales/Catalog and Inventory/Vendor and order management) are absent; toggling Parts Department ON reveals all 3.</t>
+          <t>UI (role with View and Manage AP/AR Data ON): the Edit Customer modal shows all 7 sensitive fields — Credit Terms, Credit Limit, Default Labor Rate, Default Shop Supplies, Min, Max, Taxes (and PO-required). screenshot customer-apar-on.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>C26408</t>
+          <t>C26404</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26408</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26404</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>A saved role with Parts Department OFF hides the Parts navigation and its pages</t>
+          <t>Customers View OFF hides Customers from the top navigation</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4728,32 +4728,32 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>UI: the Technician role (no Parts Department perms) has NO Parts item in the top navigation — Parts Department OFF hides the Parts navigation.</t>
+          <t>UI: the Time Clock User role (no customersView) shows top nav Work Orders | Schedule only — no Customers entry. Customers View OFF hides Customers from the top navigation.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>C26409</t>
+          <t>C26405</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26409</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26405</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3538</v>
+        <v>3537</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Turning Parts Department OFF then ON keeps the 3 child card choices</t>
+          <t>Customer names still show on work orders and invoices even when Customers is hidden</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4768,19 +4768,19 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>UI: Parts Department OFF hides 3 children then ON again retains prior child choices (Part sales Delete + Catalog Delete stayed ON).</t>
+          <t>UI: the customer name is part of the work order / invoice record and shows on the WO header (verified via C26386 with a no-Customers-View role); it is not gated by the Customers permission. Customer names still show on work orders/invoices even when Customers is hidden.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>C26410</t>
+          <t>C26406</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26410</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26406</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Part sales View gives read access to part sales records</t>
+          <t>Turning Parts Department ON shows exactly 3 child cards</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4803,24 +4803,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>UI (Parts Manager): the Part Sales list at /parts/part-sales loads via in-app nav (columns Number/Status, "New Part Sale" button). NOTE: a direct URL goto to /parts/part-sales redirects to /workorders even for a fully-permissioned role — this is an SPA route-guard-on-fresh-load quirk (not a permission bug); in-app navigation works.</t>
+          <t>Parts Department children + descriptions build-verified (PermissionGrid).</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>C26411</t>
+          <t>C26407</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26411</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26407</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Part sales Create &amp; Edit lets the user create part sales, returns and transactions</t>
+          <t>Turning Parts Department OFF hides the 3 child cards</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4848,19 +4848,19 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>UI (Parts Manager, partSalesCreateAndEdit): the Part Sales page shows the "New Part Sale" create control.</t>
+          <t>UI: on blank form the 3 child cards (Part sales/Catalog and Inventory/Vendor and order management) are absent; toggling Parts Department ON reveals all 3.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>C26413</t>
+          <t>C26408</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26413</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26408</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Catalog and Inventory View gives read access to the catalog and inventory</t>
+          <t>A saved role with Parts Department OFF hides the Parts navigation and its pages</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4888,19 +4888,19 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>UI: a role with Catalog and Inventory View opens /parts/parts-catalogue and the catalogue renders (read access to the catalog).</t>
+          <t>UI: the Technician role (no Parts Department perms) has NO Parts item in the top navigation — Parts Department OFF hides the Parts navigation.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>C26414</t>
+          <t>C26409</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26414</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26409</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Catalog and Inventory Create &amp; Edit lets the user create/edit items and make adjustments (cost/price shown only with See Financial Data)</t>
+          <t>Turning Parts Department OFF then ON keeps the 3 child card choices</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4928,19 +4928,19 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>UI (Parts Manager, catalogInventoryCreateAndEdit): the Catalog page shows the "New Catalog Part" create control.</t>
+          <t>UI: Parts Department OFF hides 3 children then ON again retains prior child choices (Part sales Delete + Catalog Delete stayed ON).</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>C26416</t>
+          <t>C26410</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26416</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26410</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Vendor and order management View gives visibility of vendors, purchase orders and deliveries</t>
+          <t>Part sales View gives read access to part sales records</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4968,19 +4968,19 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>UI: a role with Vendor and order management View opens /parts/orders and the Purchase Orders list renders (visibility of vendors/POs/deliveries).</t>
+          <t>UI (Parts Manager): the Part Sales list at /parts/part-sales loads via in-app nav (columns Number/Status, "New Part Sale" button). NOTE: a direct URL goto to /parts/part-sales redirects to /workorders even for a fully-permissioned role — this is an SPA route-guard-on-fresh-load quirk (not a permission bug); in-app navigation works.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>C26417</t>
+          <t>C26411</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26417</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26411</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Vendor and order management Create &amp; Edit lets the user manage vendors, purchase orders, receiving and returns</t>
+          <t>Part sales Create &amp; Edit lets the user create part sales, returns and transactions</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5008,19 +5008,19 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>UI (Parts Manager, vendorOrderManagementCreateAndEdit): the Purchase Orders page shows the "New PO" create control.</t>
+          <t>UI (Parts Manager, partSalesCreateAndEdit): the Part Sales page shows the "New Part Sale" create control.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>C27876</t>
+          <t>C26413</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27876</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26413</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>A Vendor and order management View-only role can open the Purchase Orders list and a purchase order</t>
+          <t>Catalog and Inventory View gives read access to the catalog and inventory</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5048,32 +5048,32 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>UI: a Vendor and order management View-only role (ZZAUTOTEST Viewer) opens the Purchase Orders list at /parts/orders successfully (list access confirmed).</t>
+          <t>UI: a role with Catalog and Inventory View opens /parts/parts-catalogue and the catalogue renders (read access to the catalog).</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>C26420</t>
+          <t>C26414</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26420</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26414</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Invoicing &amp; payments View shows the Finance tab and lets the user see invoices</t>
+          <t>Catalog and Inventory Create &amp; Edit lets the user create/edit items and make adjustments (cost/price shown only with See Financial Data)</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5088,32 +5088,32 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>UI (role Invoicing View + SFD, no C&amp;E/Delete): the WO Finance tab is shown and invoices can be opened; the Finance tab has NO create/edit/reverse buttons (view-only). screenshot inv-invView.</t>
+          <t>UI (Parts Manager, catalogInventoryCreateAndEdit): the Catalog page shows the "New Catalog Part" create control.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>C26421</t>
+          <t>C26416</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26421</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26416</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Invoicing &amp; payments Create &amp; Edit lets the user create invoices and take payments</t>
+          <t>Vendor and order management View gives visibility of vendors, purchase orders and deliveries</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5128,32 +5128,32 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>UI (Service Advisor, Invoicing Create&amp;Edit): the WO Finance tab shows Create Invoice + Add Deposit actions (create invoices/take payments). screenshot inv-invCE.</t>
+          <t>UI: a role with Vendor and order management View opens /parts/orders and the Purchase Orders list renders (visibility of vendors/POs/deliveries).</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>C26425</t>
+          <t>C26417</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26425</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26417</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>See Financial Data OFF makes Invoicing &amp; payments inaccessible even with View, Create &amp; Edit and Delete</t>
+          <t>Vendor and order management Create &amp; Edit lets the user manage vendors, purchase orders, receiving and returns</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5168,32 +5168,32 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>UI/editor: See Financial Data OFF makes Invoicing &amp; payments inaccessible — SFD-off roles (e.g. Technician) show no Finance tab on the WO, and the editor forces SFD ON before Invoicing can be enabled (C26471/C26474). Invoicing is unreachable without SFD even with View/C&amp;E/Delete.</t>
+          <t>UI (Parts Manager, vendorOrderManagementCreateAndEdit): the Purchase Orders page shows the "New PO" create control.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>C26426</t>
+          <t>C27876</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26426</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27876</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>3539</v>
+        <v>3538</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Invoicing &amp; payments View OFF with See Financial Data ON: prices show but invoices are not reachable</t>
+          <t>A Vendor and order management View-only role can open the Purchase Orders list and a purchase order</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5208,19 +5208,19 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>UI (role SFD ON + WO C&amp;E, NO Invoicing View): the WO shows pricing/totals (SFD on) but the tabs are Lines/Notes/Stats — the Finance tab is hidden and invoices cannot be reached. screenshot inv-sfdNoInv.</t>
+          <t>UI: a Vendor and order management View-only role (ZZAUTOTEST Viewer) opens the Purchase Orders list at /parts/orders successfully (list access confirmed).</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>C26428</t>
+          <t>C26420</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26428</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26420</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Taking Deposits on a work order needs Invoicing &amp; payments Create &amp; Edit</t>
+          <t>Invoicing &amp; payments View shows the Finance tab and lets the user see invoices</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5248,19 +5248,19 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>UI: Taking Deposits needs Invoicing Create&amp;Edit — Add Deposit is shown for User B (Service Advisor, invoicing C&amp;E) and NOT shown for User A (Invoicing View-only).</t>
+          <t>UI (role Invoicing View + SFD, no C&amp;E/Delete): the WO Finance tab is shown and invoices can be opened; the Finance tab has NO create/edit/reverse buttons (view-only). screenshot inv-invView.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>C27740</t>
+          <t>C26421</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27740</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26421</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>The Invoicing &amp; payments delete column is labelled 'Delete / Reverse'</t>
+          <t>Invoicing &amp; payments Create &amp; Edit lets the user create invoices and take payments</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5283,37 +5283,37 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>'Delete / Reverse' column confirmed in build (PermissionGrid).</t>
+          <t>UI (Service Advisor, Invoicing Create&amp;Edit): the WO Finance tab shows Create Invoice + Add Deposit actions (create invoices/take payments). screenshot inv-invCE.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>C26429</t>
+          <t>C26425</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26429</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26425</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>The Timesheets card shows View and Create &amp; Edit only (no Delete)</t>
+          <t>See Financial Data OFF makes Invoicing &amp; payments inaccessible even with View, Create &amp; Edit and Delete</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5323,37 +5323,37 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Timesheets card title + 'Track and review technician labor hours and time entries.' + no Delete column build-verified (PermissionGrid).</t>
+          <t>UI/editor: See Financial Data OFF makes Invoicing &amp; payments inaccessible — SFD-off roles (e.g. Technician) show no Finance tab on the WO, and the editor forces SFD ON before Invoicing can be enabled (C26471/C26474). Invoicing is unreachable without SFD even with View/C&amp;E/Delete.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>C26430</t>
+          <t>C26426</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26430</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26426</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Timesheets View only: timesheet entries are read-only</t>
+          <t>Invoicing &amp; payments View OFF with See Financial Data ON: prices show but invoices are not reachable</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5368,32 +5368,32 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>UI (Time Clock User = timesheetsView only): the WO Timesheets tab shows entries but has no edit/add/delete affordances (read-only). screenshot ts-TCUview.</t>
+          <t>UI (role SFD ON + WO C&amp;E, NO Invoicing View): the WO shows pricing/totals (SFD on) but the tabs are Lines/Notes/Stats — the Finance tab is hidden and invoices cannot be reached. screenshot inv-sfdNoInv.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>C26432</t>
+          <t>C26428</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26432</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26428</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Clock in / clock out is always available, whatever the Timesheets permission</t>
+          <t>Taking Deposits on a work order needs Invoicing &amp; payments Create &amp; Edit</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5408,32 +5408,32 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>UI: the universal Clock In control (top bar "timer | Clock In") is present for the Time Clock User role, which has no Timesheets Create&amp;Edit — clock in/out is available regardless of the Timesheets permission.</t>
+          <t>UI: Taking Deposits needs Invoicing Create&amp;Edit — Add Deposit is shown for User B (Service Advisor, invoicing C&amp;E) and NOT shown for User A (Invoicing View-only).</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>C26433</t>
+          <t>C27740</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26433</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27740</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>3540</v>
+        <v>3539</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Timesheets View OFF with Reports ON: the timesheet activities report is still available</t>
+          <t>The Invoicing &amp; payments delete column is labelled 'Delete / Reverse'</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5443,24 +5443,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>UI: a Reports-on role without Timesheets View (ZZAUTOTEST ReportsNoAPAR, round 5) still shows the Timesheet Activities report under LABOR on /reports — the timesheet activities report follows the Reports permission, available even with Timesheets View off. screenshot reports-noapar.</t>
+          <t>'Delete / Reverse' column confirmed in build (PermissionGrid).</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>C26434</t>
+          <t>C26429</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26434</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26429</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>All Timesheets permissions OFF and Reports OFF: no timesheet navigation anywhere</t>
+          <t>The Timesheets card shows View and Create &amp; Edit only (no Delete)</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5483,24 +5483,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>UI: a role with no timesheetsView and no reportsPageAccess (e.g. HistOn: woView+SFD+histlogs) has NO Timesheets tab on the work order and no Timesheet Activities report — no timesheet access anywhere. (Time Clock User, which has timesheetsView, DOES show a Timesheets tab, confirming the gate.)</t>
+          <t>Timesheets card title + 'Track and review technician labor hours and time entries.' + no Delete column build-verified (PermissionGrid).</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>C27394</t>
+          <t>C26430</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27394</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26430</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>A clock-capable role without Timesheets View can still see and open My Timesheets</t>
+          <t>Timesheets View only: timesheet entries are read-only</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5528,32 +5528,32 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>UI (Technician = clockable, NO timesheetsView): /timesheets is accessible (not restricted) and shows the user My Timesheets entries — a clock-capable role without Timesheets View can still see and open My Timesheets. screenshot myts-tech.</t>
+          <t>UI (Time Clock User = timesheetsView only): the WO Timesheets tab shows entries but has no edit/add/delete affordances (read-only). screenshot ts-TCUview.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>C26435</t>
+          <t>C26432</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26435</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26432</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Reports ON gives access to the Reports page with all reports (no per-report on/off)</t>
+          <t>Clock in / clock out is always available, whatever the Timesheets permission</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5568,32 +5568,32 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>UI (admin /reports): Reports appears in top nav; the Reports page lists ALL reports grouped by category (LABOR, PERFORMANCE, FINANCE, ACCOUNTS RECEIVABLE, ACCOUNTS PAYABLE, ACCOUNTING, COMMUNICATIONS) with no per-report on/off control — Reports is all-or-nothing. screenshot reports-admin.</t>
+          <t>UI: the universal Clock In control (top bar "timer | Clock In") is present for the Time Clock User role, which has no Timesheets Create&amp;Edit — clock in/out is available regardless of the Timesheets permission.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>C26436</t>
+          <t>C26433</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26436</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26433</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>3541</v>
+        <v>3540</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Reports OFF removes Reports from the top navigation</t>
+          <t>Timesheets View OFF with Reports ON: the timesheet activities report is still available</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5608,32 +5608,32 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>UI: the Technician role (no reportsPageAccess) has NO Reports item in the top navigation — Reports OFF removes Reports from nav.</t>
+          <t>UI: a Reports-on role without Timesheets View (ZZAUTOTEST ReportsNoAPAR, round 5) still shows the Timesheet Activities report under LABOR on /reports — the timesheet activities report follows the Reports permission, available even with Timesheets View off. screenshot reports-noapar.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>C26441</t>
+          <t>C26434</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26441</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26434</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>3542</v>
+        <v>3540</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Turning Settings ON reveals its sub-toggles</t>
+          <t>All Timesheets permissions OFF and Reports OFF: no timesheet navigation anywhere</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5643,37 +5643,37 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Verified-Label (build) — Integrations sub-toggle now present (was previously flagged missing)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>PageAndSettingsToggles build chunk shows 7 Settings sub-toggles incl. Integrations. Prior 'Integrations missing' gap is resolved/built.</t>
+          <t>UI: a role with no timesheetsView and no reportsPageAccess (e.g. HistOn: woView+SFD+histlogs) has NO Timesheets tab on the work order and no Timesheet Activities report — no timesheet access anywhere. (Time Clock User, which has timesheetsView, DOES show a Timesheets tab, confirming the gate.)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>C26442</t>
+          <t>C27394</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26442</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27394</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3542</v>
+        <v>3540</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Turning Settings OFF hides its sub-toggles</t>
+          <t>A clock-capable role without Timesheets View can still see and open My Timesheets</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5688,32 +5688,32 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>UI: with Settings off the 7 sub-toggles are absent; toggling Settings ON reveals App Settings/Service/Parts/Finance/Integrations/Data Import/View-Manage Wages.</t>
+          <t>UI (Technician = clockable, NO timesheetsView): /timesheets is accessible (not restricted) and shows the user My Timesheets entries — a clock-capable role without Timesheets View can still see and open My Timesheets. screenshot myts-tech.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>C26443</t>
+          <t>C26435</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26443</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26435</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>A saved role with Settings OFF has no Settings area in the sidebar</t>
+          <t>Reports ON gives access to the Reports page with all reports (no per-report on/off)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -5728,32 +5728,32 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>UI: the Technician role (no settings* perms) has no Settings area in the sidebar — a saved role with Settings OFF has no Settings section.</t>
+          <t>UI (admin /reports): Reports appears in top nav; the Reports page lists ALL reports grouped by category (LABOR, PERFORMANCE, FINANCE, ACCOUNTS RECEIVABLE, ACCOUNTS PAYABLE, ACCOUNTING, COMMUNICATIONS) with no per-report on/off control — Reports is all-or-nothing. screenshot reports-admin.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>C26444</t>
+          <t>C26436</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26444</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26436</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>3542</v>
+        <v>3541</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Turning Settings OFF then ON keeps the sub-toggle choices</t>
+          <t>Reports OFF removes Reports from the top navigation</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5768,19 +5768,19 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>UI: turning Settings OFF then ON keeps the sub-toggle choices (App Settings + Finance stayed ON after the parent was toggled off then on).</t>
+          <t>UI: the Technician role (no reportsPageAccess) has NO Reports item in the top navigation — Reports OFF removes Reports from nav.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>C26445</t>
+          <t>C26441</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26445</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26441</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>App Settings ON gives access to the admin pages</t>
+          <t>Turning Settings ON reveals its sub-toggles</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5803,24 +5803,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build) — Integrations sub-toggle now present (was previously flagged missing)</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>UI (role settingsApp): the SETTINGS admin group is present — Settings, Staff, Roles &amp; Permissions, Locations, Departments. screenshot settings-SetX.</t>
+          <t>PageAndSettingsToggles build chunk shows 7 Settings sub-toggles incl. Integrations. Prior 'Integrations missing' gap is resolved/built.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>C26446</t>
+          <t>C26442</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26446</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26442</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Service ON gives access to the Service configuration pages</t>
+          <t>Turning Settings OFF hides its sub-toggles</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5848,19 +5848,19 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>UI (role settingsService): the SERVICE group is present — Labor Rates, Canned Lines, Asset Types, Inspection Templates. screenshot settings-SetX.</t>
+          <t>UI: with Settings off the 7 sub-toggles are absent; toggling Settings ON reveals App Settings/Service/Parts/Finance/Integrations/Data Import/View-Manage Wages.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>C26447</t>
+          <t>C26443</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26447</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26443</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Parts ON gives access to the Parts configuration pages</t>
+          <t>A saved role with Settings OFF has no Settings area in the sidebar</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5888,19 +5888,19 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>UI (role settingsParts): the PARTS config group is present — Pricing, Bin Locations, Categories. screenshot settings-SetX.</t>
+          <t>UI: the Technician role (no settings* perms) has no Settings area in the sidebar — a saved role with Settings OFF has no Settings section.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>C26448</t>
+          <t>C26444</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26448</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26444</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Finance ON shows the Finance pages, and Integrations ON shows QuickBooks, IBS and Open API</t>
+          <t>Turning Settings OFF then ON keeps the sub-toggle choices</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5928,19 +5928,19 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>UI: Finance ON shows the FINANCE group (Payment Methods, Taxes) [SetFin]; Integrations ON shows the INTEGRATIONS group (IBS, Open API; QuickBooks gated under Integrations) [SetAppIntg]. Roles without each toggle lack the respective group. screenshot settings-SetFin/settings-SetAppIntg.</t>
+          <t>UI: turning Settings OFF then ON keeps the sub-toggle choices (App Settings + Finance stayed ON after the parent was toggled off then on).</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>C26449</t>
+          <t>C26445</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26449</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26445</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Data Import ON gives access to the Imports pages</t>
+          <t>App Settings ON gives access to the admin pages</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5968,19 +5968,19 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>UI (role settingsDataImport): the IMPORTS group is present — Contacts, Assets, Vendors, Inventory, Invoices. screenshot settings-SetX.</t>
+          <t>UI (role settingsApp): the SETTINGS admin group is present — Settings, Staff, Roles &amp; Permissions, Locations, Departments. screenshot settings-SetX.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>C26451</t>
+          <t>C26446</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26451</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26446</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>The Settings sub-toggles work independently (Service on, Finance off)</t>
+          <t>Service ON gives access to the Service configuration pages</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6008,19 +6008,19 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>UI (role with Service ON, Finance OFF = SetX): the SERVICE pages show and there is NO FINANCE group — the Settings sub-toggles work independently.</t>
+          <t>UI (role settingsService): the SERVICE group is present — Labor Rates, Canned Lines, Asset Types, Inspection Templates. screenshot settings-SetX.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>C27395</t>
+          <t>C26447</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27395</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26447</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Turning off the last Settings sub-toggle collapses the Settings section</t>
+          <t>Parts ON gives access to the Parts configuration pages</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -6048,19 +6048,19 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>UI: turning off the last remaining Settings sub-toggle (App Settings) collapses the Settings section — the parent Settings toggle goes off and the sub-toggles disappear.</t>
+          <t>UI (role settingsParts): the PARTS config group is present — Pricing, Bin Locations, Categories. screenshot settings-SetX.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>C29273</t>
+          <t>C26448</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29273</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26448</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>The Integrations admin pages depend on the Integrations sub-toggle, not on Finance</t>
+          <t>Finance ON shows the Finance pages, and Integrations ON shows QuickBooks, IBS and Open API</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6088,19 +6088,19 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>UI: a Finance-only role (settingsFinance, no settingsIntegrations = SetFin) shows the FINANCE group (Payment Methods, Taxes) but NO INTEGRATIONS group (no IBS/Open API/QuickBooks) — Integrations admin pages depend on the Integrations sub-toggle, not on Finance. screenshot settings-SetFin.</t>
+          <t>UI: Finance ON shows the FINANCE group (Payment Methods, Taxes) [SetFin]; Integrations ON shows the INTEGRATIONS group (IBS, Open API; QuickBooks gated under Integrations) [SetAppIntg]. Roles without each toggle lack the respective group. screenshot settings-SetFin/settings-SetAppIntg.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>C29274</t>
+          <t>C26449</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29274</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26449</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>The QuickBooks connection check does not run for roles without Integrations</t>
+          <t>Data Import ON gives access to the Imports pages</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -6128,32 +6128,32 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>UI (inference from gating): QuickBooks lives under the INTEGRATIONS group which is only shown for roles with settingsIntegrations (present for SetAppIntg, absent for SetX/SetFin). Roles without Integrations never reach the QuickBooks surface, so the QuickBooks connection check is not triggered for them. (The background check API call itself is not directly observable in the harness; verified via the Integrations gating.)</t>
+          <t>UI (role settingsDataImport): the IMPORTS group is present — Contacts, Assets, Vendors, Inventory, Invoices. screenshot settings-SetX.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>C26452</t>
+          <t>C26451</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26452</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26451</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>The Work orders card has 'Full View' and 'Tech view' options</t>
+          <t>The Settings sub-toggles work independently (Service on, Finance off)</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6163,37 +6163,37 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>'View mode', 'Full View', 'Tech view' confirmed in build (WoSettingsRow).</t>
+          <t>UI (role with Service ON, Finance OFF = SetX): the SERVICE pages show and there is NO FINANCE group — the Settings sub-toggles work independently.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>C26453</t>
+          <t>C27395</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26453</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27395</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>The Full View description</t>
+          <t>Turning off the last Settings sub-toggle collapses the Settings section</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6208,32 +6208,32 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>UI: Full View description reads "Complete interface with all fields visible and editable (subject to CRUD permissions). The estimate column shows the actual estimate value. Full parts request form with all fields. All workflow actions available (approve, review, split etc...)."</t>
+          <t>UI: turning off the last remaining Settings sub-toggle (App Settings) collapses the Settings section — the parent Settings toggle goes off and the sub-toggles disappear.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>C26454</t>
+          <t>C29273</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26454</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29273</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>The Tech view description, and Tech view stays disabled until a Work orders permission is on</t>
+          <t>The Integrations admin pages depend on the Integrations sub-toggle, not on Finance</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6243,37 +6243,37 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Verified-Label (Tech view text build-verified); disabled-state needs live check</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Tech view description string confirmed verbatim in build (WoSettingsRow). Disabled-until-WO-perm needs live editor.</t>
+          <t>UI: a Finance-only role (settingsFinance, no settingsIntegrations = SetFin) shows the FINANCE group (Payment Methods, Taxes) but NO INTEGRATIONS group (no IBS/Open API/QuickBooks) — Integrations admin pages depend on the Integrations sub-toggle, not on Finance. screenshot settings-SetFin.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>C26455</t>
+          <t>C29274</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26455</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29274</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>3543</v>
+        <v>3542</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Tech view: the Estimate column shows the Tech Time value</t>
+          <t>The QuickBooks connection check does not run for roles without Integrations</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6288,19 +6288,19 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>UI (Technician, tech view): WO lines Actual/Estimate column shows tech-time hours (e.g. 0.00 / 1.00, 0.00 / 1.50) and header "Total Tech Hours" — not a money estimate. screenshot techview-lines-estimate/approved.</t>
+          <t>UI (inference from gating): QuickBooks lives under the INTEGRATIONS group which is only shown for roles with settingsIntegrations (present for SetAppIntg, absent for SetX/SetFin). Roles without Integrations never reach the QuickBooks surface, so the QuickBooks connection check is not triggered for them. (The background check API call itself is not directly observable in the harness; verified via the Integrations gating.)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>C26456</t>
+          <t>C26452</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26456</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26452</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Tech view: the tech time input field is hidden on work order lines</t>
+          <t>The Work orders card has 'Full View' and 'Tech view' options</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6323,24 +6323,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>UI (tech view): no tech-time input field rendered on the WO lines for this user (0 tech-time inputs found).</t>
+          <t>'View mode', 'Full View', 'Tech view' confirmed in build (WoSettingsRow).</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>C26457</t>
+          <t>C26453</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26457</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26453</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Tech view: the user cannot approve work orders (no Approve button)</t>
+          <t>The Full View description</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6368,19 +6368,19 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>UI (tech view): no Approve button anywhere on the work order (estimate and approved WOs both) — Technician lacks Review Work Orders.</t>
+          <t>UI: Full View description reads "Complete interface with all fields visible and editable (subject to CRUD permissions). The estimate column shows the actual estimate value. Full parts request form with all fields. All workflow actions available (approve, review, split etc...)."</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>C26458</t>
+          <t>C26454</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26458</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26454</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Tech view: the user cannot approve work order lines</t>
+          <t>The Tech view description, and Tech view stays disabled until a Work orders permission is on</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6403,24 +6403,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (Tech view text build-verified); disabled-state needs live check</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>UI (tech view): no approve-line action on any line; line actions are tech-only (Complete / Story / Start), no approve control.</t>
+          <t>Tech view description string confirmed verbatim in build (WoSettingsRow). Disabled-until-WO-perm needs live editor.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>C26463</t>
+          <t>C26455</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26463</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26455</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>View mode only changes the look, not what the user is allowed to do</t>
+          <t>Tech view: the Estimate column shows the Tech Time value</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6448,19 +6448,19 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>UI/enforcement: tech view is purely presentational — the tech-view role retains workOrderLinesCreateAndEdit and can add lines (New Line functional on the lines screen); data-level create/edit is governed by CRUD perms, not the view mode (estimate column renders as hours but edit capability persists).</t>
+          <t>UI (Technician, tech view): WO lines Actual/Estimate column shows tech-time hours (e.g. 0.00 / 1.00, 0.00 / 1.50) and header "Total Tech Hours" — not a money estimate. screenshot techview-lines-estimate/approved.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>C26465</t>
+          <t>C26456</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26465</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26456</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Tech view: the 'Send to Portal' button is hidden</t>
+          <t>Tech view: the tech time input field is hidden on work order lines</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -6488,32 +6488,32 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>UI (tech view): the Send to Portal button is not shown anywhere on the work order (header, line, or action menus).</t>
+          <t>UI (tech view): no tech-time input field rendered on the WO lines for this user (0 tech-time inputs found).</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>C26467</t>
+          <t>C26457</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26467</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26457</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>See Financial Data toggle appears in the Cross-Cutting Toggles card</t>
+          <t>Tech view: the user cannot approve work orders (no Approve button)</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6523,37 +6523,37 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Verified-Label (build); subtitle placeholder flagged</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Card 'Cross-Cutting Toggles' + toggle 'See Financial Data' confirmed in shipped build (CrossTogglesSection chunk). Reused subtitle string flagged.</t>
+          <t>UI (tech view): no Approve button anywhere on the work order (estimate and approved WOs both) — Technician lacks Review Work Orders.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>C26468</t>
+          <t>C26458</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26468</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26458</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>See Financial Data ON: prices, costs, margins and labor rates are shown</t>
+          <t>Tech view: the user cannot approve work order lines</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6568,32 +6568,32 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>UI: with See Financial Data ON (admin full view + TechSFD), WO lines show prices, costs, margins and labor rates — Rate ($100), Margin (%), Total ($261.54), parts prices ($3.33 etc), labor ($150). screenshot fullview-lines-admin/techview-sfd-lines.</t>
+          <t>UI (tech view): no approve-line action on any line; line actions are tech-only (Complete / Story / Start), no approve control.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>C26469</t>
+          <t>C26461</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26469</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26461</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>See Financial Data OFF: money amounts, rates, costs and margins are hidden</t>
+          <t>Tech view: the user can add new work order lines but cannot edit existing ones</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6608,32 +6608,32 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>UI: with See Financial Data OFF (plain Technician), WO lines show NO money — no $ amounts, no Rate/Margin/Total columns; only tech-time hours (0.00/1.00). screenshot techview-lines-estimate.</t>
+          <t>UI (Technician tech view): New Line is present (can add lines); an existing APPROVED line is read-only (clicking it adds no editable inputs), while the user can still add new lines. Existing authorized lines read-only + add-new works. screenshot approved-line-readonly.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>C26470</t>
+          <t>C26462</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26470</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26462</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>With See Financial Data OFF, Part sales and Invoicing &amp; payments stay inaccessible even with View, Create &amp; Edit and Delete on</t>
+          <t>Tech view: a line becomes read-only once its authorization is approved</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6648,32 +6648,32 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>UI/editor enforcement: a role cannot hold Part sales or Invoicing &amp; payments with See Financial Data OFF — ticking either forces the "Enable See Financial Data?" dialog (C26471/C26474). So SFD OFF makes Part sales and Invoicing &amp; payments unreachable even if View/Create&amp;Edit/Delete were desired; the combination is prevented at save time.</t>
+          <t>UI (Technician tech view): a PENDING/Needs-Approval line is editable (clicking it reveals editable inputs), and once the line authorization is APPROVED the line is read-only (no editable inputs on click). Line becomes read-only after approval. screenshot techline-edit / approved-line-readonly.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>C26471</t>
+          <t>C26463</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26471</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26463</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Ticking Part sales while See Financial Data is OFF asks you to turn See Financial Data on</t>
+          <t>View mode only changes the look, not what the user is allowed to do</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6688,32 +6688,32 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>UI dialog: ticking Part sales while SFD off shows "Enable See Financial Data? — Part Sales requires See Financial Data. Enable it to grant this permission?" [Cancel|Enable].</t>
+          <t>UI/enforcement: tech view is purely presentational — the tech-view role retains workOrderLinesCreateAndEdit and can add lines (New Line functional on the lines screen); data-level create/edit is governed by CRUD perms, not the view mode (estimate column renders as hours but edit capability persists).</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>C26472</t>
+          <t>C26465</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26472</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26465</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>3544</v>
+        <v>3543</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>See Financial Data</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>'Enable See Financial Data?' dialog — Enable: turns See Financial Data on and keeps the box ticked</t>
+          <t>Tech view: the 'Send to Portal' button is hidden</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6728,19 +6728,19 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>UI: Enable on the SFD dialog turns See Financial Data ON and keeps Part sales View+Create&amp;Edit ticked.</t>
+          <t>UI (tech view): the Send to Portal button is not shown anywhere on the work order (header, line, or action menus).</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>C26473</t>
+          <t>C26467</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26473</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26467</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>'Enable See Financial Data?' dialog — Cancel: undoes the tick</t>
+          <t>See Financial Data toggle appears in the Cross-Cutting Toggles card</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6763,24 +6763,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build); subtitle placeholder flagged</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>UI: Cancel on the SFD dialog undoes the tick (See Financial Data off, Part sales off).</t>
+          <t>Card 'Cross-Cutting Toggles' + toggle 'See Financial Data' confirmed in shipped build (CrossTogglesSection chunk). Reused subtitle string flagged.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>C26474</t>
+          <t>C26468</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26474</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26468</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>The same 'Enable See Financial Data?' dialog appears for Invoicing &amp; payments when See Financial Data is OFF</t>
+          <t>See Financial Data ON: prices, costs, margins and labor rates are shown</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6808,19 +6808,19 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>UI dialog: ticking Invoicing &amp; payments while SFD off shows "Enable See Financial Data? — Invoicing &amp; Payments requires See Financial Data..." [Cancel|Enable]; Enable -&gt; SFD ON + Invoicing View+C&amp;E ON.</t>
+          <t>UI: with See Financial Data ON (admin full view + TechSFD), WO lines show prices, costs, margins and labor rates — Rate ($100), Margin (%), Total ($261.54), parts prices ($3.33 etc), labor ($150). screenshot fullview-lines-admin/techview-sfd-lines.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>C26475</t>
+          <t>C26469</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26475</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26469</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Turning See Financial Data OFF asks you to also turn off the settings that depend on it</t>
+          <t>See Financial Data OFF: money amounts, rates, costs and margins are hidden</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6848,19 +6848,19 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>UI (RUN331 FAIL NOW FIXED): turning See Financial Data OFF while Invoicing on shows "Disable See Financial Data? — Disabling See Financial Data will also disable Invoicing &amp; Payments. Continue?" [Cancel|Disable] (FinancialDataDisableConfirmModal). screenshot sfd-disable-dialog.</t>
+          <t>UI: with See Financial Data OFF (plain Technician), WO lines show NO money — no $ amounts, no Rate/Margin/Total columns; only tech-time hours (0.00/1.00). screenshot techview-lines-estimate.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>C27869</t>
+          <t>C26470</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27869</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26470</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Turning on Order parts while See Financial Data is OFF asks you to also turn on See Financial Data</t>
+          <t>With See Financial Data OFF, Part sales and Invoicing &amp; payments stay inaccessible even with View, Create &amp; Edit and Delete on</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -6888,32 +6888,32 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>UI dialog: ticking Order parts while SFD off shows "Enable See Financial Data? — Order Parts requires See Financial Data. Enable it to grant this permission?" [Cancel|Enable].</t>
+          <t>UI/editor enforcement: a role cannot hold Part sales or Invoicing &amp; payments with See Financial Data OFF — ticking either forces the "Enable See Financial Data?" dialog (C26471/C26474). So SFD OFF makes Part sales and Invoicing &amp; payments unreachable even if View/Create&amp;Edit/Delete were desired; the combination is prevented at save time.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>C26476</t>
+          <t>C26471</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26476</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26471</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data ON shows the Unpaid Invoices, Payments and Credits tabs on a customer</t>
+          <t>Ticking Part sales while See Financial Data is OFF asks you to turn See Financial Data on</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -6928,32 +6928,32 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>UI: role with AP/AR Data ON shows the financial tabs on a customer page — build labels are Invoices / Payments / Deposits (case prose says Unpaid Invoices/Payments/Credits; the AP/AR toggle description uses that wording, actual tab labels are Invoices/Payments/Deposits). Tabs absent when AP/AR off.</t>
+          <t>UI dialog: ticking Part sales while SFD off shows "Enable See Financial Data? — Part Sales requires See Financial Data. Enable it to grant this permission?" [Cancel|Enable].</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>C26477</t>
+          <t>C26472</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26477</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26472</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data ON shows the same three tabs on a vendor</t>
+          <t>'Enable See Financial Data?' dialog — Enable: turns See Financial Data on and keeps the box ticked</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -6968,32 +6968,32 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>UI (Parts Manager, AP/AR ON): the vendor page (/parts/vendor/{id}) shows the AP/AR tabs — Contacts, Unpaid Invoices (30), Payments (4). screenshot vendordetail-vendON.</t>
+          <t>UI: Enable on the SFD dialog turns See Financial Data ON and keeps Part sales View+Create&amp;Edit ticked.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>C26478</t>
+          <t>C26473</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26478</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26473</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>With Reports ON, all 6 AP/AR aging reports are listed (whether or not AP/AR is on)</t>
+          <t>'Enable See Financial Data?' dialog — Cancel: undoes the tick</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -7008,32 +7008,32 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>UI (admin /reports, Reports ON): all 6 AP/AR aging reports are listed — A/R Aging Summary, A/R Aging Detail, A/R Aging Collection, A/P Aging Summary, A/P Aging Detail, A/P Unpaid Invoices. screenshot reports-admin.</t>
+          <t>UI: Cancel on the SFD dialog undoes the tick (See Financial Data off, Part sales off).</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>C26480</t>
+          <t>C26474</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26480</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26474</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data OFF hides the three tabs on a customer</t>
+          <t>The same 'Enable See Financial Data?' dialog appears for Invoicing &amp; payments when See Financial Data is OFF</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -7048,32 +7048,32 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>UI: AP/AR Data OFF (Service Advisor) — the customer page shows only Work Orders/Part Sales/Contacts/Assets/Notes; the Invoices/Payments/Deposits tabs are hidden.</t>
+          <t>UI dialog: ticking Invoicing &amp; payments while SFD off shows "Enable See Financial Data? — Invoicing &amp; Payments requires See Financial Data..." [Cancel|Enable]; Enable -&gt; SFD ON + Invoicing View+C&amp;E ON.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>C26481</t>
+          <t>C26475</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26481</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26475</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data OFF hides the three tabs on a vendor</t>
+          <t>Turning See Financial Data OFF asks you to also turn off the settings that depend on it</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -7088,32 +7088,32 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>UI (Service Advisor, AP/AR OFF): the same vendor page shows only the Contacts tab — Unpaid Invoices/Payments tabs are hidden. screenshot vendordetail-vendOFF.</t>
+          <t>UI (RUN331 FAIL NOW FIXED): turning See Financial Data OFF while Invoicing on shows "Disable See Financial Data? — Disabling See Financial Data will also disable Invoicing &amp; Payments. Continue?" [Cancel|Disable] (FinancialDataDisableConfirmModal). screenshot sfd-disable-dialog.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>C26482</t>
+          <t>C27869</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26482</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27869</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>3545</v>
+        <v>3544</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>See Financial Data</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>With AP/AR OFF but Reports ON, all 6 AP/AR aging reports are still listed</t>
+          <t>Turning on Order parts while See Financial Data is OFF asks you to also turn on See Financial Data</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -7128,19 +7128,19 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>UI (RUN331 FAIL NOW FIXED): a role with Reports ON but View and Manage AP/AR Data OFF (ZZAUTOTEST ReportsNoAPAR) still sees all 6 AP/AR aging reports on /reports (A/R Aging Summary/Detail/Collection, A/P Aging Summary/Detail, A/P Unpaid Invoices). Aging reports follow the Reports permission, not AP/AR. screenshot reports-noapar.</t>
+          <t>UI dialog: ticking Order parts while SFD off shows "Enable See Financial Data? — Order Parts requires See Financial Data. Enable it to grant this permission?" [Cancel|Enable].</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>C26483</t>
+          <t>C26476</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26483</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26476</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data OFF hides the sensitive money fields on Edit Customer</t>
+          <t>View and Manage AP/AR Data ON shows the Unpaid Invoices, Payments and Credits tabs on a customer</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -7168,19 +7168,19 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>UI: AP/AR Data OFF hides the sensitive money fields on Edit Customer (Credit Limit, Taxes, Default Labor Rate, Default Shop Supplies, Min, Max, Credit Terms) — same observation as C26402.</t>
+          <t>UI: role with AP/AR Data ON shows the financial tabs on a customer page — build labels are Invoices / Payments / Deposits (case prose says Unpaid Invoices/Payments/Credits; the AP/AR toggle description uses that wording, actual tab labels are Invoices/Payments/Deposits). Tabs absent when AP/AR off.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>C26484</t>
+          <t>C26477</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26484</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26477</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data OFF still lets a user create invoices and take payments if Invoicing &amp; payments allows it</t>
+          <t>View and Manage AP/AR Data ON shows the same three tabs on a vendor</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -7208,19 +7208,19 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>UI/perms: AP/AR Data OFF still allows creating invoices/taking payments when Invoicing allows — Service Advisor has invoicingPaymentsCreateAndEdit+Delete with AP/AR off; invoicing capability is independent of AP/AR.</t>
+          <t>UI (Parts Manager, AP/AR ON): the vendor page (/parts/vendor/{id}) shows the AP/AR tabs — Contacts, Unpaid Invoices (30), Payments (4). screenshot vendordetail-vendON.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>C26485</t>
+          <t>C26478</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26485</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26478</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data works independently of See Financial Data</t>
+          <t>With Reports ON, all 6 AP/AR aging reports are listed (whether or not AP/AR is on)</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -7248,19 +7248,19 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>UI: See Financial Data and View and Manage AP/AR Data are separate Cross-Cutting Toggles (both present independently alongside View History Logs); AP/AR is not tied to SFD in the editor.</t>
+          <t>UI (admin /reports, Reports ON): all 6 AP/AR aging reports are listed — A/R Aging Summary, A/R Aging Detail, A/R Aging Collection, A/P Aging Summary, A/P Aging Detail, A/P Unpaid Invoices. screenshot reports-admin.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>C26486</t>
+          <t>C26480</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26486</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26480</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data OFF does not block any add/edit/delete area</t>
+          <t>View and Manage AP/AR Data OFF hides the three tabs on a customer</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -7288,32 +7288,32 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>UI: AP/AR Data OFF does not block any add/edit/delete — Service Advisor (AP/AR off) still opens the editable Edit Customer modal and retains full customer/WO/parts create-edit; only the financial tabs/fields are hidden.</t>
+          <t>UI: AP/AR Data OFF (Service Advisor) — the customer page shows only Work Orders/Part Sales/Contacts/Assets/Notes; the Invoices/Payments/Deposits tabs are hidden.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>C26488</t>
+          <t>C26481</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26488</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26481</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>3546</v>
+        <v>3545</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>View History Logs</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>View History Logs ON: work order history and line history are visible (work orders only)</t>
+          <t>View and Manage AP/AR Data OFF hides the three tabs on a vendor</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -7328,32 +7328,32 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>UI (role with View History Logs ON): the WO detail shows the History (15) tab exposing work order + line history/change events. screenshot hist-HistOn.</t>
+          <t>UI (Service Advisor, AP/AR OFF): the same vendor page shows only the Contacts tab — Unpaid Invoices/Payments tabs are hidden. screenshot vendordetail-vendOFF.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>C26489</t>
+          <t>C26482</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26489</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26482</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>3546</v>
+        <v>3545</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>View History Logs</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>View History Logs OFF: work order history and line history are hidden (work orders only)</t>
+          <t>With AP/AR OFF but Reports ON, all 6 AP/AR aging reports are still listed</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -7368,32 +7368,32 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>UI (role with View History Logs OFF = Time Clock User): the WO detail has NO History tab (Lines/Notes/Timesheets/Stats only) — work order and line history are hidden. screenshot hist-HistOff.</t>
+          <t>UI (RUN331 FAIL NOW FIXED): a role with Reports ON but View and Manage AP/AR Data OFF (ZZAUTOTEST ReportsNoAPAR) still sees all 6 AP/AR aging reports on /reports (A/R Aging Summary/Detail/Collection, A/P Aging Summary/Detail, A/P Unpaid Invoices). Aging reports follow the Reports permission, not AP/AR. screenshot reports-noapar.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>C26492</t>
+          <t>C26483</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26492</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26483</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>3547</v>
+        <v>3545</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Staff Page Role Assignment</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Changing a user's role logs them out immediately</t>
+          <t>View and Manage AP/AR Data OFF hides the sensitive money fields on Edit Customer</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -7408,32 +7408,32 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>API/session: changing a user role logs them out immediately — the prior session is invalidated (409 Session has expired) right after the change.</t>
+          <t>UI: AP/AR Data OFF hides the sensitive money fields on Edit Customer (Credit Limit, Taxes, Default Labor Rate, Default Shop Supplies, Min, Max, Credit Terms) — same observation as C26402.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>C26494</t>
+          <t>C26484</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26494</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26484</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>3547</v>
+        <v>3545</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Staff Page Role Assignment</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>A logged-in user is logged out immediately when their role changes</t>
+          <t>View and Manage AP/AR Data OFF still lets a user create invoices and take payments if Invoicing &amp; payments allows it</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -7448,32 +7448,32 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>API/session: a logged-in user is logged out immediately when their role changes (session invalidated -&gt; 409 on next request).</t>
+          <t>UI/perms: AP/AR Data OFF still allows creating invoices/taking payments when Invoicing allows — Service Advisor has invoicingPaymentsCreateAndEdit+Delete with AP/AR off; invoicing capability is independent of AP/AR.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>C26495</t>
+          <t>C26485</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26495</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26485</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Administrator: role permissions match the expected set</t>
+          <t>View and Manage AP/AR Data works independently of See Financial Data</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -7483,37 +7483,37 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Administrator permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI: See Financial Data and View and Manage AP/AR Data are separate Cross-Cutting Toggles (both present independently alongside View History Logs); AP/AR is not tied to SFD in the editor.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>C26496</t>
+          <t>C26486</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26496</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26486</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>3548</v>
+        <v>3545</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Service Manager: role permissions match the expected set</t>
+          <t>View and Manage AP/AR Data OFF does not block any add/edit/delete area</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -7523,37 +7523,37 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Service Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI: AP/AR Data OFF does not block any add/edit/delete — Service Advisor (AP/AR off) still opens the editable Edit Customer modal and retains full customer/WO/parts create-edit; only the financial tabs/fields are hidden.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>C26497</t>
+          <t>C26488</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26497</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26488</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>3548</v>
+        <v>3546</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View History Logs</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Senior Service Advisor: role permissions match the expected set</t>
+          <t>View History Logs ON: work order history and line history are visible (work orders only)</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -7563,37 +7563,37 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Senior Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI (role with View History Logs ON): the WO detail shows the History (15) tab exposing work order + line history/change events. screenshot hist-HistOn.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>C26498</t>
+          <t>C26489</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26498</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26489</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>3548</v>
+        <v>3546</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>View History Logs</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Service Advisor: role permissions match the expected set</t>
+          <t>View History Logs OFF: work order history and line history are hidden (work orders only)</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -7603,37 +7603,37 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>UI (role with View History Logs OFF = Time Clock User): the WO detail has NO History tab (Lines/Notes/Timesheets/Stats only) — work order and line history are hidden. screenshot hist-HistOff.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>C26499</t>
+          <t>C26492</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26499</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26492</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Foreman: role permissions match the expected set</t>
+          <t>Changing a user's role logs them out immediately</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -7643,37 +7643,37 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Foreman permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>API/session: changing a user role logs them out immediately — the prior session is invalidated (409 Session has expired) right after the change.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>C26500</t>
+          <t>C26494</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26500</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26494</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Technician: role permissions match the expected set</t>
+          <t>A logged-in user is logged out immediately when their role changes</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -7683,24 +7683,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>API/session: a logged-in user is logged out immediately when their role changes (session invalidated -&gt; 409 on next request).</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>C26501</t>
+          <t>C26495</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26501</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26495</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Parts Manager: role permissions match the expected set</t>
+          <t>Administrator: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -7728,19 +7728,19 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Parts Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Administrator permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>C26502</t>
+          <t>C26496</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26502</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26496</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Parts Technician: role permissions match the expected set</t>
+          <t>Service Manager: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -7768,19 +7768,19 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Parts Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Service Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>C26503</t>
+          <t>C26497</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26503</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26497</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Office User: role permissions match the expected set</t>
+          <t>Senior Service Advisor: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -7808,19 +7808,19 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Office User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Senior Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>C26504</t>
+          <t>C26498</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26504</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26498</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -7833,7 +7833,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Sales Representative: role permissions match the expected set</t>
+          <t>Service Advisor: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -7848,19 +7848,19 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Sales Representative permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>C26505</t>
+          <t>C26499</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26505</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26499</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Time Clock User: role permissions match the expected set</t>
+          <t>Foreman: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -7888,19 +7888,19 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Time Clock User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Foreman permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>C26506</t>
+          <t>C26500</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26506</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26500</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -7913,7 +7913,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Customer portal is on by default only for Service Advisor, Senior Service Advisor, Service Manager and Parts Manager (and Administrator)</t>
+          <t>Technician: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -7923,37 +7923,37 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (matches live per-role customerPortalPageAccess)</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>customerPortalPageAccess per role confirmed live: on for Admin/SM/SSA/SA/PM; off for the rest (roles-matrix-2026-07-13).</t>
+          <t>Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>C26510</t>
+          <t>C26501</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26510</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26501</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Legacy 'Admin / Administrator' users become 'Administrator' after migration</t>
+          <t>Parts Manager: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -7963,37 +7963,37 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Live roles API: destination system role exists = "Admin" (build name; case prose says Administrator), isEditable=true, 89 users, 42 perms. Migration is a completed historical event; destination state verified (role present, editable with pencil, populated).</t>
+          <t>Parts Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>C26511</t>
+          <t>C26502</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26511</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26502</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Legacy 'Office' users become 'Office User' after migration</t>
+          <t>Parts Technician: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -8003,37 +8003,37 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Live roles API: "Office User" exists, isEditable=false (lock + eye only), 5 users, 23 perms — matches legacy Office -&gt; Office User destination.</t>
+          <t>Parts Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>C26512</t>
+          <t>C26503</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26512</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26503</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Legacy 'Time Clock' users become 'Time Clock User' after migration</t>
+          <t>Office User: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -8043,37 +8043,37 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Live roles API: "Time Clock User" exists, isEditable=false (lock + eye only), 11 users, 3 perms — matches legacy Time Clock -&gt; Time Clock User.</t>
+          <t>Office User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>C26513</t>
+          <t>C26504</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26513</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26504</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Legacy 'Service Manager' users become 'Service Manager' after migration</t>
+          <t>Sales Representative: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -8083,37 +8083,37 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Live roles API: "Service Manager" exists, isEditable=true, 3 users, 35 perms.</t>
+          <t>Sales Representative permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>C26514</t>
+          <t>C26505</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26514</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26505</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Legacy 'Senior Service Advisor' users become 'Senior Service Advisor' after migration</t>
+          <t>Time Clock User: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -8123,37 +8123,37 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Live roles API: "Senior Service Advisor" exists, isEditable=true, 8 users, 32 perms.</t>
+          <t>Time Clock User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>C26515</t>
+          <t>C26506</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26515</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26506</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Legacy 'Service Advisor' users become 'Service Advisor' after migration</t>
+          <t>Customer portal is on by default only for Service Advisor, Senior Service Advisor, Service Manager and Parts Manager (and Administrator)</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -8163,24 +8163,24 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (matches live per-role customerPortalPageAccess)</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Live roles API: "Service Advisor" exists, isEditable=true, 2 users, 26 perms.</t>
+          <t>customerPortalPageAccess per role confirmed live: on for Admin/SM/SSA/SA/PM; off for the rest (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>C26516</t>
+          <t>C26510</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26516</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26510</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Legacy 'Foreman' users become 'Foreman' after migration</t>
+          <t>Legacy 'Admin / Administrator' users become 'Administrator' after migration</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -8208,19 +8208,19 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Live roles API: "Foreman" exists, isEditable=true, 16 users, 23 perms.</t>
+          <t>Live roles API: destination system role exists = "Admin" (build name; case prose says Administrator), isEditable=true, 89 users, 42 perms. Migration is a completed historical event; destination state verified (role present, editable with pencil, populated).</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>C26517</t>
+          <t>C26511</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26517</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26511</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Legacy 'Technician' users become 'Technician' after migration</t>
+          <t>Legacy 'Office' users become 'Office User' after migration</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -8248,19 +8248,19 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Live roles API: "Technician" exists, isEditable=true, 66 users, 6 perms, view_mode tech (confirmed via role detail) — matches legacy Technician destination.</t>
+          <t>Live roles API: "Office User" exists, isEditable=false (lock + eye only), 5 users, 23 perms — matches legacy Office -&gt; Office User destination.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>C26518</t>
+          <t>C26512</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26518</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26512</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Legacy 'Parts Manager' users become 'Parts Manager' after migration</t>
+          <t>Legacy 'Time Clock' users become 'Time Clock User' after migration</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -8288,19 +8288,19 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Live roles API: "Parts Manager" exists, isEditable=true, 4 users, 31 perms.</t>
+          <t>Live roles API: "Time Clock User" exists, isEditable=false (lock + eye only), 11 users, 3 perms — matches legacy Time Clock -&gt; Time Clock User.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>C26519</t>
+          <t>C26513</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26519</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26513</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Legacy 'Parts Tech / Parts Technician' users become 'Parts Technician' after migration</t>
+          <t>Legacy 'Service Manager' users become 'Service Manager' after migration</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -8328,19 +8328,19 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Live roles API: "Parts Technician" exists, isEditable=true, 10 users, 19 perms — matches legacy Parts Tech -&gt; Parts Technician.</t>
+          <t>Live roles API: "Service Manager" exists, isEditable=true, 3 users, 35 perms.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>C26520</t>
+          <t>C26514</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26520</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26514</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -8353,7 +8353,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Legacy 'Sales Representative' users become 'Sales Representative' after migration</t>
+          <t>Legacy 'Senior Service Advisor' users become 'Senior Service Advisor' after migration</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -8368,19 +8368,19 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Live roles API: "Sales Representative" exists, isEditable=true, 15 users, 4 perms.</t>
+          <t>Live roles API: "Senior Service Advisor" exists, isEditable=true, 8 users, 32 perms.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>C26525</t>
+          <t>C26515</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26525</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26515</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Changing a user's role logs that user out and forces them to log in again</t>
+          <t>Legacy 'Service Advisor' users become 'Service Advisor' after migration</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -8408,32 +8408,32 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>UI/API: after an admin changed the Tech user role, the user existing session returned 409 "Session has expired." on the next call — the role change logs the user out and forces re-login.</t>
+          <t>Live roles API: "Service Advisor" exists, isEditable=true, 2 users, 26 perms.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>C26528</t>
+          <t>C26516</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26528</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26516</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Staff Record Settings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>The universal clock in / out is available to any active staff member, whatever their role</t>
+          <t>Legacy 'Foreman' users become 'Foreman' after migration</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -8448,32 +8448,32 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>UI: the universal Clock In control appears in the top bar for every role observed (Admin, Technician, Time Clock User) — available to any active staff member whatever their role.</t>
+          <t>Live roles API: "Foreman" exists, isEditable=true, 16 users, 23 perms.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>C26532</t>
+          <t>C26517</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26532</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26517</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Create success message wording</t>
+          <t>Legacy 'Technician' users become 'Technician' after migration</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -8483,37 +8483,37 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>'Role created successfully.' confirmed in build.</t>
+          <t>Live roles API: "Technician" exists, isEditable=true, 66 users, 6 perms, view_mode tech (confirmed via role detail) — matches legacy Technician destination.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>C26533</t>
+          <t>C26518</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26533</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26518</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Update success message wording</t>
+          <t>Legacy 'Parts Manager' users become 'Parts Manager' after migration</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -8523,37 +8523,37 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>'Role updated successfully.' confirmed in build.</t>
+          <t>Live roles API: "Parts Manager" exists, isEditable=true, 4 users, 31 perms.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>C26534</t>
+          <t>C26519</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26534</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26519</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Deleting a custom role with 0 users shows a confirmation dialog</t>
+          <t>Legacy 'Parts Tech / Parts Technician' users become 'Parts Technician' after migration</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -8568,32 +8568,32 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>UI: deleting a 0-user custom role opens dialog "Confirmation — Are you sure you want to delete this role? This action cannot be undone." [Cancel|Delete]. screenshot delete-confirm-dialog.</t>
+          <t>Live roles API: "Parts Technician" exists, isEditable=true, 10 users, 19 perms — matches legacy Parts Tech -&gt; Parts Technician.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>C26535</t>
+          <t>C26520</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26535</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26520</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Deleting a custom role that has users is blocked</t>
+          <t>Legacy 'Sales Representative' users become 'Sales Representative' after migration</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -8608,32 +8608,32 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>UI: a custom role with users (Parth Cust1, 1 user) has no Delete option in its 3-dot menu — deletion is blocked.</t>
+          <t>Live roles API: "Sales Representative" exists, isEditable=true, 15 users, 4 perms.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>C26536</t>
+          <t>C26525</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26536</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26525</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>3552</v>
+        <v>3549</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Turning See Financial Data on shows a confirmation dialog</t>
+          <t>Changing a user's role logs that user out and forces them to log in again</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -8643,37 +8643,37 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>'Enable See Financial Data?' + Cancel/Enable confirmed in build (FinancialDataConfirmModal).</t>
+          <t>UI/API: after an admin changed the Tech user role, the user existing session returned 409 "Session has expired." on the next call — the role change logs the user out and forces re-login.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>C26537</t>
+          <t>C26528</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26537</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26528</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>3552</v>
+        <v>3550</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Staff Record Settings</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Creating a role with no name is blocked with a required-field error</t>
+          <t>The universal clock in / out is available to any active staff member, whatever their role</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -8688,19 +8688,19 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>UI: creating a role with no name is blocked — Create disabled and inline "Role name is a required field" error when the field is touched/cleared.</t>
+          <t>UI: the universal Clock In control appears in the top bar for every role observed (Admin, Technician, Time Clock User) — available to any active staff member whatever their role.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>C26538</t>
+          <t>C26532</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26538</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26532</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Creating a role with the same permissions as an existing role shows a 'similar role' warning</t>
+          <t>Create success message wording</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -8723,37 +8723,37 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>UI: creating a role with the same permissions as an existing role shows "Similar role already exists" warning with "Create Anyway" (SimilarRoleWarningModal, keyed on identical permissions).</t>
+          <t>'Role created successfully.' confirmed in build.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>C26540</t>
+          <t>C26533</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26540</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26533</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Cross-Permission Combinations</t>
+          <t>User Feedback Strings</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>A role with all permissions off blocks the user from every feature</t>
+          <t>Update success message wording</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -8763,37 +8763,37 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>UI: a near-minimal custom role (only scheduleView) shows a minimal nav (just Schedule + Clock In); navigating to /reports or /administration/staff is refused and redirects to /schedule. (A truly all-off role cannot be saved — Create is disabled at zero perms, C26335 — so the practical minimum is one feature perm; that user is blocked from every other feature.) screenshot xperm-MinRole.</t>
+          <t>'Role updated successfully.' confirmed in build.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>C26541</t>
+          <t>C26534</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26541</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26534</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Cross-Permission Combinations</t>
+          <t>User Feedback Strings</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>A role with all permissions on behaves like Administrator but is still a custom role</t>
+          <t>Deleting a custom role with 0 users shows a confirmation dialog</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -8808,32 +8808,32 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>UI: an all-permissions custom role (42 perms, all cross-toggles on, type Custom) behaves like Administrator — full nav (Work Orders/Schedule/Customers/Parts/Reports), /reports and /administration/staff accessible — yet it is a Custom role (created via Create Custom Role). screenshot xperm-AllOn.</t>
+          <t>UI: deleting a 0-user custom role opens dialog "Confirmation — Are you sure you want to delete this role? This action cannot be undone." [Cancel|Delete]. screenshot delete-confirm-dialog.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>C26542</t>
+          <t>C26535</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26542</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26535</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Cross-Permission Combinations</t>
+          <t>User Feedback Strings</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>A system role cannot be deleted</t>
+          <t>Deleting a custom role that has users is blocked</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -8843,37 +8843,37 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (all system roles deletable=false)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>deletable=false for all system roles (live roles API).</t>
+          <t>UI: a custom role with users (Parth Cust1, 1 user) has no Delete option in its 3-dot menu — deletion is blocked.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>C26543</t>
+          <t>C26536</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26543</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26536</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Cross-Permission Combinations</t>
+          <t>User Feedback Strings</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Only Office User and Time Clock User are non-editable; every other system role (including Administrator) is editable</t>
+          <t>Turning See Financial Data on shows a confirmation dialog</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -8883,37 +8883,37 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (editable flags match live)</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Live roles API: Office User &amp; Time Clock User editable=false; all others (incl. Administrator) editable=true.</t>
+          <t>'Enable See Financial Data?' + Cancel/Enable confirmed in build (FinancialDataConfirmModal).</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>C26544</t>
+          <t>C26537</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26544</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26537</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Cross-Permission Combinations</t>
+          <t>User Feedback Strings</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Being unable to open Customers does not stop a user from picking a customer when creating a work order</t>
+          <t>Creating a role with no name is blocked with a required-field error</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -8928,32 +8928,32 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>UI: verified via C26385 — a role with Work Orders Create&amp;Edit but NO Customers View cannot open Customers (hidden from nav), yet the New Work Order customer picker still opens and lists existing customers, so a customer can be selected when creating a WO.</t>
+          <t>UI: creating a role with no name is blocked — Create disabled and inline "Role name is a required field" error when the field is touched/cleared.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>C26545</t>
+          <t>C26538</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26545</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26538</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Cross-Permission Combinations</t>
+          <t>User Feedback Strings</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>A Page Access toggle that is off overrides the add/edit/delete boxes inside it</t>
+          <t>Creating a role with the same permissions as an existing role shows a 'similar role' warning</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -8968,19 +8968,19 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>UI: a Page Access toggle that is off overrides inner boxes — a role without reportsPageAccess has no Reports nav entry and /reports is refused (redirects away); a role with Parts Department off hides its 3 child cards (C26407). The Page Access toggle is checked first regardless of inner add/edit/delete.</t>
+          <t>UI: creating a role with the same permissions as an existing role shows "Similar role already exists" warning with "Create Anyway" (SimilarRoleWarningModal, keyed on identical permissions).</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>C26548</t>
+          <t>C26540</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26548</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26540</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>View off with Create &amp; Edit on is prevented by the tick-cascade</t>
+          <t>A role with all permissions off blocks the user from every feature</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -9008,19 +9008,19 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>UI/editor: View-off + Create&amp;Edit-on cannot be saved — the tick-cascade (verified C26360/C26362/C26363) auto-ticks View when Create&amp;Edit is ticked, and unticks Create&amp;Edit+Delete when View is unticked, so that invalid combination is impossible in the editor.</t>
+          <t>UI: a near-minimal custom role (only scheduleView) shows a minimal nav (just Schedule + Clock In); navigating to /reports or /administration/staff is refused and redirects to /schedule. (A truly all-off role cannot be saved — Create is disabled at zero perms, C26335 — so the practical minimum is one feature perm; that user is blocked from every other feature.) screenshot xperm-MinRole.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>C26549</t>
+          <t>C26541</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26549</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26541</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>AP/AR OFF hides the sensitive customer fields on both the Edit Customer window and the customer overview</t>
+          <t>A role with all permissions on behaves like Administrator but is still a custom role</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -9048,19 +9048,19 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>UI: AP/AR Data OFF hides the sensitive customer fields on the Edit Customer modal (and the financial tabs on the customer overview) — confirmed via Service Advisor (off) vs CustAPAR (on).</t>
+          <t>UI: an all-permissions custom role (42 perms, all cross-toggles on, type Custom) behaves like Administrator — full nav (Work Orders/Schedule/Customers/Parts/Reports), /reports and /administration/staff accessible — yet it is a Custom role (created via Create Custom Role). screenshot xperm-AllOn.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>C26551</t>
+          <t>C26542</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26551</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26542</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -9073,20 +9073,260 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
+          <t>A system role cannot be deleted</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Roles-API-Verified (all system roles deletable=false)</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>deletable=false for all system roles (live roles API).</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>C26543</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26543</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Only Office User and Time Clock User are non-editable; every other system role (including Administrator) is editable</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Roles-API-Verified (editable flags match live)</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Live roles API: Office User &amp; Time Clock User editable=false; all others (incl. Administrator) editable=true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>C26544</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26544</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Being unable to open Customers does not stop a user from picking a customer when creating a work order</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>UI: verified via C26385 — a role with Work Orders Create&amp;Edit but NO Customers View cannot open Customers (hidden from nav), yet the New Work Order customer picker still opens and lists existing customers, so a customer can be selected when creating a WO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>C26545</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26545</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>A Page Access toggle that is off overrides the add/edit/delete boxes inside it</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>UI: a Page Access toggle that is off overrides inner boxes — a role without reportsPageAccess has no Reports nav entry and /reports is refused (redirects away); a role with Parts Department off hides its 3 child cards (C26407). The Page Access toggle is checked first regardless of inner add/edit/delete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>C26548</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26548</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>View off with Create &amp; Edit on is prevented by the tick-cascade</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>UI/editor: View-off + Create&amp;Edit-on cannot be saved — the tick-cascade (verified C26360/C26362/C26363) auto-ticks View when Create&amp;Edit is ticked, and unticks Create&amp;Edit+Delete when View is unticked, so that invalid combination is impossible in the editor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>C26549</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26549</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>AP/AR OFF hides the sensitive customer fields on both the Edit Customer window and the customer overview</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>UI: AP/AR Data OFF hides the sensitive customer fields on the Edit Customer modal (and the financial tabs on the customer overview) — confirmed via Service Advisor (off) vs CustAPAR (on).</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>C26551</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26551</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
           <t>Universal clock in/out works even for a user whose role has (almost) no permissions</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
         <is>
           <t>UI: the Time Clock User role (only 3 perms: scheduleView/timesheetsView/workOrdersView) still shows the universal Clock In control — universal clock in is not gated by role/permissions.</t>
         </is>
@@ -9291,6 +9531,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B196" r:id="rId195"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B197" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B204" r:id="rId203"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9302,7 +9548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9360,25 +9606,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C26317</t>
+          <t>C26356</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26317</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26356</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3528</v>
+        <v>3532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Roles List Page</t>
+          <t>Permission Summary</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Roles &amp; Permissions is hidden for users without the App Settings sub-toggle</t>
+          <t>You can view a role's Permission Summary from Edit Staff Member using the eye icon next to the Role dropdown</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -9388,37 +9634,37 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); App Settings gates Roles &amp; Permissions (build-verified)</t>
+          <t>Blocked-UI: needs the Edit Staff Member modal Role selector + its eye (View Permissions) icon; the staff row action reached opens Manage-staff-enrollments (departments/workplaces), not the role editor. Follow-up: open Edit Staff Member via the correct control.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>settingsApp gates the Roles &amp; Permissions page (build route metadata).</t>
+          <t>Eye-icon-in-staff-modal needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C26356</t>
+          <t>C26379</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26356</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26379</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3532</v>
+        <v>3534</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Permission Summary</t>
+          <t>Work Orders Permissions</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>You can view a role's Permission Summary from Edit Staff Member using the eye icon next to the Role dropdown</t>
+          <t>The Review work orders sub-toggle controls the Review action on work orders</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -9428,24 +9674,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blocked-UI: needs the Edit Staff Member modal Role selector + its eye (View Permissions) icon; the staff row action reached opens Manage-staff-enrollments (departments/workplaces), not the role editor. Follow-up: open Edit Staff Member via the correct control.</t>
+          <t>Blocked-UI: with woReviewWorkOrders the WO/line showed no explicit Review/Approve action (header menu: Audit Log/Add Fee-Discount; line menu: Add line note/Story history/Audit log). The Review action likely requires a submitted line-authorization state to appear; needs seeding that authorization workflow to show toggle on vs off.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Eye-icon-in-staff-modal needs live UI.</t>
+          <t>Needs live UI + role edit.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C26379</t>
+          <t>C26380</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26379</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26380</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -9458,7 +9704,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>The Review work orders sub-toggle controls the Review action on work orders</t>
+          <t>Pick parts needs only Work orders View, not Create &amp; Edit</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -9468,24 +9714,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Blocked-UI: with woReviewWorkOrders the WO/line showed no explicit Review/Approve action (header menu: Audit Log/Add Fee-Discount; line menu: Add line note/Story history/Audit log). The Review action likely requires a submitted line-authorization state to appear; needs seeding that authorization workflow to show toggle on vs off.</t>
+          <t>Blocked-UI: Technician (woPickParts + WO View, no C&amp;E) shows Complete/Start on lines but no Pick action was visible on the test WO (parts already picked/requested). Needs a seeded pending pickable part-request state to display and exercise the Pick action.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Needs live UI + role edit.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C26380</t>
+          <t>C27873</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26380</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27873</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -9498,7 +9744,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pick parts needs only Work orders View, not Create &amp; Edit</t>
+          <t>Edit/delete options on another user's customer note are hidden without the right permission</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -9508,24 +9754,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Blocked-UI: Technician (woPickParts + WO View, no C&amp;E) shows Complete/Start on lines but no Pick action was visible on the test WO (parts already picked/requested). Needs a seeded pending pickable part-request state to display and exercise the Pick action.</t>
+          <t>Blocked-UI: needs a customer note authored by a DIFFERENT user, then observe edit/delete affordance hidden for a role lacking the note permission — requires seeding a note as user A and viewing as user B; not reachable with single Tech identity this pass.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded; customer notes governed by Customers permission (not WO Delete). API/element jargon stripped.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C27873</t>
+          <t>C29435</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27873</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29435</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -9538,7 +9784,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Edit/delete options on another user's customer note are hidden without the right permission</t>
+          <t>A Pick/Order Parts role can edit the Quantity on the Part Requests tab</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -9548,37 +9794,37 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Blocked-UI: needs a customer note authored by a DIFFERENT user, then observe edit/delete affordance hidden for a role lacking the note permission — requires seeding a note as user A and viewing as user B; not reachable with single Tech identity this pass.</t>
+          <t>Blocked-UI: the Part Requests tab (Order-Parts role) shows a Quantity column, but the inline quantity-edit interaction could not be triggered in this harness (cell-click did not open an editable input). Needs manual confirm that qty is editable.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Reworded; customer notes governed by Customers permission (not WO Delete). API/element jargon stripped.</t>
+          <t>Reworded; element-id jargon stripped.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C29435</t>
+          <t>C26391</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29435</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26391</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3534</v>
+        <v>3535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Work Orders Permissions</t>
+          <t>Work Order Lines Permissions</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>A Pick/Order Parts role can edit the Quantity on the Part Requests tab</t>
+          <t>Work order lines Delete allows removing lines</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -9588,24 +9834,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Blocked-UI: the Part Requests tab (Order-Parts role) shows a Quantity column, but the inline quantity-edit interaction could not be triggered in this harness (cell-click did not open an editable input). Needs manual confirm that qty is editable.</t>
+          <t>Blocked-UI: WOL Delete role shows line-selection checkboxes but no line delete/remove button was exposed (selecting a line revealed no bulk-delete control; no per-line delete icon). Line-delete affordance not reachable in the harness; needs the expanded-line editor delete control or the line-delete endpoint confirmed.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Reworded; element-id jargon stripped.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C26391</t>
+          <t>C27866</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26391</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27866</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -9618,7 +9864,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Work order lines Delete allows removing lines</t>
+          <t>A default Technician (with Work order lines Create &amp; Edit) can bulk-complete another tech's line via Set Line Status</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -9628,24 +9874,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Blocked-UI: WOL Delete role shows line-selection checkboxes but no line delete/remove button was exposed (selecting a line revealed no bulk-delete control; no per-line delete icon). Line-delete affordance not reachable in the harness; needs the expanded-line editor delete control or the line-delete endpoint confirmed.</t>
+          <t>Blocked-UI: needs multiple lines assigned to a DIFFERENT technician plus the Set Line Status bulk control; Set Line Status was not present on the test WO for the Technician role. Requires seeding another tech-s lines + reaching the bulk Set Line Status action.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded; SV-ref/URL/403 jargon stripped. Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C27866</t>
+          <t>C27870</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27866</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27870</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -9658,7 +9904,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>A default Technician (with Work order lines Create &amp; Edit) can bulk-complete another tech's line via Set Line Status</t>
+          <t>Work order lines Create &amp; Edit lets the user mark a core OK/Not-OK and add line history</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -9668,37 +9914,37 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Blocked-UI: needs multiple lines assigned to a DIFFERENT technician plus the Set Line Status bulk control; Set Line Status was not present on the test WO for the Technician role. Requires seeding another tech-s lines + reaching the bulk Set Line Status action.</t>
+          <t>Blocked-UI: needs a work order line with a cored part to expose the core OK/Not-OK control; no cored-part line was present on the test WOs. Requires seeding a core part on a line (New Part Request with a cored catalog PN) then observe the core control + line history for a WOL C&amp;E role.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Reworded; SV-ref/URL/403 jargon stripped. Needs live UI.</t>
+          <t>Needs live UI with a cored part.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C27870</t>
+          <t>C26395</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27870</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26395</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3535</v>
+        <v>3536</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Work Order Lines Permissions</t>
+          <t>Schedule Permissions</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Work order lines Create &amp; Edit lets the user mark a core OK/Not-OK and add line history</t>
+          <t>Schedule Create &amp; Edit allows creating, changing and dragging appointments</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -9708,24 +9954,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Blocked-UI: needs a work order line with a cored part to expose the core OK/Not-OK control; no cored-part line was present on the test WOs. Requires seeding a core part on a line (New Part Request with a cored catalog PN) then observe the core control + line history for a WOL C&amp;E role.</t>
+          <t>Blocked-UI: the Schedule calendar renders for a scheduleCreateAndEdit role, but creating/dragging/editing an appointment requires real calendar drag/slot mouse interaction that does not trigger headless (Schedule button + calendar-cell clicks opened no create dialog); appointment CRUD API endpoint not exposed at standard paths. Needs a real browser.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Needs live UI with a cored part.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C26395</t>
+          <t>C26396</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26395</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26396</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -9738,7 +9984,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Schedule Create &amp; Edit allows creating, changing and dragging appointments</t>
+          <t>Schedule Delete allows removing appointments</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -9748,7 +9994,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Blocked-UI: the Schedule calendar renders for a scheduleCreateAndEdit role, but creating/dragging/editing an appointment requires real calendar drag/slot mouse interaction that does not trigger headless (Schedule button + calendar-cell clicks opened no create dialog); appointment CRUD API endpoint not exposed at standard paths. Needs a real browser.</t>
+          <t>Blocked-UI: appointment delete requires selecting an existing appointment on the calendar (drag/slot interaction) which is not triggerable headless; same calendar-automation limitation as C26395.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -9760,12 +10006,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C26396</t>
+          <t>C27867</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26396</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27867</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -9778,7 +10024,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Schedule Delete allows removing appointments</t>
+          <t>A Schedule Create &amp; Edit only role can open 'Assign existing work order' and the unscheduled work order list loads</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -9788,37 +10034,37 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Blocked-UI: appointment delete requires selecting an existing appointment on the calendar (drag/slot interaction) which is not triggerable headless; same calendar-automation limitation as C26395.</t>
+          <t>Blocked-UI: the Assign existing work order dialog / unscheduled WO list could not be opened headless (Schedule button + calendar clicks opened no dialog); needs the calendar create-entry interaction in a real browser.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded; API endpoint jargon stripped. Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C27867</t>
+          <t>C26401</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27867</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26401</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3536</v>
+        <v>3537</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Schedule Permissions</t>
+          <t>Customer Management Permissions</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>A Schedule Create &amp; Edit only role can open 'Assign existing work order' and the unscheduled work order list loads</t>
+          <t>Customers Delete does NOT let the user delete customer payments (that needs Invoicing &amp; payments Delete)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -9828,37 +10074,37 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Blocked-UI: the Assign existing work order dialog / unscheduled WO list could not be opened headless (Schedule button + calendar clicks opened no dialog); needs the calendar create-entry interaction in a real browser.</t>
+          <t>Blocked-UI: verifying that Customers Delete does NOT delete payments needs a role with customersDelete + AP/AR (to see the customer Payments tab) but WITHOUT invoicingPaymentsDelete, on a customer with payments, to observe no payment-delete option. The payment-delete UI affordance was not reachable in the harness (same limitation as C26422/C26423). Customer-delete itself is verified (C26400); payment delete is gated by invoicingPaymentsDelete per the perm model.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Reworded; API endpoint jargon stripped. Needs live UI.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C26399</t>
+          <t>C26412</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26399</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26412</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3537</v>
+        <v>3538</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Customers Create &amp; Edit allows creating customers, contacts and vehicles</t>
+          <t>Part sales Delete lets the user delete part sales and reverse part sales invoices</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -9868,7 +10114,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: Part sales Delete affordance (delete/reverse a part sale) not located in this pass — the part-sale row menu did not open in the harness; needs the part-sale detail-page delete control with a with/without partSalesDelete contrast.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9880,25 +10126,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C26400</t>
+          <t>C26415</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26400</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26415</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3537</v>
+        <v>3538</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Customers Delete removes the customer record</t>
+          <t>Catalog and Inventory Delete removes catalog parts</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -9908,7 +10154,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: Catalog Delete affordance not located — the catalogue row more_vert menu did not open in the harness; needs the catalog-part detail delete control (Parts Manager has catalogInventoryDelete) vs a no-delete role.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9920,25 +10166,25 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C26401</t>
+          <t>C26418</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26401</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26418</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3537</v>
+        <v>3538</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Customers Delete does NOT let the user delete customer payments (that needs Invoicing &amp; payments Delete)</t>
+          <t>Vendor and order management Delete lets the user delete vendors and purchase orders and reverse vendor transactions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -9948,37 +10194,37 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: Vendor/PO Delete affordance (delete vendor/PO, reverse vendor txn) not located this pass; needs the vendor/PO detail delete control with/without vendorOrderManagementDelete.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Needs live UI; AP/AR dependency on the vendor Payments tab is build-observed.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C26405</t>
+          <t>C26419</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26405</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26419</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3537</v>
+        <v>3538</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Customer Management Permissions</t>
+          <t>Parts Department Permissions</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Customer names still show on work orders and invoices even when Customers is hidden</t>
+          <t>Returning a part to inventory (restocking) is controlled by Vendor and order management</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -9988,7 +10234,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: restocking (return part to inventory) control not reached — needs a WO/PO with a picked part to exercise the return-to-inventory action gated by Vendor and order management.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10000,25 +10246,25 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C26412</t>
+          <t>C26422</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26412</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26422</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3538</v>
+        <v>3539</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Part sales Delete lets the user delete part sales and reverse part sales invoices</t>
+          <t>Invoicing &amp; payments Delete lets the user delete payments and void transactions (but not reverse invoices)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -10028,7 +10274,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Blocked-UI: Part sales Delete affordance (delete/reverse a part sale) not located in this pass — the part-sale row menu did not open in the harness; needs the part-sale detail-page delete control with a with/without partSalesDelete contrast.</t>
+          <t>Blocked-UI: per-payment delete/void affordance not located on the WO Finance tab in the harness (payment rows/menus did not expose a delete/void control); needs the invoice-&gt;payment detail view with a with/without invoicingPaymentsDelete contrast.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10040,25 +10286,25 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C26415</t>
+          <t>C26423</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26415</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26423</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3538</v>
+        <v>3539</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Catalog and Inventory Delete removes catalog parts</t>
+          <t>Deleting a customer payment needs Invoicing &amp; payments Delete, not Customers Delete</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -10068,7 +10314,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Blocked-UI: Catalog Delete affordance not located — the catalogue row more_vert menu did not open in the harness; needs the catalog-part detail delete control (Parts Manager has catalogInventoryDelete) vs a no-delete role.</t>
+          <t>Blocked-UI: deleting a customer payment (gated by Invoicing Delete not Customers Delete) needs the payment delete control located; the Finance-tab payment row menu was not reachable this pass.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10080,25 +10326,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C26418</t>
+          <t>C26427</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26418</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26427</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3538</v>
+        <v>3539</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vendor and order management Delete lets the user delete vendors and purchase orders and reverse vendor transactions</t>
+          <t>The Send to Terminal action needs Invoicing &amp; payments Create &amp; Edit</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -10108,37 +10354,37 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Blocked-UI: Vendor/PO Delete affordance (delete vendor/PO, reverse vendor txn) not located this pass; needs the vendor/PO detail delete control with/without vendorOrderManagementDelete.</t>
+          <t>Blocked-UI: Send to Terminal was not shown at the WO Finance-tab level even for a role with Invoicing C&amp;E + Customer Portal (Service Advisor); it appears within the take-payment flow on an open invoice — needs seeding an open invoice + entering the payment dialog.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Needs live UI; AP/AR dependency on the vendor Payments tab is build-observed.</t>
+          <t>Needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C26419</t>
+          <t>C27871</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26419</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27871</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3538</v>
+        <v>3539</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Parts Department Permissions</t>
+          <t>Invoicing and Payments Permissions</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Returning a part to inventory (restocking) is controlled by Vendor and order management</t>
+          <t>Deleting or cancelling a return is controlled by Invoicing &amp; payments Delete</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -10148,24 +10394,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Blocked-UI: restocking (return part to inventory) control not reached — needs a WO/PO with a picked part to exercise the return-to-inventory action gated by Vendor and order management.</t>
+          <t>Blocked-UI: deleting/cancelling a return (gated by Invoicing Delete) needs a part return seeded first (create return via admin) then observe the delete/cancel gate; return flow not seeded this pass.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded; SV-ref/element-id jargon stripped.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C26422</t>
+          <t>C29434</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26422</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29434</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -10178,7 +10424,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Invoicing &amp; payments Delete lets the user delete payments and void transactions (but not reverse invoices)</t>
+          <t>Send to Terminal needs Invoicing &amp; payments Create &amp; Edit AND Customer portal ON</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -10188,24 +10434,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Blocked-UI: per-payment delete/void affordance not located on the WO Finance tab in the harness (payment rows/menus did not expose a delete/void control); needs the invoice-&gt;payment detail view with a with/without invoicingPaymentsDelete contrast.</t>
+          <t>Blocked-UI: same as C26427 — Send to Terminal (needs Invoicing C&amp;E AND Customer Portal) is in the payment dialog, not reached; needs an open invoice + payment flow to observe both-gates.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded; feature-flag/element-id/SV jargon stripped.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C26423</t>
+          <t>C29438</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26423</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29438</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -10218,7 +10464,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Deleting a customer payment needs Invoicing &amp; payments Delete, not Customers Delete</t>
+          <t>Invoicing &amp; payments Create &amp; Edit gives the edit control on the work order Financial Info card</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -10228,37 +10474,37 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Blocked-UI: deleting a customer payment (gated by Invoicing Delete not Customers Delete) needs the payment delete control located; the Finance-tab payment row menu was not reachable this pass.</t>
+          <t>Blocked-UI: on an open WO the Financial Info card shows an edit affordance, but the same generic WO-header edit affordance appears for BOTH an invoicing-C&amp;E role and a WO-C&amp;E-only (no invoicing) role — the invoicing-specific Financial Info edit control could not be isolated from general WO-edit affordances in the harness. Needs a real browser to confirm the invoicing-gated edit control specifically.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Reworded; element-id/SV jargon stripped.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C26427</t>
+          <t>C26431</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26427</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26431</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3539</v>
+        <v>3540</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Timesheets Permissions</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>The Send to Terminal action needs Invoicing &amp; payments Create &amp; Edit</t>
+          <t>Timesheets Create &amp; Edit lets the user edit entries</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -10268,37 +10514,37 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Blocked-UI: Send to Terminal was not shown at the WO Finance-tab level even for a role with Invoicing C&amp;E + Customer Portal (Service Advisor); it appears within the take-payment flow on an open invoice — needs seeding an open invoice + entering the payment dialog.</t>
+          <t>Blocked-UI: the timesheet entry EDIT affordance was not reachable in the harness for a timesheetsCreateAndEdit role — the WO Timesheets tab is a summary (no edit for view or C&amp;E) and the /timesheets page exposed no per-row edit control/dialog/menu on click. Needs the timesheet entry editor (real browser) to confirm edit works; view-only read-only is confirmed (C26430).</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Edit behavior needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C27871</t>
+          <t>C26437</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/27871</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26437</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3539</v>
+        <v>3541</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Deleting or cancelling a return is controlled by Invoicing &amp; payments Delete</t>
+          <t>Customer portal ON lets the user manage the customer portal</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -10308,37 +10554,37 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Blocked-UI: deleting/cancelling a return (gated by Invoicing Delete) needs a part return seeded first (create return via admin) then observe the delete/cancel gate; return flow not seeded this pass.</t>
+          <t>Blocked-UI: the Customer Portal management surface is not exposed in the app nav/sidebar/customer-detail even for Admin (who has customerPortalPageAccess). The portal page-access toggle exists in the role editor but no managed Customer Portal page is reachable in this environment — cannot verify manage/edit. Needs the portal feature surfaced (real browser / env with portal enabled).</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Reworded; SV-ref/element-id jargon stripped.</t>
+          <t>Toggle 'Customer portal' confirmed in build. Manage behavior needs live check.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C29434</t>
+          <t>C26438</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29434</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26438</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3539</v>
+        <v>3541</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Send to Terminal needs Invoicing &amp; payments Create &amp; Edit AND Customer portal ON</t>
+          <t>Customer portal OFF hides the customer portal from navigation</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -10348,37 +10594,37 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Blocked-UI: same as C26427 — Send to Terminal (needs Invoicing C&amp;E AND Customer Portal) is in the payment dialog, not reached; needs an open invoice + payment flow to observe both-gates.</t>
+          <t>Blocked-UI: cannot confirm gating — no Customer Portal nav entry is shown for ANY role including Admin (surface not exposed in this env), so on/off cannot be compared.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Reworded; feature-flag/element-id/SV jargon stripped.</t>
+          <t>Nav-hide needs live check.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>C29438</t>
+          <t>C26439</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29438</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26439</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3539</v>
+        <v>3541</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Invoicing &amp; payments Create &amp; Edit gives the edit control on the work order Financial Info card</t>
+          <t>Billing Portal ON lets the user manage the billing portal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -10388,37 +10634,37 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Blocked-UI: the WO Financial Info card is present but no edit control was detected for either an Invoicing-C&amp;E role or a view-only role on a PAID WO (balance $0, editing locked). Needs an open/unpaid WO with a balance to observe the C&amp;E edit control.</t>
+          <t>Blocked-UI: the Billing Portal management surface is not present in the Settings area even for Admin (who has billingPortalPageAccess) — no Billing Portal page reachable in this env; cannot verify manage/edit.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Reworded; element-id/SV jargon stripped.</t>
+          <t>Toggle 'Billing Portal' confirmed in build. Manage behavior needs live check.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C26431</t>
+          <t>C26440</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26431</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26440</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3540</v>
+        <v>3541</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Timesheets Permissions</t>
+          <t>Page Access Toggles</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Timesheets Create &amp; Edit lets the user edit entries</t>
+          <t>Billing Portal OFF hides the Billing Portal item in the Settings area</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -10428,37 +10674,37 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Blocked-UI: the timesheet entry EDIT affordance was not reachable in the harness for a timesheetsCreateAndEdit role — the WO Timesheets tab is a summary (no edit for view or C&amp;E) and the /timesheets page exposed no per-row edit control/dialog/menu on click. Needs the timesheet entry editor (real browser) to confirm edit works; view-only read-only is confirmed (C26430).</t>
+          <t>Blocked-UI: cannot confirm gating — Billing Portal is not shown in the Settings area for any role including Admin (surface not exposed in this env), so on/off cannot be compared.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Edit behavior needs live UI.</t>
+          <t>Nav-hide needs live check.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>C26437</t>
+          <t>C26450</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26437</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26450</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3541</v>
+        <v>3542</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>Settings Access</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Customer portal ON lets the user manage the customer portal</t>
+          <t>View/Manage Wages ON lets the user manage wages</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -10468,37 +10714,37 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); toggle label 'Customer portal' build-verified</t>
+          <t>Blocked-UI: wage rate fields live on the Edit Staff Member profile, which is not reachable in this harness (the staff row action opens Manage-staff-enrollments, not the profile/wage editor — same limitation as C26356/C26490/C26491). Role has settingsWages; needs the staff profile editor opened (real browser) to confirm wage fields shown/editable.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Toggle 'Customer portal' confirmed in build. Manage behavior needs live check.</t>
+          <t>Toggle 'View/Manage Wages' confirmed in build. Wage editing needs live check.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C26438</t>
+          <t>C26460</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26438</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26460</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3541</v>
+        <v>3543</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Customer portal OFF hides the customer portal from navigation</t>
+          <t>Tech view: the parts request form shows fewer fields</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -10508,37 +10754,37 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: needs the New Part Request form opened in tech view vs full view to compare field counts; the lines screen is drivable but the request-form modal step was not reached this pass.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Nav-hide needs live check.</t>
+          <t>precise reason logged</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C26439</t>
+          <t>C26466</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26439</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26466</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3541</v>
+        <v>3543</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>View Mode</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Billing Portal ON lets the user manage the billing portal</t>
+          <t>Full View: a user who can approve lines sees the 'Send to Portal' button</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -10548,37 +10794,37 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); toggle label 'Billing Portal' build-verified</t>
+          <t>Blocked-UI: Send to Portal was NOT found on the full-view (admin) lines page body; it is likely in the WO header more_vert menu or gated by WO state — needs the header action menu expanded to confirm.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Toggle 'Billing Portal' confirmed in build. Manage behavior needs live check.</t>
+          <t>Send-to-Portal flow needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>C26440</t>
+          <t>C26479</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26440</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26479</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3541</v>
+        <v>3545</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Page Access Toggles</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Billing Portal OFF hides the Billing Portal item in the Settings area</t>
+          <t>View and Manage AP/AR Data ON allows paying several invoices at once from the Unpaid Invoices tab</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -10588,37 +10834,37 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI (needs seeded role + live payment)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Nav-hide needs live check.</t>
+          <t>Bulk payment needs live UI + payment (create-customer-payment 500s intermittently per prior run).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>C26450</t>
+          <t>C26490</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26450</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26490</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3542</v>
+        <v>3547</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Settings Access</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>View/Manage Wages ON lets the user manage wages</t>
+          <t>The Staff role dropdown groups roles into System Roles and Custom Roles</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -10628,37 +10874,37 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Blocked-UI: wage rate fields live on the Edit Staff Member profile, which is not reachable in this harness (the staff row action opens Manage-staff-enrollments, not the profile/wage editor — same limitation as C26356/C26490/C26491). Role has settingsWages; needs the staff profile editor opened (real browser) to confirm wage fields shown/editable.</t>
+          <t>Blocked-UI: the Edit Staff Member Role dropdown (System/Custom grouping) was not reached — the staff row click opened Manage-staff-enrollments. Follow-up: locate the Edit Staff Member action, open the Role selector.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Toggle 'View/Manage Wages' confirmed in build. Wage editing needs live check.</t>
+          <t>11 system roles confirmed in live roles list (was '12'). Grouping labels need live Staff page.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>C26460</t>
+          <t>C26491</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26460</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26491</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3543</v>
+        <v>3547</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tech view: the parts request form shows fewer fields</t>
+          <t>The View Permissions button next to the role selector opens the Permission Summary</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -10668,37 +10914,37 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Blocked-UI: needs the New Part Request form opened in tech view vs full view to compare field counts; the lines screen is drivable but the request-form modal step was not reached this pass.</t>
+          <t>Blocked-UI: View Permissions eye next to the staff Role selector not reached (same Edit-Staff-Member surface as C26490).</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>precise reason logged</t>
+          <t>'View Permissions' confirmed in build. Needs live Staff page.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>C26461</t>
+          <t>C26493</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26461</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26493</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3543</v>
+        <v>3547</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tech view: the user can add new work order lines but cannot edit existing ones</t>
+          <t>If a role change fails, the user keeps their previous role</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -10708,37 +10954,37 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Blocked-UI: New Line (add) confirmed present in tech view, but the existing-line read-only lock was not directly exercised (would require attempting to edit a pending line inline). Precise follow-up: open a pending line editor as the tech.</t>
+          <t>Blocked-UI: forcing a failed role change (to confirm the user keeps the prior role) requires inducing a server error on /change; not reproducible on demand this pass.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>Failed-save path needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C26462</t>
+          <t>C26526</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26462</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26526</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3543</v>
+        <v>3550</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Staff Record Settings</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tech view: a line becomes read-only once its authorization is approved</t>
+          <t>Whether a technician can be scheduled depends on their department, not their role</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -10748,37 +10994,37 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Blocked-UI: approved-WO lines showed only tech status actions (Complete/Story/Start) with no edit control (consistent with read-only), but the pending-&gt;approved edit-lock transition was not directly exercised.</t>
+          <t>Blocked-UI (needs two seeded users + departments)</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Needs live UI + a second user.</t>
+          <t>Department-gated scheduling needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C26466</t>
+          <t>C26527</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26466</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26527</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3543</v>
+        <v>3550</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>View Mode</t>
+          <t>Staff Record Settings</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Full View: a user who can approve lines sees the 'Send to Portal' button</t>
+          <t>Clocking in on a work order line depends on the per-staff Time Clock setting</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -10788,37 +11034,37 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Blocked-UI: Send to Portal was NOT found on the full-view (admin) lines page body; it is likely in the WO header more_vert menu or gated by WO state — needs the header action menu expanded to confirm.</t>
+          <t>Blocked-UI (needs two seeded users)</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Send-to-Portal flow needs live UI.</t>
+          <t>Per-staff Time Clock gating needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C26479</t>
+          <t>C26539</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26479</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26539</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3545</v>
+        <v>3552</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data</t>
+          <t>User Feedback Strings</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data ON allows paying several invoices at once from the Unpaid Invoices tab</t>
+          <t>Reassigning a staff member's role updates the row with no success message (billing note in the window)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -10828,37 +11074,37 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role + live payment)</t>
+          <t>Blocked-UI (needs live Staff page); billing note not re-captured this pass</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Bulk payment needs live UI + payment (create-customer-payment 500s intermittently per prior run).</t>
+          <t>No-toast-on-reassign + billing note need live Staff page (EditStaffMember chunk not fetched).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C26490</t>
+          <t>C26550</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26490</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26550</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3547</v>
+        <v>3553</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Staff Page Role Assignment</t>
+          <t>Cross-Permission Combinations</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>The Staff role dropdown groups roles into System Roles and Custom Roles</t>
+          <t>The last Administrator cannot be left with zero users</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -10868,250 +11114,10 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Blocked-UI: the Edit Staff Member Role dropdown (System/Custom grouping) was not reached — the staff row click opened Manage-staff-enrollments. Follow-up: locate the Edit Staff Member action, open the Role selector.</t>
+          <t>Blocked-UI: cannot test the last-Administrator guard on shared staging — the org has 89 users on the Admin role, so the single-last-admin state cannot be created without mass-reassigning real users (destructive/irreversible on a shared env). Product rule; needs an isolated org or DB-level setup. Route to product team to confirm the rule exists.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
-        <is>
-          <t>11 system roles confirmed in live roles list (was '12'). Grouping labels need live Staff page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>C26491</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26491</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>3547</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Staff Page Role Assignment</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>The View Permissions button next to the role selector opens the Permission Summary</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Blocked-UI: View Permissions eye next to the staff Role selector not reached (same Edit-Staff-Member surface as C26490).</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>'View Permissions' confirmed in build. Needs live Staff page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>C26493</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26493</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>3547</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Staff Page Role Assignment</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>If a role change fails, the user keeps their previous role</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Blocked-UI: forcing a failed role change (to confirm the user keeps the prior role) requires inducing a server error on /change; not reproducible on demand this pass.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Failed-save path needs live UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>C26526</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26526</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>3550</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Staff Record Settings</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Whether a technician can be scheduled depends on their department, not their role</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs two seeded users + departments)</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Department-gated scheduling needs live UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>C26527</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26527</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>3550</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Staff Record Settings</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Clocking in on a work order line depends on the per-staff Time Clock setting</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs two seeded users)</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Per-staff Time Clock gating needs live UI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>C26539</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26539</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>3552</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>User Feedback Strings</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Reassigning a staff member's role updates the row with no success message (billing note in the window)</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Blocked-UI (needs live Staff page); billing note not re-captured this pass</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>No-toast-on-reassign + billing note need live Staff page (EditStaffMember chunk not fetched).</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>C26550</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26550</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>3553</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>The last Administrator cannot be left with zero users</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Blocked-UI: cannot test the last-Administrator guard on shared staging — the org has 89 users on the Admin role, so the single-last-admin state cannot be created without mass-reassigning real users (destructive/irreversible on a shared env). Product rule; needs an isolated org or DB-level setup. Route to product team to confirm the rule exists.</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
         <is>
           <t>Needs live UI; invariant to confirm.</t>
         </is>
@@ -11157,12 +11163,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12134,17 +12134,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); App Settings gates Roles &amp; Permissions (build-verified)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>settingsApp gates the Roles &amp; Permissions page (build route metadata).</t>
+          <t>UI: a role with a Settings sub-toggle but WITHOUT App Settings (ZZAUTOTEST SetFin = settingsFinance only, round 6) shows a Settings area with only its Finance items (Payment Methods, Taxes) and NO Roles &amp; Permissions / Staff entries — Roles &amp; Permissions is hidden for users without the App Settings sub-toggle. screenshot settings-SetFin.</t>
         </is>
       </c>
     </row>
@@ -15734,17 +15734,17 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>UI (role with Customers Create&amp;Edit = Service Advisor): the /customers list shows the New Customer create control; a customer without customersDelete shows no Delete. Create customers/contacts/vehicles is enabled by Customers Create&amp;Edit. screenshot cust-SAce.</t>
         </is>
       </c>
     </row>
@@ -15774,17 +15774,17 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>UI (role with Customers Delete): the Edit Customer modal shows a Delete button -&gt; Confirmation dialog "Are you sure you want to delete this company?" [Cancel|Delete] -&gt; confirming removes the customer and returns to /customers. Verified end-to-end on a seeded ZZAUTOTEST customer (created then deleted). screenshot cust-delete2.</t>
         </is>
       </c>
     </row>
@@ -15819,7 +15819,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: verifying that Customers Delete does NOT delete payments needs a role with customersDelete + AP/AR (to see the customer Payments tab) but WITHOUT invoicingPaymentsDelete, on a customer with payments, to observe no payment-delete option. The payment-delete UI affordance was not reachable in the harness (same limitation as C26422/C26423). Customer-delete itself is verified (C26400); payment delete is gated by invoicingPaymentsDelete per the perm model.</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -15974,17 +15974,17 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>UI: the customer name is part of the work order / invoice record and shows on the WO header (verified via C26386 with a no-Customers-View role); it is not gated by the Customers permission. Customer names still show on work orders/invoices even when Customers is hidden.</t>
         </is>
       </c>
     </row>
@@ -17099,7 +17099,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Blocked-UI: the WO Financial Info card is present but no edit control was detected for either an Invoicing-C&amp;E role or a view-only role on a PAID WO (balance $0, editing locked). Needs an open/unpaid WO with a balance to observe the C&amp;E edit control.</t>
+          <t>Blocked-UI: on an open WO the Financial Info card shows an edit affordance, but the same generic WO-header edit affordance appears for BOTH an invoicing-C&amp;E role and a WO-C&amp;E-only (no invoicing) role — the invoicing-specific Financial Info edit control could not be isolated from general WO-edit affordances in the harness. Needs a real browser to confirm the invoicing-gated edit control specifically.</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -17499,7 +17499,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); toggle label 'Customer portal' build-verified</t>
+          <t>Blocked-UI: the Customer Portal management surface is not exposed in the app nav/sidebar/customer-detail even for Admin (who has customerPortalPageAccess). The portal page-access toggle exists in the role editor but no managed Customer Portal page is reachable in this environment — cannot verify manage/edit. Needs the portal feature surfaced (real browser / env with portal enabled).</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -17539,7 +17539,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: cannot confirm gating — no Customer Portal nav entry is shown for ANY role including Admin (surface not exposed in this env), so on/off cannot be compared.</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -17579,7 +17579,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role); toggle label 'Billing Portal' build-verified</t>
+          <t>Blocked-UI: the Billing Portal management surface is not present in the Settings area even for Admin (who has billingPortalPageAccess) — no Billing Portal page reachable in this env; cannot verify manage/edit.</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -17619,7 +17619,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs seeded role)</t>
+          <t>Blocked-UI: cannot confirm gating — Billing Portal is not shown in the Settings area for any role including Admin (surface not exposed in this env), so on/off cannot be compared.</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -18574,17 +18574,17 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Blocked-UI: New Line (add) confirmed present in tech view, but the existing-line read-only lock was not directly exercised (would require attempting to edit a pending line inline). Precise follow-up: open a pending line editor as the tech.</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Needs live UI.</t>
+          <t>UI (Technician tech view): New Line is present (can add lines); an existing APPROVED line is read-only (clicking it adds no editable inputs), while the user can still add new lines. Existing authorized lines read-only + add-new works. screenshot approved-line-readonly.</t>
         </is>
       </c>
     </row>
@@ -18614,17 +18614,17 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Blocked-UI: approved-WO lines showed only tech status actions (Complete/Story/Start) with no edit control (consistent with read-only), but the pending-&gt;approved edit-lock transition was not directly exercised.</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Needs live UI + a second user.</t>
+          <t>UI (Technician tech view): a PENDING/Needs-Approval line is editable (clicking it reveals editable inputs), and once the line authorization is APPROVED the line is read-only (no editable inputs on click). Line becomes read-only after approval. screenshot techline-edit / approved-line-readonly.</t>
         </is>
       </c>
     </row>

--- a/build/custom-roles-run/CustomRoles_WordingVIU_2026-07-13.xlsx
+++ b/build/custom-roles-run/CustomRoles_WordingVIU_2026-07-13.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -476,178 +476,163 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Section 3658 dedupe: 3 duplicates deleted (C27735, C27733, C27737); 7 flagged for ruling.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+          <t>Section 3658 dedupe: 3 duplicates deleted (C27735, C27733, C27737).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Section 3658 resolution 2026-07-13: 2 valid stubs MOVED into 3527 sub-sections + reworded/pushed (C27731-&gt;3549 Migration, C27736-&gt;3545 View and Manage AP/AR Data); 5 left in 3658 for QA-lead decision (C27729, C27730, C27732, C27734, C27738 - redundant or build-wrong). See section-3658-resolution-2026-07-13.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>203</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Deviation/Finding</t>
+          <t>Blocked-UI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Deviation/Finding</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B12" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="B13" s="3" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Blocked-UI</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Deviation/Finding</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Roles List Page (3528)</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>18</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Create Custom Role (3529)</t>
+          <t>Roles List Page (3528)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Edit Role (3530)</t>
+          <t>Create Custom Role (3529)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Delete Role (3531)</t>
+          <t>Edit Role (3530)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -659,20 +644,20 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Permission Summary (3532)</t>
+          <t>Delete Role (3531)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -687,14 +672,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CRUD Cascade Rules (3533)</t>
+          <t>Permission Summary (3532)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -703,61 +688,61 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Work Orders Permissions (3534)</t>
+          <t>CRUD Cascade Rules (3533)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Work Order Lines Permissions (3535)</t>
+          <t>Work Orders Permissions (3534)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Schedule Permissions (3536)</t>
+          <t>Work Order Lines Permissions (3535)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
@@ -769,20 +754,20 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Customer Management Permissions (3537)</t>
+          <t>Schedule Permissions (3536)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -791,20 +776,20 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Parts Department Permissions (3538)</t>
+          <t>Customer Management Permissions (3537)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -813,64 +798,64 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions (3539)</t>
+          <t>Parts Department Permissions (3538)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Timesheets Permissions (3540)</t>
+          <t>Invoicing and Payments Permissions (3539)</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>6</v>
       </c>
       <c r="C27" t="n">
+        <v>6</v>
+      </c>
+      <c r="D27" t="n">
         <v>1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Page Access Toggles (3541)</t>
+          <t>Timesheets Permissions (3540)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -879,20 +864,20 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Settings Access (3542)</t>
+          <t>Page Access Toggles (3541)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -901,64 +886,64 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>View Mode (3543)</t>
+          <t>Settings Access (3542)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>See Financial Data (3544)</t>
+          <t>View Mode (3543)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data (3545)</t>
+          <t>See Financial Data (3544)</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>10</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -967,20 +952,20 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>View History Logs (3546)</t>
+          <t>View and Manage AP/AR Data (3545)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -989,20 +974,20 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Staff Page Role Assignment (3547)</t>
+          <t>View History Logs (3546)</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>2</v>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -1011,20 +996,20 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Per-Role Verification (3548)</t>
+          <t>Staff Page Role Assignment (3547)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1033,13 +1018,13 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Migration (3549)</t>
+          <t>Per-Role Verification (3548)</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1061,14 +1046,14 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Staff Record Settings (3550)</t>
+          <t>Migration (3549)</t>
         </is>
       </c>
       <c r="B37" t="n">
+        <v>12</v>
+      </c>
+      <c r="C37" t="n">
         <v>1</v>
-      </c>
-      <c r="C37" t="n">
-        <v>2</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1077,23 +1062,23 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>QuickBooks Relocation (3551)</t>
+          <t>Staff Record Settings (3550)</t>
         </is>
       </c>
       <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="n">
         <v>0</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="n">
-        <v>3</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -1105,33 +1090,33 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>User Feedback Strings (3552)</t>
+          <t>QuickBooks Relocation (3551)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cross-Permission Combinations (3553)</t>
+          <t>User Feedback Strings (3552)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
@@ -1143,6 +1128,28 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations (3553)</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>9</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1157,7 +1164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H204"/>
+  <dimension ref="A1:H205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7535,25 +7542,25 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>C26488</t>
+          <t>C27736</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26488</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27736</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>3546</v>
+        <v>3545</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>View History Logs</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>View History Logs ON: work order history and line history are visible (work orders only)</t>
+          <t>The AP/AR cross-cutting toggle is labeled 'View and Manage AP/AR Data'</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -7568,19 +7575,19 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>UI (role with View History Logs ON): the WO detail shows the History (15) tab exposing work order + line history/change events. screenshot hist-HistOn.</t>
+          <t>Moved from stub section 3663 into 3545 (distinct structural check: 3545 had no toggle-label case; parallels the SFD toggle-exists case). Original stub claimed the label 'Manage Accounts Payable and Receivable' - BUILD-WRONG; corrected to the live build label. LABEL VIU-VERIFIED from the shipped build chunk CrossTogglesSection.ChT56hCk.js: 'Cross-Cutting Toggles' card contains 'See Financial Data', 'View and Manage AP/AR Data' (seeApArData), 'View History Logs'.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>C26489</t>
+          <t>C26488</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26489</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26488</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -7593,7 +7600,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>View History Logs OFF: work order history and line history are hidden (work orders only)</t>
+          <t>View History Logs ON: work order history and line history are visible (work orders only)</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -7608,32 +7615,32 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>UI (role with View History Logs OFF = Time Clock User): the WO detail has NO History tab (Lines/Notes/Timesheets/Stats only) — work order and line history are hidden. screenshot hist-HistOff.</t>
+          <t>UI (role with View History Logs ON): the WO detail shows the History (15) tab exposing work order + line history/change events. screenshot hist-HistOn.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>C26492</t>
+          <t>C26489</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26492</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26489</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Staff Page Role Assignment</t>
+          <t>View History Logs</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Changing a user's role logs them out immediately</t>
+          <t>View History Logs OFF: work order history and line history are hidden (work orders only)</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -7648,19 +7655,19 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>API/session: changing a user role logs them out immediately — the prior session is invalidated (409 Session has expired) right after the change.</t>
+          <t>UI (role with View History Logs OFF = Time Clock User): the WO detail has NO History tab (Lines/Notes/Timesheets/Stats only) — work order and line history are hidden. screenshot hist-HistOff.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>C26494</t>
+          <t>C26492</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26494</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26492</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -7673,7 +7680,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>A logged-in user is logged out immediately when their role changes</t>
+          <t>Changing a user's role logs them out immediately</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -7688,32 +7695,32 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>API/session: a logged-in user is logged out immediately when their role changes (session invalidated -&gt; 409 on next request).</t>
+          <t>API/session: changing a user role logs them out immediately — the prior session is invalidated (409 Session has expired) right after the change.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>C26495</t>
+          <t>C26494</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26495</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26494</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Administrator: role permissions match the expected set</t>
+          <t>A logged-in user is logged out immediately when their role changes</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -7723,24 +7730,24 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Administrator permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>API/session: a logged-in user is logged out immediately when their role changes (session invalidated -&gt; 409 on next request).</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>C26496</t>
+          <t>C26495</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26496</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26495</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -7753,7 +7760,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Service Manager: role permissions match the expected set</t>
+          <t>Administrator: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -7768,19 +7775,19 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Service Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Administrator permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>C26497</t>
+          <t>C26496</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26497</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26496</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -7793,7 +7800,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Senior Service Advisor: role permissions match the expected set</t>
+          <t>Service Manager: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -7808,19 +7815,19 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Senior Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Service Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>C26498</t>
+          <t>C26497</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26498</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26497</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -7833,7 +7840,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Service Advisor: role permissions match the expected set</t>
+          <t>Senior Service Advisor: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -7848,19 +7855,19 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Senior Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>C26499</t>
+          <t>C26498</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26499</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26498</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -7873,7 +7880,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Foreman: role permissions match the expected set</t>
+          <t>Service Advisor: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -7888,19 +7895,19 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Foreman permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>C26500</t>
+          <t>C26499</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26500</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26499</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -7913,7 +7920,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Technician: role permissions match the expected set</t>
+          <t>Foreman: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -7928,19 +7935,19 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Foreman permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>C26501</t>
+          <t>C26500</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26501</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26500</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -7953,7 +7960,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Parts Manager: role permissions match the expected set</t>
+          <t>Technician: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -7968,19 +7975,19 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Parts Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>C26502</t>
+          <t>C26501</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26502</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26501</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -7993,7 +8000,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Parts Technician: role permissions match the expected set</t>
+          <t>Parts Manager: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -8008,19 +8015,19 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Parts Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Parts Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>C26503</t>
+          <t>C26502</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26503</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26502</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -8033,7 +8040,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Office User: role permissions match the expected set</t>
+          <t>Parts Technician: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -8048,19 +8055,19 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Office User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Parts Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>C26504</t>
+          <t>C26503</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26504</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26503</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -8073,7 +8080,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Sales Representative: role permissions match the expected set</t>
+          <t>Office User: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -8088,19 +8095,19 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Sales Representative permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Office User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>C26505</t>
+          <t>C26504</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26505</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26504</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -8113,7 +8120,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Time Clock User: role permissions match the expected set</t>
+          <t>Sales Representative: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -8128,19 +8135,19 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Time Clock User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Sales Representative permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>C26506</t>
+          <t>C26505</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26506</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26505</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -8153,7 +8160,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Customer portal is on by default only for Service Advisor, Senior Service Advisor, Service Manager and Parts Manager (and Administrator)</t>
+          <t>Time Clock User: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -8163,37 +8170,37 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (matches live per-role customerPortalPageAccess)</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>customerPortalPageAccess per role confirmed live: on for Admin/SM/SSA/SA/PM; off for the rest (roles-matrix-2026-07-13).</t>
+          <t>Time Clock User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>C26510</t>
+          <t>C26506</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26510</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26506</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Legacy 'Admin / Administrator' users become 'Administrator' after migration</t>
+          <t>Customer portal is on by default only for Service Advisor, Senior Service Advisor, Service Manager and Parts Manager (and Administrator)</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -8203,24 +8210,24 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (matches live per-role customerPortalPageAccess)</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Live roles API: destination system role exists = "Admin" (build name; case prose says Administrator), isEditable=true, 89 users, 42 perms. Migration is a completed historical event; destination state verified (role present, editable with pencil, populated).</t>
+          <t>customerPortalPageAccess per role confirmed live: on for Admin/SM/SSA/SA/PM; off for the rest (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>C26511</t>
+          <t>C26510</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26511</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26510</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -8233,7 +8240,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Legacy 'Office' users become 'Office User' after migration</t>
+          <t>Legacy 'Admin / Administrator' users become 'Administrator' after migration</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -8248,19 +8255,19 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Live roles API: "Office User" exists, isEditable=false (lock + eye only), 5 users, 23 perms — matches legacy Office -&gt; Office User destination.</t>
+          <t>Live roles API: destination system role exists = "Admin" (build name; case prose says Administrator), isEditable=true, 89 users, 42 perms. Migration is a completed historical event; destination state verified (role present, editable with pencil, populated).</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>C26512</t>
+          <t>C26511</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26512</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26511</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -8273,7 +8280,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Legacy 'Time Clock' users become 'Time Clock User' after migration</t>
+          <t>Legacy 'Office' users become 'Office User' after migration</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -8288,19 +8295,19 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Live roles API: "Time Clock User" exists, isEditable=false (lock + eye only), 11 users, 3 perms — matches legacy Time Clock -&gt; Time Clock User.</t>
+          <t>Live roles API: "Office User" exists, isEditable=false (lock + eye only), 5 users, 23 perms — matches legacy Office -&gt; Office User destination.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>C26513</t>
+          <t>C26512</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26513</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26512</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -8313,7 +8320,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Legacy 'Service Manager' users become 'Service Manager' after migration</t>
+          <t>Legacy 'Time Clock' users become 'Time Clock User' after migration</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -8328,19 +8335,19 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Live roles API: "Service Manager" exists, isEditable=true, 3 users, 35 perms.</t>
+          <t>Live roles API: "Time Clock User" exists, isEditable=false (lock + eye only), 11 users, 3 perms — matches legacy Time Clock -&gt; Time Clock User.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>C26514</t>
+          <t>C26513</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26514</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26513</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -8353,7 +8360,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Legacy 'Senior Service Advisor' users become 'Senior Service Advisor' after migration</t>
+          <t>Legacy 'Service Manager' users become 'Service Manager' after migration</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -8368,19 +8375,19 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Live roles API: "Senior Service Advisor" exists, isEditable=true, 8 users, 32 perms.</t>
+          <t>Live roles API: "Service Manager" exists, isEditable=true, 3 users, 35 perms.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>C26515</t>
+          <t>C26514</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26515</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26514</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -8393,7 +8400,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Legacy 'Service Advisor' users become 'Service Advisor' after migration</t>
+          <t>Legacy 'Senior Service Advisor' users become 'Senior Service Advisor' after migration</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -8408,19 +8415,19 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Live roles API: "Service Advisor" exists, isEditable=true, 2 users, 26 perms.</t>
+          <t>Live roles API: "Senior Service Advisor" exists, isEditable=true, 8 users, 32 perms.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>C26516</t>
+          <t>C26515</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26516</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26515</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -8433,7 +8440,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Legacy 'Foreman' users become 'Foreman' after migration</t>
+          <t>Legacy 'Service Advisor' users become 'Service Advisor' after migration</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -8448,19 +8455,19 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Live roles API: "Foreman" exists, isEditable=true, 16 users, 23 perms.</t>
+          <t>Live roles API: "Service Advisor" exists, isEditable=true, 2 users, 26 perms.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>C26517</t>
+          <t>C26516</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26517</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26516</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -8473,7 +8480,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Legacy 'Technician' users become 'Technician' after migration</t>
+          <t>Legacy 'Foreman' users become 'Foreman' after migration</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -8488,19 +8495,19 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Live roles API: "Technician" exists, isEditable=true, 66 users, 6 perms, view_mode tech (confirmed via role detail) — matches legacy Technician destination.</t>
+          <t>Live roles API: "Foreman" exists, isEditable=true, 16 users, 23 perms.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>C26518</t>
+          <t>C26517</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26518</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26517</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -8513,7 +8520,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Legacy 'Parts Manager' users become 'Parts Manager' after migration</t>
+          <t>Legacy 'Technician' users become 'Technician' after migration</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -8528,19 +8535,19 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Live roles API: "Parts Manager" exists, isEditable=true, 4 users, 31 perms.</t>
+          <t>Live roles API: "Technician" exists, isEditable=true, 66 users, 6 perms, view_mode tech (confirmed via role detail) — matches legacy Technician destination.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>C26519</t>
+          <t>C26518</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26519</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26518</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -8553,7 +8560,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Legacy 'Parts Tech / Parts Technician' users become 'Parts Technician' after migration</t>
+          <t>Legacy 'Parts Manager' users become 'Parts Manager' after migration</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -8568,19 +8575,19 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Live roles API: "Parts Technician" exists, isEditable=true, 10 users, 19 perms — matches legacy Parts Tech -&gt; Parts Technician.</t>
+          <t>Live roles API: "Parts Manager" exists, isEditable=true, 4 users, 31 perms.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>C26520</t>
+          <t>C26519</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26520</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26519</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -8593,7 +8600,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Legacy 'Sales Representative' users become 'Sales Representative' after migration</t>
+          <t>Legacy 'Parts Tech / Parts Technician' users become 'Parts Technician' after migration</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -8608,19 +8615,19 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Live roles API: "Sales Representative" exists, isEditable=true, 15 users, 4 perms.</t>
+          <t>Live roles API: "Parts Technician" exists, isEditable=true, 10 users, 19 perms — matches legacy Parts Tech -&gt; Parts Technician.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>C26525</t>
+          <t>C26520</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26525</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26520</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -8633,7 +8640,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Changing a user's role logs that user out and forces them to log in again</t>
+          <t>Legacy 'Sales Representative' users become 'Sales Representative' after migration</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -8648,32 +8655,32 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>UI/API: after an admin changed the Tech user role, the user existing session returned 409 "Session has expired." on the next call — the role change logs the user out and forces re-login.</t>
+          <t>Live roles API: "Sales Representative" exists, isEditable=true, 15 users, 4 perms.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>C26528</t>
+          <t>C26525</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26528</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26525</t>
         </is>
       </c>
       <c r="C188" t="n">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Staff Record Settings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>The universal clock in / out is available to any active staff member, whatever their role</t>
+          <t>Changing a user's role logs that user out and forces them to log in again</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -8688,32 +8695,32 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>UI: the universal Clock In control appears in the top bar for every role observed (Admin, Technician, Time Clock User) — available to any active staff member whatever their role.</t>
+          <t>UI/API: after an admin changed the Tech user role, the user existing session returned 409 "Session has expired." on the next call — the role change logs the user out and forces re-login.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>C26532</t>
+          <t>C26528</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26532</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26528</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>3552</v>
+        <v>3550</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Staff Record Settings</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Create success message wording</t>
+          <t>The universal clock in / out is available to any active staff member, whatever their role</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -8723,24 +8730,24 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>'Role created successfully.' confirmed in build.</t>
+          <t>UI: the universal Clock In control appears in the top bar for every role observed (Admin, Technician, Time Clock User) — available to any active staff member whatever their role.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>C26533</t>
+          <t>C26532</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26533</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26532</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -8753,7 +8760,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Update success message wording</t>
+          <t>Create success message wording</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -8768,19 +8775,19 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>'Role updated successfully.' confirmed in build.</t>
+          <t>'Role created successfully.' confirmed in build.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>C26534</t>
+          <t>C26533</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26534</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26533</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -8793,7 +8800,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Deleting a custom role with 0 users shows a confirmation dialog</t>
+          <t>Update success message wording</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -8803,24 +8810,24 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>UI: deleting a 0-user custom role opens dialog "Confirmation — Are you sure you want to delete this role? This action cannot be undone." [Cancel|Delete]. screenshot delete-confirm-dialog.</t>
+          <t>'Role updated successfully.' confirmed in build.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>C26535</t>
+          <t>C26534</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26535</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26534</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -8833,7 +8840,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Deleting a custom role that has users is blocked</t>
+          <t>Deleting a custom role with 0 users shows a confirmation dialog</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -8848,19 +8855,19 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>UI: a custom role with users (Parth Cust1, 1 user) has no Delete option in its 3-dot menu — deletion is blocked.</t>
+          <t>UI: deleting a 0-user custom role opens dialog "Confirmation — Are you sure you want to delete this role? This action cannot be undone." [Cancel|Delete]. screenshot delete-confirm-dialog.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>C26536</t>
+          <t>C26535</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26536</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26535</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -8873,7 +8880,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Turning See Financial Data on shows a confirmation dialog</t>
+          <t>Deleting a custom role that has users is blocked</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -8883,24 +8890,24 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>'Enable See Financial Data?' + Cancel/Enable confirmed in build (FinancialDataConfirmModal).</t>
+          <t>UI: a custom role with users (Parth Cust1, 1 user) has no Delete option in its 3-dot menu — deletion is blocked.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>C26537</t>
+          <t>C26536</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26537</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26536</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -8913,7 +8920,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Creating a role with no name is blocked with a required-field error</t>
+          <t>Turning See Financial Data on shows a confirmation dialog</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -8923,24 +8930,24 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>UI: creating a role with no name is blocked — Create disabled and inline "Role name is a required field" error when the field is touched/cleared.</t>
+          <t>'Enable See Financial Data?' + Cancel/Enable confirmed in build (FinancialDataConfirmModal).</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>C26538</t>
+          <t>C26537</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26538</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26537</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -8953,7 +8960,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Creating a role with the same permissions as an existing role shows a 'similar role' warning</t>
+          <t>Creating a role with no name is blocked with a required-field error</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -8968,32 +8975,32 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>UI: creating a role with the same permissions as an existing role shows "Similar role already exists" warning with "Create Anyway" (SimilarRoleWarningModal, keyed on identical permissions).</t>
+          <t>UI: creating a role with no name is blocked — Create disabled and inline "Role name is a required field" error when the field is touched/cleared.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>C26540</t>
+          <t>C26538</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26540</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26538</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Cross-Permission Combinations</t>
+          <t>User Feedback Strings</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>A role with all permissions off blocks the user from every feature</t>
+          <t>Creating a role with the same permissions as an existing role shows a 'similar role' warning</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -9008,19 +9015,19 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>UI: a near-minimal custom role (only scheduleView) shows a minimal nav (just Schedule + Clock In); navigating to /reports or /administration/staff is refused and redirects to /schedule. (A truly all-off role cannot be saved — Create is disabled at zero perms, C26335 — so the practical minimum is one feature perm; that user is blocked from every other feature.) screenshot xperm-MinRole.</t>
+          <t>UI: creating a role with the same permissions as an existing role shows "Similar role already exists" warning with "Create Anyway" (SimilarRoleWarningModal, keyed on identical permissions).</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>C26541</t>
+          <t>C26540</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26541</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26540</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -9033,7 +9040,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>A role with all permissions on behaves like Administrator but is still a custom role</t>
+          <t>A role with all permissions off blocks the user from every feature</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -9048,19 +9055,19 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>UI: an all-permissions custom role (42 perms, all cross-toggles on, type Custom) behaves like Administrator — full nav (Work Orders/Schedule/Customers/Parts/Reports), /reports and /administration/staff accessible — yet it is a Custom role (created via Create Custom Role). screenshot xperm-AllOn.</t>
+          <t>UI: a near-minimal custom role (only scheduleView) shows a minimal nav (just Schedule + Clock In); navigating to /reports or /administration/staff is refused and redirects to /schedule. (A truly all-off role cannot be saved — Create is disabled at zero perms, C26335 — so the practical minimum is one feature perm; that user is blocked from every other feature.) screenshot xperm-MinRole.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>C26542</t>
+          <t>C26541</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26542</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26541</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -9073,7 +9080,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>A system role cannot be deleted</t>
+          <t>A role with all permissions on behaves like Administrator but is still a custom role</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -9083,24 +9090,24 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (all system roles deletable=false)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>deletable=false for all system roles (live roles API).</t>
+          <t>UI: an all-permissions custom role (42 perms, all cross-toggles on, type Custom) behaves like Administrator — full nav (Work Orders/Schedule/Customers/Parts/Reports), /reports and /administration/staff accessible — yet it is a Custom role (created via Create Custom Role). screenshot xperm-AllOn.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>C26543</t>
+          <t>C26542</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26543</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26542</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -9113,7 +9120,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Only Office User and Time Clock User are non-editable; every other system role (including Administrator) is editable</t>
+          <t>A system role cannot be deleted</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -9123,24 +9130,24 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (editable flags match live)</t>
+          <t>Roles-API-Verified (all system roles deletable=false)</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Live roles API: Office User &amp; Time Clock User editable=false; all others (incl. Administrator) editable=true.</t>
+          <t>deletable=false for all system roles (live roles API).</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>C26544</t>
+          <t>C26543</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26544</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26543</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -9153,7 +9160,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Being unable to open Customers does not stop a user from picking a customer when creating a work order</t>
+          <t>Only Office User and Time Clock User are non-editable; every other system role (including Administrator) is editable</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -9163,24 +9170,24 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (editable flags match live)</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>UI: verified via C26385 — a role with Work Orders Create&amp;Edit but NO Customers View cannot open Customers (hidden from nav), yet the New Work Order customer picker still opens and lists existing customers, so a customer can be selected when creating a WO.</t>
+          <t>Live roles API: Office User &amp; Time Clock User editable=false; all others (incl. Administrator) editable=true.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>C26545</t>
+          <t>C26544</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26545</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26544</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -9193,7 +9200,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>A Page Access toggle that is off overrides the add/edit/delete boxes inside it</t>
+          <t>Being unable to open Customers does not stop a user from picking a customer when creating a work order</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -9208,19 +9215,19 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>UI: a Page Access toggle that is off overrides inner boxes — a role without reportsPageAccess has no Reports nav entry and /reports is refused (redirects away); a role with Parts Department off hides its 3 child cards (C26407). The Page Access toggle is checked first regardless of inner add/edit/delete.</t>
+          <t>UI: verified via C26385 — a role with Work Orders Create&amp;Edit but NO Customers View cannot open Customers (hidden from nav), yet the New Work Order customer picker still opens and lists existing customers, so a customer can be selected when creating a WO.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>C26548</t>
+          <t>C26545</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26548</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26545</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -9233,7 +9240,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>View off with Create &amp; Edit on is prevented by the tick-cascade</t>
+          <t>A Page Access toggle that is off overrides the add/edit/delete boxes inside it</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -9248,19 +9255,19 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>UI/editor: View-off + Create&amp;Edit-on cannot be saved — the tick-cascade (verified C26360/C26362/C26363) auto-ticks View when Create&amp;Edit is ticked, and unticks Create&amp;Edit+Delete when View is unticked, so that invalid combination is impossible in the editor.</t>
+          <t>UI: a Page Access toggle that is off overrides inner boxes — a role without reportsPageAccess has no Reports nav entry and /reports is refused (redirects away); a role with Parts Department off hides its 3 child cards (C26407). The Page Access toggle is checked first regardless of inner add/edit/delete.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>C26549</t>
+          <t>C26548</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26549</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26548</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -9273,7 +9280,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>AP/AR OFF hides the sensitive customer fields on both the Edit Customer window and the customer overview</t>
+          <t>View off with Create &amp; Edit on is prevented by the tick-cascade</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -9288,19 +9295,19 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>UI: AP/AR Data OFF hides the sensitive customer fields on the Edit Customer modal (and the financial tabs on the customer overview) — confirmed via Service Advisor (off) vs CustAPAR (on).</t>
+          <t>UI/editor: View-off + Create&amp;Edit-on cannot be saved — the tick-cascade (verified C26360/C26362/C26363) auto-ticks View when Create&amp;Edit is ticked, and unticks Create&amp;Edit+Delete when View is unticked, so that invalid combination is impossible in the editor.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>C26551</t>
+          <t>C26549</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26551</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26549</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -9313,20 +9320,60 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
+          <t>AP/AR OFF hides the sensitive customer fields on both the Edit Customer window and the customer overview</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>UI: AP/AR Data OFF hides the sensitive customer fields on the Edit Customer modal (and the financial tabs on the customer overview) — confirmed via Service Advisor (off) vs CustAPAR (on).</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>C26551</t>
+        </is>
+      </c>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26551</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
           <t>Universal clock in/out works even for a user whose role has (almost) no permissions</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
         <is>
           <t>UI: the Time Clock User role (only 3 perms: scheduleView/timesheetsView/workOrdersView) still shows the universal Clock In control — universal clock in is not gated by role/permissions.</t>
         </is>
@@ -9537,6 +9584,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B202" r:id="rId201"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B203" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B205" r:id="rId204"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9548,7 +9596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10966,25 +11014,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>C26526</t>
+          <t>C27731</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26526</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27731</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Staff Record Settings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Whether a technician can be scheduled depends on their department, not their role</t>
+          <t>Legacy 'Owner' users become 'Administrator' after migration (Owner merged into Admin)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -10994,24 +11042,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs two seeded users + departments)</t>
+          <t>Blocked-UI</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Department-gated scheduling needs live UI.</t>
+          <t>Moved from stub section 3660 into 3549 Migration (was distinct: core 3549 had no legacy-Owner case; Owner is merged into Administrator). Migration LANDING outcome not drivable in this env - needs a real pre-migration 'Owner' user and a migration run (not seedable). Partial confirmation (roles-API): there is NO 'Owner' system role among the 11 shipped system roles, and the Administrator role is editable (roles-matrix-2026-07-13). Full behavior = manual/second-real-user.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>C26527</t>
+          <t>C26526</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26527</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26526</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -11024,7 +11072,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Clocking in on a work order line depends on the per-staff Time Clock setting</t>
+          <t>Whether a technician can be scheduled depends on their department, not their role</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -11034,37 +11082,37 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs two seeded users)</t>
+          <t>Blocked-UI (needs two seeded users + departments)</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Per-staff Time Clock gating needs live UI.</t>
+          <t>Department-gated scheduling needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C26539</t>
+          <t>C26527</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26539</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26527</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3552</v>
+        <v>3550</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>Staff Record Settings</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Reassigning a staff member's role updates the row with no success message (billing note in the window)</t>
+          <t>Clocking in on a work order line depends on the per-staff Time Clock setting</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -11074,50 +11122,90 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs live Staff page); billing note not re-captured this pass</t>
+          <t>Blocked-UI (needs two seeded users)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>No-toast-on-reassign + billing note need live Staff page (EditStaffMember chunk not fetched).</t>
+          <t>Per-staff Time Clock gating needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>C26539</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26539</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>3552</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>User Feedback Strings</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Reassigning a staff member's role updates the row with no success message (billing note in the window)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blocked-UI</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Blocked-UI (needs live Staff page); billing note not re-captured this pass</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>No-toast-on-reassign + billing note need live Staff page (EditStaffMember chunk not fetched).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>C26550</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/26550</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="C40" t="n">
         <v>3553</v>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Cross-Permission Combinations</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>The last Administrator cannot be left with zero users</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Blocked-UI</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>Blocked-UI: cannot test the last-Administrator guard on shared staging — the org has 89 users on the Admin role, so the single-last-admin state cannot be created without mass-reassigning real users (destructive/irreversible on a shared env). Product rule; needs an isolated org or DB-level setup. Route to product team to confirm the rule exists.</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Needs live UI; invariant to confirm.</t>
         </is>
@@ -11163,6 +11251,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11693,7 +11782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:H255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -19631,25 +19720,25 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>C26488</t>
+          <t>C27736</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26488</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27736</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>3546</v>
+        <v>3545</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>View History Logs</t>
+          <t>View and Manage AP/AR Data</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>View History Logs ON: work order history and line history are visible (work orders only)</t>
+          <t>The AP/AR cross-cutting toggle is labeled 'View and Manage AP/AR Data'</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -19664,19 +19753,19 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>UI (role with View History Logs ON): the WO detail shows the History (15) tab exposing work order + line history/change events. screenshot hist-HistOn.</t>
+          <t>Moved from stub section 3663 into 3545 (distinct structural check: 3545 had no toggle-label case; parallels the SFD toggle-exists case). Original stub claimed the label 'Manage Accounts Payable and Receivable' - BUILD-WRONG; corrected to the live build label. LABEL VIU-VERIFIED from the shipped build chunk CrossTogglesSection.ChT56hCk.js: 'Cross-Cutting Toggles' card contains 'See Financial Data', 'View and Manage AP/AR Data' (seeApArData), 'View History Logs'.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>C26489</t>
+          <t>C26488</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26489</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26488</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -19689,7 +19778,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>View History Logs OFF: work order history and line history are hidden (work orders only)</t>
+          <t>View History Logs ON: work order history and line history are visible (work orders only)</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -19704,59 +19793,59 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>UI (role with View History Logs OFF = Time Clock User): the WO detail has NO History tab (Lines/Notes/Timesheets/Stats only) — work order and line history are hidden. screenshot hist-HistOff.</t>
+          <t>UI (role with View History Logs ON): the WO detail shows the History (15) tab exposing work order + line history/change events. screenshot hist-HistOn.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>C26490</t>
+          <t>C26489</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26490</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26489</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>3547</v>
+        <v>3546</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Staff Page Role Assignment</t>
+          <t>View History Logs</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>The Staff role dropdown groups roles into System Roles and Custom Roles</t>
+          <t>View History Logs OFF: work order history and line history are hidden (work orders only)</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Blocked-UI: the Edit Staff Member Role dropdown (System/Custom grouping) was not reached — the staff row click opened Manage-staff-enrollments. Follow-up: locate the Edit Staff Member action, open the Role selector.</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>11 system roles confirmed in live roles list (was '12'). Grouping labels need live Staff page.</t>
+          <t>UI (role with View History Logs OFF = Time Clock User): the WO detail has NO History tab (Lines/Notes/Timesheets/Stats only) — work order and line history are hidden. screenshot hist-HistOff.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>C26491</t>
+          <t>C26490</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26491</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26490</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -19769,7 +19858,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>The View Permissions button next to the role selector opens the Permission Summary</t>
+          <t>The Staff role dropdown groups roles into System Roles and Custom Roles</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -19779,24 +19868,24 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Blocked-UI: View Permissions eye next to the staff Role selector not reached (same Edit-Staff-Member surface as C26490).</t>
+          <t>Blocked-UI: the Edit Staff Member Role dropdown (System/Custom grouping) was not reached — the staff row click opened Manage-staff-enrollments. Follow-up: locate the Edit Staff Member action, open the Role selector.</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>'View Permissions' confirmed in build. Needs live Staff page.</t>
+          <t>11 system roles confirmed in live roles list (was '12'). Grouping labels need live Staff page.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>C26492</t>
+          <t>C26491</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26492</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26491</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -19809,34 +19898,34 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Changing a user's role logs them out immediately</t>
+          <t>The View Permissions button next to the role selector opens the Permission Summary</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Blocked-UI</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Blocked-UI: View Permissions eye next to the staff Role selector not reached (same Edit-Staff-Member surface as C26490).</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>API/session: changing a user role logs them out immediately — the prior session is invalidated (409 Session has expired) right after the change.</t>
+          <t>'View Permissions' confirmed in build. Needs live Staff page.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>C26493</t>
+          <t>C26492</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26493</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26492</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -19849,34 +19938,34 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>If a role change fails, the user keeps their previous role</t>
+          <t>Changing a user's role logs them out immediately</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Blocked-UI: forcing a failed role change (to confirm the user keeps the prior role) requires inducing a server error on /change; not reproducible on demand this pass.</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Failed-save path needs live UI.</t>
+          <t>API/session: changing a user role logs them out immediately — the prior session is invalidated (409 Session has expired) right after the change.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>C26494</t>
+          <t>C26493</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26494</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26493</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -19889,47 +19978,47 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>A logged-in user is logged out immediately when their role changes</t>
+          <t>If a role change fails, the user keeps their previous role</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Blocked-UI</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Blocked-UI: forcing a failed role change (to confirm the user keeps the prior role) requires inducing a server error on /change; not reproducible on demand this pass.</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>API/session: a logged-in user is logged out immediately when their role changes (session invalidated -&gt; 409 on next request).</t>
+          <t>Failed-save path needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>C26495</t>
+          <t>C26494</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26495</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26494</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>3548</v>
+        <v>3547</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Per-Role Verification</t>
+          <t>Staff Page Role Assignment</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Administrator: role permissions match the expected set</t>
+          <t>A logged-in user is logged out immediately when their role changes</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -19939,24 +20028,24 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Administrator permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>API/session: a logged-in user is logged out immediately when their role changes (session invalidated -&gt; 409 on next request).</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>C26496</t>
+          <t>C26495</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26496</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26495</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -19969,7 +20058,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Service Manager: role permissions match the expected set</t>
+          <t>Administrator: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -19984,19 +20073,19 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Service Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Administrator permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>C26497</t>
+          <t>C26496</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26497</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26496</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -20009,7 +20098,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Senior Service Advisor: role permissions match the expected set</t>
+          <t>Service Manager: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -20024,19 +20113,19 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Senior Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Service Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>C26498</t>
+          <t>C26497</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26498</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26497</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -20049,7 +20138,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Service Advisor: role permissions match the expected set</t>
+          <t>Senior Service Advisor: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -20064,19 +20153,19 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Senior Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>C26499</t>
+          <t>C26498</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26499</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26498</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -20089,7 +20178,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Foreman: role permissions match the expected set</t>
+          <t>Service Advisor: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -20104,19 +20193,19 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Foreman permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Service Advisor permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>C26500</t>
+          <t>C26499</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26500</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26499</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -20129,7 +20218,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Technician: role permissions match the expected set</t>
+          <t>Foreman: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -20144,19 +20233,19 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Foreman permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>C26501</t>
+          <t>C26500</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26501</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26500</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -20169,7 +20258,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Parts Manager: role permissions match the expected set</t>
+          <t>Technician: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -20184,19 +20273,19 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Parts Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>C26502</t>
+          <t>C26501</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26502</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26501</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -20209,7 +20298,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Parts Technician: role permissions match the expected set</t>
+          <t>Parts Manager: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -20224,19 +20313,19 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Parts Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Parts Manager permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>C26503</t>
+          <t>C26502</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26503</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26502</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -20249,7 +20338,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Office User: role permissions match the expected set</t>
+          <t>Parts Technician: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -20264,19 +20353,19 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Office User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Parts Technician permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>C26504</t>
+          <t>C26503</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26504</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26503</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -20289,7 +20378,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Sales Representative: role permissions match the expected set</t>
+          <t>Office User: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -20304,19 +20393,19 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Sales Representative permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Office User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>C26505</t>
+          <t>C26504</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26505</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26504</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -20329,7 +20418,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Time Clock User: role permissions match the expected set</t>
+          <t>Sales Representative: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -20344,19 +20433,19 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Time Clock User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
+          <t>Sales Representative permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>C26506</t>
+          <t>C26505</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26506</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26505</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -20369,7 +20458,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Customer portal is on by default only for Service Advisor, Senior Service Advisor, Service Manager and Parts Manager (and Administrator)</t>
+          <t>Time Clock User: role permissions match the expected set</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -20379,37 +20468,37 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (matches live per-role customerPortalPageAccess)</t>
+          <t>Roles-API-Verified (permission set matches the live role); workflow spot-checks Blocked-UI</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>customerPortalPageAccess per role confirmed live: on for Admin/SM/SSA/SA/PM; off for the rest (roles-matrix-2026-07-13).</t>
+          <t>Time Clock User permission set confirmed live via GET /api/roles/{id} (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>C26510</t>
+          <t>C26506</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26510</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26506</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>3549</v>
+        <v>3548</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Per-Role Verification</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Legacy 'Admin / Administrator' users become 'Administrator' after migration</t>
+          <t>Customer portal is on by default only for Service Advisor, Senior Service Advisor, Service Manager and Parts Manager (and Administrator)</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -20419,24 +20508,24 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (matches live per-role customerPortalPageAccess)</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Live roles API: destination system role exists = "Admin" (build name; case prose says Administrator), isEditable=true, 89 users, 42 perms. Migration is a completed historical event; destination state verified (role present, editable with pencil, populated).</t>
+          <t>customerPortalPageAccess per role confirmed live: on for Admin/SM/SSA/SA/PM; off for the rest (roles-matrix-2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>C26511</t>
+          <t>C26510</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26511</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26510</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -20449,7 +20538,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Legacy 'Office' users become 'Office User' after migration</t>
+          <t>Legacy 'Admin / Administrator' users become 'Administrator' after migration</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -20464,19 +20553,19 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Live roles API: "Office User" exists, isEditable=false (lock + eye only), 5 users, 23 perms — matches legacy Office -&gt; Office User destination.</t>
+          <t>Live roles API: destination system role exists = "Admin" (build name; case prose says Administrator), isEditable=true, 89 users, 42 perms. Migration is a completed historical event; destination state verified (role present, editable with pencil, populated).</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>C26512</t>
+          <t>C26511</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26512</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26511</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -20489,7 +20578,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Legacy 'Time Clock' users become 'Time Clock User' after migration</t>
+          <t>Legacy 'Office' users become 'Office User' after migration</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -20504,19 +20593,19 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Live roles API: "Time Clock User" exists, isEditable=false (lock + eye only), 11 users, 3 perms — matches legacy Time Clock -&gt; Time Clock User.</t>
+          <t>Live roles API: "Office User" exists, isEditable=false (lock + eye only), 5 users, 23 perms — matches legacy Office -&gt; Office User destination.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>C26513</t>
+          <t>C26512</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26513</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26512</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -20529,7 +20618,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Legacy 'Service Manager' users become 'Service Manager' after migration</t>
+          <t>Legacy 'Time Clock' users become 'Time Clock User' after migration</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -20544,19 +20633,19 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Live roles API: "Service Manager" exists, isEditable=true, 3 users, 35 perms.</t>
+          <t>Live roles API: "Time Clock User" exists, isEditable=false (lock + eye only), 11 users, 3 perms — matches legacy Time Clock -&gt; Time Clock User.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>C26514</t>
+          <t>C26513</t>
         </is>
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26514</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26513</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -20569,7 +20658,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Legacy 'Senior Service Advisor' users become 'Senior Service Advisor' after migration</t>
+          <t>Legacy 'Service Manager' users become 'Service Manager' after migration</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -20584,19 +20673,19 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Live roles API: "Senior Service Advisor" exists, isEditable=true, 8 users, 32 perms.</t>
+          <t>Live roles API: "Service Manager" exists, isEditable=true, 3 users, 35 perms.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>C26515</t>
+          <t>C26514</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26515</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26514</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -20609,7 +20698,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Legacy 'Service Advisor' users become 'Service Advisor' after migration</t>
+          <t>Legacy 'Senior Service Advisor' users become 'Senior Service Advisor' after migration</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -20624,19 +20713,19 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Live roles API: "Service Advisor" exists, isEditable=true, 2 users, 26 perms.</t>
+          <t>Live roles API: "Senior Service Advisor" exists, isEditable=true, 8 users, 32 perms.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>C26516</t>
+          <t>C26515</t>
         </is>
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26516</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26515</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -20649,7 +20738,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Legacy 'Foreman' users become 'Foreman' after migration</t>
+          <t>Legacy 'Service Advisor' users become 'Service Advisor' after migration</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -20664,19 +20753,19 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Live roles API: "Foreman" exists, isEditable=true, 16 users, 23 perms.</t>
+          <t>Live roles API: "Service Advisor" exists, isEditable=true, 2 users, 26 perms.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>C26517</t>
+          <t>C26516</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26517</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26516</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -20689,7 +20778,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Legacy 'Technician' users become 'Technician' after migration</t>
+          <t>Legacy 'Foreman' users become 'Foreman' after migration</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -20704,19 +20793,19 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Live roles API: "Technician" exists, isEditable=true, 66 users, 6 perms, view_mode tech (confirmed via role detail) — matches legacy Technician destination.</t>
+          <t>Live roles API: "Foreman" exists, isEditable=true, 16 users, 23 perms.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>C26518</t>
+          <t>C26517</t>
         </is>
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26518</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26517</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -20729,7 +20818,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Legacy 'Parts Manager' users become 'Parts Manager' after migration</t>
+          <t>Legacy 'Technician' users become 'Technician' after migration</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -20744,19 +20833,19 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Live roles API: "Parts Manager" exists, isEditable=true, 4 users, 31 perms.</t>
+          <t>Live roles API: "Technician" exists, isEditable=true, 66 users, 6 perms, view_mode tech (confirmed via role detail) — matches legacy Technician destination.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>C26519</t>
+          <t>C26518</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26519</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26518</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -20769,7 +20858,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Legacy 'Parts Tech / Parts Technician' users become 'Parts Technician' after migration</t>
+          <t>Legacy 'Parts Manager' users become 'Parts Manager' after migration</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -20784,19 +20873,19 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Live roles API: "Parts Technician" exists, isEditable=true, 10 users, 19 perms — matches legacy Parts Tech -&gt; Parts Technician.</t>
+          <t>Live roles API: "Parts Manager" exists, isEditable=true, 4 users, 31 perms.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>C26520</t>
+          <t>C26519</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26520</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26519</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -20809,7 +20898,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Legacy 'Sales Representative' users become 'Sales Representative' after migration</t>
+          <t>Legacy 'Parts Tech / Parts Technician' users become 'Parts Technician' after migration</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -20824,19 +20913,19 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Live roles API: "Sales Representative" exists, isEditable=true, 15 users, 4 perms.</t>
+          <t>Live roles API: "Parts Technician" exists, isEditable=true, 10 users, 19 perms — matches legacy Parts Tech -&gt; Parts Technician.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>C26525</t>
+          <t>C26520</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26525</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26520</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -20849,7 +20938,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Changing a user's role logs that user out and forces them to log in again</t>
+          <t>Legacy 'Sales Representative' users become 'Sales Representative' after migration</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -20864,72 +20953,72 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>UI/API: after an admin changed the Tech user role, the user existing session returned 409 "Session has expired." on the next call — the role change logs the user out and forces re-login.</t>
+          <t>Live roles API: "Sales Representative" exists, isEditable=true, 15 users, 4 perms.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>C26526</t>
+          <t>C26525</t>
         </is>
       </c>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26526</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26525</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Staff Record Settings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Whether a technician can be scheduled depends on their department, not their role</t>
+          <t>Changing a user's role logs that user out and forces them to log in again</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs two seeded users + departments)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Department-gated scheduling needs live UI.</t>
+          <t>UI/API: after an admin changed the Tech user role, the user existing session returned 409 "Session has expired." on the next call — the role change logs the user out and forces re-login.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>C26527</t>
+          <t>C27731</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26527</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/27731</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>3550</v>
+        <v>3549</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Staff Record Settings</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Clocking in on a work order line depends on the per-staff Time Clock setting</t>
+          <t>Legacy 'Owner' users become 'Administrator' after migration (Owner merged into Admin)</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -20939,24 +21028,24 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs two seeded users)</t>
+          <t>Blocked-UI</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Per-staff Time Clock gating needs live UI.</t>
+          <t>Moved from stub section 3660 into 3549 Migration (was distinct: core 3549 had no legacy-Owner case; Owner is merged into Administrator). Migration LANDING outcome not drivable in this env - needs a real pre-migration 'Owner' user and a migration run (not seedable). Partial confirmation (roles-API): there is NO 'Owner' system role among the 11 shipped system roles, and the Administrator role is editable (roles-matrix-2026-07-13). Full behavior = manual/second-real-user.</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>C26528</t>
+          <t>C26526</t>
         </is>
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26528</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26526</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -20969,114 +21058,114 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>The universal clock in / out is available to any active staff member, whatever their role</t>
+          <t>Whether a technician can be scheduled depends on their department, not their role</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Blocked-UI</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Blocked-UI (needs two seeded users + departments)</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>UI: the universal Clock In control appears in the top bar for every role observed (Admin, Technician, Time Clock User) — available to any active staff member whatever their role.</t>
+          <t>Department-gated scheduling needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>C26529</t>
+          <t>C26527</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26529</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26527</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>3551</v>
+        <v>3550</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>QuickBooks Relocation</t>
+          <t>Staff Record Settings</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>QuickBooks settings appear under Integrations when the Integrations sub-toggle is ON</t>
+          <t>Clocking in on a work order line depends on the per-staff Time Clock setting</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Deviation/Finding</t>
+          <t>Blocked-UI</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Deviation-vs-old-case: build has QuickBooks under Integrations, not Finance</t>
+          <t>Blocked-UI (needs two seeded users)</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Route metadata: Integrations gates IBS/Open API/QuickBooks; Finance gates Payment Methods/Taxes (no QuickBooks). QuickBooks is under Integrations in the build.</t>
+          <t>Per-staff Time Clock gating needs live UI.</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>C26530</t>
+          <t>C26528</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26530</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26528</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>3551</v>
+        <v>3550</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>QuickBooks Relocation</t>
+          <t>Staff Record Settings</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>QuickBooks settings are hidden when the Integrations sub-toggle is OFF</t>
+          <t>The universal clock in / out is available to any active staff member, whatever their role</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Deviation/Finding</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Deviation-vs-old-case: QuickBooks gated by Integrations, not Finance</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>QuickBooks gated by settingsIntegrations in the build.</t>
+          <t>UI: the universal Clock In control appears in the top bar for every role observed (Admin, Technician, Time Clock User) — available to any active staff member whatever their role.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>C26531</t>
+          <t>C26529</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26531</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26529</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -21089,7 +21178,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>The Integrations settings section is present and hosts QuickBooks, IBS and Open API</t>
+          <t>QuickBooks settings appear under Integrations when the Integrations sub-toggle is ON</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -21099,104 +21188,104 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Deviation-vs-old-case: Integrations IS present in build (old case said removed)</t>
+          <t>Deviation-vs-old-case: build has QuickBooks under Integrations, not Finance</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>settingsIntegrations gates IBS/Open API/QuickBooks; the Settings 'Integrations' sub-toggle exists. Integrations is present in the build.</t>
+          <t>Route metadata: Integrations gates IBS/Open API/QuickBooks; Finance gates Payment Methods/Taxes (no QuickBooks). QuickBooks is under Integrations in the build.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>C26532</t>
+          <t>C26530</t>
         </is>
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26532</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26530</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>3552</v>
+        <v>3551</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>QuickBooks Relocation</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Create success message wording</t>
+          <t>QuickBooks settings are hidden when the Integrations sub-toggle is OFF</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Deviation/Finding</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>Deviation-vs-old-case: QuickBooks gated by Integrations, not Finance</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>'Role created successfully.' confirmed in build.</t>
+          <t>QuickBooks gated by settingsIntegrations in the build.</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>C26533</t>
+          <t>C26531</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26533</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26531</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>3552</v>
+        <v>3551</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>User Feedback Strings</t>
+          <t>QuickBooks Relocation</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Update success message wording</t>
+          <t>The Integrations settings section is present and hosts QuickBooks, IBS and Open API</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Deviation/Finding</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>Deviation-vs-old-case: Integrations IS present in build (old case said removed)</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>'Role updated successfully.' confirmed in build.</t>
+          <t>settingsIntegrations gates IBS/Open API/QuickBooks; the Settings 'Integrations' sub-toggle exists. Integrations is present in the build.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>C26534</t>
+          <t>C26532</t>
         </is>
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26534</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26532</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -21209,7 +21298,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Deleting a custom role with 0 users shows a confirmation dialog</t>
+          <t>Create success message wording</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -21219,24 +21308,24 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>UI: deleting a 0-user custom role opens dialog "Confirmation — Are you sure you want to delete this role? This action cannot be undone." [Cancel|Delete]. screenshot delete-confirm-dialog.</t>
+          <t>'Role created successfully.' confirmed in build.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>C26535</t>
+          <t>C26533</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26535</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26533</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -21249,7 +21338,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Deleting a custom role that has users is blocked</t>
+          <t>Update success message wording</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -21259,24 +21348,24 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>UI: a custom role with users (Parth Cust1, 1 user) has no Delete option in its 3-dot menu — deletion is blocked.</t>
+          <t>'Role updated successfully.' confirmed in build.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>C26536</t>
+          <t>C26534</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26536</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26534</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -21289,7 +21378,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Turning See Financial Data on shows a confirmation dialog</t>
+          <t>Deleting a custom role with 0 users shows a confirmation dialog</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -21299,24 +21388,24 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Verified-Label (build)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>'Enable See Financial Data?' + Cancel/Enable confirmed in build (FinancialDataConfirmModal).</t>
+          <t>UI: deleting a 0-user custom role opens dialog "Confirmation — Are you sure you want to delete this role? This action cannot be undone." [Cancel|Delete]. screenshot delete-confirm-dialog.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>C26537</t>
+          <t>C26535</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26537</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26535</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -21329,7 +21418,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Creating a role with no name is blocked with a required-field error</t>
+          <t>Deleting a custom role that has users is blocked</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -21344,19 +21433,19 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>UI: creating a role with no name is blocked — Create disabled and inline "Role name is a required field" error when the field is touched/cleared.</t>
+          <t>UI: a custom role with users (Parth Cust1, 1 user) has no Delete option in its 3-dot menu — deletion is blocked.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>C26538</t>
+          <t>C26536</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26538</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26536</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -21369,7 +21458,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Creating a role with the same permissions as an existing role shows a 'similar role' warning</t>
+          <t>Turning See Financial Data on shows a confirmation dialog</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -21379,24 +21468,24 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Verified-Label (build)</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>UI: creating a role with the same permissions as an existing role shows "Similar role already exists" warning with "Create Anyway" (SimilarRoleWarningModal, keyed on identical permissions).</t>
+          <t>'Enable See Financial Data?' + Cancel/Enable confirmed in build (FinancialDataConfirmModal).</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>C26539</t>
+          <t>C26537</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26539</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26537</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -21409,47 +21498,47 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Reassigning a staff member's role updates the row with no success message (billing note in the window)</t>
+          <t>Creating a role with no name is blocked with a required-field error</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Blocked-UI (needs live Staff page); billing note not re-captured this pass</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>No-toast-on-reassign + billing note need live Staff page (EditStaffMember chunk not fetched).</t>
+          <t>UI: creating a role with no name is blocked — Create disabled and inline "Role name is a required field" error when the field is touched/cleared.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>C26540</t>
+          <t>C26538</t>
         </is>
       </c>
       <c r="B244" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26540</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26538</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Cross-Permission Combinations</t>
+          <t>User Feedback Strings</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>A role with all permissions off blocks the user from every feature</t>
+          <t>Creating a role with the same permissions as an existing role shows a 'similar role' warning</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -21464,59 +21553,59 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>UI: a near-minimal custom role (only scheduleView) shows a minimal nav (just Schedule + Clock In); navigating to /reports or /administration/staff is refused and redirects to /schedule. (A truly all-off role cannot be saved — Create is disabled at zero perms, C26335 — so the practical minimum is one feature perm; that user is blocked from every other feature.) screenshot xperm-MinRole.</t>
+          <t>UI: creating a role with the same permissions as an existing role shows "Similar role already exists" warning with "Create Anyway" (SimilarRoleWarningModal, keyed on identical permissions).</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>C26541</t>
+          <t>C26539</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26541</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26539</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>3553</v>
+        <v>3552</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Cross-Permission Combinations</t>
+          <t>User Feedback Strings</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>A role with all permissions on behaves like Administrator but is still a custom role</t>
+          <t>Reassigning a staff member's role updates the row with no success message (billing note in the window)</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Blocked-UI</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Blocked-UI (needs live Staff page); billing note not re-captured this pass</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>UI: an all-permissions custom role (42 perms, all cross-toggles on, type Custom) behaves like Administrator — full nav (Work Orders/Schedule/Customers/Parts/Reports), /reports and /administration/staff accessible — yet it is a Custom role (created via Create Custom Role). screenshot xperm-AllOn.</t>
+          <t>No-toast-on-reassign + billing note need live Staff page (EditStaffMember chunk not fetched).</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>C26542</t>
+          <t>C26540</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26542</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26540</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -21529,7 +21618,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>A system role cannot be deleted</t>
+          <t>A role with all permissions off blocks the user from every feature</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -21539,24 +21628,24 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (all system roles deletable=false)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>deletable=false for all system roles (live roles API).</t>
+          <t>UI: a near-minimal custom role (only scheduleView) shows a minimal nav (just Schedule + Clock In); navigating to /reports or /administration/staff is refused and redirects to /schedule. (A truly all-off role cannot be saved — Create is disabled at zero perms, C26335 — so the practical minimum is one feature perm; that user is blocked from every other feature.) screenshot xperm-MinRole.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>C26543</t>
+          <t>C26541</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26543</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26541</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -21569,7 +21658,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Only Office User and Time Clock User are non-editable; every other system role (including Administrator) is editable</t>
+          <t>A role with all permissions on behaves like Administrator but is still a custom role</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -21579,24 +21668,24 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Roles-API-Verified (editable flags match live)</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Live roles API: Office User &amp; Time Clock User editable=false; all others (incl. Administrator) editable=true.</t>
+          <t>UI: an all-permissions custom role (42 perms, all cross-toggles on, type Custom) behaves like Administrator — full nav (Work Orders/Schedule/Customers/Parts/Reports), /reports and /administration/staff accessible — yet it is a Custom role (created via Create Custom Role). screenshot xperm-AllOn.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>C26544</t>
+          <t>C26542</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26544</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26542</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -21609,7 +21698,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Being unable to open Customers does not stop a user from picking a customer when creating a work order</t>
+          <t>A system role cannot be deleted</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -21619,24 +21708,24 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (all system roles deletable=false)</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>UI: verified via C26385 — a role with Work Orders Create&amp;Edit but NO Customers View cannot open Customers (hidden from nav), yet the New Work Order customer picker still opens and lists existing customers, so a customer can be selected when creating a WO.</t>
+          <t>deletable=false for all system roles (live roles API).</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>C26545</t>
+          <t>C26543</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26545</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26543</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -21649,7 +21738,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>A Page Access toggle that is off overrides the add/edit/delete boxes inside it</t>
+          <t>Only Office User and Time Clock User are non-editable; every other system role (including Administrator) is editable</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -21659,24 +21748,24 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Roles-API-Verified (editable flags match live)</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>UI: a Page Access toggle that is off overrides inner boxes — a role without reportsPageAccess has no Reports nav entry and /reports is refused (redirects away); a role with Parts Department off hides its 3 child cards (C26407). The Page Access toggle is checked first regardless of inner add/edit/delete.</t>
+          <t>Live roles API: Office User &amp; Time Clock User editable=false; all others (incl. Administrator) editable=true.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>C26548</t>
+          <t>C26544</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26548</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26544</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -21689,7 +21778,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>View off with Create &amp; Edit on is prevented by the tick-cascade</t>
+          <t>Being unable to open Customers does not stop a user from picking a customer when creating a work order</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -21704,19 +21793,19 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>UI/editor: View-off + Create&amp;Edit-on cannot be saved — the tick-cascade (verified C26360/C26362/C26363) auto-ticks View when Create&amp;Edit is ticked, and unticks Create&amp;Edit+Delete when View is unticked, so that invalid combination is impossible in the editor.</t>
+          <t>UI: verified via C26385 — a role with Work Orders Create&amp;Edit but NO Customers View cannot open Customers (hidden from nav), yet the New Work Order customer picker still opens and lists existing customers, so a customer can be selected when creating a WO.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>C26549</t>
+          <t>C26545</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26549</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26545</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -21729,7 +21818,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>AP/AR OFF hides the sensitive customer fields on both the Edit Customer window and the customer overview</t>
+          <t>A Page Access toggle that is off overrides the add/edit/delete boxes inside it</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -21744,19 +21833,19 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>UI: AP/AR Data OFF hides the sensitive customer fields on the Edit Customer modal (and the financial tabs on the customer overview) — confirmed via Service Advisor (off) vs CustAPAR (on).</t>
+          <t>UI: a Page Access toggle that is off overrides inner boxes — a role without reportsPageAccess has no Reports nav entry and /reports is refused (redirects away); a role with Parts Department off hides its 3 child cards (C26407). The Page Access toggle is checked first regardless of inner add/edit/delete.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>C26550</t>
+          <t>C26548</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26550</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26548</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -21769,34 +21858,34 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>The last Administrator cannot be left with zero users</t>
+          <t>View off with Create &amp; Edit on is prevented by the tick-cascade</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Blocked-UI: cannot test the last-Administrator guard on shared staging — the org has 89 users on the Admin role, so the single-last-admin state cannot be created without mass-reassigning real users (destructive/irreversible on a shared env). Product rule; needs an isolated org or DB-level setup. Route to product team to confirm the rule exists.</t>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Needs live UI; invariant to confirm.</t>
+          <t>UI/editor: View-off + Create&amp;Edit-on cannot be saved — the tick-cascade (verified C26360/C26362/C26363) auto-ticks View when Create&amp;Edit is ticked, and unticks Create&amp;Edit+Delete when View is unticked, so that invalid combination is impossible in the editor.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>C26551</t>
+          <t>C26549</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/26551</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26549</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -21809,20 +21898,100 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
+          <t>AP/AR OFF hides the sensitive customer fields on both the Edit Customer window and the customer overview</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>UI: AP/AR Data OFF hides the sensitive customer fields on the Edit Customer modal (and the financial tabs on the customer overview) — confirmed via Service Advisor (off) vs CustAPAR (on).</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>C26550</t>
+        </is>
+      </c>
+      <c r="B254" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26550</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>The last Administrator cannot be left with zero users</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Blocked-UI</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Blocked-UI: cannot test the last-Administrator guard on shared staging — the org has 89 users on the Admin role, so the single-last-admin state cannot be created without mass-reassigning real users (destructive/irreversible on a shared env). Product rule; needs an isolated org or DB-level setup. Route to product team to confirm the rule exists.</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Needs live UI; invariant to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>C26551</t>
+        </is>
+      </c>
+      <c r="B255" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/26551</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>3553</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Cross-Permission Combinations</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
           <t>Universal clock in/out works even for a user whose role has (almost) no permissions</t>
         </is>
       </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H253" t="inlineStr">
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
         <is>
           <t>UI: the Time Clock User role (only 3 perms: scheduleView/timesheetsView/workOrdersView) still shows the universal Clock In control — universal clock in is not gated by role/permissions.</t>
         </is>
@@ -22082,6 +22251,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B251" r:id="rId250"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B252" r:id="rId251"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B255" r:id="rId254"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/build/custom-roles-run/CustomRoles_WordingVIU_2026-07-13.xlsx
+++ b/build/custom-roles-run/CustomRoles_WordingVIU_2026-07-13.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -462,7 +462,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TestRail push: all 252 core cases (sections 3528–3553) updated via update_case, 200/200, 0 errors (wording pass).</t>
+          <t>TestRail push: all 252 core cases (sections 3528–3553) updated via update_case, 200/200, 0 errors (wording pass); + 2 valid stubs moved into 3527 and reworded/pushed = 254 cases total in this workbook.</t>
         </is>
       </c>
     </row>
@@ -476,163 +476,178 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Section 3658 dedupe: 3 duplicates deleted (C27735, C27733, C27737).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Section 3658 resolution 2026-07-13: 2 valid stubs MOVED into 3527 sub-sections + reworded/pushed (C27731-&gt;3549 Migration, C27736-&gt;3545 View and Manage AP/AR Data); 5 left in 3658 for QA-lead decision (C27729, C27730, C27732, C27734, C27738 - redundant or build-wrong). See section-3658-resolution-2026-07-13.md.</t>
+          <t>Section 3658 stub tree FULLY RESOLVED 2026-07-13: original 10 stubs = 3 duplicates deleted early (C27735, C27733, C27737) + 2 valid stubs MOVED into 3527 sub-sections + reworded/pushed (C27731-&gt;3549 Migration, C27736-&gt;3545 View and Manage AP/AR Data) + 5 not-valid stubs DELETED (C27729, C27730, C27732, C27734, C27738 - redundant or build-wrong, QA-lead authorized). Section 3658 subtree (3658–3665) now EMPTY. See section-3658-resolution-2026-07-13.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Bucket</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Count</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Bucket</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>204</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VIU-Verified</t>
+          <t>Blocked-UI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>204</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Blocked-UI</t>
+          <t>Deviation/Finding</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Blocked-UI</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>Deviation/Finding</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Roles List Page (3528)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>18</v>
+      </c>
+      <c r="C15" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Blocked-UI</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Deviation/Finding</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Roles List Page (3528)</t>
+          <t>Create Custom Role (3529)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Create Custom Role (3529)</t>
+          <t>Edit Role (3530)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Edit Role (3530)</t>
+          <t>Delete Role (3531)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -644,20 +659,20 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Delete Role (3531)</t>
+          <t>Permission Summary (3532)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -672,14 +687,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Permission Summary (3532)</t>
+          <t>CRUD Cascade Rules (3533)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -688,61 +703,61 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CRUD Cascade Rules (3533)</t>
+          <t>Work Orders Permissions (3534)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Work Orders Permissions (3534)</t>
+          <t>Work Order Lines Permissions (3535)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Work Order Lines Permissions (3535)</t>
+          <t>Schedule Permissions (3536)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
@@ -754,20 +769,20 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Schedule Permissions (3536)</t>
+          <t>Customer Management Permissions (3537)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -776,20 +791,20 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Customer Management Permissions (3537)</t>
+          <t>Parts Department Permissions (3538)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -798,64 +813,64 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Parts Department Permissions (3538)</t>
+          <t>Invoicing and Payments Permissions (3539)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Invoicing and Payments Permissions (3539)</t>
+          <t>Timesheets Permissions (3540)</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Timesheets Permissions (3540)</t>
+          <t>Page Access Toggles (3541)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -864,20 +879,20 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Page Access Toggles (3541)</t>
+          <t>Settings Access (3542)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -886,64 +901,64 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Settings Access (3542)</t>
+          <t>View Mode (3543)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>View Mode (3543)</t>
+          <t>See Financial Data (3544)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>See Financial Data (3544)</t>
+          <t>View and Manage AP/AR Data (3545)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -952,20 +967,20 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>View and Manage AP/AR Data (3545)</t>
+          <t>View History Logs (3546)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -974,20 +989,20 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>View History Logs (3546)</t>
+          <t>Staff Page Role Assignment (3547)</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>2</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -996,20 +1011,20 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Staff Page Role Assignment (3547)</t>
+          <t>Per-Role Verification (3548)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1018,20 +1033,20 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Per-Role Verification (3548)</t>
+          <t>Migration (3549)</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>12</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1040,20 +1055,20 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Migration (3549)</t>
+          <t>Staff Record Settings (3550)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1062,23 +1077,23 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Staff Record Settings (3550)</t>
+          <t>QuickBooks Relocation (3551)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -1090,33 +1105,33 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>QuickBooks Relocation (3551)</t>
+          <t>User Feedback Strings (3552)</t>
         </is>
       </c>
       <c r="B39" t="n">
+        <v>7</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
         <v>0</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="n">
-        <v>3</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>User Feedback Strings (3552)</t>
+          <t>Cross-Permission Combinations (3553)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
@@ -1128,28 +1143,6 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Cross-Permission Combinations (3553)</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>9</v>
-      </c>
-      <c r="C41" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="n">
         <v>10</v>
       </c>
     </row>
